--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -3818,19 +3818,19 @@
         <v>260</v>
       </c>
       <c r="B5" s="34">
-        <v>52233</v>
+        <v>76570</v>
       </c>
       <c r="C5" s="34">
-        <v>212273</v>
+        <v>236610</v>
       </c>
       <c r="D5" s="34">
-        <v>455409</v>
+        <v>479746</v>
       </c>
       <c r="E5" s="34">
-        <v>766321</v>
+        <v>790659</v>
       </c>
       <c r="F5" s="34">
-        <v>1086561</v>
+        <v>1110899</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3898,19 +3898,19 @@
         <v>264</v>
       </c>
       <c r="B9" s="29">
-        <v>57233</v>
+        <v>81570</v>
       </c>
       <c r="C9" s="29">
-        <v>217273</v>
+        <v>241610</v>
       </c>
       <c r="D9" s="29">
-        <v>460409</v>
+        <v>484746</v>
       </c>
       <c r="E9" s="29">
-        <v>771321</v>
+        <v>795659</v>
       </c>
       <c r="F9" s="29">
-        <v>1091561</v>
+        <v>1115899</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3998,19 +3998,19 @@
         <v>270</v>
       </c>
       <c r="B17" s="25">
-        <v>57233</v>
+        <v>81570</v>
       </c>
       <c r="C17" s="25">
-        <v>217273</v>
+        <v>241610</v>
       </c>
       <c r="D17" s="25">
-        <v>460409</v>
+        <v>484746</v>
       </c>
       <c r="E17" s="25">
-        <v>771321</v>
+        <v>795659</v>
       </c>
       <c r="F17" s="25">
-        <v>1091561</v>
+        <v>1115899</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4172,19 +4172,19 @@
         <v>278</v>
       </c>
       <c r="B10" s="24">
-        <v>52233</v>
+        <v>76570</v>
       </c>
       <c r="C10" s="24">
-        <v>212273</v>
+        <v>236610</v>
       </c>
       <c r="D10" s="24">
-        <v>455409</v>
+        <v>479746</v>
       </c>
       <c r="E10" s="24">
-        <v>766321</v>
+        <v>790659</v>
       </c>
       <c r="F10" s="24">
-        <v>1086561</v>
+        <v>1110899</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4192,19 +4192,19 @@
         <v>279</v>
       </c>
       <c r="B11" s="21">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="C11" s="21">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="D11" s="21">
-        <v>786</v>
+        <v>828</v>
       </c>
       <c r="E11" s="21">
-        <v>1269</v>
+        <v>1309</v>
       </c>
       <c r="F11" s="21">
-        <v>1747</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4212,19 +4212,19 @@
         <v>280</v>
       </c>
       <c r="B12" s="28">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="C12" s="28">
-        <v>12.6</v>
+        <v>14.1</v>
       </c>
       <c r="D12" s="28">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="E12" s="28">
-        <v>41.7</v>
+        <v>43</v>
       </c>
       <c r="F12" s="28">
-        <v>57.4</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5216,19 +5216,19 @@
         <v>311</v>
       </c>
       <c r="D16" s="24">
-        <v>52233</v>
+        <v>76570</v>
       </c>
       <c r="E16" s="24">
-        <v>212273</v>
+        <v>236610</v>
       </c>
       <c r="F16" s="24">
-        <v>455409</v>
+        <v>479746</v>
       </c>
       <c r="G16" s="24">
-        <v>766321</v>
+        <v>790659</v>
       </c>
       <c r="H16" s="24">
-        <v>1086561</v>
+        <v>1110899</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -72,7 +72,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -360,7 +360,7 @@
     <t>Annual Fundraising</t>
   </si>
   <si>
-    <t>Grants &amp; Contributions</t>
+    <t>Philanthropy</t>
   </si>
   <si>
     <t>Annual Fixed</t>
@@ -549,7 +549,7 @@
     <t>AZ ESA Funds (School Choice)</t>
   </si>
   <si>
-    <t>Annual Fundraising (Grants &amp; Contributions)</t>
+    <t>Annual Fundraising (Philanthropy)</t>
   </si>
   <si>
     <t>TOTAL REVENUE</t>
@@ -995,7 +995,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1039,7 +1039,7 @@
     <font>
       <i/>
       <color rgb="FF999999"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1057,7 +1057,7 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1081,12 +1081,6 @@
     <font>
       <b/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF666666"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1161,7 +1155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1218,7 +1212,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4722,7 +4715,7 @@
       <c r="F3" s="13"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="12" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4830,19 +4823,19 @@
       <c r="A10" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="42" t="s">
         <v>276</v>
       </c>
     </row>
@@ -4877,7 +4870,7 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="12" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4985,19 +4978,19 @@
       <c r="A20" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="F20" s="43" t="s">
+      <c r="F20" s="42" t="s">
         <v>276</v>
       </c>
     </row>
@@ -5135,19 +5128,19 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="43" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5273,19 +5266,19 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="43" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5313,19 +5306,19 @@
       <c r="A22" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D22" s="43" t="s">
+      <c r="D22" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="F22" s="43" t="s">
+      <c r="F22" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="G22" s="43" t="s">
+      <c r="G22" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="42" t="s">
         <v>276</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="318">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -690,6 +690,9 @@
     <t xml:space="preserve">    Insurance</t>
   </si>
   <si>
+    <t xml:space="preserve">  Total Occupancy / Facility</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Marketing</t>
   </si>
   <si>
@@ -855,6 +858,9 @@
     <t>CASH FLOW &amp; DEBT</t>
   </si>
   <si>
+    <t>Revenue</t>
+  </si>
+  <si>
     <t>CFADS (Rev - Pers - OpEx)</t>
   </si>
   <si>
@@ -943,9 +949,6 @@
   </si>
   <si>
     <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +0%</t>
-  </si>
-  <si>
-    <t>Revenue</t>
   </si>
   <si>
     <t>LOW ENROLLMENT</t>
@@ -2017,18 +2020,23 @@
         <v>173</v>
       </c>
       <c r="B11" s="25">
+        <f>SUM(B7:B10)</f>
         <v>236000</v>
       </c>
       <c r="C11" s="25">
+        <f>SUM(C7:C10)</f>
         <v>362045</v>
       </c>
       <c r="D11" s="25">
+        <f>SUM(D7:D10)</f>
         <v>454596</v>
       </c>
       <c r="E11" s="25">
+        <f>SUM(E7:E10)</f>
         <v>531339</v>
       </c>
       <c r="F11" s="25">
+        <f>SUM(F7:F10)</f>
         <v>547279</v>
       </c>
     </row>
@@ -2161,18 +2169,23 @@
         <v>202</v>
       </c>
       <c r="B7" s="29">
+        <f>SUM(B5:B6)</f>
         <v>60428</v>
       </c>
       <c r="C7" s="29">
+        <f>SUM(C5:C6)</f>
         <v>74689</v>
       </c>
       <c r="D7" s="29">
+        <f>SUM(D5:D6)</f>
         <v>76930</v>
       </c>
       <c r="E7" s="29">
+        <f>SUM(E5:E6)</f>
         <v>79237</v>
       </c>
       <c r="F7" s="29">
+        <f>SUM(F5:F6)</f>
         <v>81615</v>
       </c>
     </row>
@@ -2211,18 +2224,23 @@
         <v>204</v>
       </c>
       <c r="B10" s="29">
+        <f>SUM(B9:B9)</f>
         <v>58506</v>
       </c>
       <c r="C10" s="29">
+        <f>SUM(C9:C9)</f>
         <v>72314</v>
       </c>
       <c r="D10" s="29">
+        <f>SUM(D9:D9)</f>
         <v>74483</v>
       </c>
       <c r="E10" s="29">
+        <f>SUM(E9:E9)</f>
         <v>76718</v>
       </c>
       <c r="F10" s="29">
+        <f>SUM(F9:F9)</f>
         <v>79019</v>
       </c>
     </row>
@@ -2231,18 +2249,23 @@
         <v>205</v>
       </c>
       <c r="B12" s="25">
+        <f>B7+B10</f>
         <v>118934</v>
       </c>
       <c r="C12" s="25">
+        <f>C7+C10</f>
         <v>147003</v>
       </c>
       <c r="D12" s="25">
+        <f>D7+D10</f>
         <v>151413</v>
       </c>
       <c r="E12" s="25">
+        <f>E7+E10</f>
         <v>155955</v>
       </c>
       <c r="F12" s="25">
+        <f>F7+F10</f>
         <v>160634</v>
       </c>
     </row>
@@ -2263,7 +2286,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -2395,18 +2418,23 @@
         <v>212</v>
       </c>
       <c r="B9" s="29">
+        <f>SUM(B5:B8)</f>
         <v>196667</v>
       </c>
       <c r="C9" s="29">
+        <f>SUM(C5:C8)</f>
         <v>362045</v>
       </c>
       <c r="D9" s="29">
+        <f>SUM(D5:D8)</f>
         <v>454596</v>
       </c>
       <c r="E9" s="29">
+        <f>SUM(E5:E8)</f>
         <v>531339</v>
       </c>
       <c r="F9" s="29">
+        <f>SUM(F5:F8)</f>
         <v>547279</v>
       </c>
     </row>
@@ -2485,18 +2513,23 @@
         <v>177</v>
       </c>
       <c r="B15" s="29">
+        <f>SUM(B12:B14)</f>
         <v>118934</v>
       </c>
       <c r="C15" s="29">
+        <f>SUM(C12:C14)</f>
         <v>147003</v>
       </c>
       <c r="D15" s="29">
+        <f>SUM(D12:D14)</f>
         <v>151413</v>
       </c>
       <c r="E15" s="29">
+        <f>SUM(E12:E14)</f>
         <v>155955</v>
       </c>
       <c r="F15" s="29">
+        <f>SUM(F12:F14)</f>
         <v>160634</v>
       </c>
     </row>
@@ -2625,78 +2658,113 @@
         <v>2701</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="29">
+        <f>SUM(B23:B25)</f>
+        <v>30000</v>
+      </c>
+      <c r="C26" s="29">
+        <f>SUM(C23:C25)</f>
+        <v>37080</v>
+      </c>
+      <c r="D26" s="29">
+        <f>SUM(D23:D25)</f>
+        <v>38192</v>
+      </c>
+      <c r="E26" s="29">
+        <f>SUM(E23:E25)</f>
+        <v>39338</v>
+      </c>
+      <c r="F26" s="29">
+        <f>SUM(F23:F25)</f>
+        <v>40518</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="31" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B27" s="24">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B28" s="24">
         <v>2500</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C28" s="24">
         <v>3090</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D28" s="24">
         <v>3183</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E28" s="24">
         <v>3278</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F28" s="24">
         <v>3377</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B28" s="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B29" s="29">
+        <f>B19+B21+B26+B28</f>
         <v>40500</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
+        <f>C19+C21+C26+C28</f>
         <v>55002</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D29" s="29">
+        <f>D19+D21+D26+D28</f>
         <v>60047</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E29" s="29">
+        <f>E19+E21+E26+E28</f>
         <v>64471</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F29" s="29">
+        <f>F19+F21+F26+F28</f>
         <v>66405</v>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B31" s="29">
-        <v>0</v>
-      </c>
-      <c r="C31" s="29">
-        <v>0</v>
-      </c>
-      <c r="D31" s="29">
-        <v>0</v>
-      </c>
-      <c r="E31" s="29">
-        <v>0</v>
-      </c>
-      <c r="F31" s="29">
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" s="29" t="str">
+        <f>SUM(B32:B31)</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="29" t="str">
+        <f>SUM(C32:C31)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="29" t="str">
+        <f>SUM(D32:D31)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="29" t="str">
+        <f>SUM(E32:E31)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="29" t="str">
+        <f>SUM(F32:F31)</f>
         <v>0</v>
       </c>
     </row>
@@ -2726,7 +2794,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2759,18 +2827,23 @@
         <v>212</v>
       </c>
       <c r="B4" s="27">
+        <f>'Budget Detail'!B9</f>
         <v>196667</v>
       </c>
       <c r="C4" s="27">
+        <f>'Budget Detail'!C9</f>
         <v>362045</v>
       </c>
       <c r="D4" s="27">
+        <f>'Budget Detail'!D9</f>
         <v>454596</v>
       </c>
       <c r="E4" s="27">
+        <f>'Budget Detail'!E9</f>
         <v>531339</v>
       </c>
       <c r="F4" s="27">
+        <f>'Budget Detail'!F9</f>
         <v>547279</v>
       </c>
     </row>
@@ -2779,84 +2852,104 @@
         <v>177</v>
       </c>
       <c r="B5" s="27">
+        <f>'Budget Detail'!B15</f>
         <v>118934</v>
       </c>
       <c r="C5" s="27">
+        <f>'Budget Detail'!C15</f>
         <v>147003</v>
       </c>
       <c r="D5" s="27">
+        <f>'Budget Detail'!D15</f>
         <v>151413</v>
       </c>
       <c r="E5" s="27">
+        <f>'Budget Detail'!E15</f>
         <v>155955</v>
       </c>
       <c r="F5" s="27">
+        <f>'Budget Detail'!F15</f>
         <v>160634</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B6" s="27">
+        <f>'Budget Detail'!B29</f>
         <v>40500</v>
       </c>
       <c r="C6" s="27">
+        <f>'Budget Detail'!C29</f>
         <v>55002</v>
       </c>
       <c r="D6" s="27">
+        <f>'Budget Detail'!D29</f>
         <v>60047</v>
       </c>
       <c r="E6" s="27">
+        <f>'Budget Detail'!E29</f>
         <v>64471</v>
       </c>
       <c r="F6" s="27">
+        <f>'Budget Detail'!F29</f>
         <v>66405</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B7" s="27">
-        <v>0</v>
-      </c>
-      <c r="C7" s="27">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27">
+        <v>225</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>'Budget Detail'!B32</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="27" t="str">
+        <f>'Budget Detail'!C32</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="27" t="str">
+        <f>'Budget Detail'!D32</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="27" t="str">
+        <f>'Budget Detail'!E32</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="27" t="str">
+        <f>'Budget Detail'!F32</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B8" s="29">
+        <f>SUM(B5:B7)</f>
         <v>159434</v>
       </c>
       <c r="C8" s="29">
+        <f>SUM(C5:C7)</f>
         <v>202005</v>
       </c>
       <c r="D8" s="29">
+        <f>SUM(D5:D7)</f>
         <v>211460</v>
       </c>
       <c r="E8" s="29">
+        <f>SUM(E5:E7)</f>
         <v>220426</v>
       </c>
       <c r="F8" s="29">
+        <f>SUM(F5:F7)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -2866,47 +2959,57 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B11" s="25">
+        <f>B4-B8</f>
         <v>37233</v>
       </c>
       <c r="C11" s="25">
+        <f>C4-C8</f>
         <v>160040</v>
       </c>
       <c r="D11" s="25">
+        <f>D4-D8</f>
         <v>243136</v>
       </c>
       <c r="E11" s="25">
+        <f>E4-E8</f>
         <v>310913</v>
       </c>
       <c r="F11" s="25">
+        <f>F4-F8</f>
         <v>320240</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B12" s="23">
-        <v>0.18931779661016948</v>
+        <f>IF(B4=0,0,B11/B4)</f>
+        <v>0.1893178</v>
       </c>
       <c r="C12" s="23">
-        <v>0.44204551920341395</v>
+        <f>IF(C4=0,0,C11/C4)</f>
+        <v>0.44204552</v>
       </c>
       <c r="D12" s="23">
-        <v>0.5348401400233372</v>
+        <f>IF(D4=0,0,D11/D4)</f>
+        <v>0.53484014</v>
       </c>
       <c r="E12" s="23">
-        <v>0.5851496143958869</v>
+        <f>IF(E4=0,0,E11/E4)</f>
+        <v>0.58514961</v>
       </c>
       <c r="F12" s="23">
-        <v>0.5851496143958869</v>
+        <f>IF(F4=0,0,F11/F4)</f>
+        <v>0.58514961</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B13" s="24">
         <v>37233</v>
@@ -2946,7 +3049,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B15" s="24">
         <v>13286</v>
@@ -2991,7 +3094,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3012,43 +3115,43 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3115,7 +3218,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3133,7 +3236,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B7" s="24">
         <v>11893</v>
@@ -3177,7 +3280,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B8" s="24">
         <v>4050</v>
@@ -3221,7 +3324,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B9" s="24">
         <v>0</v>
@@ -3265,7 +3368,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3283,7 +3386,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B12" s="27">
         <v>15943</v>
@@ -3327,7 +3430,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B13" s="27">
         <v>-6793</v>
@@ -3371,7 +3474,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B14" s="32">
         <v>-6793</v>
@@ -3415,7 +3518,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -3430,7 +3533,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B18" s="32">
         <v>76570</v>
@@ -3438,7 +3541,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B19" s="24">
         <v>-6793</v>
@@ -3470,7 +3573,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3528,19 +3631,9 @@
         <v>547279</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -3550,7 +3643,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B8" s="27">
         <v>118934</v>
@@ -3570,7 +3663,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B9" s="27">
         <v>40500</v>
@@ -3590,7 +3683,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B10" s="27">
         <v>0</v>
@@ -3610,37 +3703,32 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B11" s="29">
+        <f>SUM(B8:B10)</f>
         <v>159434</v>
       </c>
       <c r="C11" s="29">
+        <f>SUM(C8:C10)</f>
         <v>202005</v>
       </c>
       <c r="D11" s="29">
+        <f>SUM(D8:D10)</f>
         <v>211460</v>
       </c>
       <c r="E11" s="29">
+        <f>SUM(E8:E10)</f>
         <v>220426</v>
       </c>
       <c r="F11" s="29">
+        <f>SUM(F8:F10)</f>
         <v>227039</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -3650,42 +3738,52 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B14" s="25">
+        <f>B5-B11</f>
         <v>37233</v>
       </c>
       <c r="C14" s="25">
+        <f>C5-C11</f>
         <v>160040</v>
       </c>
       <c r="D14" s="25">
+        <f>D5-D11</f>
         <v>243136</v>
       </c>
       <c r="E14" s="25">
+        <f>E5-E11</f>
         <v>310913</v>
       </c>
       <c r="F14" s="25">
+        <f>F5-F11</f>
         <v>320240</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B15" s="23">
-        <v>0.18931779661016948</v>
+        <f>IF(B5=0,0,B14/B5)</f>
+        <v>0.1893178</v>
       </c>
       <c r="C15" s="23">
-        <v>0.44204551920341395</v>
+        <f>IF(C5=0,0,C14/C5)</f>
+        <v>0.44204552</v>
       </c>
       <c r="D15" s="23">
-        <v>0.5348401400233372</v>
+        <f>IF(D5=0,0,D14/D5)</f>
+        <v>0.53484014</v>
       </c>
       <c r="E15" s="23">
-        <v>0.5851496143958869</v>
+        <f>IF(E5=0,0,E14/E5)</f>
+        <v>0.58514961</v>
       </c>
       <c r="F15" s="23">
-        <v>0.5851496143958869</v>
+        <f>IF(F5=0,0,F14/F5)</f>
+        <v>0.58514961</v>
       </c>
     </row>
   </sheetData>
@@ -3768,7 +3866,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3798,7 +3896,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3808,7 +3906,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B5" s="34">
         <v>76570</v>
@@ -3828,7 +3926,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B6" s="24">
         <v>0</v>
@@ -3848,7 +3946,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B7" s="24">
         <v>5000</v>
@@ -3868,7 +3966,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B8" s="24">
         <v>0</v>
@@ -3888,7 +3986,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B9" s="29">
         <v>81570</v>
@@ -3908,7 +4006,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3918,7 +4016,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B12" s="24">
         <v>0</v>
@@ -3938,7 +4036,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B13" s="24">
         <v>0</v>
@@ -3958,7 +4056,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B14" s="29">
         <v>0</v>
@@ -3978,7 +4076,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -3988,7 +4086,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B17" s="25">
         <v>81570</v>
@@ -4008,7 +4106,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B19" s="35">
         <v>0</v>
@@ -4043,7 +4141,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4052,7 +4150,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4082,7 +4180,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4092,352 +4190,427 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B5" s="24">
-        <v>37233</v>
+        <v>196667</v>
       </c>
       <c r="C5" s="24">
-        <v>160040</v>
+        <v>362045</v>
       </c>
       <c r="D5" s="24">
-        <v>243136</v>
+        <v>454596</v>
       </c>
       <c r="E5" s="24">
-        <v>310913</v>
+        <v>531339</v>
       </c>
       <c r="F5" s="24">
-        <v>320240</v>
+        <v>547279</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" s="24">
+        <v>118934</v>
+      </c>
+      <c r="C6" s="24">
+        <v>147003</v>
+      </c>
+      <c r="D6" s="24">
+        <v>151413</v>
+      </c>
+      <c r="E6" s="24">
+        <v>155955</v>
+      </c>
+      <c r="F6" s="24">
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B6" s="24">
-        <v>0</v>
-      </c>
-      <c r="C6" s="24">
-        <v>0</v>
-      </c>
-      <c r="D6" s="24">
-        <v>0</v>
-      </c>
-      <c r="E6" s="24">
-        <v>0</v>
-      </c>
-      <c r="F6" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="24">
+        <v>40500</v>
+      </c>
+      <c r="C7" s="24">
+        <v>55002</v>
+      </c>
+      <c r="D7" s="24">
+        <v>60047</v>
+      </c>
+      <c r="E7" s="24">
+        <v>64471</v>
+      </c>
+      <c r="F7" s="24">
+        <v>66405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="B8" s="27">
+        <f>B5-B6-B7</f>
+        <v>37233</v>
+      </c>
+      <c r="C8" s="27">
+        <f>C5-C6-C7</f>
+        <v>160040</v>
+      </c>
+      <c r="D8" s="27">
+        <f>D5-D6-D7</f>
+        <v>243136</v>
+      </c>
+      <c r="E8" s="27">
+        <f>E5-E6-E7</f>
+        <v>310913</v>
+      </c>
+      <c r="F8" s="27">
+        <f>F5-F6-F7</f>
+        <v>320240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="24">
+        <v>0</v>
+      </c>
+      <c r="C9" s="24">
+        <v>0</v>
+      </c>
+      <c r="D9" s="24">
+        <v>0</v>
+      </c>
+      <c r="E9" s="24">
+        <v>0</v>
+      </c>
+      <c r="F9" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="36" t="s">
         <v>278</v>
       </c>
-      <c r="B10" s="24">
-        <v>76570</v>
-      </c>
-      <c r="C10" s="24">
-        <v>236610</v>
-      </c>
-      <c r="D10" s="24">
-        <v>479746</v>
-      </c>
-      <c r="E10" s="24">
-        <v>790659</v>
-      </c>
-      <c r="F10" s="24">
-        <v>1110899</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="C10" s="36" t="s">
+        <v>278</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>278</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>278</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B11" s="21">
-        <v>175</v>
-      </c>
-      <c r="C11" s="21">
-        <v>428</v>
-      </c>
-      <c r="D11" s="21">
-        <v>828</v>
-      </c>
-      <c r="E11" s="21">
-        <v>1309</v>
-      </c>
-      <c r="F11" s="21">
-        <v>1786</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B12" s="28">
-        <v>5.8</v>
-      </c>
-      <c r="C12" s="28">
-        <v>14.1</v>
-      </c>
-      <c r="D12" s="28">
-        <v>27.2</v>
-      </c>
-      <c r="E12" s="28">
-        <v>43</v>
-      </c>
-      <c r="F12" s="28">
-        <v>58.7</v>
-      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B13" s="23">
-        <v>0.48</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0.72</v>
-      </c>
-      <c r="D13" s="23">
-        <v>0.88</v>
-      </c>
-      <c r="E13" s="23">
-        <v>1</v>
-      </c>
-      <c r="F13" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="24">
+        <v>76570</v>
+      </c>
+      <c r="C13" s="24">
+        <v>236610</v>
+      </c>
+      <c r="D13" s="24">
+        <v>479746</v>
+      </c>
+      <c r="E13" s="24">
+        <v>790659</v>
+      </c>
+      <c r="F13" s="24">
+        <v>1110899</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="B14" s="21">
+        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
+        <v>175</v>
+      </c>
+      <c r="C14" s="21">
+        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
+        <v>428</v>
+      </c>
+      <c r="D14" s="21">
+        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
+        <v>828</v>
+      </c>
+      <c r="E14" s="21">
+        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
+        <v>1309</v>
+      </c>
+      <c r="F14" s="21">
+        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B15" s="28">
+        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
+        <v>5.8</v>
+      </c>
+      <c r="C15" s="28">
+        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
+        <v>14.1</v>
+      </c>
+      <c r="D15" s="28">
+        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
+        <v>27.2</v>
+      </c>
+      <c r="E15" s="28">
+        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
+        <v>43</v>
+      </c>
+      <c r="F15" s="28">
+        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
+        <v>58.7</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="23">
+        <v>0.48</v>
+      </c>
+      <c r="C16" s="23">
+        <v>0.72</v>
+      </c>
+      <c r="D16" s="23">
+        <v>0.88</v>
+      </c>
+      <c r="E16" s="23">
+        <v>1</v>
+      </c>
+      <c r="F16" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B19" s="24">
         <v>16389</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C19" s="24">
         <v>20114</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D19" s="24">
         <v>20663</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E19" s="24">
         <v>21254</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F19" s="24">
         <v>21891</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B17" s="24">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B20" s="24">
         <v>118934</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C20" s="24">
         <v>147003</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D20" s="24">
         <v>151413</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E20" s="24">
         <v>155955</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F20" s="24">
         <v>160634</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B18" s="24">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="24">
         <v>3375</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C21" s="24">
         <v>3056</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D21" s="24">
         <v>2729</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E21" s="24">
         <v>2579</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F21" s="24">
         <v>2656</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B19" s="37">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B22" s="37">
         <v>10</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C22" s="37">
         <v>9</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D22" s="37">
         <v>9</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E22" s="37">
         <v>9</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F22" s="37">
         <v>9</v>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="B23" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>288</v>
-      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B25" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="C25" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="E25" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>288</v>
+      <c r="B25" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B27" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="B26" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>288</v>
+      <c r="C27" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="D29" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -4478,13 +4651,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B3" s="41" t="s">
         <v>100</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E3" s="41" t="s">
         <v>100</v>
@@ -4492,13 +4665,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B4" s="24">
         <v>20000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E4" s="24">
         <v>15000</v>
@@ -4506,7 +4679,7 @@
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E5" s="24">
         <v>5000</v>
@@ -4514,13 +4687,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B7" s="25">
         <v>20000</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E7" s="25">
         <v>20000</v>
@@ -4528,7 +4701,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B8" s="35">
         <v>0</v>
@@ -4696,7 +4869,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4706,7 +4879,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -4716,7 +4889,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4741,7 +4914,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="B6" s="24">
         <v>196667</v>
@@ -4761,7 +4934,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B7" s="24">
         <v>159434</v>
@@ -4781,7 +4954,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B8" s="25">
         <v>37233</v>
@@ -4801,7 +4974,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B9" s="23">
         <v>0.18931779661016948</v>
@@ -4821,27 +4994,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B11" s="21">
         <v>10</v>
@@ -4861,7 +5034,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4871,7 +5044,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4896,7 +5069,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="B16" s="24">
         <v>196667</v>
@@ -4916,7 +5089,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B17" s="24">
         <v>159434</v>
@@ -4936,7 +5109,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B18" s="25">
         <v>37233</v>
@@ -4956,7 +5129,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B19" s="23">
         <v>0.18931779661016948</v>
@@ -4976,27 +5149,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E20" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B21" s="21">
         <v>8</v>
@@ -5042,7 +5215,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5076,7 +5249,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -5100,7 +5273,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -5108,7 +5281,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5146,7 +5319,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="D13" s="24">
         <v>196667</v>
@@ -5166,7 +5339,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D14" s="24">
         <v>159434</v>
@@ -5186,7 +5359,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D15" s="24">
         <v>37233</v>
@@ -5206,7 +5379,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D16" s="24">
         <v>76570</v>
@@ -5226,7 +5399,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D17" s="24">
         <v>0</v>
@@ -5246,7 +5419,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -5284,7 +5457,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D21" s="23">
         <v>0.18931779661016948</v>
@@ -5304,22 +5477,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G22" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H22" s="42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -5344,7 +5517,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D24" s="21">
         <v>12</v>
@@ -5364,7 +5537,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6382,18 +6555,23 @@
         <v>173</v>
       </c>
       <c r="B9" s="25">
+        <f>SUM(B5:B8)</f>
         <v>236000</v>
       </c>
       <c r="C9" s="25">
+        <f>SUM(C5:C8)</f>
         <v>362045</v>
       </c>
       <c r="D9" s="25">
+        <f>SUM(D5:D8)</f>
         <v>454596</v>
       </c>
       <c r="E9" s="25">
+        <f>SUM(E5:E8)</f>
         <v>531339</v>
       </c>
       <c r="F9" s="25">
+        <f>SUM(F5:F8)</f>
         <v>547279</v>
       </c>
     </row>
@@ -6708,18 +6886,23 @@
         <v>182</v>
       </c>
       <c r="B6" s="29">
+        <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
       <c r="C6" s="29">
+        <f>SUM(C5:C5)</f>
         <v>9270</v>
       </c>
       <c r="D6" s="29">
+        <f>SUM(D5:D5)</f>
         <v>11670</v>
       </c>
       <c r="E6" s="29">
+        <f>SUM(E5:E5)</f>
         <v>13659</v>
       </c>
       <c r="F6" s="29">
+        <f>SUM(F5:F5)</f>
         <v>14069</v>
       </c>
     </row>
@@ -6758,18 +6941,23 @@
         <v>184</v>
       </c>
       <c r="B9" s="29">
+        <f>SUM(B8:B8)</f>
         <v>3600</v>
       </c>
       <c r="C9" s="29">
+        <f>SUM(C8:C8)</f>
         <v>5562</v>
       </c>
       <c r="D9" s="29">
+        <f>SUM(D8:D8)</f>
         <v>7002</v>
       </c>
       <c r="E9" s="29">
+        <f>SUM(E8:E8)</f>
         <v>8195</v>
       </c>
       <c r="F9" s="29">
+        <f>SUM(F8:F8)</f>
         <v>8441</v>
       </c>
     </row>
@@ -6848,18 +7036,23 @@
         <v>188</v>
       </c>
       <c r="B14" s="29">
+        <f>SUM(B11:B13)</f>
         <v>36000</v>
       </c>
       <c r="C14" s="29">
+        <f>SUM(C11:C13)</f>
         <v>37080</v>
       </c>
       <c r="D14" s="29">
+        <f>SUM(D11:D13)</f>
         <v>38192</v>
       </c>
       <c r="E14" s="29">
+        <f>SUM(E11:E13)</f>
         <v>39338</v>
       </c>
       <c r="F14" s="29">
+        <f>SUM(F11:F13)</f>
         <v>40518</v>
       </c>
     </row>
@@ -6898,18 +7091,23 @@
         <v>190</v>
       </c>
       <c r="B17" s="29">
+        <f>SUM(B16:B16)</f>
         <v>3000</v>
       </c>
       <c r="C17" s="29">
+        <f>SUM(C16:C16)</f>
         <v>3090</v>
       </c>
       <c r="D17" s="29">
+        <f>SUM(D16:D16)</f>
         <v>3183</v>
       </c>
       <c r="E17" s="29">
+        <f>SUM(E16:E16)</f>
         <v>3278</v>
       </c>
       <c r="F17" s="29">
+        <f>SUM(F16:F16)</f>
         <v>3377</v>
       </c>
     </row>
@@ -6918,18 +7116,23 @@
         <v>191</v>
       </c>
       <c r="B19" s="25">
+        <f>B6+B9+B14+B17</f>
         <v>48600</v>
       </c>
       <c r="C19" s="25">
+        <f>C6+C9+C14+C17</f>
         <v>55002</v>
       </c>
       <c r="D19" s="25">
+        <f>D6+D9+D14+D17</f>
         <v>60047</v>
       </c>
       <c r="E19" s="25">
+        <f>E6+E9+E14+E17</f>
         <v>64471</v>
       </c>
       <c r="F19" s="25">
+        <f>F6+F9+F14+F17</f>
         <v>66405</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -216,7 +216,7 @@
     <t>Underwriting Snapshot</t>
   </si>
   <si>
-    <t>CONFIDENTIAL — Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
+    <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
     <t>How to Use This Workbook</t>
@@ -225,10 +225,10 @@
     <t>Color Legend</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>Gray cells contain formulas — do not edit.</t>
+    <t>Yellow cells are editable inputs - change these to update your model.</t>
+  </si>
+  <si>
+    <t>Gray cells contain formulas - do not edit.</t>
   </si>
   <si>
     <t>Green cells are key outputs and summary metrics.</t>
@@ -240,7 +240,7 @@
     <t>Navigation</t>
   </si>
   <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+    <t>The Assumptions tab is the central control panel - all other tabs reference it.</t>
   </si>
   <si>
     <t>Structure</t>
@@ -279,7 +279,7 @@
     <t>user-provided assumptions and should be independently verified.</t>
   </si>
   <si>
-    <t>Bright Horizons Microschool — Assumptions</t>
+    <t>Bright Horizons Microschool - Assumptions</t>
   </si>
   <si>
     <t>Yellow cells are editable inputs. All other cells are formulas.</t>
@@ -531,7 +531,7 @@
     <t>Enrollment Growth Rate</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>Tuition &amp; Funding Drivers</t>
@@ -651,7 +651,7 @@
     <t>TOTAL PERSONNEL</t>
   </si>
   <si>
-    <t>Bright Horizons Microschool — Budget Detail</t>
+    <t>Bright Horizons Microschool - Budget Detail</t>
   </si>
   <si>
     <t>REVENUE</t>
@@ -705,7 +705,7 @@
     <t>Total Capital &amp; Debt</t>
   </si>
   <si>
-    <t>Bright Horizons Microschool — Budget Summary</t>
+    <t>Bright Horizons Microschool - Budget Summary</t>
   </si>
   <si>
     <t>Total Capital &amp; Debt Service</t>
@@ -729,7 +729,7 @@
     <t>Cost per Student</t>
   </si>
   <si>
-    <t>Bright Horizons Microschool — Year 1 Monthly Cash Flow</t>
+    <t>Bright Horizons Microschool - Year 1 Monthly Cash Flow</t>
   </si>
   <si>
     <t>July</t>
@@ -801,7 +801,7 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
-    <t>Bright Horizons Microschool — 5-Year Operating Statement</t>
+    <t>Bright Horizons Microschool - 5-Year Operating Statement</t>
   </si>
   <si>
     <t>Capital &amp; Debt Service</t>
@@ -810,7 +810,7 @@
     <t>BOTTOM LINE</t>
   </si>
   <si>
-    <t>Bright Horizons Microschool — Balance Sheet</t>
+    <t>Bright Horizons Microschool - Balance Sheet</t>
   </si>
   <si>
     <t>ASSETS</t>
@@ -957,7 +957,7 @@
     <t>Enrollment: -20%  |  Revenue: +0%  |  Expenses: +0%</t>
   </si>
   <si>
-    <t>Underwriting Snapshot — Loan Committee Summary</t>
+    <t>Underwriting Snapshot - Loan Committee Summary</t>
   </si>
   <si>
     <t>Entity</t>
@@ -984,7 +984,7 @@
     <t>Enrollment</t>
   </si>
   <si>
-    <t>Prepared by SchoolStack Budget — budget.schoolstack.ai</t>
+    <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -948,13 +948,13 @@
     <t>BASE CASE</t>
   </si>
   <si>
-    <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +0%</t>
+    <t>Enrollment: +0%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>LOW ENROLLMENT</t>
   </si>
   <si>
-    <t>Enrollment: -20%  |  Revenue: +0%  |  Expenses: +0%</t>
+    <t>Enrollment: -20%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>Underwriting Snapshot - Loan Committee Summary</t>
@@ -5072,19 +5072,19 @@
         <v>275</v>
       </c>
       <c r="B16" s="24">
-        <v>196667</v>
+        <v>157333</v>
       </c>
       <c r="C16" s="24">
-        <v>362045</v>
+        <v>289636</v>
       </c>
       <c r="D16" s="24">
-        <v>454596</v>
+        <v>363677</v>
       </c>
       <c r="E16" s="24">
-        <v>531339</v>
+        <v>425071</v>
       </c>
       <c r="F16" s="24">
-        <v>547279</v>
+        <v>437823</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5112,19 +5112,19 @@
         <v>228</v>
       </c>
       <c r="B18" s="25">
-        <v>37233</v>
+        <v>-2101</v>
       </c>
       <c r="C18" s="25">
-        <v>160040</v>
+        <v>87631</v>
       </c>
       <c r="D18" s="25">
-        <v>243136</v>
+        <v>152217</v>
       </c>
       <c r="E18" s="25">
-        <v>310913</v>
+        <v>204645</v>
       </c>
       <c r="F18" s="25">
-        <v>320240</v>
+        <v>210784</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5132,19 +5132,19 @@
         <v>229</v>
       </c>
       <c r="B19" s="23">
-        <v>0.18931779661016948</v>
+        <v>-0.013352754237288008</v>
       </c>
       <c r="C19" s="23">
-        <v>0.44204551920341395</v>
+        <v>0.3025568990042674</v>
       </c>
       <c r="D19" s="23">
-        <v>0.5348401400233372</v>
+        <v>0.41855017502917163</v>
       </c>
       <c r="E19" s="23">
-        <v>0.5851496143958869</v>
+        <v>0.4814370179948587</v>
       </c>
       <c r="F19" s="23">
-        <v>0.5851496143958869</v>
+        <v>0.48143701799485866</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5172,19 +5172,19 @@
         <v>286</v>
       </c>
       <c r="B21" s="21">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C21" s="21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D21" s="21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21" s="21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" s="21">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -4940,16 +4940,16 @@
         <v>159434</v>
       </c>
       <c r="C7" s="24">
-        <v>202005</v>
+        <v>201888</v>
       </c>
       <c r="D7" s="24">
-        <v>211460</v>
+        <v>211186</v>
       </c>
       <c r="E7" s="24">
-        <v>220426</v>
+        <v>219967</v>
       </c>
       <c r="F7" s="24">
-        <v>227039</v>
+        <v>226410</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4960,16 +4960,16 @@
         <v>37233</v>
       </c>
       <c r="C8" s="25">
-        <v>160040</v>
+        <v>160157</v>
       </c>
       <c r="D8" s="25">
-        <v>243136</v>
+        <v>243409</v>
       </c>
       <c r="E8" s="25">
-        <v>310913</v>
+        <v>311372</v>
       </c>
       <c r="F8" s="25">
-        <v>320240</v>
+        <v>320869</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4980,16 +4980,16 @@
         <v>0.18931779661016948</v>
       </c>
       <c r="C9" s="23">
-        <v>0.44204551920341395</v>
+        <v>0.4423686834509522</v>
       </c>
       <c r="D9" s="23">
-        <v>0.5348401400233372</v>
+        <v>0.5354413666298831</v>
       </c>
       <c r="E9" s="23">
-        <v>0.5851496143958869</v>
+        <v>0.5860139501663209</v>
       </c>
       <c r="F9" s="23">
-        <v>0.5851496143958869</v>
+        <v>0.5862992694238808</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5095,16 +5095,16 @@
         <v>159434</v>
       </c>
       <c r="C17" s="24">
-        <v>202005</v>
+        <v>201888</v>
       </c>
       <c r="D17" s="24">
-        <v>211460</v>
+        <v>211186</v>
       </c>
       <c r="E17" s="24">
-        <v>220426</v>
+        <v>219967</v>
       </c>
       <c r="F17" s="24">
-        <v>227039</v>
+        <v>226410</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5115,16 +5115,16 @@
         <v>-2101</v>
       </c>
       <c r="C18" s="25">
-        <v>87631</v>
+        <v>87748</v>
       </c>
       <c r="D18" s="25">
-        <v>152217</v>
+        <v>152490</v>
       </c>
       <c r="E18" s="25">
-        <v>204645</v>
+        <v>205104</v>
       </c>
       <c r="F18" s="25">
-        <v>210784</v>
+        <v>211413</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5135,16 +5135,16 @@
         <v>-0.013352754237288008</v>
       </c>
       <c r="C19" s="23">
-        <v>0.3025568990042674</v>
+        <v>0.3029608543136903</v>
       </c>
       <c r="D19" s="23">
-        <v>0.41855017502917163</v>
+        <v>0.41930170828735386</v>
       </c>
       <c r="E19" s="23">
-        <v>0.4814370179948587</v>
+        <v>0.48251743770790123</v>
       </c>
       <c r="F19" s="23">
-        <v>0.48143701799485866</v>
+        <v>0.4828740867798511</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="319">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -457,6 +457,9 @@
   </si>
   <si>
     <t>Salary Escalation Rate</t>
+  </si>
+  <si>
+    <t>Derived from tuition escalation rate</t>
   </si>
   <si>
     <t>Cost Inflation Rate</t>
@@ -998,7 +1001,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1066,6 +1069,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF808080"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1158,7 +1167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1187,6 +1196,7 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1202,16 +1212,16 @@
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1877,7 +1887,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1909,25 +1919,25 @@
       <c r="A4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="31">
         <v>12</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <v>18</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>22</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>25</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>25</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1939,19 +1949,19 @@
       <c r="A7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="25">
         <v>144000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>222480</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>280078</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>327818</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>337653</v>
       </c>
     </row>
@@ -1959,19 +1969,19 @@
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <v>3000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>4635</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>5835</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>6830</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>7034</v>
       </c>
     </row>
@@ -1979,19 +1989,19 @@
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <v>84000</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>129780</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>163379</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>191227</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>196964</v>
       </c>
     </row>
@@ -1999,64 +2009,64 @@
       <c r="A10" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="25">
         <v>5000</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>5150</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>5305</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>5464</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>5628</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="B11" s="25">
+        <v>174</v>
+      </c>
+      <c r="B11" s="26">
         <f>SUM(B7:B10)</f>
         <v>236000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>SUM(C7:C10)</f>
         <v>362045</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>SUM(D7:D10)</f>
         <v>454596</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>SUM(E7:E10)</f>
         <v>531339</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>SUM(F7:F10)</f>
         <v>547279</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="24">
+        <v>199</v>
+      </c>
+      <c r="B13" s="25">
         <v>19667</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>20114</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>20663</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>21254</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>21891</v>
       </c>
     </row>
@@ -2086,7 +2096,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2126,65 +2136,65 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="24">
+        <v>201</v>
+      </c>
+      <c r="B5" s="25">
         <v>47869</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>59166</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>60941</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>62769</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>64652</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="24">
+        <v>202</v>
+      </c>
+      <c r="B6" s="25">
         <v>12559</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>15523</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>15989</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>16468</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>16963</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="29">
+        <v>203</v>
+      </c>
+      <c r="B7" s="30">
         <f>SUM(B5:B6)</f>
         <v>60428</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>SUM(C5:C6)</f>
         <v>74689</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>SUM(D5:D6)</f>
         <v>76930</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>SUM(E5:E6)</f>
         <v>79237</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>SUM(F5:F6)</f>
         <v>81615</v>
       </c>
@@ -2201,70 +2211,70 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="24">
+        <v>204</v>
+      </c>
+      <c r="B9" s="25">
         <v>58506</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>72314</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>74483</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>76718</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>79019</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="29">
+        <v>205</v>
+      </c>
+      <c r="B10" s="30">
         <f>SUM(B9:B9)</f>
         <v>58506</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>SUM(C9:C9)</f>
         <v>72314</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>SUM(D9:D9)</f>
         <v>74483</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>SUM(E9:E9)</f>
         <v>76718</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>SUM(F9:F9)</f>
         <v>79019</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="25">
+        <v>206</v>
+      </c>
+      <c r="B12" s="26">
         <f>B7+B10</f>
         <v>118934</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>C7+C10</f>
         <v>147003</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>D7+D10</f>
         <v>151413</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>E7+E10</f>
         <v>155955</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <f>F7+F10</f>
         <v>160634</v>
       </c>
@@ -2295,7 +2305,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2325,7 +2335,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2335,112 +2345,112 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="24">
+        <v>209</v>
+      </c>
+      <c r="B5" s="25">
         <v>120000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>222480</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>280078</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>327818</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B6" s="24">
+        <v>210</v>
+      </c>
+      <c r="B6" s="25">
         <v>2500</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>4635</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>5835</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>6830</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B7" s="24">
+        <v>211</v>
+      </c>
+      <c r="B7" s="25">
         <v>70000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>129780</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>163379</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>191227</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>196964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B8" s="24">
+        <v>212</v>
+      </c>
+      <c r="B8" s="25">
         <v>4167</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>5150</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>5305</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>5464</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>5628</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="29">
+        <v>213</v>
+      </c>
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>196667</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>SUM(C5:C8)</f>
         <v>362045</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>SUM(D5:D8)</f>
         <v>454596</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>SUM(E5:E8)</f>
         <v>531339</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>SUM(F5:F8)</f>
         <v>547279</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2450,85 +2460,85 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B12" s="24">
+        <v>204</v>
+      </c>
+      <c r="B12" s="25">
         <v>58506</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>72314</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>74483</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <v>76718</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>79019</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="24">
+        <v>201</v>
+      </c>
+      <c r="B13" s="25">
         <v>47869</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>59166</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>60941</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>62769</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>64652</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="24">
+        <v>202</v>
+      </c>
+      <c r="B14" s="25">
         <v>12559</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>15523</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>15989</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>16468</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>16963</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B15" s="29">
+        <v>178</v>
+      </c>
+      <c r="B15" s="30">
         <f>SUM(B12:B14)</f>
         <v>118934</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>SUM(C12:C14)</f>
         <v>147003</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>SUM(D12:D14)</f>
         <v>151413</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>SUM(E12:E14)</f>
         <v>155955</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>SUM(F12:F14)</f>
         <v>160634</v>
       </c>
@@ -2544,198 +2554,198 @@
       <c r="F17" s="13"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="32" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B19" s="24">
+        <v>215</v>
+      </c>
+      <c r="B19" s="25">
         <v>5000</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>9270</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <v>11670</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <v>13659</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <v>14069</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="32" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B21" s="24">
+        <v>216</v>
+      </c>
+      <c r="B21" s="25">
         <v>3000</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <v>5562</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <v>7002</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <v>8195</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <v>8441</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="32" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B23" s="24">
+        <v>217</v>
+      </c>
+      <c r="B23" s="25">
         <v>25000</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="25">
         <v>30900</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="25">
         <v>31827</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="25">
         <v>32782</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B24" s="24">
+        <v>218</v>
+      </c>
+      <c r="B24" s="25">
         <v>3000</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="25">
         <v>3708</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="25">
         <v>3819</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="25">
         <v>3934</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="25">
         <v>4052</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B25" s="24">
+        <v>219</v>
+      </c>
+      <c r="B25" s="25">
         <v>2000</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="25">
         <v>2472</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="25">
         <v>2546</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="25">
         <v>2623</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="25">
         <v>2701</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B26" s="29">
+        <v>220</v>
+      </c>
+      <c r="B26" s="30">
         <f>SUM(B23:B25)</f>
         <v>30000</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <f>SUM(C23:C25)</f>
         <v>37080</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <f>SUM(D23:D25)</f>
         <v>38192</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <f>SUM(E23:E25)</f>
         <v>39338</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <f>SUM(F23:F25)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="32" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B28" s="24">
+        <v>221</v>
+      </c>
+      <c r="B28" s="25">
         <v>2500</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="25">
         <v>3090</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="25">
         <v>3183</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="25">
         <v>3278</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="25">
         <v>3377</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B29" s="29">
+        <v>222</v>
+      </c>
+      <c r="B29" s="30">
         <f>B19+B21+B26+B28</f>
         <v>40500</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>C19+C21+C26+C28</f>
         <v>55002</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <f>D19+D21+D26+D28</f>
         <v>60047</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <f>E19+E21+E26+E28</f>
         <v>64471</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <f>F19+F21+F26+F28</f>
         <v>66405</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -2745,25 +2755,25 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B32" s="29" t="str">
+        <v>224</v>
+      </c>
+      <c r="B32" s="30" t="str">
         <f>SUM(B32:B31)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="29" t="str">
+      <c r="C32" s="30" t="str">
         <f>SUM(C32:C31)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="29" t="str">
+      <c r="D32" s="30" t="str">
         <f>SUM(D32:D31)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="29" t="str">
+      <c r="E32" s="30" t="str">
         <f>SUM(E32:E31)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="29" t="str">
+      <c r="F32" s="30" t="str">
         <f>SUM(F32:F31)</f>
         <v>0</v>
       </c>
@@ -2794,7 +2804,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2824,132 +2834,132 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="27">
+        <v>213</v>
+      </c>
+      <c r="B4" s="28">
         <f>'Budget Detail'!B9</f>
         <v>196667</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="28">
         <f>'Budget Detail'!C9</f>
         <v>362045</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="28">
         <f>'Budget Detail'!D9</f>
         <v>454596</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="28">
         <f>'Budget Detail'!E9</f>
         <v>531339</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="28">
         <f>'Budget Detail'!F9</f>
         <v>547279</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="27">
+        <v>178</v>
+      </c>
+      <c r="B5" s="28">
         <f>'Budget Detail'!B15</f>
         <v>118934</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <f>'Budget Detail'!C15</f>
         <v>147003</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>'Budget Detail'!D15</f>
         <v>151413</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <f>'Budget Detail'!E15</f>
         <v>155955</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <f>'Budget Detail'!F15</f>
         <v>160634</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" s="27">
+        <v>222</v>
+      </c>
+      <c r="B6" s="28">
         <f>'Budget Detail'!B29</f>
         <v>40500</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>'Budget Detail'!C29</f>
         <v>55002</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>'Budget Detail'!D29</f>
         <v>60047</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>'Budget Detail'!E29</f>
         <v>64471</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>'Budget Detail'!F29</f>
         <v>66405</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B7" s="27" t="str">
+        <v>226</v>
+      </c>
+      <c r="B7" s="28" t="str">
         <f>'Budget Detail'!B32</f>
         <v>0</v>
       </c>
-      <c r="C7" s="27" t="str">
+      <c r="C7" s="28" t="str">
         <f>'Budget Detail'!C32</f>
         <v>0</v>
       </c>
-      <c r="D7" s="27" t="str">
+      <c r="D7" s="28" t="str">
         <f>'Budget Detail'!D32</f>
         <v>0</v>
       </c>
-      <c r="E7" s="27" t="str">
+      <c r="E7" s="28" t="str">
         <f>'Budget Detail'!E32</f>
         <v>0</v>
       </c>
-      <c r="F7" s="27" t="str">
+      <c r="F7" s="28" t="str">
         <f>'Budget Detail'!F32</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B8" s="29">
+        <v>227</v>
+      </c>
+      <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
         <v>159434</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>SUM(C5:C7)</f>
         <v>202005</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>SUM(D5:D7)</f>
         <v>211460</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>SUM(E5:E7)</f>
         <v>220426</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>SUM(F5:F7)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -2959,111 +2969,111 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B11" s="25">
+        <v>229</v>
+      </c>
+      <c r="B11" s="26">
         <f>B4-B8</f>
         <v>37233</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>C4-C8</f>
         <v>160040</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>D4-D8</f>
         <v>243136</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>E4-E8</f>
         <v>310913</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>F4-F8</f>
         <v>320240</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B12" s="23">
+        <v>230</v>
+      </c>
+      <c r="B12" s="24">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.1893178</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="24">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.44204552</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="24">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.53484014</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="24">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.58514961</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.58514961</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B13" s="24">
+        <v>231</v>
+      </c>
+      <c r="B13" s="25">
         <v>37233</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>197273</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>440409</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>751321</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>1071561</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B14" s="24">
+        <v>199</v>
+      </c>
+      <c r="B14" s="25">
         <v>16389</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>20114</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>20663</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>21254</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>21891</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B15" s="24">
+        <v>232</v>
+      </c>
+      <c r="B15" s="25">
         <v>13286</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <v>11222</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>9612</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>8817</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>9082</v>
       </c>
     </row>
@@ -3094,7 +3104,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3115,48 +3125,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3174,51 +3184,51 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="29">
+        <v>213</v>
+      </c>
+      <c r="B4" s="30">
         <v>9150</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <v>23550</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>23550</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>23550</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <v>23550</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="30">
         <v>23550</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="30">
         <v>23550</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="30">
         <v>23550</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="30">
         <v>23550</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="30">
         <v>23550</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="30">
         <v>14650</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="30">
         <v>250</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="30">
         <v>236000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3236,139 +3246,139 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B7" s="24">
+        <v>248</v>
+      </c>
+      <c r="B7" s="25">
         <v>11893</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>11893</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>11893</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>11893</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>11893</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="25">
         <v>11893</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="25">
         <v>11893</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="25">
         <v>11893</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="25">
         <v>11893</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="25">
         <v>11893</v>
       </c>
-      <c r="L7" s="24">
-        <v>0</v>
-      </c>
-      <c r="M7" s="24">
-        <v>0</v>
-      </c>
-      <c r="N7" s="24">
+      <c r="L7" s="25">
+        <v>0</v>
+      </c>
+      <c r="M7" s="25">
+        <v>0</v>
+      </c>
+      <c r="N7" s="25">
         <v>118934</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B8" s="24">
+        <v>249</v>
+      </c>
+      <c r="B8" s="25">
         <v>4050</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>4050</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>4050</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>4050</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>4050</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="25">
         <v>4050</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="25">
         <v>4050</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="25">
         <v>4050</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="25">
         <v>4050</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="25">
         <v>4050</v>
       </c>
-      <c r="L8" s="24">
-        <v>0</v>
-      </c>
-      <c r="M8" s="24">
-        <v>0</v>
-      </c>
-      <c r="N8" s="24">
+      <c r="L8" s="25">
+        <v>0</v>
+      </c>
+      <c r="M8" s="25">
+        <v>0</v>
+      </c>
+      <c r="N8" s="25">
         <v>40500</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B9" s="24">
-        <v>0</v>
-      </c>
-      <c r="C9" s="24">
-        <v>0</v>
-      </c>
-      <c r="D9" s="24">
-        <v>0</v>
-      </c>
-      <c r="E9" s="24">
-        <v>0</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0</v>
-      </c>
-      <c r="H9" s="24">
-        <v>0</v>
-      </c>
-      <c r="I9" s="24">
-        <v>0</v>
-      </c>
-      <c r="J9" s="24">
-        <v>0</v>
-      </c>
-      <c r="K9" s="24">
-        <v>0</v>
-      </c>
-      <c r="L9" s="24">
-        <v>0</v>
-      </c>
-      <c r="M9" s="24">
-        <v>0</v>
-      </c>
-      <c r="N9" s="24">
+        <v>250</v>
+      </c>
+      <c r="B9" s="25">
+        <v>0</v>
+      </c>
+      <c r="C9" s="25">
+        <v>0</v>
+      </c>
+      <c r="D9" s="25">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25">
+        <v>0</v>
+      </c>
+      <c r="F9" s="25">
+        <v>0</v>
+      </c>
+      <c r="G9" s="25">
+        <v>0</v>
+      </c>
+      <c r="H9" s="25">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25">
+        <v>0</v>
+      </c>
+      <c r="J9" s="25">
+        <v>0</v>
+      </c>
+      <c r="K9" s="25">
+        <v>0</v>
+      </c>
+      <c r="L9" s="25">
+        <v>0</v>
+      </c>
+      <c r="M9" s="25">
+        <v>0</v>
+      </c>
+      <c r="N9" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3386,164 +3396,164 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B12" s="27">
+        <v>227</v>
+      </c>
+      <c r="B12" s="28">
         <v>15943</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <v>15943</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <v>15943</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <v>15943</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <v>15943</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="28">
         <v>15943</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="28">
         <v>15943</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="28">
         <v>15943</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="28">
         <v>15943</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="28">
         <v>15943</v>
       </c>
-      <c r="L12" s="27">
-        <v>0</v>
-      </c>
-      <c r="M12" s="27">
-        <v>0</v>
-      </c>
-      <c r="N12" s="27">
+      <c r="L12" s="28">
+        <v>0</v>
+      </c>
+      <c r="M12" s="28">
+        <v>0</v>
+      </c>
+      <c r="N12" s="28">
         <v>159430</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B13" s="27">
+        <v>252</v>
+      </c>
+      <c r="B13" s="28">
         <v>-6793</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <v>7607</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <v>7607</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="28">
         <v>7607</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
         <v>7607</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="28">
         <v>7607</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="28">
         <v>7607</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="28">
         <v>7607</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="28">
         <v>7607</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="28">
         <v>7607</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="28">
         <v>14650</v>
       </c>
-      <c r="M13" s="27">
+      <c r="M13" s="28">
         <v>250</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="28">
         <v>76570</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B14" s="32">
+        <v>253</v>
+      </c>
+      <c r="B14" s="33">
         <v>-6793</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <v>814</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <v>8421</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <v>16028</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <v>23635</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="33">
         <v>31242</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="33">
         <v>38849</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="33">
         <v>46456</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="33">
         <v>54063</v>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="33">
         <v>61670</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="33">
         <v>76320</v>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="33">
         <v>76570</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="26">
         <v>76570</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B17" s="24">
+        <v>145</v>
+      </c>
+      <c r="B17" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B18" s="32">
+        <v>255</v>
+      </c>
+      <c r="B18" s="33">
         <v>76570</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B19" s="24">
+        <v>256</v>
+      </c>
+      <c r="B19" s="25">
         <v>-6793</v>
       </c>
     </row>
@@ -3573,7 +3583,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3603,7 +3613,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3612,28 +3622,28 @@
       <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="A5" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="30">
         <v>196667</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>362045</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>454596</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>531339</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>547279</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -3643,92 +3653,92 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B8" s="27">
+        <v>248</v>
+      </c>
+      <c r="B8" s="28">
         <v>118934</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <v>147003</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <v>151413</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <v>155955</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <v>160634</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B9" s="27">
+        <v>249</v>
+      </c>
+      <c r="B9" s="28">
         <v>40500</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <v>55002</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <v>60047</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <v>64471</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="28">
         <v>66405</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="27">
-        <v>0</v>
-      </c>
-      <c r="C10" s="27">
-        <v>0</v>
-      </c>
-      <c r="D10" s="27">
-        <v>0</v>
-      </c>
-      <c r="E10" s="27">
-        <v>0</v>
-      </c>
-      <c r="F10" s="27">
+        <v>258</v>
+      </c>
+      <c r="B10" s="28">
+        <v>0</v>
+      </c>
+      <c r="C10" s="28">
+        <v>0</v>
+      </c>
+      <c r="D10" s="28">
+        <v>0</v>
+      </c>
+      <c r="E10" s="28">
+        <v>0</v>
+      </c>
+      <c r="F10" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="B11" s="29">
+      <c r="A11" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
         <v>159434</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>SUM(C8:C10)</f>
         <v>202005</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>SUM(D8:D10)</f>
         <v>211460</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>SUM(E8:E10)</f>
         <v>220426</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>SUM(F8:F10)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -3737,51 +3747,51 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="B14" s="25">
+      <c r="A14" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="26">
         <f>B5-B11</f>
         <v>37233</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <f>C5-C11</f>
         <v>160040</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>D5-D11</f>
         <v>243136</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>E5-E11</f>
         <v>310913</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <f>F5-F11</f>
         <v>320240</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="23">
+        <v>230</v>
+      </c>
+      <c r="B15" s="24">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>0.1893178</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="24">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.44204552</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.53484014</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="24">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.58514961</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="24">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.58514961</v>
       </c>
@@ -3866,7 +3876,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3896,7 +3906,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3906,107 +3916,107 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B5" s="34">
+        <v>262</v>
+      </c>
+      <c r="B5" s="35">
         <v>76570</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="35">
         <v>236610</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="35">
         <v>479746</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="35">
         <v>790659</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <v>1110899</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B6" s="24">
-        <v>0</v>
-      </c>
-      <c r="C6" s="24">
-        <v>0</v>
-      </c>
-      <c r="D6" s="24">
-        <v>0</v>
-      </c>
-      <c r="E6" s="24">
-        <v>0</v>
-      </c>
-      <c r="F6" s="24">
+        <v>263</v>
+      </c>
+      <c r="B6" s="25">
+        <v>0</v>
+      </c>
+      <c r="C6" s="25">
+        <v>0</v>
+      </c>
+      <c r="D6" s="25">
+        <v>0</v>
+      </c>
+      <c r="E6" s="25">
+        <v>0</v>
+      </c>
+      <c r="F6" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B7" s="24">
+        <v>264</v>
+      </c>
+      <c r="B7" s="25">
         <v>5000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>5000</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>5000</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>5000</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>5000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B8" s="24">
-        <v>0</v>
-      </c>
-      <c r="C8" s="24">
-        <v>0</v>
-      </c>
-      <c r="D8" s="24">
-        <v>0</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0</v>
-      </c>
-      <c r="F8" s="24">
+        <v>265</v>
+      </c>
+      <c r="B8" s="25">
+        <v>0</v>
+      </c>
+      <c r="C8" s="25">
+        <v>0</v>
+      </c>
+      <c r="D8" s="25">
+        <v>0</v>
+      </c>
+      <c r="E8" s="25">
+        <v>0</v>
+      </c>
+      <c r="F8" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B9" s="29">
+        <v>266</v>
+      </c>
+      <c r="B9" s="30">
         <v>81570</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>241610</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>484746</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>795659</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>1115899</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4016,67 +4026,67 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" s="24">
-        <v>0</v>
-      </c>
-      <c r="C12" s="24">
-        <v>0</v>
-      </c>
-      <c r="D12" s="24">
-        <v>0</v>
-      </c>
-      <c r="E12" s="24">
-        <v>0</v>
-      </c>
-      <c r="F12" s="24">
+        <v>268</v>
+      </c>
+      <c r="B12" s="25">
+        <v>0</v>
+      </c>
+      <c r="C12" s="25">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25">
+        <v>0</v>
+      </c>
+      <c r="F12" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B13" s="24">
-        <v>0</v>
-      </c>
-      <c r="C13" s="24">
-        <v>0</v>
-      </c>
-      <c r="D13" s="24">
-        <v>0</v>
-      </c>
-      <c r="E13" s="24">
-        <v>0</v>
-      </c>
-      <c r="F13" s="24">
+        <v>269</v>
+      </c>
+      <c r="B13" s="25">
+        <v>0</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>0</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0</v>
+      </c>
+      <c r="F13" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="29">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29">
+        <v>270</v>
+      </c>
+      <c r="B14" s="30">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4086,41 +4096,41 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B17" s="25">
+        <v>272</v>
+      </c>
+      <c r="B17" s="26">
         <v>81570</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <v>241610</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <v>484746</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>795659</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>1115899</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B19" s="35">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35">
-        <v>0</v>
-      </c>
-      <c r="D19" s="35">
-        <v>0</v>
-      </c>
-      <c r="E19" s="35">
-        <v>0</v>
-      </c>
-      <c r="F19" s="35">
+        <v>273</v>
+      </c>
+      <c r="B19" s="36">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36">
+        <v>0</v>
+      </c>
+      <c r="D19" s="36">
+        <v>0</v>
+      </c>
+      <c r="E19" s="36">
+        <v>0</v>
+      </c>
+      <c r="F19" s="36">
         <v>0</v>
       </c>
     </row>
@@ -4150,7 +4160,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4180,7 +4190,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4190,132 +4200,132 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B5" s="24">
+        <v>276</v>
+      </c>
+      <c r="B5" s="25">
         <v>196667</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>362045</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>454596</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>531339</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>547279</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B6" s="24">
+        <v>248</v>
+      </c>
+      <c r="B6" s="25">
         <v>118934</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>147003</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>151413</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>155955</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>160634</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B7" s="24">
+        <v>249</v>
+      </c>
+      <c r="B7" s="25">
         <v>40500</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>55002</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>60047</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>64471</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>66405</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" s="27">
+        <v>277</v>
+      </c>
+      <c r="B8" s="28">
         <f>B5-B6-B7</f>
         <v>37233</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>C5-C6-C7</f>
         <v>160040</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>D5-D6-D7</f>
         <v>243136</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>E5-E6-E7</f>
         <v>310913</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>F5-F6-F7</f>
         <v>320240</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B9" s="24">
-        <v>0</v>
-      </c>
-      <c r="C9" s="24">
-        <v>0</v>
-      </c>
-      <c r="D9" s="24">
-        <v>0</v>
-      </c>
-      <c r="E9" s="24">
-        <v>0</v>
-      </c>
-      <c r="F9" s="24">
+        <v>250</v>
+      </c>
+      <c r="B9" s="25">
+        <v>0</v>
+      </c>
+      <c r="C9" s="25">
+        <v>0</v>
+      </c>
+      <c r="D9" s="25">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25">
+        <v>0</v>
+      </c>
+      <c r="F9" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" s="36" t="s">
         <v>278</v>
       </c>
-      <c r="C10" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>278</v>
+      <c r="B10" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -4325,97 +4335,97 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B13" s="24">
+        <v>281</v>
+      </c>
+      <c r="B13" s="25">
         <v>76570</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>236610</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>479746</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>790659</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>1110899</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B14" s="21">
+        <v>282</v>
+      </c>
+      <c r="B14" s="22">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>175</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="22">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>428</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="22">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>828</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="22">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>1309</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>1786</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B15" s="28">
+        <v>283</v>
+      </c>
+      <c r="B15" s="29">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>5.8</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>14.1</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>27.2</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>43</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>58.7</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="23">
+        <v>165</v>
+      </c>
+      <c r="B16" s="24">
         <v>0.48</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="24">
         <v>0.72</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="24">
         <v>0.88</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="24">
         <v>1</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -4425,87 +4435,87 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B19" s="24">
+        <v>199</v>
+      </c>
+      <c r="B19" s="25">
         <v>16389</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>20114</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <v>20663</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <v>21254</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <v>21891</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B20" s="24">
+        <v>285</v>
+      </c>
+      <c r="B20" s="25">
         <v>118934</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="25">
         <v>147003</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="25">
         <v>151413</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <v>155955</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="25">
         <v>160634</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B21" s="24">
+        <v>286</v>
+      </c>
+      <c r="B21" s="25">
         <v>3375</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <v>3056</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <v>2729</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <v>2579</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <v>2656</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B22" s="37">
+        <v>287</v>
+      </c>
+      <c r="B22" s="38">
         <v>10</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="38">
         <v>9</v>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="38">
         <v>9</v>
       </c>
-      <c r="E22" s="37">
+      <c r="E22" s="38">
         <v>9</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="38">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -4515,102 +4525,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B25" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>278</v>
+        <v>289</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="E25" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="F25" s="39" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B26" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="C26" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>290</v>
+      <c r="B26" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="C27" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>290</v>
+      <c r="D27" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="F27" s="40" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>290</v>
+        <v>294</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="E29" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>290</v>
+        <v>295</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="E29" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4650,60 +4660,60 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
-        <v>295</v>
-      </c>
-      <c r="B3" s="41" t="s">
+      <c r="A3" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>296</v>
-      </c>
-      <c r="E3" s="41" t="s">
+      <c r="D3" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B4" s="24">
+        <v>298</v>
+      </c>
+      <c r="B4" s="25">
         <v>20000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="E4" s="24">
+        <v>299</v>
+      </c>
+      <c r="E4" s="25">
         <v>15000</v>
       </c>
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="E5" s="24">
+        <v>300</v>
+      </c>
+      <c r="E5" s="25">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B7" s="25">
+        <v>301</v>
+      </c>
+      <c r="B7" s="26">
         <v>20000</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E7" s="25">
+        <v>302</v>
+      </c>
+      <c r="E7" s="26">
         <v>20000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B8" s="35">
+        <v>303</v>
+      </c>
+      <c r="B8" s="36">
         <v>0</v>
       </c>
     </row>
@@ -4869,7 +4879,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4879,7 +4889,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -4889,7 +4899,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4914,127 +4924,127 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B6" s="24">
+        <v>276</v>
+      </c>
+      <c r="B6" s="25">
         <v>196667</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>362045</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>454596</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>531339</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>547279</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="24">
+        <v>227</v>
+      </c>
+      <c r="B7" s="25">
         <v>159434</v>
       </c>
-      <c r="C7" s="24">
-        <v>201888</v>
-      </c>
-      <c r="D7" s="24">
-        <v>211186</v>
-      </c>
-      <c r="E7" s="24">
-        <v>219967</v>
-      </c>
-      <c r="F7" s="24">
-        <v>226410</v>
+      <c r="C7" s="25">
+        <v>202005</v>
+      </c>
+      <c r="D7" s="25">
+        <v>211460</v>
+      </c>
+      <c r="E7" s="25">
+        <v>220426</v>
+      </c>
+      <c r="F7" s="25">
+        <v>227039</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="25">
+        <v>229</v>
+      </c>
+      <c r="B8" s="26">
         <v>37233</v>
       </c>
-      <c r="C8" s="25">
-        <v>160157</v>
-      </c>
-      <c r="D8" s="25">
-        <v>243409</v>
-      </c>
-      <c r="E8" s="25">
-        <v>311372</v>
-      </c>
-      <c r="F8" s="25">
-        <v>320869</v>
+      <c r="C8" s="26">
+        <v>160040</v>
+      </c>
+      <c r="D8" s="26">
+        <v>243136</v>
+      </c>
+      <c r="E8" s="26">
+        <v>310913</v>
+      </c>
+      <c r="F8" s="26">
+        <v>320240</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B9" s="23">
+        <v>230</v>
+      </c>
+      <c r="B9" s="24">
         <v>0.18931779661016948</v>
       </c>
-      <c r="C9" s="23">
-        <v>0.4423686834509522</v>
-      </c>
-      <c r="D9" s="23">
-        <v>0.5354413666298831</v>
-      </c>
-      <c r="E9" s="23">
-        <v>0.5860139501663209</v>
-      </c>
-      <c r="F9" s="23">
-        <v>0.5862992694238808</v>
+      <c r="C9" s="24">
+        <v>0.44204551920341395</v>
+      </c>
+      <c r="D9" s="24">
+        <v>0.5348401400233372</v>
+      </c>
+      <c r="E9" s="24">
+        <v>0.5851496143958869</v>
+      </c>
+      <c r="F9" s="24">
+        <v>0.5851496143958869</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="C10" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="F10" s="42" t="s">
-        <v>278</v>
+      <c r="B10" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B11" s="21">
+        <v>287</v>
+      </c>
+      <c r="B11" s="22">
         <v>10</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <v>9</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="22">
         <v>9</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="22">
         <v>9</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5044,7 +5054,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5069,121 +5079,121 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B16" s="24">
+        <v>276</v>
+      </c>
+      <c r="B16" s="25">
         <v>157333</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>289636</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>363677</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>425071</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>437823</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B17" s="24">
+        <v>227</v>
+      </c>
+      <c r="B17" s="25">
         <v>159434</v>
       </c>
-      <c r="C17" s="24">
-        <v>201888</v>
-      </c>
-      <c r="D17" s="24">
-        <v>211186</v>
-      </c>
-      <c r="E17" s="24">
-        <v>219967</v>
-      </c>
-      <c r="F17" s="24">
-        <v>226410</v>
+      <c r="C17" s="25">
+        <v>202005</v>
+      </c>
+      <c r="D17" s="25">
+        <v>211460</v>
+      </c>
+      <c r="E17" s="25">
+        <v>220426</v>
+      </c>
+      <c r="F17" s="25">
+        <v>227039</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B18" s="25">
+        <v>229</v>
+      </c>
+      <c r="B18" s="26">
         <v>-2101</v>
       </c>
-      <c r="C18" s="25">
-        <v>87748</v>
-      </c>
-      <c r="D18" s="25">
-        <v>152490</v>
-      </c>
-      <c r="E18" s="25">
-        <v>205104</v>
-      </c>
-      <c r="F18" s="25">
-        <v>211413</v>
+      <c r="C18" s="26">
+        <v>87631</v>
+      </c>
+      <c r="D18" s="26">
+        <v>152217</v>
+      </c>
+      <c r="E18" s="26">
+        <v>204645</v>
+      </c>
+      <c r="F18" s="26">
+        <v>210784</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B19" s="23">
+        <v>230</v>
+      </c>
+      <c r="B19" s="24">
         <v>-0.013352754237288008</v>
       </c>
-      <c r="C19" s="23">
-        <v>0.3029608543136903</v>
-      </c>
-      <c r="D19" s="23">
-        <v>0.41930170828735386</v>
-      </c>
-      <c r="E19" s="23">
-        <v>0.48251743770790123</v>
-      </c>
-      <c r="F19" s="23">
-        <v>0.4828740867798511</v>
+      <c r="C19" s="24">
+        <v>0.3025568990042674</v>
+      </c>
+      <c r="D19" s="24">
+        <v>0.41855017502917163</v>
+      </c>
+      <c r="E19" s="24">
+        <v>0.4814370179948587</v>
+      </c>
+      <c r="F19" s="24">
+        <v>0.48143701799485866</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B20" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="C20" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="D20" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="E20" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="F20" s="42" t="s">
-        <v>278</v>
+      <c r="B20" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B21" s="21">
+        <v>287</v>
+      </c>
+      <c r="B21" s="22">
         <v>11</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="22">
         <v>9</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="22">
         <v>9</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="22">
         <v>9</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="22">
         <v>9</v>
       </c>
     </row>
@@ -5215,7 +5225,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5249,7 +5259,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -5273,7 +5283,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -5281,7 +5291,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5301,125 +5311,125 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="F12" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="D13" s="24">
+        <v>276</v>
+      </c>
+      <c r="D13" s="25">
         <v>196667</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>362045</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>454596</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="25">
         <v>531339</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="25">
         <v>547279</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="D14" s="24">
+        <v>227</v>
+      </c>
+      <c r="D14" s="25">
         <v>159434</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>202005</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>211460</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="25">
         <v>220426</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="25">
         <v>227039</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" s="24">
+        <v>229</v>
+      </c>
+      <c r="D15" s="25">
         <v>37233</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>160040</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>243136</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="25">
         <v>310913</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="25">
         <v>320240</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="D16" s="24">
+        <v>313</v>
+      </c>
+      <c r="D16" s="25">
         <v>76570</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>236610</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>479746</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="25">
         <v>790659</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="25">
         <v>1110899</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D17" s="24">
-        <v>0</v>
-      </c>
-      <c r="E17" s="24">
-        <v>0</v>
-      </c>
-      <c r="F17" s="24">
-        <v>0</v>
-      </c>
-      <c r="G17" s="24">
-        <v>0</v>
-      </c>
-      <c r="H17" s="24">
+        <v>314</v>
+      </c>
+      <c r="D17" s="25">
+        <v>0</v>
+      </c>
+      <c r="E17" s="25">
+        <v>0</v>
+      </c>
+      <c r="F17" s="25">
+        <v>0</v>
+      </c>
+      <c r="G17" s="25">
+        <v>0</v>
+      </c>
+      <c r="H17" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -5439,105 +5449,105 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="43" t="s">
+      <c r="F20" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="43" t="s">
+      <c r="G20" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="43" t="s">
+      <c r="H20" s="44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D21" s="23">
+        <v>316</v>
+      </c>
+      <c r="D21" s="24">
         <v>0.18931779661016948</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <v>0.44204551920341395</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="24">
         <v>0.5348401400233372</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="24">
         <v>0.5851496143958869</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="24">
         <v>0.5851496143958869</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D22" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="E22" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="F22" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="G22" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="H22" s="42" t="s">
-        <v>278</v>
+      <c r="D22" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="G22" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="H22" s="43" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D23" s="23">
+        <v>165</v>
+      </c>
+      <c r="D23" s="24">
         <v>0.48</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>0.72</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="24">
         <v>0.88</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="24">
         <v>1</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D24" s="21">
+        <v>317</v>
+      </c>
+      <c r="D24" s="22">
         <v>12</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="22">
         <v>18</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="22">
         <v>22</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="22">
         <v>25</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="22">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6091,25 +6101,31 @@
       <c r="F44" s="13"/>
       <c r="G44" s="13"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>141</v>
       </c>
       <c r="B45" s="18">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C45" s="20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B46" s="18">
         <v>0.03</v>
       </c>
+      <c r="C46" s="20" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B47" s="19">
         <v>0.8333333333333334</v>
@@ -6117,7 +6133,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B48" s="17">
         <v>0</v>
@@ -6125,10 +6141,10 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -6163,10 +6179,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6187,10 +6203,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6203,7 +6219,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -6214,31 +6230,31 @@
         <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -6246,31 +6262,31 @@
         <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -6330,7 +6346,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -6342,19 +6358,19 @@
       <c r="A6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <v>12</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>18</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>22</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>25</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>25</v>
       </c>
     </row>
@@ -6362,47 +6378,47 @@
       <c r="A7" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="22">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B8" s="22">
+        <v>165</v>
+      </c>
+      <c r="B8" s="23">
         <v>0.48</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="23">
         <v>0.72</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <v>0.88</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="23">
         <v>1</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C10" s="23">
+        <v>167</v>
+      </c>
+      <c r="C10" s="24">
         <v>0.5</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="24">
         <v>0.2222222222222222</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="24">
         <v>0.13636363636363635</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="24">
         <v>0</v>
       </c>
     </row>
@@ -6432,7 +6448,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6462,7 +6478,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6472,105 +6488,105 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="24">
+        <v>170</v>
+      </c>
+      <c r="B5" s="25">
         <v>144000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>222480</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>280078</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>327818</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="24">
+        <v>171</v>
+      </c>
+      <c r="B6" s="25">
         <v>3000</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>4635</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>5835</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>6830</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="24">
+        <v>172</v>
+      </c>
+      <c r="B7" s="25">
         <v>84000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>129780</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>163379</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>191227</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>196964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" s="24">
+        <v>173</v>
+      </c>
+      <c r="B8" s="25">
         <v>5000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>5150</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>5305</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>5464</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>5628</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" s="25">
+        <v>174</v>
+      </c>
+      <c r="B9" s="26">
         <f>SUM(B5:B8)</f>
         <v>236000</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <f>SUM(C5:C8)</f>
         <v>362045</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <f>SUM(D5:D8)</f>
         <v>454596</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>SUM(E5:E8)</f>
         <v>531339</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <f>SUM(F5:F8)</f>
         <v>547279</v>
       </c>
@@ -6625,7 +6641,7 @@
         <v>114</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>116</v>
@@ -6634,7 +6650,7 @@
         <v>117</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6644,19 +6660,19 @@
       <c r="B4" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>1</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="25">
         <v>55000</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="24">
         <v>0.2</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="28">
         <v>70208</v>
       </c>
     </row>
@@ -6667,19 +6683,19 @@
       <c r="B5" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <v>1</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>45000</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="24">
         <v>0.2</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="28">
         <v>57443</v>
       </c>
     </row>
@@ -6690,25 +6706,25 @@
       <c r="B6" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>0.5</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>28000</v>
       </c>
-      <c r="E6" s="23">
-        <v>0</v>
-      </c>
-      <c r="F6" s="23">
+      <c r="E6" s="24">
+        <v>0</v>
+      </c>
+      <c r="F6" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="28">
         <v>15071</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -6739,61 +6755,61 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B10" s="25">
+        <v>178</v>
+      </c>
+      <c r="B10" s="26">
         <v>118934</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>147003</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>151413</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <v>155955</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <v>160634</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B11" s="23">
+        <v>179</v>
+      </c>
+      <c r="B11" s="24">
         <v>0.5039583333333334</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="24">
         <v>0.40603413940256045</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="24">
         <v>0.333071178529755</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="24">
         <v>0.2935136246786632</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <v>0.2935136246786632</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" s="28">
+        <v>180</v>
+      </c>
+      <c r="B12" s="29">
         <v>4.8</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <v>7.2</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <v>8.8</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <v>10</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <v>10</v>
       </c>
     </row>
@@ -6823,7 +6839,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6863,45 +6879,45 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="24">
+        <v>182</v>
+      </c>
+      <c r="B5" s="25">
         <v>6000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>9270</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>11670</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>13659</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>14069</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" s="29">
+        <v>183</v>
+      </c>
+      <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <f>SUM(C5:C5)</f>
         <v>9270</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>SUM(D5:D5)</f>
         <v>11670</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <f>SUM(E5:E5)</f>
         <v>13659</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <f>SUM(F5:F5)</f>
         <v>14069</v>
       </c>
@@ -6918,45 +6934,45 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B8" s="24">
+        <v>184</v>
+      </c>
+      <c r="B8" s="25">
         <v>3600</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>5562</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>7002</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>8195</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>8441</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B9" s="29">
+        <v>185</v>
+      </c>
+      <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
         <v>3600</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>SUM(C8:C8)</f>
         <v>5562</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>SUM(D8:D8)</f>
         <v>7002</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>SUM(E8:E8)</f>
         <v>8195</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>SUM(F8:F8)</f>
         <v>8441</v>
       </c>
@@ -6973,85 +6989,85 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B11" s="24">
+        <v>186</v>
+      </c>
+      <c r="B11" s="25">
         <v>30000</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <v>30900</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>31827</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <v>32782</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B12" s="24">
+        <v>187</v>
+      </c>
+      <c r="B12" s="25">
         <v>3600</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>3708</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>3819</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <v>3934</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>4052</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="24">
+        <v>188</v>
+      </c>
+      <c r="B13" s="25">
         <v>2400</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>2472</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>2546</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>2623</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>2701</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B14" s="29">
+        <v>189</v>
+      </c>
+      <c r="B14" s="30">
         <f>SUM(B11:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>SUM(C11:C13)</f>
         <v>37080</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>SUM(D11:D13)</f>
         <v>38192</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>SUM(E11:E13)</f>
         <v>39338</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>SUM(F11:F13)</f>
         <v>40518</v>
       </c>
@@ -7068,70 +7084,70 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B16" s="24">
+        <v>190</v>
+      </c>
+      <c r="B16" s="25">
         <v>3000</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>3090</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>3183</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>3278</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>3377</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="29">
+        <v>191</v>
+      </c>
+      <c r="B17" s="30">
         <f>SUM(B16:B16)</f>
         <v>3000</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>SUM(C16:C16)</f>
         <v>3090</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>SUM(D16:D16)</f>
         <v>3183</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>SUM(E16:E16)</f>
         <v>3278</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>SUM(F16:F16)</f>
         <v>3377</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="25">
+        <v>192</v>
+      </c>
+      <c r="B19" s="26">
         <f>B6+B9+B14+B17</f>
         <v>48600</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <f>C6+C9+C14+C17</f>
         <v>55002</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <f>D6+D9+D14+D17</f>
         <v>60047</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <f>E6+E9+E14+E17</f>
         <v>64471</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <f>F6+F9+F14+F17</f>
         <v>66405</v>
       </c>
@@ -7163,7 +7179,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7188,22 +7204,22 @@
         <v>139</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F5" s="25">
+        <v>195</v>
+      </c>
+      <c r="F5" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F6" s="29">
+        <v>196</v>
+      </c>
+      <c r="F6" s="30">
         <v>0</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="320">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -459,10 +459,13 @@
     <t>Salary Escalation Rate</t>
   </si>
   <si>
-    <t>Derived from tuition escalation rate</t>
+    <t>Salary input or tuition escalation fallback</t>
   </si>
   <si>
     <t>Cost Inflation Rate</t>
+  </si>
+  <si>
+    <t>Cost inflation input or tuition escalation fallback</t>
   </si>
   <si>
     <t>Year 1 Proration Factor</t>
@@ -1887,7 +1890,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1937,7 +1940,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2027,7 +2030,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B11" s="26">
         <f>SUM(B7:B10)</f>
@@ -2052,7 +2055,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B13" s="25">
         <v>19667</v>
@@ -2096,7 +2099,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2136,7 +2139,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B5" s="25">
         <v>47869</v>
@@ -2156,7 +2159,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B6" s="25">
         <v>12559</v>
@@ -2176,7 +2179,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B7" s="30">
         <f>SUM(B5:B6)</f>
@@ -2211,7 +2214,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B9" s="25">
         <v>58506</v>
@@ -2231,7 +2234,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B10" s="30">
         <f>SUM(B9:B9)</f>
@@ -2256,7 +2259,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B12" s="26">
         <f>B7+B10</f>
@@ -2305,7 +2308,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2335,7 +2338,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2345,7 +2348,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B5" s="25">
         <v>120000</v>
@@ -2365,7 +2368,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B6" s="25">
         <v>2500</v>
@@ -2385,7 +2388,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B7" s="25">
         <v>70000</v>
@@ -2405,7 +2408,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B8" s="25">
         <v>4167</v>
@@ -2425,7 +2428,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
@@ -2450,7 +2453,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2460,7 +2463,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B12" s="25">
         <v>58506</v>
@@ -2480,7 +2483,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B13" s="25">
         <v>47869</v>
@@ -2500,7 +2503,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B14" s="25">
         <v>12559</v>
@@ -2520,7 +2523,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" s="30">
         <f>SUM(B12:B14)</f>
@@ -2560,7 +2563,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" s="25">
         <v>5000</v>
@@ -2585,7 +2588,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B21" s="25">
         <v>3000</v>
@@ -2610,7 +2613,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23" s="25">
         <v>25000</v>
@@ -2630,7 +2633,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" s="25">
         <v>3000</v>
@@ -2650,7 +2653,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B25" s="25">
         <v>2000</v>
@@ -2670,7 +2673,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B26" s="30">
         <f>SUM(B23:B25)</f>
@@ -2700,7 +2703,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B28" s="25">
         <v>2500</v>
@@ -2720,7 +2723,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B29" s="30">
         <f>B19+B21+B26+B28</f>
@@ -2745,7 +2748,7 @@
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -2755,7 +2758,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B32" s="30" t="str">
         <f>SUM(B32:B31)</f>
@@ -2804,7 +2807,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2834,7 +2837,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B4" s="28">
         <f>'Budget Detail'!B9</f>
@@ -2859,7 +2862,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B5" s="28">
         <f>'Budget Detail'!B15</f>
@@ -2884,7 +2887,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B6" s="28">
         <f>'Budget Detail'!B29</f>
@@ -2909,7 +2912,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B7" s="28" t="str">
         <f>'Budget Detail'!B32</f>
@@ -2934,7 +2937,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
@@ -2959,7 +2962,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -2969,7 +2972,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B11" s="26">
         <f>B4-B8</f>
@@ -2994,7 +2997,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B12" s="24">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3019,7 +3022,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B13" s="25">
         <v>37233</v>
@@ -3039,7 +3042,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B14" s="25">
         <v>16389</v>
@@ -3059,7 +3062,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B15" s="25">
         <v>13286</v>
@@ -3104,7 +3107,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3125,48 +3128,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3184,7 +3187,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B4" s="30">
         <v>9150</v>
@@ -3228,7 +3231,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3246,7 +3249,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B7" s="25">
         <v>11893</v>
@@ -3290,7 +3293,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B8" s="25">
         <v>4050</v>
@@ -3334,7 +3337,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B9" s="25">
         <v>0</v>
@@ -3378,7 +3381,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3396,7 +3399,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B12" s="28">
         <v>15943</v>
@@ -3440,7 +3443,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B13" s="28">
         <v>-6793</v>
@@ -3484,7 +3487,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B14" s="33">
         <v>-6793</v>
@@ -3528,14 +3531,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B17" s="25">
         <v>0</v>
@@ -3543,7 +3546,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B18" s="33">
         <v>76570</v>
@@ -3551,7 +3554,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B19" s="25">
         <v>-6793</v>
@@ -3583,7 +3586,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3613,7 +3616,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3623,7 +3626,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B5" s="30">
         <v>196667</v>
@@ -3643,7 +3646,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -3653,7 +3656,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B8" s="28">
         <v>118934</v>
@@ -3673,7 +3676,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B9" s="28">
         <v>40500</v>
@@ -3693,7 +3696,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B10" s="28">
         <v>0</v>
@@ -3713,7 +3716,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
@@ -3738,7 +3741,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -3748,7 +3751,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B14" s="26">
         <f>B5-B11</f>
@@ -3773,7 +3776,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B15" s="24">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -3876,7 +3879,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3906,7 +3909,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3916,7 +3919,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B5" s="35">
         <v>76570</v>
@@ -3936,7 +3939,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B6" s="25">
         <v>0</v>
@@ -3956,7 +3959,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B7" s="25">
         <v>5000</v>
@@ -3976,7 +3979,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B8" s="25">
         <v>0</v>
@@ -3996,7 +3999,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B9" s="30">
         <v>81570</v>
@@ -4016,7 +4019,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4026,7 +4029,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B12" s="25">
         <v>0</v>
@@ -4046,7 +4049,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B13" s="25">
         <v>0</v>
@@ -4066,7 +4069,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B14" s="30">
         <v>0</v>
@@ -4086,7 +4089,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4096,7 +4099,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B17" s="26">
         <v>81570</v>
@@ -4116,7 +4119,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B19" s="36">
         <v>0</v>
@@ -4160,7 +4163,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4190,7 +4193,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4200,7 +4203,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B5" s="25">
         <v>196667</v>
@@ -4220,7 +4223,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B6" s="25">
         <v>118934</v>
@@ -4240,7 +4243,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B7" s="25">
         <v>40500</v>
@@ -4260,7 +4263,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B8" s="28">
         <f>B5-B6-B7</f>
@@ -4285,7 +4288,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B9" s="25">
         <v>0</v>
@@ -4305,27 +4308,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -4335,7 +4338,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B13" s="25">
         <v>76570</v>
@@ -4355,7 +4358,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B14" s="22">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -4380,7 +4383,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B15" s="29">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -4405,7 +4408,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B16" s="24">
         <v>0.48</v>
@@ -4425,7 +4428,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -4435,7 +4438,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" s="25">
         <v>16389</v>
@@ -4455,7 +4458,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B20" s="25">
         <v>118934</v>
@@ -4475,7 +4478,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B21" s="25">
         <v>3375</v>
@@ -4495,7 +4498,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B22" s="38">
         <v>10</v>
@@ -4515,7 +4518,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -4525,102 +4528,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>294</v>
+      </c>
+      <c r="C27" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="B27" s="41" t="s">
-        <v>293</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>291</v>
-      </c>
       <c r="D27" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F27" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F28" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F29" s="40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4661,13 +4664,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B3" s="42" t="s">
         <v>100</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>100</v>
@@ -4675,13 +4678,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B4" s="25">
         <v>20000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E4" s="25">
         <v>15000</v>
@@ -4689,7 +4692,7 @@
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E5" s="25">
         <v>5000</v>
@@ -4697,13 +4700,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B7" s="26">
         <v>20000</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E7" s="26">
         <v>20000</v>
@@ -4711,7 +4714,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B8" s="36">
         <v>0</v>
@@ -4879,7 +4882,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4889,7 +4892,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -4899,7 +4902,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4924,7 +4927,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B6" s="25">
         <v>196667</v>
@@ -4944,7 +4947,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B7" s="25">
         <v>159434</v>
@@ -4964,7 +4967,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B8" s="26">
         <v>37233</v>
@@ -4984,7 +4987,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B9" s="24">
         <v>0.18931779661016948</v>
@@ -5004,27 +5007,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B11" s="22">
         <v>10</v>
@@ -5044,7 +5047,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5054,7 +5057,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5079,7 +5082,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B16" s="25">
         <v>157333</v>
@@ -5099,7 +5102,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B17" s="25">
         <v>159434</v>
@@ -5119,7 +5122,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B18" s="26">
         <v>-2101</v>
@@ -5139,7 +5142,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B19" s="24">
         <v>-0.013352754237288008</v>
@@ -5159,27 +5162,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B21" s="22">
         <v>11</v>
@@ -5225,7 +5228,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5259,7 +5262,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -5283,7 +5286,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -5291,7 +5294,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5329,7 +5332,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D13" s="25">
         <v>196667</v>
@@ -5349,7 +5352,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D14" s="25">
         <v>159434</v>
@@ -5369,7 +5372,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D15" s="25">
         <v>37233</v>
@@ -5389,7 +5392,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D16" s="25">
         <v>76570</v>
@@ -5409,7 +5412,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D17" s="25">
         <v>0</v>
@@ -5429,7 +5432,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -5467,7 +5470,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D21" s="24">
         <v>0.18931779661016948</v>
@@ -5487,27 +5490,27 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G22" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H22" s="43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D23" s="24">
         <v>0.48</v>
@@ -5527,7 +5530,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D24" s="22">
         <v>12</v>
@@ -5547,7 +5550,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6120,12 +6123,12 @@
         <v>0.03</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B47" s="19">
         <v>0.8333333333333334</v>
@@ -6133,7 +6136,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B48" s="17">
         <v>0</v>
@@ -6141,10 +6144,10 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -6179,10 +6182,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6203,10 +6206,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6219,7 +6222,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -6230,31 +6233,31 @@
         <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -6262,31 +6265,31 @@
         <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -6346,7 +6349,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -6384,7 +6387,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B8" s="23">
         <v>0.48</v>
@@ -6404,10 +6407,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C10" s="24">
         <v>0.5</v>
@@ -6448,7 +6451,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6478,7 +6481,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6488,7 +6491,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B5" s="25">
         <v>144000</v>
@@ -6508,7 +6511,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B6" s="25">
         <v>3000</v>
@@ -6528,7 +6531,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B7" s="25">
         <v>84000</v>
@@ -6548,7 +6551,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B8" s="25">
         <v>5000</v>
@@ -6568,7 +6571,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B9" s="26">
         <f>SUM(B5:B8)</f>
@@ -6641,7 +6644,7 @@
         <v>114</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>116</v>
@@ -6650,7 +6653,7 @@
         <v>117</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6724,7 +6727,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -6755,7 +6758,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B10" s="26">
         <v>118934</v>
@@ -6775,7 +6778,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B11" s="24">
         <v>0.5039583333333334</v>
@@ -6795,7 +6798,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B12" s="29">
         <v>4.8</v>
@@ -6839,7 +6842,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6879,7 +6882,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B5" s="25">
         <v>6000</v>
@@ -6899,7 +6902,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
@@ -6934,7 +6937,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B8" s="25">
         <v>3600</v>
@@ -6954,7 +6957,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
@@ -6989,7 +6992,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B11" s="25">
         <v>30000</v>
@@ -7009,7 +7012,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B12" s="25">
         <v>3600</v>
@@ -7029,7 +7032,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B13" s="25">
         <v>2400</v>
@@ -7049,7 +7052,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B14" s="30">
         <f>SUM(B11:B13)</f>
@@ -7084,7 +7087,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="25">
         <v>3000</v>
@@ -7104,7 +7107,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B17" s="30">
         <f>SUM(B16:B16)</f>
@@ -7129,7 +7132,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B19" s="26">
         <f>B6+B9+B14+B17</f>
@@ -7179,7 +7182,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7204,12 +7207,12 @@
         <v>139</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F5" s="26">
         <v>0</v>
@@ -7217,7 +7220,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F6" s="30">
         <v>0</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -26,7 +26,7 @@
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -72,7 +72,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>Stage</t>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="337">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -222,13 +222,13 @@
     <t>How to Use This Workbook</t>
   </si>
   <si>
-    <t>Color Legend</t>
-  </si>
-  <si>
-    <t>Yellow cells are editable inputs - change these to update your model.</t>
-  </si>
-  <si>
-    <t>Gray cells contain formulas - do not edit.</t>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Yellow cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
   </si>
   <si>
     <t>Green cells are key outputs and summary metrics.</t>
@@ -240,7 +240,7 @@
     <t>Navigation</t>
   </si>
   <si>
-    <t>The Assumptions tab is the central control panel - all other tabs reference it.</t>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
   </si>
   <si>
     <t>Structure</t>
@@ -258,6 +258,24 @@
     <t>Tabs 18-21: Analysis &amp; underwriting</t>
   </si>
   <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the 5-Year Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs: the Cash Flow, Balance Sheet, and DSCR</t>
+  </si>
+  <si>
+    <t>schedules all reference the same debt service figures. The Debt Schedule</t>
+  </si>
+  <si>
+    <t>tab breaks out interest and principal separately for detailed analysis.</t>
+  </si>
+  <si>
     <t>Tips</t>
   </si>
   <si>
@@ -366,6 +384,15 @@
     <t>Annual Fixed</t>
   </si>
   <si>
+    <t>Scholarship Discount</t>
+  </si>
+  <si>
+    <t>Tuition Offsets</t>
+  </si>
+  <si>
+    <t>% of Base</t>
+  </si>
+  <si>
     <t>STAFFING</t>
   </si>
   <si>
@@ -453,6 +480,12 @@
     <t>Term (Yrs)</t>
   </si>
   <si>
+    <t>Equipment Loan</t>
+  </si>
+  <si>
+    <t>Loan</t>
+  </si>
+  <si>
     <t>GROWTH &amp; TIMING</t>
   </si>
   <si>
@@ -558,6 +591,9 @@
     <t>Annual Fundraising (Philanthropy)</t>
   </si>
   <si>
+    <t>Scholarship Discount (Tuition Offsets)</t>
+  </si>
+  <si>
     <t>TOTAL REVENUE</t>
   </si>
   <si>
@@ -675,6 +711,9 @@
     <t xml:space="preserve">  Annual Fundraising</t>
   </si>
   <si>
+    <t xml:space="preserve">  Scholarship Discount</t>
+  </si>
+  <si>
     <t>Total Revenue</t>
   </si>
   <si>
@@ -814,6 +853,18 @@
   </si>
   <si>
     <t>BOTTOM LINE</t>
+  </si>
+  <si>
+    <t>LOAN TERMS</t>
+  </si>
+  <si>
+    <t>Loan Name</t>
+  </si>
+  <si>
+    <t>Annual Rate</t>
+  </si>
+  <si>
+    <t>Term (Years)</t>
   </si>
   <si>
     <t>Bright Horizons Microschool - Balance Sheet</t>
@@ -1170,7 +1221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1214,6 +1265,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1881,7 +1935,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -1890,7 +1944,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1903,24 +1957,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B4" s="31">
         <v>12</v>
@@ -1940,7 +1994,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1950,7 +2004,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B7" s="25">
         <v>144000</v>
@@ -1970,7 +2024,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B8" s="25">
         <v>3000</v>
@@ -1990,7 +2044,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" s="25">
         <v>84000</v>
@@ -2010,7 +2064,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B10" s="25">
         <v>5000</v>
@@ -2028,49 +2082,69 @@
         <v>5628</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="26">
-        <f>SUM(B7:B10)</f>
-        <v>236000</v>
-      </c>
-      <c r="C11" s="26">
-        <f>SUM(C7:C10)</f>
-        <v>362045</v>
-      </c>
-      <c r="D11" s="26">
-        <f>SUM(D7:D10)</f>
-        <v>454596</v>
-      </c>
-      <c r="E11" s="26">
-        <f>SUM(E7:E10)</f>
-        <v>531339</v>
-      </c>
-      <c r="F11" s="26">
-        <f>SUM(F7:F10)</f>
-        <v>547279</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="25">
-        <v>19667</v>
-      </c>
-      <c r="C13" s="25">
-        <v>20114</v>
-      </c>
-      <c r="D13" s="25">
-        <v>20663</v>
-      </c>
-      <c r="E13" s="25">
-        <v>21254</v>
-      </c>
-      <c r="F13" s="25">
-        <v>21891</v>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="25">
+        <v>-10</v>
+      </c>
+      <c r="C11" s="25">
+        <v>-10</v>
+      </c>
+      <c r="D11" s="25">
+        <v>-11</v>
+      </c>
+      <c r="E11" s="25">
+        <v>-11</v>
+      </c>
+      <c r="F11" s="25">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="26">
+        <f>SUM(B7:B11)</f>
+        <v>221600</v>
+      </c>
+      <c r="C12" s="26">
+        <f>SUM(C7:C11)</f>
+        <v>339797</v>
+      </c>
+      <c r="D12" s="26">
+        <f>SUM(D7:D11)</f>
+        <v>426588</v>
+      </c>
+      <c r="E12" s="26">
+        <f>SUM(E7:E11)</f>
+        <v>498557</v>
+      </c>
+      <c r="F12" s="26">
+        <f>SUM(F7:F11)</f>
+        <v>513513</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="25">
+        <v>18467</v>
+      </c>
+      <c r="C14" s="25">
+        <v>18878</v>
+      </c>
+      <c r="D14" s="25">
+        <v>19390</v>
+      </c>
+      <c r="E14" s="25">
+        <v>19942</v>
+      </c>
+      <c r="F14" s="25">
+        <v>20541</v>
       </c>
     </row>
   </sheetData>
@@ -2099,7 +2173,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2112,24 +2186,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2139,7 +2213,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="B5" s="25">
         <v>47869</v>
@@ -2159,7 +2233,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B6" s="25">
         <v>12559</v>
@@ -2179,7 +2253,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B7" s="30">
         <f>SUM(B5:B6)</f>
@@ -2204,7 +2278,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -2214,7 +2288,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B9" s="25">
         <v>58506</v>
@@ -2234,7 +2308,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B10" s="30">
         <f>SUM(B9:B9)</f>
@@ -2259,7 +2333,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B12" s="26">
         <f>B7+B10</f>
@@ -2299,7 +2373,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -2308,7 +2382,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2321,24 +2395,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2348,7 +2422,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B5" s="25">
         <v>120000</v>
@@ -2368,7 +2442,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B6" s="25">
         <v>2500</v>
@@ -2388,7 +2462,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B7" s="25">
         <v>70000</v>
@@ -2408,7 +2482,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B8" s="25">
         <v>4167</v>
@@ -2427,357 +2501,377 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B9" s="30">
-        <f>SUM(B5:B8)</f>
-        <v>196667</v>
-      </c>
-      <c r="C9" s="30">
-        <f>SUM(C5:C8)</f>
-        <v>362045</v>
-      </c>
-      <c r="D9" s="30">
-        <f>SUM(D5:D8)</f>
-        <v>454596</v>
-      </c>
-      <c r="E9" s="30">
-        <f>SUM(E5:E8)</f>
-        <v>531339</v>
-      </c>
-      <c r="F9" s="30">
-        <f>SUM(F5:F8)</f>
-        <v>547279</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="25">
-        <v>58506</v>
-      </c>
-      <c r="C12" s="25">
-        <v>72314</v>
-      </c>
-      <c r="D12" s="25">
-        <v>74483</v>
-      </c>
-      <c r="E12" s="25">
-        <v>76718</v>
-      </c>
-      <c r="F12" s="25">
-        <v>79019</v>
-      </c>
+      <c r="A9" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="25">
+        <v>-8</v>
+      </c>
+      <c r="C9" s="25">
+        <v>-10</v>
+      </c>
+      <c r="D9" s="25">
+        <v>-11</v>
+      </c>
+      <c r="E9" s="25">
+        <v>-11</v>
+      </c>
+      <c r="F9" s="25">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" s="30">
+        <f>SUM(B5:B9)</f>
+        <v>184667</v>
+      </c>
+      <c r="C10" s="30">
+        <f>SUM(C5:C9)</f>
+        <v>339797</v>
+      </c>
+      <c r="D10" s="30">
+        <f>SUM(D5:D9)</f>
+        <v>426588</v>
+      </c>
+      <c r="E10" s="30">
+        <f>SUM(E5:E9)</f>
+        <v>498557</v>
+      </c>
+      <c r="F10" s="30">
+        <f>SUM(F5:F9)</f>
+        <v>513513</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B13" s="25">
-        <v>47869</v>
+        <v>58506</v>
       </c>
       <c r="C13" s="25">
-        <v>59166</v>
+        <v>72314</v>
       </c>
       <c r="D13" s="25">
-        <v>60941</v>
+        <v>74483</v>
       </c>
       <c r="E13" s="25">
-        <v>62769</v>
+        <v>76718</v>
       </c>
       <c r="F13" s="25">
-        <v>64652</v>
+        <v>79019</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B14" s="25">
+        <v>47869</v>
+      </c>
+      <c r="C14" s="25">
+        <v>59166</v>
+      </c>
+      <c r="D14" s="25">
+        <v>60941</v>
+      </c>
+      <c r="E14" s="25">
+        <v>62769</v>
+      </c>
+      <c r="F14" s="25">
+        <v>64652</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" s="25">
         <v>12559</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C15" s="25">
         <v>15523</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D15" s="25">
         <v>15989</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E15" s="25">
         <v>16468</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F15" s="25">
         <v>16963</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15" s="30">
-        <f>SUM(B12:B14)</f>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="30">
+        <f>SUM(B13:B15)</f>
         <v>118934</v>
       </c>
-      <c r="C15" s="30">
-        <f>SUM(C12:C14)</f>
+      <c r="C16" s="30">
+        <f>SUM(C13:C15)</f>
         <v>147003</v>
       </c>
-      <c r="D15" s="30">
-        <f>SUM(D12:D14)</f>
+      <c r="D16" s="30">
+        <f>SUM(D13:D15)</f>
         <v>151413</v>
       </c>
-      <c r="E15" s="30">
-        <f>SUM(E12:E14)</f>
+      <c r="E16" s="30">
+        <f>SUM(E13:E15)</f>
         <v>155955</v>
       </c>
-      <c r="F15" s="30">
-        <f>SUM(F12:F14)</f>
+      <c r="F16" s="30">
+        <f>SUM(F13:F15)</f>
         <v>160634</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="32" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B19" s="25">
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="25">
         <v>5000</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C20" s="25">
         <v>9270</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D20" s="25">
         <v>11670</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E20" s="25">
         <v>13659</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F20" s="25">
         <v>14069</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="32" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B21" s="25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" s="25">
         <v>3000</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C22" s="25">
         <v>5562</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D22" s="25">
         <v>7002</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E22" s="25">
         <v>8195</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F22" s="25">
         <v>8441</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B23" s="25">
-        <v>25000</v>
-      </c>
-      <c r="C23" s="25">
-        <v>30900</v>
-      </c>
-      <c r="D23" s="25">
-        <v>31827</v>
-      </c>
-      <c r="E23" s="25">
-        <v>32782</v>
-      </c>
-      <c r="F23" s="25">
-        <v>33765</v>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="32" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B24" s="25">
-        <v>3000</v>
+        <v>25000</v>
       </c>
       <c r="C24" s="25">
-        <v>3708</v>
+        <v>30900</v>
       </c>
       <c r="D24" s="25">
-        <v>3819</v>
+        <v>31827</v>
       </c>
       <c r="E24" s="25">
-        <v>3934</v>
+        <v>32782</v>
       </c>
       <c r="F24" s="25">
-        <v>4052</v>
+        <v>33765</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B25" s="25">
+        <v>3000</v>
+      </c>
+      <c r="C25" s="25">
+        <v>3708</v>
+      </c>
+      <c r="D25" s="25">
+        <v>3819</v>
+      </c>
+      <c r="E25" s="25">
+        <v>3934</v>
+      </c>
+      <c r="F25" s="25">
+        <v>4052</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B26" s="25">
         <v>2000</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C26" s="25">
         <v>2472</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D26" s="25">
         <v>2546</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E26" s="25">
         <v>2623</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F26" s="25">
         <v>2701</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B26" s="30">
-        <f>SUM(B23:B25)</f>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B27" s="30">
+        <f>SUM(B24:B26)</f>
         <v>30000</v>
       </c>
-      <c r="C26" s="30">
-        <f>SUM(C23:C25)</f>
+      <c r="C27" s="30">
+        <f>SUM(C24:C26)</f>
         <v>37080</v>
       </c>
-      <c r="D26" s="30">
-        <f>SUM(D23:D25)</f>
+      <c r="D27" s="30">
+        <f>SUM(D24:D26)</f>
         <v>38192</v>
       </c>
-      <c r="E26" s="30">
-        <f>SUM(E23:E25)</f>
+      <c r="E27" s="30">
+        <f>SUM(E24:E26)</f>
         <v>39338</v>
       </c>
-      <c r="F26" s="30">
-        <f>SUM(F23:F25)</f>
+      <c r="F27" s="30">
+        <f>SUM(F24:F26)</f>
         <v>40518</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B28" s="25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B29" s="25">
         <v>2500</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C29" s="25">
         <v>3090</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D29" s="25">
         <v>3183</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E29" s="25">
         <v>3278</v>
       </c>
-      <c r="F28" s="25">
+      <c r="F29" s="25">
         <v>3377</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B29" s="30">
-        <f>B19+B21+B26+B28</f>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B30" s="30">
+        <f>B20+B22+B27+B29</f>
         <v>40500</v>
       </c>
-      <c r="C29" s="30">
-        <f>C19+C21+C26+C28</f>
+      <c r="C30" s="30">
+        <f>C20+C22+C27+C29</f>
         <v>55002</v>
       </c>
-      <c r="D29" s="30">
-        <f>D19+D21+D26+D28</f>
+      <c r="D30" s="30">
+        <f>D20+D22+D27+D29</f>
         <v>60047</v>
       </c>
-      <c r="E29" s="30">
-        <f>E19+E21+E26+E28</f>
+      <c r="E30" s="30">
+        <f>E20+E22+E27+E29</f>
         <v>64471</v>
       </c>
-      <c r="F29" s="30">
-        <f>F19+F21+F26+F28</f>
+      <c r="F30" s="30">
+        <f>F20+F22+F27+F29</f>
         <v>66405</v>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B32" s="30" t="str">
-        <f>SUM(B32:B31)</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="30" t="str">
-        <f>SUM(C32:C31)</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="30" t="str">
-        <f>SUM(D32:D31)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="30" t="str">
-        <f>SUM(E32:E31)</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="30" t="str">
-        <f>SUM(F32:F31)</f>
+    <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33" s="30" t="str">
+        <f>SUM(B33:B32)</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="30" t="str">
+        <f>SUM(C33:C32)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="30" t="str">
+        <f>SUM(D33:D32)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="30" t="str">
+        <f>SUM(E33:E32)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="30" t="str">
+        <f>SUM(F33:F32)</f>
         <v>0</v>
       </c>
     </row>
@@ -2807,7 +2901,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2820,124 +2914,124 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B4" s="28">
-        <f>'Budget Detail'!B9</f>
-        <v>196667</v>
+        <f>'Budget Detail'!B10</f>
+        <v>184667</v>
       </c>
       <c r="C4" s="28">
-        <f>'Budget Detail'!C9</f>
-        <v>362045</v>
+        <f>'Budget Detail'!C10</f>
+        <v>339797</v>
       </c>
       <c r="D4" s="28">
-        <f>'Budget Detail'!D9</f>
-        <v>454596</v>
+        <f>'Budget Detail'!D10</f>
+        <v>426588</v>
       </c>
       <c r="E4" s="28">
-        <f>'Budget Detail'!E9</f>
-        <v>531339</v>
+        <f>'Budget Detail'!E10</f>
+        <v>498557</v>
       </c>
       <c r="F4" s="28">
-        <f>'Budget Detail'!F9</f>
-        <v>547279</v>
+        <f>'Budget Detail'!F10</f>
+        <v>513513</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="B5" s="28">
-        <f>'Budget Detail'!B15</f>
+        <f>'Budget Detail'!B16</f>
         <v>118934</v>
       </c>
       <c r="C5" s="28">
-        <f>'Budget Detail'!C15</f>
+        <f>'Budget Detail'!C16</f>
         <v>147003</v>
       </c>
       <c r="D5" s="28">
-        <f>'Budget Detail'!D15</f>
+        <f>'Budget Detail'!D16</f>
         <v>151413</v>
       </c>
       <c r="E5" s="28">
-        <f>'Budget Detail'!E15</f>
+        <f>'Budget Detail'!E16</f>
         <v>155955</v>
       </c>
       <c r="F5" s="28">
-        <f>'Budget Detail'!F15</f>
+        <f>'Budget Detail'!F16</f>
         <v>160634</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B6" s="28">
-        <f>'Budget Detail'!B29</f>
+        <f>'Budget Detail'!B30</f>
         <v>40500</v>
       </c>
       <c r="C6" s="28">
-        <f>'Budget Detail'!C29</f>
+        <f>'Budget Detail'!C30</f>
         <v>55002</v>
       </c>
       <c r="D6" s="28">
-        <f>'Budget Detail'!D29</f>
+        <f>'Budget Detail'!D30</f>
         <v>60047</v>
       </c>
       <c r="E6" s="28">
-        <f>'Budget Detail'!E29</f>
+        <f>'Budget Detail'!E30</f>
         <v>64471</v>
       </c>
       <c r="F6" s="28">
-        <f>'Budget Detail'!F29</f>
+        <f>'Budget Detail'!F30</f>
         <v>66405</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B7" s="28" t="str">
-        <f>'Budget Detail'!B32</f>
+        <f>'Budget Detail'!B33</f>
         <v>0</v>
       </c>
       <c r="C7" s="28" t="str">
-        <f>'Budget Detail'!C32</f>
+        <f>'Budget Detail'!C33</f>
         <v>0</v>
       </c>
       <c r="D7" s="28" t="str">
-        <f>'Budget Detail'!D32</f>
+        <f>'Budget Detail'!D33</f>
         <v>0</v>
       </c>
       <c r="E7" s="28" t="str">
-        <f>'Budget Detail'!E32</f>
+        <f>'Budget Detail'!E33</f>
         <v>0</v>
       </c>
       <c r="F7" s="28" t="str">
-        <f>'Budget Detail'!F32</f>
+        <f>'Budget Detail'!F33</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
@@ -2962,7 +3056,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -2972,97 +3066,97 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B11" s="26">
         <f>B4-B8</f>
-        <v>37233</v>
+        <v>25233</v>
       </c>
       <c r="C11" s="26">
         <f>C4-C8</f>
-        <v>160040</v>
+        <v>137792</v>
       </c>
       <c r="D11" s="26">
         <f>D4-D8</f>
-        <v>243136</v>
+        <v>215128</v>
       </c>
       <c r="E11" s="26">
         <f>E4-E8</f>
-        <v>310913</v>
+        <v>278131</v>
       </c>
       <c r="F11" s="26">
         <f>F4-F8</f>
-        <v>320240</v>
+        <v>286475</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B12" s="24">
         <f>IF(B4=0,0,B11/B4)</f>
-        <v>0.1893178</v>
+        <v>0.13663809</v>
       </c>
       <c r="C12" s="24">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.44204552</v>
+        <v>0.40551379</v>
       </c>
       <c r="D12" s="24">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.53484014</v>
+        <v>0.50429993</v>
       </c>
       <c r="E12" s="24">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.58514961</v>
+        <v>0.55787178</v>
       </c>
       <c r="F12" s="24">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.58514961</v>
+        <v>0.55787178</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B13" s="25">
-        <v>37233</v>
+        <v>25233</v>
       </c>
       <c r="C13" s="25">
-        <v>197273</v>
+        <v>163025</v>
       </c>
       <c r="D13" s="25">
-        <v>440409</v>
+        <v>378153</v>
       </c>
       <c r="E13" s="25">
-        <v>751321</v>
+        <v>656284</v>
       </c>
       <c r="F13" s="25">
-        <v>1071561</v>
+        <v>942758</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B14" s="25">
-        <v>16389</v>
+        <v>15389</v>
       </c>
       <c r="C14" s="25">
-        <v>20114</v>
+        <v>18878</v>
       </c>
       <c r="D14" s="25">
-        <v>20663</v>
+        <v>19390</v>
       </c>
       <c r="E14" s="25">
-        <v>21254</v>
+        <v>19942</v>
       </c>
       <c r="F14" s="25">
-        <v>21891</v>
+        <v>20541</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B15" s="25">
         <v>13286</v>
@@ -3107,7 +3201,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3128,48 +3222,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3187,51 +3281,51 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B4" s="30">
         <v>9150</v>
       </c>
       <c r="C4" s="30">
-        <v>23550</v>
+        <v>22110</v>
       </c>
       <c r="D4" s="30">
-        <v>23550</v>
+        <v>22110</v>
       </c>
       <c r="E4" s="30">
-        <v>23550</v>
+        <v>22110</v>
       </c>
       <c r="F4" s="30">
-        <v>23550</v>
+        <v>22110</v>
       </c>
       <c r="G4" s="30">
-        <v>23550</v>
+        <v>22110</v>
       </c>
       <c r="H4" s="30">
-        <v>23550</v>
+        <v>22110</v>
       </c>
       <c r="I4" s="30">
-        <v>23550</v>
+        <v>22110</v>
       </c>
       <c r="J4" s="30">
-        <v>23550</v>
+        <v>22110</v>
       </c>
       <c r="K4" s="30">
-        <v>23550</v>
+        <v>22110</v>
       </c>
       <c r="L4" s="30">
-        <v>14650</v>
+        <v>13210</v>
       </c>
       <c r="M4" s="30">
         <v>250</v>
       </c>
       <c r="N4" s="30">
-        <v>236000</v>
+        <v>221600</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3249,7 +3343,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B7" s="25">
         <v>11893</v>
@@ -3293,7 +3387,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B8" s="25">
         <v>4050</v>
@@ -3337,7 +3431,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B9" s="25">
         <v>0</v>
@@ -3381,7 +3475,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3399,7 +3493,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B12" s="28">
         <v>15943</v>
@@ -3443,102 +3537,102 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B13" s="28">
         <v>-6793</v>
       </c>
       <c r="C13" s="28">
-        <v>7607</v>
+        <v>6167</v>
       </c>
       <c r="D13" s="28">
-        <v>7607</v>
+        <v>6167</v>
       </c>
       <c r="E13" s="28">
-        <v>7607</v>
+        <v>6167</v>
       </c>
       <c r="F13" s="28">
-        <v>7607</v>
+        <v>6167</v>
       </c>
       <c r="G13" s="28">
-        <v>7607</v>
+        <v>6167</v>
       </c>
       <c r="H13" s="28">
-        <v>7607</v>
+        <v>6167</v>
       </c>
       <c r="I13" s="28">
-        <v>7607</v>
+        <v>6167</v>
       </c>
       <c r="J13" s="28">
-        <v>7607</v>
+        <v>6167</v>
       </c>
       <c r="K13" s="28">
-        <v>7607</v>
+        <v>6167</v>
       </c>
       <c r="L13" s="28">
-        <v>14650</v>
+        <v>13210</v>
       </c>
       <c r="M13" s="28">
         <v>250</v>
       </c>
       <c r="N13" s="28">
-        <v>76570</v>
+        <v>62170</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B14" s="33">
         <v>-6793</v>
       </c>
       <c r="C14" s="33">
-        <v>814</v>
+        <v>-626</v>
       </c>
       <c r="D14" s="33">
-        <v>8421</v>
+        <v>5541</v>
       </c>
       <c r="E14" s="33">
-        <v>16028</v>
+        <v>11708</v>
       </c>
       <c r="F14" s="33">
-        <v>23635</v>
+        <v>17875</v>
       </c>
       <c r="G14" s="33">
-        <v>31242</v>
+        <v>24042</v>
       </c>
       <c r="H14" s="33">
-        <v>38849</v>
+        <v>30209</v>
       </c>
       <c r="I14" s="33">
-        <v>46456</v>
+        <v>36376</v>
       </c>
       <c r="J14" s="33">
-        <v>54063</v>
+        <v>42543</v>
       </c>
       <c r="K14" s="33">
-        <v>61670</v>
+        <v>48710</v>
       </c>
       <c r="L14" s="33">
-        <v>76320</v>
+        <v>61920</v>
       </c>
       <c r="M14" s="33">
-        <v>76570</v>
+        <v>62170</v>
       </c>
       <c r="N14" s="26">
-        <v>76570</v>
+        <v>62170</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B17" s="25">
         <v>0</v>
@@ -3546,15 +3640,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B18" s="33">
-        <v>76570</v>
+        <v>62170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="B19" s="25">
         <v>-6793</v>
@@ -3586,7 +3680,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3599,24 +3693,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3626,27 +3720,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B5" s="30">
-        <v>196667</v>
+        <v>184667</v>
       </c>
       <c r="C5" s="30">
-        <v>362045</v>
+        <v>339797</v>
       </c>
       <c r="D5" s="30">
-        <v>454596</v>
+        <v>426588</v>
       </c>
       <c r="E5" s="30">
-        <v>531339</v>
+        <v>498557</v>
       </c>
       <c r="F5" s="30">
-        <v>547279</v>
+        <v>513513</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -3656,7 +3750,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B8" s="28">
         <v>118934</v>
@@ -3676,7 +3770,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B9" s="28">
         <v>40500</v>
@@ -3696,7 +3790,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="B10" s="28">
         <v>0</v>
@@ -3716,7 +3810,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
@@ -3741,7 +3835,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -3751,52 +3845,52 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B14" s="26">
         <f>B5-B11</f>
-        <v>37233</v>
+        <v>25233</v>
       </c>
       <c r="C14" s="26">
         <f>C5-C11</f>
-        <v>160040</v>
+        <v>137792</v>
       </c>
       <c r="D14" s="26">
         <f>D5-D11</f>
-        <v>243136</v>
+        <v>215128</v>
       </c>
       <c r="E14" s="26">
         <f>E5-E11</f>
-        <v>310913</v>
+        <v>278131</v>
       </c>
       <c r="F14" s="26">
         <f>F5-F11</f>
-        <v>320240</v>
+        <v>286475</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B15" s="24">
         <f>IF(B5=0,0,B14/B5)</f>
-        <v>0.1893178</v>
+        <v>0.13663809</v>
       </c>
       <c r="C15" s="24">
         <f>IF(C5=0,0,C14/C5)</f>
-        <v>0.44204552</v>
+        <v>0.40551379</v>
       </c>
       <c r="D15" s="24">
         <f>IF(D5=0,0,D14/D5)</f>
-        <v>0.53484014</v>
+        <v>0.50429993</v>
       </c>
       <c r="E15" s="24">
         <f>IF(E5=0,0,E14/E5)</f>
-        <v>0.58514961</v>
+        <v>0.55787178</v>
       </c>
       <c r="F15" s="24">
         <f>IF(F5=0,0,F14/F5)</f>
-        <v>0.58514961</v>
+        <v>0.55787178</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3910,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3838,19 +3932,46 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3879,7 +4000,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3892,24 +4013,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3919,27 +4040,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B5" s="35">
-        <v>76570</v>
-      </c>
-      <c r="C5" s="35">
-        <v>236610</v>
-      </c>
-      <c r="D5" s="35">
-        <v>479746</v>
-      </c>
-      <c r="E5" s="35">
-        <v>790659</v>
-      </c>
-      <c r="F5" s="35">
-        <v>1110899</v>
+        <v>280</v>
+      </c>
+      <c r="B5" s="38">
+        <v>62170</v>
+      </c>
+      <c r="C5" s="38">
+        <v>199962</v>
+      </c>
+      <c r="D5" s="38">
+        <v>415091</v>
+      </c>
+      <c r="E5" s="38">
+        <v>693221</v>
+      </c>
+      <c r="F5" s="38">
+        <v>979696</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="B6" s="25">
         <v>0</v>
@@ -3959,7 +4080,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="B7" s="25">
         <v>5000</v>
@@ -3979,7 +4100,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B8" s="25">
         <v>0</v>
@@ -3999,27 +4120,27 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="B9" s="30">
-        <v>81570</v>
+        <v>67170</v>
       </c>
       <c r="C9" s="30">
-        <v>241610</v>
+        <v>204962</v>
       </c>
       <c r="D9" s="30">
-        <v>484746</v>
+        <v>420091</v>
       </c>
       <c r="E9" s="30">
-        <v>795659</v>
+        <v>698221</v>
       </c>
       <c r="F9" s="30">
-        <v>1115899</v>
+        <v>984696</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4029,7 +4150,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="B12" s="25">
         <v>0</v>
@@ -4049,7 +4170,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B13" s="25">
         <v>0</v>
@@ -4069,7 +4190,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="B14" s="30">
         <v>0</v>
@@ -4089,7 +4210,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4099,41 +4220,41 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B17" s="26">
-        <v>81570</v>
+        <v>67170</v>
       </c>
       <c r="C17" s="26">
-        <v>241610</v>
+        <v>204962</v>
       </c>
       <c r="D17" s="26">
-        <v>484746</v>
+        <v>420091</v>
       </c>
       <c r="E17" s="26">
-        <v>795659</v>
+        <v>698221</v>
       </c>
       <c r="F17" s="26">
-        <v>1115899</v>
+        <v>984696</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B19" s="36">
-        <v>0</v>
-      </c>
-      <c r="C19" s="36">
-        <v>0</v>
-      </c>
-      <c r="D19" s="36">
-        <v>0</v>
-      </c>
-      <c r="E19" s="36">
-        <v>0</v>
-      </c>
-      <c r="F19" s="36">
+        <v>291</v>
+      </c>
+      <c r="B19" s="39">
+        <v>0</v>
+      </c>
+      <c r="C19" s="39">
+        <v>0</v>
+      </c>
+      <c r="D19" s="39">
+        <v>0</v>
+      </c>
+      <c r="E19" s="39">
+        <v>0</v>
+      </c>
+      <c r="F19" s="39">
         <v>0</v>
       </c>
     </row>
@@ -4163,7 +4284,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4176,24 +4297,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4203,27 +4324,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B5" s="25">
-        <v>196667</v>
+        <v>184667</v>
       </c>
       <c r="C5" s="25">
-        <v>362045</v>
+        <v>339797</v>
       </c>
       <c r="D5" s="25">
-        <v>454596</v>
+        <v>426588</v>
       </c>
       <c r="E5" s="25">
-        <v>531339</v>
+        <v>498557</v>
       </c>
       <c r="F5" s="25">
-        <v>547279</v>
+        <v>513513</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B6" s="25">
         <v>118934</v>
@@ -4243,7 +4364,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B7" s="25">
         <v>40500</v>
@@ -4263,32 +4384,32 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B8" s="28">
         <f>B5-B6-B7</f>
-        <v>37233</v>
+        <v>25233</v>
       </c>
       <c r="C8" s="28">
         <f>C5-C6-C7</f>
-        <v>160040</v>
+        <v>137792</v>
       </c>
       <c r="D8" s="28">
         <f>D5-D6-D7</f>
-        <v>243136</v>
+        <v>215128</v>
       </c>
       <c r="E8" s="28">
         <f>E5-E6-E7</f>
-        <v>310913</v>
+        <v>278131</v>
       </c>
       <c r="F8" s="28">
         <f>F5-F6-F7</f>
-        <v>320240</v>
+        <v>286475</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B9" s="25">
         <v>0</v>
@@ -4308,27 +4429,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>280</v>
+        <v>296</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -4338,77 +4459,77 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B13" s="25">
-        <v>76570</v>
+        <v>62170</v>
       </c>
       <c r="C13" s="25">
-        <v>236610</v>
+        <v>199962</v>
       </c>
       <c r="D13" s="25">
-        <v>479746</v>
+        <v>415091</v>
       </c>
       <c r="E13" s="25">
-        <v>790659</v>
+        <v>693221</v>
       </c>
       <c r="F13" s="25">
-        <v>1110899</v>
+        <v>979696</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B14" s="22">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="C14" s="22">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
-        <v>428</v>
+        <v>361</v>
       </c>
       <c r="D14" s="22">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
-        <v>828</v>
+        <v>716</v>
       </c>
       <c r="E14" s="22">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
-        <v>1309</v>
+        <v>1148</v>
       </c>
       <c r="F14" s="22">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
-        <v>1786</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="B15" s="29">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="C15" s="29">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
-        <v>14.1</v>
+        <v>11.9</v>
       </c>
       <c r="D15" s="29">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
-        <v>27.2</v>
+        <v>23.6</v>
       </c>
       <c r="E15" s="29">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
-        <v>43</v>
+        <v>37.7</v>
       </c>
       <c r="F15" s="29">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
-        <v>58.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B16" s="24">
         <v>0.48</v>
@@ -4428,7 +4549,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -4438,27 +4559,27 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B19" s="25">
-        <v>16389</v>
+        <v>15389</v>
       </c>
       <c r="C19" s="25">
-        <v>20114</v>
+        <v>18878</v>
       </c>
       <c r="D19" s="25">
-        <v>20663</v>
+        <v>19390</v>
       </c>
       <c r="E19" s="25">
-        <v>21254</v>
+        <v>19942</v>
       </c>
       <c r="F19" s="25">
-        <v>21891</v>
+        <v>20541</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="B20" s="25">
         <v>118934</v>
@@ -4478,7 +4599,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="B21" s="25">
         <v>3375</v>
@@ -4498,27 +4619,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B22" s="38">
+        <v>305</v>
+      </c>
+      <c r="B22" s="41">
         <v>10</v>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="41">
+        <v>10</v>
+      </c>
+      <c r="D22" s="41">
+        <v>10</v>
+      </c>
+      <c r="E22" s="41">
         <v>9</v>
       </c>
-      <c r="D22" s="38">
-        <v>9</v>
-      </c>
-      <c r="E22" s="38">
-        <v>9</v>
-      </c>
-      <c r="F22" s="38">
+      <c r="F22" s="41">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -4528,102 +4649,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="E25" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>280</v>
+        <v>307</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="D25" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B26" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="D26" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="F26" s="40" t="s">
-        <v>292</v>
+        <v>308</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B27" s="41" t="s">
-        <v>294</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="D27" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="F27" s="40" t="s">
-        <v>292</v>
+        <v>310</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="D28" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="E28" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="F28" s="40" t="s">
-        <v>292</v>
+        <v>312</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="E29" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="F29" s="40" t="s">
-        <v>292</v>
+        <v>313</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -4663,28 +4784,28 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
-        <v>297</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>298</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>100</v>
+      <c r="A3" s="45" t="s">
+        <v>314</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B4" s="25">
         <v>20000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="E4" s="25">
         <v>15000</v>
@@ -4692,7 +4813,7 @@
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="4" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="E5" s="25">
         <v>5000</v>
@@ -4700,13 +4821,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B7" s="26">
         <v>20000</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="E7" s="26">
         <v>20000</v>
@@ -4714,9 +4835,9 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B8" s="36">
+        <v>321</v>
+      </c>
+      <c r="B8" s="39">
         <v>0</v>
       </c>
     </row>
@@ -4737,7 +4858,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="B2:B32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4841,22 +4962,57 @@
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>79</v>
+      <c r="B23" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="10" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4882,7 +5038,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4892,7 +5048,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -4902,7 +5058,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4910,44 +5066,44 @@
         <v>67</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B6" s="25">
-        <v>196667</v>
+        <v>184667</v>
       </c>
       <c r="C6" s="25">
-        <v>362045</v>
+        <v>339797</v>
       </c>
       <c r="D6" s="25">
-        <v>454596</v>
+        <v>426588</v>
       </c>
       <c r="E6" s="25">
-        <v>531339</v>
+        <v>498557</v>
       </c>
       <c r="F6" s="25">
-        <v>547279</v>
+        <v>513513</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B7" s="25">
         <v>159434</v>
@@ -4967,76 +5123,76 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B8" s="26">
-        <v>37233</v>
+        <v>25233</v>
       </c>
       <c r="C8" s="26">
-        <v>160040</v>
+        <v>137792</v>
       </c>
       <c r="D8" s="26">
-        <v>243136</v>
+        <v>215128</v>
       </c>
       <c r="E8" s="26">
-        <v>310913</v>
+        <v>278131</v>
       </c>
       <c r="F8" s="26">
-        <v>320240</v>
+        <v>286475</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B9" s="24">
-        <v>0.18931779661016948</v>
+        <v>0.13663808664259927</v>
       </c>
       <c r="C9" s="24">
-        <v>0.44204551920341395</v>
+        <v>0.40551379205819943</v>
       </c>
       <c r="D9" s="24">
-        <v>0.5348401400233372</v>
+        <v>0.5042999253916937</v>
       </c>
       <c r="E9" s="24">
-        <v>0.5851496143958869</v>
+        <v>0.5578717808219178</v>
       </c>
       <c r="F9" s="24">
-        <v>0.5851496143958869</v>
+        <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>280</v>
+        <v>296</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B11" s="22">
         <v>10</v>
       </c>
       <c r="C11" s="22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="22">
         <v>9</v>
@@ -5047,7 +5203,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5057,7 +5213,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5065,44 +5221,44 @@
         <v>67</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B16" s="25">
-        <v>157333</v>
+        <v>147733</v>
       </c>
       <c r="C16" s="25">
-        <v>289636</v>
+        <v>271838</v>
       </c>
       <c r="D16" s="25">
-        <v>363677</v>
+        <v>341270</v>
       </c>
       <c r="E16" s="25">
-        <v>425071</v>
+        <v>398845</v>
       </c>
       <c r="F16" s="25">
-        <v>437823</v>
+        <v>410811</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B17" s="25">
         <v>159434</v>
@@ -5122,82 +5278,82 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B18" s="26">
-        <v>-2101</v>
+        <v>-11701</v>
       </c>
       <c r="C18" s="26">
-        <v>87631</v>
+        <v>69833</v>
       </c>
       <c r="D18" s="26">
-        <v>152217</v>
+        <v>129811</v>
       </c>
       <c r="E18" s="26">
-        <v>204645</v>
+        <v>178419</v>
       </c>
       <c r="F18" s="26">
-        <v>210784</v>
+        <v>183772</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B19" s="24">
-        <v>-0.013352754237288008</v>
+        <v>-0.07920239169675096</v>
       </c>
       <c r="C19" s="24">
-        <v>0.3025568990042674</v>
+        <v>0.2568922400727494</v>
       </c>
       <c r="D19" s="24">
-        <v>0.41855017502917163</v>
+        <v>0.38037490673961705</v>
       </c>
       <c r="E19" s="24">
-        <v>0.4814370179948587</v>
+        <v>0.4473397260273973</v>
       </c>
       <c r="F19" s="24">
-        <v>0.48143701799485866</v>
+        <v>0.44733972602739736</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B20" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="E20" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="F20" s="43" t="s">
-        <v>280</v>
+        <v>296</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B21" s="22">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" s="22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5228,7 +5384,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5240,7 +5396,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B3" s="13"/>
     </row>
@@ -5254,7 +5410,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -5262,7 +5418,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -5286,7 +5442,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -5294,7 +5450,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5314,45 +5470,45 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>94</v>
+      <c r="D12" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="D13" s="25">
-        <v>196667</v>
+        <v>184667</v>
       </c>
       <c r="E13" s="25">
-        <v>362045</v>
+        <v>339797</v>
       </c>
       <c r="F13" s="25">
-        <v>454596</v>
+        <v>426588</v>
       </c>
       <c r="G13" s="25">
-        <v>531339</v>
+        <v>498557</v>
       </c>
       <c r="H13" s="25">
-        <v>547279</v>
+        <v>513513</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D14" s="25">
         <v>159434</v>
@@ -5372,47 +5528,47 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D15" s="25">
-        <v>37233</v>
+        <v>25233</v>
       </c>
       <c r="E15" s="25">
-        <v>160040</v>
+        <v>137792</v>
       </c>
       <c r="F15" s="25">
-        <v>243136</v>
+        <v>215128</v>
       </c>
       <c r="G15" s="25">
-        <v>310913</v>
+        <v>278131</v>
       </c>
       <c r="H15" s="25">
-        <v>320240</v>
+        <v>286475</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="D16" s="25">
-        <v>76570</v>
+        <v>62170</v>
       </c>
       <c r="E16" s="25">
-        <v>236610</v>
+        <v>199962</v>
       </c>
       <c r="F16" s="25">
-        <v>479746</v>
+        <v>415091</v>
       </c>
       <c r="G16" s="25">
-        <v>790659</v>
+        <v>693221</v>
       </c>
       <c r="H16" s="25">
-        <v>1110899</v>
+        <v>979696</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="D17" s="25">
         <v>0</v>
@@ -5432,7 +5588,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -5452,65 +5608,65 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="H20" s="44" t="s">
-        <v>94</v>
+      <c r="D20" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="D21" s="24">
-        <v>0.18931779661016948</v>
+        <v>0.13663808664259927</v>
       </c>
       <c r="E21" s="24">
-        <v>0.44204551920341395</v>
+        <v>0.40551379205819943</v>
       </c>
       <c r="F21" s="24">
-        <v>0.5348401400233372</v>
+        <v>0.5042999253916937</v>
       </c>
       <c r="G21" s="24">
-        <v>0.5851496143958869</v>
+        <v>0.5578717808219178</v>
       </c>
       <c r="H21" s="24">
-        <v>0.5851496143958869</v>
+        <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D22" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="E22" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="F22" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="G22" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="H22" s="43" t="s">
-        <v>280</v>
+        <v>296</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="G22" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="H22" s="46" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D23" s="24">
         <v>0.48</v>
@@ -5530,7 +5686,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="D24" s="22">
         <v>12</v>
@@ -5550,7 +5706,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -5578,7 +5734,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -5588,7 +5744,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5599,12 +5755,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5647,10 +5803,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5671,7 +5827,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B12" s="14">
         <v>7</v>
@@ -5679,7 +5835,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B13" s="14">
         <v>25</v>
@@ -5687,7 +5843,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5701,24 +5857,24 @@
         <v>67</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B17" s="16">
         <v>12</v>
@@ -5738,7 +5894,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -5749,30 +5905,30 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D21" s="17">
         <v>12000</v>
@@ -5783,13 +5939,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D22" s="17">
         <v>250</v>
@@ -5800,13 +5956,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D23" s="17">
         <v>7000</v>
@@ -5817,13 +5973,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D24" s="17">
         <v>5000</v>
@@ -5832,78 +5988,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="G27" s="15" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D25" s="17">
+        <v>10</v>
+      </c>
+      <c r="E25" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="19">
-        <v>1</v>
-      </c>
-      <c r="E28" s="17">
-        <v>55000</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="G28" s="18">
-        <v>0.0765</v>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D29" s="19">
         <v>1</v>
       </c>
       <c r="E29" s="17">
-        <v>45000</v>
+        <v>55000</v>
       </c>
       <c r="F29" s="18">
         <v>0.2</v>
@@ -5914,101 +6064,107 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D30" s="19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E30" s="17">
-        <v>28000</v>
+        <v>45000</v>
       </c>
       <c r="F30" s="18">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G30" s="18">
         <v>0.0765</v>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="17">
-        <v>2500</v>
-      </c>
-      <c r="E34" s="18">
-        <v>0.03</v>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="17">
+        <v>28000</v>
+      </c>
+      <c r="F31" s="18">
+        <v>0</v>
+      </c>
+      <c r="G31" s="18">
+        <v>0.0765</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D35" s="17">
-        <v>300</v>
+        <v>2500</v>
       </c>
       <c r="E35" s="18">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="D36" s="17">
-        <v>2400</v>
+        <v>300</v>
       </c>
       <c r="E36" s="18">
         <v>0</v>
@@ -6016,16 +6172,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D37" s="17">
-        <v>500</v>
+        <v>2400</v>
       </c>
       <c r="E37" s="18">
         <v>0</v>
@@ -6033,16 +6189,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D38" s="17">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E38" s="18">
         <v>0</v>
@@ -6050,104 +6206,138 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>110</v>
       </c>
       <c r="D39" s="17">
+        <v>300</v>
+      </c>
+      <c r="E39" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="17">
         <v>3000</v>
       </c>
-      <c r="E39" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-    </row>
-    <row r="42" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B45" s="18">
+      <c r="E40" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+    </row>
+    <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="17">
+        <v>30000</v>
+      </c>
+      <c r="D44" s="18">
+        <v>0.06</v>
+      </c>
+      <c r="E44" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="18">
         <v>0.03</v>
       </c>
-      <c r="C45" s="20" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B46" s="18">
+      <c r="C47" s="20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B48" s="18">
         <v>0.03</v>
       </c>
-      <c r="C46" s="20" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B47" s="19">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B48" s="17">
-        <v>0</v>
+      <c r="C48" s="20" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>148</v>
+        <v>156</v>
+      </c>
+      <c r="B49" s="19">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B50" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -6182,10 +6372,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6206,10 +6396,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6222,7 +6412,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -6230,66 +6420,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -6332,24 +6522,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -6359,7 +6549,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B6" s="21">
         <v>12</v>
@@ -6379,7 +6569,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B7" s="22">
         <v>25</v>
@@ -6387,7 +6577,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B8" s="23">
         <v>0.48</v>
@@ -6407,10 +6597,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C10" s="24">
         <v>0.5</v>
@@ -6442,7 +6632,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -6451,7 +6641,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6464,24 +6654,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6491,7 +6681,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B5" s="25">
         <v>144000</v>
@@ -6511,7 +6701,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B6" s="25">
         <v>3000</v>
@@ -6531,7 +6721,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B7" s="25">
         <v>84000</v>
@@ -6551,7 +6741,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B8" s="25">
         <v>5000</v>
@@ -6569,29 +6759,49 @@
         <v>5628</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="26">
-        <f>SUM(B5:B8)</f>
-        <v>236000</v>
-      </c>
-      <c r="C9" s="26">
-        <f>SUM(C5:C8)</f>
-        <v>362045</v>
-      </c>
-      <c r="D9" s="26">
-        <f>SUM(D5:D8)</f>
-        <v>454596</v>
-      </c>
-      <c r="E9" s="26">
-        <f>SUM(E5:E8)</f>
-        <v>531339</v>
-      </c>
-      <c r="F9" s="26">
-        <f>SUM(F5:F8)</f>
-        <v>547279</v>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="25">
+        <v>-10</v>
+      </c>
+      <c r="C9" s="25">
+        <v>-10</v>
+      </c>
+      <c r="D9" s="25">
+        <v>-11</v>
+      </c>
+      <c r="E9" s="25">
+        <v>-11</v>
+      </c>
+      <c r="F9" s="25">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="26">
+        <f>SUM(B5:B9)</f>
+        <v>221600</v>
+      </c>
+      <c r="C10" s="26">
+        <f>SUM(C5:C9)</f>
+        <v>339797</v>
+      </c>
+      <c r="D10" s="26">
+        <f>SUM(D5:D9)</f>
+        <v>426588</v>
+      </c>
+      <c r="E10" s="26">
+        <f>SUM(E5:E9)</f>
+        <v>498557</v>
+      </c>
+      <c r="F10" s="26">
+        <f>SUM(F5:F9)</f>
+        <v>513513</v>
       </c>
     </row>
   </sheetData>
@@ -6635,33 +6845,33 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C4" s="27">
         <v>1</v>
@@ -6681,10 +6891,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C5" s="27">
         <v>1</v>
@@ -6704,10 +6914,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C6" s="27">
         <v>0.5</v>
@@ -6727,7 +6937,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -6741,24 +6951,24 @@
         <v>67</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="B10" s="26">
         <v>118934</v>
@@ -6778,27 +6988,27 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B11" s="24">
-        <v>0.5039583333333334</v>
+        <v>0.5367065282791817</v>
       </c>
       <c r="C11" s="24">
-        <v>0.40603413940256045</v>
+        <v>0.4326189754471052</v>
       </c>
       <c r="D11" s="24">
-        <v>0.333071178529755</v>
+        <v>0.3549390698831137</v>
       </c>
       <c r="E11" s="24">
-        <v>0.2935136246786632</v>
+        <v>0.3128131506849315</v>
       </c>
       <c r="F11" s="24">
-        <v>0.2935136246786632</v>
+        <v>0.3128131506849315</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="B12" s="29">
         <v>4.8</v>
@@ -6842,7 +7052,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6855,24 +7065,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6882,7 +7092,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B5" s="25">
         <v>6000</v>
@@ -6902,7 +7112,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
@@ -6927,7 +7137,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -6937,7 +7147,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B8" s="25">
         <v>3600</v>
@@ -6957,7 +7167,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
@@ -6982,7 +7192,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -6992,7 +7202,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B11" s="25">
         <v>30000</v>
@@ -7012,7 +7222,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B12" s="25">
         <v>3600</v>
@@ -7032,7 +7242,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B13" s="25">
         <v>2400</v>
@@ -7052,7 +7262,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B14" s="30">
         <f>SUM(B11:B13)</f>
@@ -7077,7 +7287,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -7087,7 +7297,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B16" s="25">
         <v>3000</v>
@@ -7107,7 +7317,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B17" s="30">
         <f>SUM(B16:B16)</f>
@@ -7132,7 +7342,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B19" s="26">
         <f>B6+B9+B14+B17</f>
@@ -7172,7 +7382,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -7182,7 +7392,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7192,38 +7402,58 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="F5" s="26">
-        <v>0</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="17">
+        <v>30000</v>
+      </c>
+      <c r="D4" s="24">
+        <v>0.06</v>
+      </c>
+      <c r="E4" s="22">
+        <v>5</v>
+      </c>
+      <c r="F4" s="28">
+        <v>6960</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F6" s="30">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="F6" s="26">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" s="30">
+        <v>30000</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -3320,6 +3320,7 @@
         <v>250</v>
       </c>
       <c r="N4" s="30">
+        <f>SUM(B4:M4)</f>
         <v>221600</v>
       </c>
     </row>
@@ -3382,6 +3383,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="25">
+        <f>SUM(B7:M7)</f>
         <v>118934</v>
       </c>
     </row>
@@ -3426,6 +3428,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="25">
+        <f>SUM(B8:M8)</f>
         <v>40500</v>
       </c>
     </row>
@@ -3469,7 +3472,8 @@
       <c r="M9" s="25">
         <v>0</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="25" t="str">
+        <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
     </row>
@@ -3496,42 +3500,55 @@
         <v>241</v>
       </c>
       <c r="B12" s="28">
+        <f>B7+B8+B9</f>
         <v>15943</v>
       </c>
       <c r="C12" s="28">
+        <f>C7+C8+C9</f>
         <v>15943</v>
       </c>
       <c r="D12" s="28">
+        <f>D7+D8+D9</f>
         <v>15943</v>
       </c>
       <c r="E12" s="28">
+        <f>E7+E8+E9</f>
         <v>15943</v>
       </c>
       <c r="F12" s="28">
+        <f>F7+F8+F9</f>
         <v>15943</v>
       </c>
       <c r="G12" s="28">
+        <f>G7+G8+G9</f>
         <v>15943</v>
       </c>
       <c r="H12" s="28">
+        <f>H7+H8+H9</f>
         <v>15943</v>
       </c>
       <c r="I12" s="28">
+        <f>I7+I8+I9</f>
         <v>15943</v>
       </c>
       <c r="J12" s="28">
+        <f>J7+J8+J9</f>
         <v>15943</v>
       </c>
       <c r="K12" s="28">
+        <f>K7+K8+K9</f>
         <v>15943</v>
       </c>
-      <c r="L12" s="28">
-        <v>0</v>
-      </c>
-      <c r="M12" s="28">
+      <c r="L12" s="28" t="str">
+        <f>L7+L8+L9</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="28" t="str">
+        <f>M7+M8+M9</f>
         <v>0</v>
       </c>
       <c r="N12" s="28">
+        <f>SUM(B12:M12)</f>
         <v>159430</v>
       </c>
     </row>
@@ -3540,42 +3557,55 @@
         <v>266</v>
       </c>
       <c r="B13" s="28">
+        <f>B4-B12</f>
         <v>-6793</v>
       </c>
       <c r="C13" s="28">
+        <f>C4-C12</f>
         <v>6167</v>
       </c>
       <c r="D13" s="28">
+        <f>D4-D12</f>
         <v>6167</v>
       </c>
       <c r="E13" s="28">
+        <f>E4-E12</f>
         <v>6167</v>
       </c>
       <c r="F13" s="28">
+        <f>F4-F12</f>
         <v>6167</v>
       </c>
       <c r="G13" s="28">
+        <f>G4-G12</f>
         <v>6167</v>
       </c>
       <c r="H13" s="28">
+        <f>H4-H12</f>
         <v>6167</v>
       </c>
       <c r="I13" s="28">
+        <f>I4-I12</f>
         <v>6167</v>
       </c>
       <c r="J13" s="28">
+        <f>J4-J12</f>
         <v>6167</v>
       </c>
       <c r="K13" s="28">
+        <f>K4-K12</f>
         <v>6167</v>
       </c>
       <c r="L13" s="28">
+        <f>L4-L12</f>
         <v>13210</v>
       </c>
       <c r="M13" s="28">
+        <f>M4-M12</f>
         <v>250</v>
       </c>
       <c r="N13" s="28">
+        <f>SUM(B13:M13)</f>
         <v>62170</v>
       </c>
     </row>
@@ -3584,42 +3614,55 @@
         <v>267</v>
       </c>
       <c r="B14" s="33">
+        <f>B17+B13</f>
         <v>-6793</v>
       </c>
       <c r="C14" s="33">
+        <f>B14+C13</f>
         <v>-626</v>
       </c>
       <c r="D14" s="33">
+        <f>C14+D13</f>
         <v>5541</v>
       </c>
       <c r="E14" s="33">
+        <f>D14+E13</f>
         <v>11708</v>
       </c>
       <c r="F14" s="33">
+        <f>E14+F13</f>
         <v>17875</v>
       </c>
       <c r="G14" s="33">
+        <f>F14+G13</f>
         <v>24042</v>
       </c>
       <c r="H14" s="33">
+        <f>G14+H13</f>
         <v>30209</v>
       </c>
       <c r="I14" s="33">
+        <f>H14+I13</f>
         <v>36376</v>
       </c>
       <c r="J14" s="33">
+        <f>I14+J13</f>
         <v>42543</v>
       </c>
       <c r="K14" s="33">
+        <f>J14+K13</f>
         <v>48710</v>
       </c>
       <c r="L14" s="33">
+        <f>K14+L13</f>
         <v>61920</v>
       </c>
       <c r="M14" s="33">
+        <f>L14+M13</f>
         <v>62170</v>
       </c>
       <c r="N14" s="26">
+        <f>M14</f>
         <v>62170</v>
       </c>
     </row>
@@ -3634,7 +3677,7 @@
       <c r="A17" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="17">
         <v>0</v>
       </c>
     </row>
@@ -3643,6 +3686,7 @@
         <v>269</v>
       </c>
       <c r="B18" s="33">
+        <f>M14</f>
         <v>62170</v>
       </c>
     </row>
@@ -3651,6 +3695,7 @@
         <v>270</v>
       </c>
       <c r="B19" s="25">
+        <f>MIN(B14:M14)</f>
         <v>-6793</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -4088,18 +4088,23 @@
         <v>280</v>
       </c>
       <c r="B5" s="38">
+        <f>'Monthly Cash Flow Y1'!M14</f>
         <v>62170</v>
       </c>
       <c r="C5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>199962</v>
       </c>
       <c r="D5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>415091</v>
       </c>
       <c r="E5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>693221</v>
       </c>
       <c r="F5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>979696</v>
       </c>
     </row>
@@ -4168,18 +4173,23 @@
         <v>284</v>
       </c>
       <c r="B9" s="30">
+        <f>SUM(B5:B8)</f>
         <v>67170</v>
       </c>
       <c r="C9" s="30">
+        <f>SUM(C5:C8)</f>
         <v>204962</v>
       </c>
       <c r="D9" s="30">
+        <f>SUM(D5:D8)</f>
         <v>420091</v>
       </c>
       <c r="E9" s="30">
+        <f>SUM(E5:E8)</f>
         <v>698221</v>
       </c>
       <c r="F9" s="30">
+        <f>SUM(F5:F8)</f>
         <v>984696</v>
       </c>
     </row>
@@ -4237,19 +4247,24 @@
       <c r="A14" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B14" s="30">
-        <v>0</v>
-      </c>
-      <c r="C14" s="30">
-        <v>0</v>
-      </c>
-      <c r="D14" s="30">
-        <v>0</v>
-      </c>
-      <c r="E14" s="30">
-        <v>0</v>
-      </c>
-      <c r="F14" s="30">
+      <c r="B14" s="30" t="str">
+        <f>SUM(B12:B13)</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="str">
+        <f>SUM(C12:C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="str">
+        <f>SUM(D12:D13)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="str">
+        <f>SUM(E12:E13)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="str">
+        <f>SUM(F12:F13)</f>
         <v>0</v>
       </c>
     </row>
@@ -4268,18 +4283,23 @@
         <v>290</v>
       </c>
       <c r="B17" s="26">
+        <f>B9-B14</f>
         <v>67170</v>
       </c>
       <c r="C17" s="26">
+        <f>C9-C14</f>
         <v>204962</v>
       </c>
       <c r="D17" s="26">
+        <f>D9-D14</f>
         <v>420091</v>
       </c>
       <c r="E17" s="26">
+        <f>E9-E14</f>
         <v>698221</v>
       </c>
       <c r="F17" s="26">
+        <f>F9-F14</f>
         <v>984696</v>
       </c>
     </row>
@@ -4287,19 +4307,24 @@
       <c r="A19" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B19" s="39">
-        <v>0</v>
-      </c>
-      <c r="C19" s="39">
-        <v>0</v>
-      </c>
-      <c r="D19" s="39">
-        <v>0</v>
-      </c>
-      <c r="E19" s="39">
-        <v>0</v>
-      </c>
-      <c r="F19" s="39">
+      <c r="B19" s="39" t="str">
+        <f>B9-B14-B17</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="39" t="str">
+        <f>C9-C14-C17</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="39" t="str">
+        <f>D9-D14-D17</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="39" t="str">
+        <f>E9-E14-E17</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="39" t="str">
+        <f>F9-F14-F17</f>
         <v>0</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -25,13 +25,14 @@
     <sheet sheetId="19" name="Sources &amp; Uses" state="visible" r:id="rId22"/>
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
+    <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="370">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -72,7 +73,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -216,6 +217,12 @@
     <t>Underwriting Snapshot</t>
   </si>
   <si>
+    <t>22.</t>
+  </si>
+  <si>
+    <t>Financial Health</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -225,7 +232,7 @@
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs — change these to update your model.</t>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
   </si>
   <si>
     <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
@@ -255,37 +262,28 @@
     <t>Tabs 14-17: Financial statements</t>
   </si>
   <si>
-    <t>Tabs 18-21: Analysis &amp; underwriting</t>
+    <t>Tabs 18-22: Analysis, underwriting &amp; dashboard</t>
   </si>
   <si>
     <t>Debt Service Convention</t>
   </si>
   <si>
-    <t>operating expense on the 5-Year Operating Statement. This is a standard</t>
+    <t>operating expense on the Operating Statement. This is a standard</t>
   </si>
   <si>
     <t>simplification used in school financial underwriting that ensures internal</t>
   </si>
   <si>
-    <t>consistency across all tabs: the Cash Flow, Balance Sheet, and DSCR</t>
-  </si>
-  <si>
-    <t>schedules all reference the same debt service figures. The Debt Schedule</t>
-  </si>
-  <si>
-    <t>tab breaks out interest and principal separately for detailed analysis.</t>
+    <t>consistency across all tabs.</t>
   </si>
   <si>
     <t>Tips</t>
   </si>
   <si>
-    <t>Review the Budget Summary for a high-level view.</t>
-  </si>
-  <si>
-    <t>Check DSCR &amp; Covenants for lender readiness.</t>
-  </si>
-  <si>
-    <t>The Underwriting Snapshot provides a one-page summary.</t>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
   </si>
   <si>
     <t>Disclaimer</t>
@@ -300,7 +298,7 @@
     <t>Bright Horizons Microschool - Assumptions</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs. All other cells are formulas.</t>
+    <t>Blue cells are editable inputs. All other cells are formulas.</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -1042,6 +1040,108 @@
   </si>
   <si>
     <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
+  </si>
+  <si>
+    <t>Bright Horizons Microschool — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches profit early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
+  </si>
+  <si>
+    <t>Maintain reserves as a buffer against seasonal revenue dips.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 31% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>51.8 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>6 Healthy  |  0 Watch  |  0 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1155,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1121,6 +1221,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -1150,6 +1255,24 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1165,7 +1288,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1221,7 +1344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1242,15 +1365,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1269,21 +1392,49 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1628,7 +1779,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C42"/>
+  <dimension ref="B3:C43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1886,18 +2037,26 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="8" t="s">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="8"/>
+      <c r="C40" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Cover'!A1"/>
@@ -1921,6 +2080,7 @@
     <hyperlink ref="C37" r:id="rId19" location="#'Sources &amp; Uses'!A1"/>
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
     <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
+    <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1944,7 +2104,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1954,27 +2114,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="31">
         <v>12</v>
@@ -1994,7 +2154,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2004,7 +2164,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" s="25">
         <v>144000</v>
@@ -2024,7 +2184,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="25">
         <v>3000</v>
@@ -2044,7 +2204,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="25">
         <v>84000</v>
@@ -2064,7 +2224,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B10" s="25">
         <v>5000</v>
@@ -2084,7 +2244,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B11" s="25">
         <v>-10</v>
@@ -2104,7 +2264,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" s="26">
         <f>SUM(B7:B11)</f>
@@ -2129,7 +2289,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B14" s="25">
         <v>18467</v>
@@ -2173,7 +2333,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2183,27 +2343,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2213,7 +2373,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B5" s="25">
         <v>47869</v>
@@ -2233,7 +2393,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B6" s="25">
         <v>12559</v>
@@ -2253,7 +2413,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B7" s="30">
         <f>SUM(B5:B6)</f>
@@ -2278,7 +2438,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -2288,7 +2448,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B9" s="25">
         <v>58506</v>
@@ -2308,7 +2468,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B10" s="30">
         <f>SUM(B9:B9)</f>
@@ -2333,7 +2493,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B12" s="26">
         <f>B7+B10</f>
@@ -2382,7 +2542,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2392,27 +2552,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2422,7 +2582,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B5" s="25">
         <v>120000</v>
@@ -2442,7 +2602,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B6" s="25">
         <v>2500</v>
@@ -2462,7 +2622,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B7" s="25">
         <v>70000</v>
@@ -2482,7 +2642,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B8" s="25">
         <v>4167</v>
@@ -2502,7 +2662,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B9" s="25">
         <v>-8</v>
@@ -2522,7 +2682,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B10" s="30">
         <f>SUM(B5:B9)</f>
@@ -2547,7 +2707,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2557,7 +2717,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B13" s="25">
         <v>58506</v>
@@ -2577,7 +2737,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B14" s="25">
         <v>47869</v>
@@ -2597,7 +2757,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B15" s="25">
         <v>12559</v>
@@ -2617,7 +2777,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B16" s="30">
         <f>SUM(B13:B15)</f>
@@ -2642,7 +2802,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2652,12 +2812,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B20" s="25">
         <v>5000</v>
@@ -2677,12 +2837,12 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" s="25">
         <v>3000</v>
@@ -2702,12 +2862,12 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B24" s="25">
         <v>25000</v>
@@ -2727,7 +2887,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B25" s="25">
         <v>3000</v>
@@ -2747,7 +2907,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B26" s="25">
         <v>2000</v>
@@ -2767,7 +2927,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B27" s="30">
         <f>SUM(B24:B26)</f>
@@ -2792,12 +2952,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B29" s="25">
         <v>2500</v>
@@ -2817,7 +2977,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B30" s="30">
         <f>B20+B22+B27+B29</f>
@@ -2842,7 +3002,7 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -2852,7 +3012,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B33" s="30" t="str">
         <f>SUM(B33:B32)</f>
@@ -2901,7 +3061,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2911,27 +3071,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B4" s="28">
         <f>'Budget Detail'!B10</f>
@@ -2956,7 +3116,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B5" s="28">
         <f>'Budget Detail'!B16</f>
@@ -2981,7 +3141,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B6" s="28">
         <f>'Budget Detail'!B30</f>
@@ -3006,7 +3166,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B7" s="28" t="str">
         <f>'Budget Detail'!B33</f>
@@ -3031,7 +3191,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
@@ -3056,7 +3216,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3066,7 +3226,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B11" s="26">
         <f>B4-B8</f>
@@ -3091,7 +3251,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B12" s="24">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3116,7 +3276,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B13" s="25">
         <v>25233</v>
@@ -3136,7 +3296,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B14" s="25">
         <v>15389</v>
@@ -3156,7 +3316,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B15" s="25">
         <v>13286</v>
@@ -3201,7 +3361,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3219,51 +3379,51 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="N2" s="15" t="s">
         <v>259</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3281,7 +3441,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B4" s="30">
         <v>9150</v>
@@ -3326,7 +3486,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3344,7 +3504,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B7" s="25">
         <v>11893</v>
@@ -3389,7 +3549,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B8" s="25">
         <v>4050</v>
@@ -3434,7 +3594,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B9" s="25">
         <v>0</v>
@@ -3479,7 +3639,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3497,7 +3657,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B12" s="28">
         <f>B7+B8+B9</f>
@@ -3554,7 +3714,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B13" s="28">
         <f>B4-B12</f>
@@ -3611,7 +3771,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B14" s="33">
         <f>B17+B13</f>
@@ -3668,14 +3828,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B17" s="17">
         <v>0</v>
@@ -3683,7 +3843,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B18" s="33">
         <f>M14</f>
@@ -3692,7 +3852,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B19" s="25">
         <f>MIN(B14:M14)</f>
@@ -3725,7 +3885,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3735,27 +3895,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3765,7 +3925,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B5" s="30">
         <v>184667</v>
@@ -3785,7 +3945,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -3795,7 +3955,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B8" s="28">
         <v>118934</v>
@@ -3815,7 +3975,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B9" s="28">
         <v>40500</v>
@@ -3835,7 +3995,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B10" s="28">
         <v>0</v>
@@ -3855,7 +4015,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
@@ -3880,7 +4040,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -3890,7 +4050,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B14" s="26">
         <f>B5-B11</f>
@@ -3915,7 +4075,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B15" s="24">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -3974,27 +4134,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4004,19 +4164,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="B5" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="37" t="s">
+      <c r="D5" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="D5" s="35" t="s">
-        <v>277</v>
-      </c>
       <c r="E5" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -4045,7 +4205,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4055,27 +4215,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4085,7 +4245,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B5" s="38">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -4110,7 +4270,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B6" s="25">
         <v>0</v>
@@ -4130,7 +4290,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B7" s="25">
         <v>5000</v>
@@ -4150,7 +4310,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B8" s="25">
         <v>0</v>
@@ -4170,7 +4330,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
@@ -4195,7 +4355,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4205,7 +4365,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B12" s="25">
         <v>0</v>
@@ -4225,7 +4385,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B13" s="25">
         <v>0</v>
@@ -4245,7 +4405,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B14" s="30" t="str">
         <f>SUM(B12:B13)</f>
@@ -4270,7 +4430,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4280,7 +4440,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B17" s="26">
         <f>B9-B14</f>
@@ -4305,7 +4465,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B19" s="39" t="str">
         <f>B9-B14-B17</f>
@@ -4354,7 +4514,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4364,27 +4524,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4394,7 +4554,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B5" s="25">
         <v>184667</v>
@@ -4414,7 +4574,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B6" s="25">
         <v>118934</v>
@@ -4434,7 +4594,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B7" s="25">
         <v>40500</v>
@@ -4454,7 +4614,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B8" s="28">
         <f>B5-B6-B7</f>
@@ -4479,7 +4639,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B9" s="25">
         <v>0</v>
@@ -4499,27 +4659,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="40" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="40" t="s">
-        <v>297</v>
-      </c>
       <c r="C10" s="40" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -4529,7 +4689,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B13" s="25">
         <v>62170</v>
@@ -4549,7 +4709,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B14" s="22">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -4574,7 +4734,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B15" s="29">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -4599,7 +4759,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="24">
         <v>0.48</v>
@@ -4619,7 +4779,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -4629,7 +4789,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B19" s="25">
         <v>15389</v>
@@ -4649,7 +4809,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B20" s="25">
         <v>118934</v>
@@ -4669,7 +4829,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B21" s="25">
         <v>3375</v>
@@ -4689,7 +4849,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B22" s="41">
         <v>10</v>
@@ -4709,7 +4869,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -4719,102 +4879,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B26" s="43" t="s">
         <v>308</v>
       </c>
-      <c r="B26" s="43" t="s">
-        <v>309</v>
-      </c>
       <c r="C26" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F26" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B27" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="B27" s="44" t="s">
-        <v>311</v>
-      </c>
       <c r="C27" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -4855,27 +5015,27 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="B3" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>315</v>
-      </c>
       <c r="E3" s="45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B4" s="25">
         <v>20000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E4" s="25">
         <v>15000</v>
@@ -4883,7 +5043,7 @@
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E5" s="25">
         <v>5000</v>
@@ -4891,13 +5051,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B7" s="26">
         <v>20000</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E7" s="26">
         <v>20000</v>
@@ -4905,7 +5065,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B8" s="39">
         <v>0</v>
@@ -4928,7 +5088,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B32"/>
+  <dimension ref="B2:B29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4937,152 +5097,137 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>80</v>
+      <c r="B23" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
-        <v>81</v>
+      <c r="B25" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>83</v>
+      <c r="B27" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -5108,7 +5253,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5118,7 +5263,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5128,32 +5273,32 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B6" s="25">
         <v>184667</v>
@@ -5173,7 +5318,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B7" s="25">
         <v>159434</v>
@@ -5193,7 +5338,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B8" s="26">
         <v>25233</v>
@@ -5213,7 +5358,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B9" s="24">
         <v>0.13663808664259927</v>
@@ -5233,27 +5378,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="46" t="s">
-        <v>297</v>
-      </c>
       <c r="C10" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B11" s="22">
         <v>10</v>
@@ -5273,7 +5418,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5283,32 +5428,32 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B16" s="25">
         <v>147733</v>
@@ -5328,7 +5473,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B17" s="25">
         <v>159434</v>
@@ -5348,7 +5493,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B18" s="26">
         <v>-11701</v>
@@ -5368,7 +5513,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B19" s="24">
         <v>-0.07920239169675096</v>
@@ -5388,27 +5533,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B20" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="B20" s="46" t="s">
-        <v>297</v>
-      </c>
       <c r="C20" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B21" s="22">
         <v>12</v>
@@ -5454,7 +5599,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5466,7 +5611,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" s="13"/>
     </row>
@@ -5480,7 +5625,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -5488,7 +5633,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -5512,7 +5657,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -5520,7 +5665,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5532,33 +5677,33 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D12" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="F12" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="G12" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="H12" s="47" t="s">
         <v>99</v>
-      </c>
-      <c r="H12" s="47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D13" s="25">
         <v>184667</v>
@@ -5578,7 +5723,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D14" s="25">
         <v>159434</v>
@@ -5598,7 +5743,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D15" s="25">
         <v>25233</v>
@@ -5618,7 +5763,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D16" s="25">
         <v>62170</v>
@@ -5638,7 +5783,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D17" s="25">
         <v>0</v>
@@ -5658,7 +5803,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -5670,33 +5815,33 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="47" t="s">
+      <c r="F20" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="G20" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="47" t="s">
+      <c r="H20" s="47" t="s">
         <v>99</v>
-      </c>
-      <c r="H20" s="47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D21" s="24">
         <v>0.13663808664259927</v>
@@ -5716,27 +5861,27 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D22" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="D22" s="46" t="s">
-        <v>297</v>
-      </c>
       <c r="E22" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D23" s="24">
         <v>0.48</v>
@@ -5756,7 +5901,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D24" s="22">
         <v>12</v>
@@ -5776,7 +5921,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -5790,6 +5935,381 @@
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A26:H26"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="48" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>339</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>340</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>341</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>342</v>
+      </c>
+      <c r="G5" s="49" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="50">
+        <v>12</v>
+      </c>
+      <c r="D6" s="50">
+        <v>18</v>
+      </c>
+      <c r="E6" s="50">
+        <v>22</v>
+      </c>
+      <c r="F6" s="50">
+        <v>25</v>
+      </c>
+      <c r="G6" s="50">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" s="51">
+        <v>184666.6666666667</v>
+      </c>
+      <c r="D7" s="51">
+        <v>339797</v>
+      </c>
+      <c r="E7" s="51">
+        <v>426587.88999999996</v>
+      </c>
+      <c r="F7" s="51">
+        <v>498556.69375000003</v>
+      </c>
+      <c r="G7" s="51">
+        <v>513513.3945625001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" s="51">
+        <v>118934.16666666667</v>
+      </c>
+      <c r="D8" s="51">
+        <v>147002.63</v>
+      </c>
+      <c r="E8" s="51">
+        <v>151412.7089</v>
+      </c>
+      <c r="F8" s="51">
+        <v>155955.090167</v>
+      </c>
+      <c r="G8" s="51">
+        <v>160633.74287201</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="51">
+        <v>40500</v>
+      </c>
+      <c r="D9" s="51">
+        <v>55002</v>
+      </c>
+      <c r="E9" s="51">
+        <v>60046.93999999999</v>
+      </c>
+      <c r="F9" s="51">
+        <v>64470.893</v>
+      </c>
+      <c r="G9" s="51">
+        <v>66405.01979</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="51">
+        <v>0</v>
+      </c>
+      <c r="D10" s="51">
+        <v>0</v>
+      </c>
+      <c r="E10" s="51">
+        <v>0</v>
+      </c>
+      <c r="F10" s="51">
+        <v>0</v>
+      </c>
+      <c r="G10" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="52">
+        <v>25232.5</v>
+      </c>
+      <c r="D11" s="52">
+        <v>137792.37</v>
+      </c>
+      <c r="E11" s="52">
+        <v>215128.24109999998</v>
+      </c>
+      <c r="F11" s="52">
+        <v>278130.71058300004</v>
+      </c>
+      <c r="G11" s="52">
+        <v>286474.6319004901</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="52">
+        <v>62170</v>
+      </c>
+      <c r="D12" s="52">
+        <v>199962.37</v>
+      </c>
+      <c r="E12" s="52">
+        <v>415090.6111</v>
+      </c>
+      <c r="F12" s="52">
+        <v>693221.3216830001</v>
+      </c>
+      <c r="G12" s="52">
+        <v>979695.9535834901</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C13" s="53">
+        <v>0.13663808664259927</v>
+      </c>
+      <c r="D13" s="53">
+        <v>0.40551379205819943</v>
+      </c>
+      <c r="E13" s="53">
+        <v>0.5042999253916937</v>
+      </c>
+      <c r="F13" s="53">
+        <v>0.5578717808219178</v>
+      </c>
+      <c r="G13" s="53">
+        <v>0.5578717808219178</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>350</v>
+      </c>
+      <c r="E16" s="55"/>
+      <c r="F16" s="56" t="s">
+        <v>351</v>
+      </c>
+      <c r="G16" s="56"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="D17" s="55" t="s">
+        <v>353</v>
+      </c>
+      <c r="E17" s="55"/>
+      <c r="F17" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="G17" s="56"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="35" t="s">
+        <v>355</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>356</v>
+      </c>
+      <c r="E18" s="55"/>
+      <c r="F18" s="56" t="s">
+        <v>357</v>
+      </c>
+      <c r="G18" s="56"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="35" t="s">
+        <v>358</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="D19" s="55" t="s">
+        <v>359</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="56" t="s">
+        <v>360</v>
+      </c>
+      <c r="G19" s="56"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="35" t="s">
+        <v>361</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>362</v>
+      </c>
+      <c r="E20" s="55"/>
+      <c r="F20" s="56" t="s">
+        <v>363</v>
+      </c>
+      <c r="G20" s="56"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="35" t="s">
+        <v>364</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>365</v>
+      </c>
+      <c r="E21" s="55"/>
+      <c r="F21" s="56" t="s">
+        <v>366</v>
+      </c>
+      <c r="G21" s="56"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="35" t="s">
+        <v>367</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="57" t="s">
+        <v>369</v>
+      </c>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="B25:G25"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5814,7 +6334,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5825,12 +6345,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5873,10 +6393,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5897,7 +6417,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="14">
         <v>7</v>
@@ -5905,7 +6425,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="14">
         <v>25</v>
@@ -5913,7 +6433,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -5924,27 +6444,27 @@
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" s="16">
         <v>12</v>
@@ -5964,7 +6484,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -5975,30 +6495,30 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="C20" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>106</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D21" s="17">
         <v>12000</v>
@@ -6009,13 +6529,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D22" s="17">
         <v>250</v>
@@ -6026,13 +6546,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="C23" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="17">
         <v>7000</v>
@@ -6043,13 +6563,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="D24" s="17">
         <v>5000</v>
@@ -6060,13 +6580,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="D25" s="17">
         <v>10</v>
@@ -6077,7 +6597,7 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -6088,36 +6608,36 @@
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" s="15" t="s">
+      <c r="D28" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="E28" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="F28" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="G28" s="15" t="s">
         <v>125</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="D29" s="19">
         <v>1</v>
@@ -6134,13 +6654,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="C30" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D30" s="19">
         <v>1</v>
@@ -6157,13 +6677,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="D31" s="19">
         <v>0.5</v>
@@ -6180,7 +6700,7 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -6191,30 +6711,30 @@
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="C34" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="D34" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="E34" s="15" t="s">
         <v>106</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="D35" s="17">
         <v>2500</v>
@@ -6225,13 +6745,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="D36" s="17">
         <v>300</v>
@@ -6242,13 +6762,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D37" s="17">
         <v>2400</v>
@@ -6259,13 +6779,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>141</v>
-      </c>
       <c r="C38" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D38" s="17">
         <v>500</v>
@@ -6276,13 +6796,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D39" s="17">
         <v>300</v>
@@ -6293,13 +6813,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="C40" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D40" s="17">
         <v>3000</v>
@@ -6310,7 +6830,7 @@
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -6321,27 +6841,27 @@
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C43" s="15" t="s">
+      <c r="D43" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="15" t="s">
         <v>147</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="C44" s="17">
         <v>30000</v>
@@ -6355,7 +6875,7 @@
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
@@ -6366,29 +6886,29 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B47" s="18">
         <v>0.03</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B48" s="18">
         <v>0.03</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B49" s="19">
         <v>0.8333333333333334</v>
@@ -6396,7 +6916,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B50" s="17">
         <v>0</v>
@@ -6404,10 +6924,10 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B51" s="14" t="s">
         <v>158</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -6442,10 +6962,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6466,10 +6986,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6482,7 +7002,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -6490,66 +7010,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -6589,27 +7109,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -6619,7 +7139,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="21">
         <v>12</v>
@@ -6639,7 +7159,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7" s="22">
         <v>25</v>
@@ -6647,7 +7167,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B8" s="23">
         <v>0.48</v>
@@ -6667,10 +7187,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="C10" s="24">
         <v>0.5</v>
@@ -6711,7 +7231,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6721,27 +7241,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6751,7 +7271,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5" s="25">
         <v>144000</v>
@@ -6771,7 +7291,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B6" s="25">
         <v>3000</v>
@@ -6791,7 +7311,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B7" s="25">
         <v>84000</v>
@@ -6811,7 +7331,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B8" s="25">
         <v>5000</v>
@@ -6831,7 +7351,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B9" s="25">
         <v>-10</v>
@@ -6851,7 +7371,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B10" s="26">
         <f>SUM(B5:B9)</f>
@@ -6915,33 +7435,33 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>188</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="C4" s="27">
         <v>1</v>
@@ -6961,10 +7481,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="C5" s="27">
         <v>1</v>
@@ -6984,10 +7504,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C6" s="27">
         <v>0.5</v>
@@ -7007,7 +7527,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -7018,27 +7538,27 @@
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="D9" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="E9" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="F9" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B10" s="26">
         <v>118934</v>
@@ -7058,7 +7578,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B11" s="24">
         <v>0.5367065282791817</v>
@@ -7078,7 +7598,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B12" s="29">
         <v>4.8</v>
@@ -7122,7 +7642,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7132,27 +7652,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7162,7 +7682,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="25">
         <v>6000</v>
@@ -7182,7 +7702,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
@@ -7207,7 +7727,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -7217,7 +7737,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B8" s="25">
         <v>3600</v>
@@ -7237,7 +7757,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
@@ -7262,7 +7782,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -7272,7 +7792,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B11" s="25">
         <v>30000</v>
@@ -7292,7 +7812,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B12" s="25">
         <v>3600</v>
@@ -7312,7 +7832,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B13" s="25">
         <v>2400</v>
@@ -7332,7 +7852,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B14" s="30">
         <f>SUM(B11:B13)</f>
@@ -7357,7 +7877,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -7367,7 +7887,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B16" s="25">
         <v>3000</v>
@@ -7387,7 +7907,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B17" s="30">
         <f>SUM(B16:B16)</f>
@@ -7412,7 +7932,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B19" s="26">
         <f>B6+B9+B14+B17</f>
@@ -7462,7 +7982,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7472,30 +7992,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>148</v>
-      </c>
       <c r="F3" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="C4" s="17">
         <v>30000</v>
@@ -7512,7 +8032,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F6" s="26">
         <v>6960</v>
@@ -7520,7 +8040,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F7" s="30">
         <v>30000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="376">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -1064,6 +1064,24 @@
   </si>
   <si>
     <t>Year 5</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1274,7 +1292,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1299,6 +1317,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1344,7 +1367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1425,6 +1448,13 @@
     <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5949,7 +5979,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G25"/>
+  <dimension ref="B2:G32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6158,158 +6188,284 @@
         <v>0.5578717808219178</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C14" s="51">
+        <v>15388.88888888889</v>
+      </c>
+      <c r="D14" s="51">
+        <v>18877.61111111111</v>
+      </c>
+      <c r="E14" s="51">
+        <v>19390.358636363635</v>
+      </c>
+      <c r="F14" s="51">
+        <v>19942.267750000003</v>
+      </c>
+      <c r="G14" s="51">
+        <v>20540.535782500006</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="54">
+        <v>0.644047833935018</v>
+      </c>
+      <c r="D15" s="53">
+        <v>0.4326189754471052</v>
+      </c>
+      <c r="E15" s="53">
+        <v>0.3549390698831137</v>
+      </c>
+      <c r="F15" s="53">
+        <v>0.3128131506849315</v>
+      </c>
+      <c r="G15" s="53">
+        <v>0.3128131506849315</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="C16" s="53">
+        <v>0.06579422382671479</v>
+      </c>
+      <c r="D16" s="53">
+        <v>0.048560169748408606</v>
+      </c>
+      <c r="E16" s="53">
+        <v>0.04222830141755781</v>
+      </c>
+      <c r="F16" s="53">
+        <v>0.0387945205479452</v>
+      </c>
+      <c r="G16" s="53">
+        <v>0.0387945205479452</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13" t="s">
+      <c r="C17" s="53">
+        <v>0.13663808664259935</v>
+      </c>
+      <c r="D17" s="53">
+        <v>0.40551379205819943</v>
+      </c>
+      <c r="E17" s="53">
+        <v>0.5042999253916934</v>
+      </c>
+      <c r="F17" s="53">
+        <v>0.5578717808219178</v>
+      </c>
+      <c r="G17" s="53">
+        <v>0.5578717808219178</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C18" s="55" t="s">
+        <v>296</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>296</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>296</v>
+      </c>
+      <c r="F18" s="55" t="s">
+        <v>296</v>
+      </c>
+      <c r="G18" s="55" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="35" t="s">
+      <c r="C19" s="56" t="s">
+        <v>339</v>
+      </c>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C20" s="56" t="s">
         <v>349</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="56" t="s">
+      <c r="C22" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="G16" s="56"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="35" t="s">
+      <c r="D22" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="C17" s="54" t="s">
-        <v>349</v>
-      </c>
-      <c r="D17" s="55" t="s">
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="E17" s="55"/>
-      <c r="F17" s="56" t="s">
+      <c r="G22" s="13"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="35" t="s">
         <v>354</v>
       </c>
-      <c r="G17" s="56"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="35" t="s">
+      <c r="C23" s="57" t="s">
         <v>355</v>
       </c>
-      <c r="C18" s="54" t="s">
-        <v>349</v>
-      </c>
-      <c r="D18" s="55" t="s">
+      <c r="D23" s="58" t="s">
         <v>356</v>
       </c>
-      <c r="E18" s="55"/>
-      <c r="F18" s="56" t="s">
+      <c r="E23" s="58"/>
+      <c r="F23" s="59" t="s">
         <v>357</v>
       </c>
-      <c r="G18" s="56"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="35" t="s">
+      <c r="G23" s="59"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="35" t="s">
         <v>358</v>
       </c>
-      <c r="C19" s="54" t="s">
-        <v>349</v>
-      </c>
-      <c r="D19" s="55" t="s">
+      <c r="C24" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="D24" s="58" t="s">
         <v>359</v>
       </c>
-      <c r="E19" s="55"/>
-      <c r="F19" s="56" t="s">
+      <c r="E24" s="58"/>
+      <c r="F24" s="59" t="s">
         <v>360</v>
       </c>
-      <c r="G19" s="56"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="35" t="s">
+      <c r="G24" s="59"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="35" t="s">
         <v>361</v>
       </c>
-      <c r="C20" s="54" t="s">
-        <v>349</v>
-      </c>
-      <c r="D20" s="55" t="s">
+      <c r="C25" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="D25" s="58" t="s">
         <v>362</v>
       </c>
-      <c r="E20" s="55"/>
-      <c r="F20" s="56" t="s">
+      <c r="E25" s="58"/>
+      <c r="F25" s="59" t="s">
         <v>363</v>
       </c>
-      <c r="G20" s="56"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="35" t="s">
+      <c r="G25" s="59"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="C21" s="54" t="s">
-        <v>349</v>
-      </c>
-      <c r="D21" s="55" t="s">
+      <c r="C26" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="D26" s="58" t="s">
         <v>365</v>
       </c>
-      <c r="E21" s="55"/>
-      <c r="F21" s="56" t="s">
+      <c r="E26" s="58"/>
+      <c r="F26" s="59" t="s">
         <v>366</v>
       </c>
-      <c r="G21" s="56"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="35" t="s">
+      <c r="G26" s="59"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="35" t="s">
         <v>367</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C27" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="58" t="s">
         <v>368</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="57" t="s">
+      <c r="E27" s="58"/>
+      <c r="F27" s="59" t="s">
         <v>369</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
+      <c r="G27" s="59"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="35" t="s">
+        <v>370</v>
+      </c>
+      <c r="C28" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="D28" s="58" t="s">
+        <v>371</v>
+      </c>
+      <c r="E28" s="58"/>
+      <c r="F28" s="59" t="s">
+        <v>372</v>
+      </c>
+      <c r="G28" s="59"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="35" t="s">
+        <v>373</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="60" t="s">
+        <v>375</v>
+      </c>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="B32:G32"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="382">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -229,16 +229,19 @@
     <t>How to Use This Workbook</t>
   </si>
   <si>
+    <t>Generated March 26, 2026 · llc_single</t>
+  </si>
+  <si>
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t>Green cells are key outputs and summary metrics.</t>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
   </si>
   <si>
     <t/>
@@ -284,6 +287,21 @@
   </si>
   <si>
     <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
   </si>
   <si>
     <t>Disclaimer</t>
@@ -1173,7 +1191,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1227,19 +1245,30 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E293B"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF666666"/>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF1E3A5F"/>
+      <i/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1301,22 +1330,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1367,7 +1396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1385,55 +1414,59 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1442,10 +1475,10 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1454,24 +1487,151 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2133,207 +2293,207 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="31">
+        <v>106</v>
+      </c>
+      <c r="B4" s="35">
         <v>12</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="35">
         <v>18</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="35">
         <v>22</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="35">
         <v>25</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="35">
         <v>25</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="A6" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="25">
+        <v>113</v>
+      </c>
+      <c r="B7" s="29">
         <v>144000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="29">
         <v>222480</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>280078</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <v>327818</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <v>337653</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="25">
+        <v>116</v>
+      </c>
+      <c r="B8" s="29">
         <v>3000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="29">
         <v>4635</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="29">
         <v>5835</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="29">
         <v>6830</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="29">
         <v>7034</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="25">
+        <v>117</v>
+      </c>
+      <c r="B9" s="29">
         <v>84000</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="29">
         <v>129780</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="29">
         <v>163379</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="29">
         <v>191227</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="29">
         <v>196964</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B10" s="25">
+        <v>119</v>
+      </c>
+      <c r="B10" s="29">
         <v>5000</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="29">
         <v>5150</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="29">
         <v>5305</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="29">
         <v>5464</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="29">
         <v>5628</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" s="25">
+        <v>122</v>
+      </c>
+      <c r="B11" s="29">
         <v>-10</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="29">
         <v>-10</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="29">
         <v>-11</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="29">
         <v>-11</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="29">
         <v>-11</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B12" s="26">
+      <c r="A12" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="30">
         <f>SUM(B7:B11)</f>
         <v>221600</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="30">
         <f>SUM(C7:C11)</f>
         <v>339797</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="30">
         <f>SUM(D7:D11)</f>
         <v>426588</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="30">
         <f>SUM(E7:E11)</f>
         <v>498557</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="30">
         <f>SUM(F7:F11)</f>
         <v>513513</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="25">
+        <v>217</v>
+      </c>
+      <c r="B14" s="29">
         <v>18467</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="29">
         <v>18878</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="29">
         <v>19390</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="29">
         <v>19942</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="29">
         <v>20541</v>
       </c>
     </row>
@@ -2362,186 +2522,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B5" s="25">
+        <v>219</v>
+      </c>
+      <c r="B5" s="29">
         <v>47869</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="29">
         <v>59166</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="29">
         <v>60941</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="29">
         <v>62769</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="29">
         <v>64652</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B6" s="25">
+        <v>220</v>
+      </c>
+      <c r="B6" s="29">
         <v>12559</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="29">
         <v>15523</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <v>15989</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="29">
         <v>16468</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="29">
         <v>16963</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B7" s="30">
+        <v>221</v>
+      </c>
+      <c r="B7" s="34">
         <f>SUM(B5:B6)</f>
         <v>60428</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="34">
         <f>SUM(C5:C6)</f>
         <v>74689</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="34">
         <f>SUM(D5:D6)</f>
         <v>76930</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="34">
         <f>SUM(E5:E6)</f>
         <v>79237</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="34">
         <f>SUM(F5:F6)</f>
         <v>81615</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="A8" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B9" s="25">
+        <v>222</v>
+      </c>
+      <c r="B9" s="29">
         <v>58506</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="29">
         <v>72314</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="29">
         <v>74483</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="29">
         <v>76718</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="29">
         <v>79019</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="30">
+        <v>223</v>
+      </c>
+      <c r="B10" s="34">
         <f>SUM(B9:B9)</f>
         <v>58506</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="34">
         <f>SUM(C9:C9)</f>
         <v>72314</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="34">
         <f>SUM(D9:D9)</f>
         <v>74483</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="34">
         <f>SUM(E9:E9)</f>
         <v>76718</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="34">
         <f>SUM(F9:F9)</f>
         <v>79019</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="B12" s="26">
+      <c r="A12" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="30">
         <f>B7+B10</f>
         <v>118934</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="30">
         <f>C7+C10</f>
         <v>147003</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="30">
         <f>D7+D10</f>
         <v>151413</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="30">
         <f>E7+E10</f>
         <v>155955</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="30">
         <f>F7+F10</f>
         <v>160634</v>
       </c>
@@ -2571,496 +2731,496 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="25">
+        <v>227</v>
+      </c>
+      <c r="B5" s="29">
         <v>120000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="29">
         <v>222480</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="29">
         <v>280078</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="29">
         <v>327818</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="29">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="25">
+        <v>228</v>
+      </c>
+      <c r="B6" s="29">
         <v>2500</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="29">
         <v>4635</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <v>5835</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="29">
         <v>6830</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="29">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B7" s="25">
+        <v>229</v>
+      </c>
+      <c r="B7" s="29">
         <v>70000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="29">
         <v>129780</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>163379</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <v>191227</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <v>196964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B8" s="25">
+        <v>230</v>
+      </c>
+      <c r="B8" s="29">
         <v>4167</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="29">
         <v>5150</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="29">
         <v>5305</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="29">
         <v>5464</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="29">
         <v>5628</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B9" s="25">
+        <v>231</v>
+      </c>
+      <c r="B9" s="29">
         <v>-8</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="29">
         <v>-10</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="29">
         <v>-11</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="29">
         <v>-11</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="29">
         <v>-11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B10" s="30">
+        <v>232</v>
+      </c>
+      <c r="B10" s="34">
         <f>SUM(B5:B9)</f>
         <v>184667</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="34">
         <f>SUM(C5:C9)</f>
         <v>339797</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="34">
         <f>SUM(D5:D9)</f>
         <v>426588</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="34">
         <f>SUM(E5:E9)</f>
         <v>498557</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="34">
         <f>SUM(F5:F9)</f>
         <v>513513</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B13" s="25">
+        <v>222</v>
+      </c>
+      <c r="B13" s="29">
         <v>58506</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="29">
         <v>72314</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="29">
         <v>74483</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="29">
         <v>76718</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="29">
         <v>79019</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B14" s="25">
+        <v>219</v>
+      </c>
+      <c r="B14" s="29">
         <v>47869</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="29">
         <v>59166</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="29">
         <v>60941</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="29">
         <v>62769</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="29">
         <v>64652</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B15" s="25">
+        <v>220</v>
+      </c>
+      <c r="B15" s="29">
         <v>12559</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="29">
         <v>15523</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="29">
         <v>15989</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="29">
         <v>16468</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="29">
         <v>16963</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B16" s="30">
+        <v>196</v>
+      </c>
+      <c r="B16" s="34">
         <f>SUM(B13:B15)</f>
         <v>118934</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="34">
         <f>SUM(C13:C15)</f>
         <v>147003</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="34">
         <f>SUM(D13:D15)</f>
         <v>151413</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="34">
         <f>SUM(E13:E15)</f>
         <v>155955</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="34">
         <f>SUM(F13:F15)</f>
         <v>160634</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="A18" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>140</v>
+      <c r="A19" s="36" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B20" s="25">
+        <v>234</v>
+      </c>
+      <c r="B20" s="29">
         <v>5000</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="29">
         <v>9270</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="29">
         <v>11670</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="29">
         <v>13659</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="29">
         <v>14069</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
-        <v>141</v>
+      <c r="A21" s="36" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B22" s="25">
+        <v>235</v>
+      </c>
+      <c r="B22" s="29">
         <v>3000</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="29">
         <v>5562</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="29">
         <v>7002</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="29">
         <v>8195</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="29">
         <v>8441</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="32" t="s">
-        <v>135</v>
+      <c r="A23" s="36" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B24" s="25">
+        <v>236</v>
+      </c>
+      <c r="B24" s="29">
         <v>25000</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="29">
         <v>30900</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="29">
         <v>31827</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="29">
         <v>32782</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="29">
         <v>33765</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B25" s="25">
+        <v>237</v>
+      </c>
+      <c r="B25" s="29">
         <v>3000</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="29">
         <v>3708</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="29">
         <v>3819</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="29">
         <v>3934</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="29">
         <v>4052</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B26" s="25">
+        <v>238</v>
+      </c>
+      <c r="B26" s="29">
         <v>2000</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="29">
         <v>2472</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="29">
         <v>2546</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="29">
         <v>2623</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="29">
         <v>2701</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B27" s="30">
+        <v>239</v>
+      </c>
+      <c r="B27" s="34">
         <f>SUM(B24:B26)</f>
         <v>30000</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="34">
         <f>SUM(C24:C26)</f>
         <v>37080</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="34">
         <f>SUM(D24:D26)</f>
         <v>38192</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="34">
         <f>SUM(E24:E26)</f>
         <v>39338</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="34">
         <f>SUM(F24:F26)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="32" t="s">
-        <v>143</v>
+      <c r="A28" s="36" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B29" s="25">
+        <v>240</v>
+      </c>
+      <c r="B29" s="29">
         <v>2500</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="29">
         <v>3090</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="29">
         <v>3183</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="29">
         <v>3278</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="29">
         <v>3377</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B30" s="30">
+        <v>241</v>
+      </c>
+      <c r="B30" s="34">
         <f>B20+B22+B27+B29</f>
         <v>40500</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="34">
         <f>C20+C22+C27+C29</f>
         <v>55002</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="34">
         <f>D20+D22+D27+D29</f>
         <v>60047</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="34">
         <f>E20+E22+E27+E29</f>
         <v>64471</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="34">
         <f>F20+F22+F27+F29</f>
         <v>66405</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+      <c r="A32" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B33" s="30" t="str">
+        <v>243</v>
+      </c>
+      <c r="B33" s="34" t="str">
         <f>SUM(B33:B32)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="30" t="str">
+      <c r="C33" s="34" t="str">
         <f>SUM(C33:C32)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="30" t="str">
+      <c r="D33" s="34" t="str">
         <f>SUM(D33:D32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="30" t="str">
+      <c r="E33" s="34" t="str">
         <f>SUM(E33:E32)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="30" t="str">
+      <c r="F33" s="34" t="str">
         <f>SUM(F33:F32)</f>
         <v>0</v>
       </c>
@@ -3090,277 +3250,277 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="28">
+        <v>232</v>
+      </c>
+      <c r="B4" s="32">
         <f>'Budget Detail'!B10</f>
         <v>184667</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="32">
         <f>'Budget Detail'!C10</f>
         <v>339797</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="32">
         <f>'Budget Detail'!D10</f>
         <v>426588</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="32">
         <f>'Budget Detail'!E10</f>
         <v>498557</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="32">
         <f>'Budget Detail'!F10</f>
         <v>513513</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" s="28">
+        <v>196</v>
+      </c>
+      <c r="B5" s="32">
         <f>'Budget Detail'!B16</f>
         <v>118934</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="32">
         <f>'Budget Detail'!C16</f>
         <v>147003</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="32">
         <f>'Budget Detail'!D16</f>
         <v>151413</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="32">
         <f>'Budget Detail'!E16</f>
         <v>155955</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="32">
         <f>'Budget Detail'!F16</f>
         <v>160634</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B6" s="28">
+        <v>241</v>
+      </c>
+      <c r="B6" s="32">
         <f>'Budget Detail'!B30</f>
         <v>40500</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="32">
         <f>'Budget Detail'!C30</f>
         <v>55002</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="32">
         <f>'Budget Detail'!D30</f>
         <v>60047</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="32">
         <f>'Budget Detail'!E30</f>
         <v>64471</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="32">
         <f>'Budget Detail'!F30</f>
         <v>66405</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="28" t="str">
+        <v>245</v>
+      </c>
+      <c r="B7" s="32" t="str">
         <f>'Budget Detail'!B33</f>
         <v>0</v>
       </c>
-      <c r="C7" s="28" t="str">
+      <c r="C7" s="32" t="str">
         <f>'Budget Detail'!C33</f>
         <v>0</v>
       </c>
-      <c r="D7" s="28" t="str">
+      <c r="D7" s="32" t="str">
         <f>'Budget Detail'!D33</f>
         <v>0</v>
       </c>
-      <c r="E7" s="28" t="str">
+      <c r="E7" s="32" t="str">
         <f>'Budget Detail'!E33</f>
         <v>0</v>
       </c>
-      <c r="F7" s="28" t="str">
+      <c r="F7" s="32" t="str">
         <f>'Budget Detail'!F33</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B8" s="30">
+        <v>246</v>
+      </c>
+      <c r="B8" s="34">
         <f>SUM(B5:B7)</f>
         <v>159434</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="34">
         <f>SUM(C5:C7)</f>
         <v>202005</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="34">
         <f>SUM(D5:D7)</f>
         <v>211460</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="34">
         <f>SUM(E5:E7)</f>
         <v>220426</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="34">
         <f>SUM(F5:F7)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="A10" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B11" s="26">
+        <v>248</v>
+      </c>
+      <c r="B11" s="30">
         <f>B4-B8</f>
         <v>25233</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="30">
         <f>C4-C8</f>
         <v>137792</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="30">
         <f>D4-D8</f>
         <v>215128</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="30">
         <f>E4-E8</f>
         <v>278131</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="30">
         <f>F4-F8</f>
         <v>286475</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B12" s="24">
+        <v>249</v>
+      </c>
+      <c r="B12" s="28">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="28">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.40551379</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="28">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.50429993</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="28">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.55787178</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="28">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.55787178</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B13" s="25">
+        <v>250</v>
+      </c>
+      <c r="B13" s="29">
         <v>25233</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="29">
         <v>163025</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="29">
         <v>378153</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="29">
         <v>656284</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="29">
         <v>942758</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="25">
+        <v>217</v>
+      </c>
+      <c r="B14" s="29">
         <v>15389</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="29">
         <v>18878</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="29">
         <v>19390</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="29">
         <v>19942</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="29">
         <v>20541</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B15" s="25">
+        <v>251</v>
+      </c>
+      <c r="B15" s="29">
         <v>13286</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="29">
         <v>11222</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="29">
         <v>9612</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="29">
         <v>8817</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="29">
         <v>9082</v>
       </c>
     </row>
@@ -3390,501 +3550,501 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="H2" s="15" t="s">
+      <c r="A2" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="C2" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="D2" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="E2" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="F2" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="G2" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="H2" s="19" t="s">
         <v>259</v>
       </c>
+      <c r="I2" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
+      <c r="A3" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="30">
+        <v>232</v>
+      </c>
+      <c r="B4" s="34">
         <v>9150</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="34">
         <v>22110</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="34">
         <v>22110</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="34">
         <v>22110</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="34">
         <v>22110</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="34">
         <v>22110</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="34">
         <v>22110</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="34">
         <v>22110</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="34">
         <v>22110</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="34">
         <v>22110</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="34">
         <v>13210</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="34">
         <v>250</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="34">
         <f>SUM(B4:M4)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
+      <c r="A6" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" s="25">
+        <v>267</v>
+      </c>
+      <c r="B7" s="29">
         <v>11893</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="29">
         <v>11893</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>11893</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <v>11893</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <v>11893</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="29">
         <v>11893</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="29">
         <v>11893</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="29">
         <v>11893</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="29">
         <v>11893</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="29">
         <v>11893</v>
       </c>
-      <c r="L7" s="25">
-        <v>0</v>
-      </c>
-      <c r="M7" s="25">
-        <v>0</v>
-      </c>
-      <c r="N7" s="25">
+      <c r="L7" s="29">
+        <v>0</v>
+      </c>
+      <c r="M7" s="29">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="25">
+        <v>268</v>
+      </c>
+      <c r="B8" s="29">
         <v>4050</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="29">
         <v>4050</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="29">
         <v>4050</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="29">
         <v>4050</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="29">
         <v>4050</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="29">
         <v>4050</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="29">
         <v>4050</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="29">
         <v>4050</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="29">
         <v>4050</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="29">
         <v>4050</v>
       </c>
-      <c r="L8" s="25">
-        <v>0</v>
-      </c>
-      <c r="M8" s="25">
-        <v>0</v>
-      </c>
-      <c r="N8" s="25">
+      <c r="L8" s="29">
+        <v>0</v>
+      </c>
+      <c r="M8" s="29">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="25">
-        <v>0</v>
-      </c>
-      <c r="C9" s="25">
-        <v>0</v>
-      </c>
-      <c r="D9" s="25">
-        <v>0</v>
-      </c>
-      <c r="E9" s="25">
-        <v>0</v>
-      </c>
-      <c r="F9" s="25">
-        <v>0</v>
-      </c>
-      <c r="G9" s="25">
-        <v>0</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0</v>
-      </c>
-      <c r="I9" s="25">
-        <v>0</v>
-      </c>
-      <c r="J9" s="25">
-        <v>0</v>
-      </c>
-      <c r="K9" s="25">
-        <v>0</v>
-      </c>
-      <c r="L9" s="25">
-        <v>0</v>
-      </c>
-      <c r="M9" s="25">
-        <v>0</v>
-      </c>
-      <c r="N9" s="25" t="str">
+        <v>269</v>
+      </c>
+      <c r="B9" s="29">
+        <v>0</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29">
+        <v>0</v>
+      </c>
+      <c r="G9" s="29">
+        <v>0</v>
+      </c>
+      <c r="H9" s="29">
+        <v>0</v>
+      </c>
+      <c r="I9" s="29">
+        <v>0</v>
+      </c>
+      <c r="J9" s="29">
+        <v>0</v>
+      </c>
+      <c r="K9" s="29">
+        <v>0</v>
+      </c>
+      <c r="L9" s="29">
+        <v>0</v>
+      </c>
+      <c r="M9" s="29">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29" t="str">
         <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
+      <c r="A11" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B12" s="28">
+        <v>246</v>
+      </c>
+      <c r="B12" s="32">
         <f>B7+B8+B9</f>
         <v>15943</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="32">
         <f>C7+C8+C9</f>
         <v>15943</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="32">
         <f>D7+D8+D9</f>
         <v>15943</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="32">
         <f>E7+E8+E9</f>
         <v>15943</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="32">
         <f>F7+F8+F9</f>
         <v>15943</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="32">
         <f>G7+G8+G9</f>
         <v>15943</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="32">
         <f>H7+H8+H9</f>
         <v>15943</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="32">
         <f>I7+I8+I9</f>
         <v>15943</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="32">
         <f>J7+J8+J9</f>
         <v>15943</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="32">
         <f>K7+K8+K9</f>
         <v>15943</v>
       </c>
-      <c r="L12" s="28" t="str">
+      <c r="L12" s="32" t="str">
         <f>L7+L8+L9</f>
         <v>0</v>
       </c>
-      <c r="M12" s="28" t="str">
+      <c r="M12" s="32" t="str">
         <f>M7+M8+M9</f>
         <v>0</v>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="32">
         <f>SUM(B12:M12)</f>
         <v>159430</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B13" s="28">
+        <v>271</v>
+      </c>
+      <c r="B13" s="32">
         <f>B4-B12</f>
         <v>-6793</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="32">
         <f>C4-C12</f>
         <v>6167</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="32">
         <f>D4-D12</f>
         <v>6167</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="32">
         <f>E4-E12</f>
         <v>6167</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="32">
         <f>F4-F12</f>
         <v>6167</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="32">
         <f>G4-G12</f>
         <v>6167</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="32">
         <f>H4-H12</f>
         <v>6167</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="32">
         <f>I4-I12</f>
         <v>6167</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="32">
         <f>J4-J12</f>
         <v>6167</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="32">
         <f>K4-K12</f>
         <v>6167</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="32">
         <f>L4-L12</f>
         <v>13210</v>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="32">
         <f>M4-M12</f>
         <v>250</v>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="32">
         <f>SUM(B13:M13)</f>
         <v>62170</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B14" s="33">
+        <v>272</v>
+      </c>
+      <c r="B14" s="37">
         <f>B17+B13</f>
         <v>-6793</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="37">
         <f>B14+C13</f>
         <v>-626</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="37">
         <f>C14+D13</f>
         <v>5541</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="37">
         <f>D14+E13</f>
         <v>11708</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="37">
         <f>E14+F13</f>
         <v>17875</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="37">
         <f>F14+G13</f>
         <v>24042</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="37">
         <f>G14+H13</f>
         <v>30209</v>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="37">
         <f>H14+I13</f>
         <v>36376</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="37">
         <f>I14+J13</f>
         <v>42543</v>
       </c>
-      <c r="K14" s="33">
+      <c r="K14" s="37">
         <f>J14+K13</f>
         <v>48710</v>
       </c>
-      <c r="L14" s="33">
+      <c r="L14" s="37">
         <f>K14+L13</f>
         <v>61920</v>
       </c>
-      <c r="M14" s="33">
+      <c r="M14" s="37">
         <f>L14+M13</f>
         <v>62170</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="30">
         <f>M14</f>
         <v>62170</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="A16" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B17" s="17">
+        <v>162</v>
+      </c>
+      <c r="B17" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B18" s="33">
+        <v>274</v>
+      </c>
+      <c r="B18" s="37">
         <f>M14</f>
         <v>62170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" s="25">
+        <v>275</v>
+      </c>
+      <c r="B19" s="29">
         <f>MIN(B14:M14)</f>
         <v>-6793</v>
       </c>
@@ -3914,216 +4074,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="30">
+      <c r="A5" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="34">
         <v>184667</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="34">
         <v>339797</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="34">
         <v>426588</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="34">
         <v>498557</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="34">
         <v>513513</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="A7" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B8" s="28">
+        <v>267</v>
+      </c>
+      <c r="B8" s="32">
         <v>118934</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="32">
         <v>147003</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="32">
         <v>151413</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="32">
         <v>155955</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="32">
         <v>160634</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B9" s="28">
+        <v>268</v>
+      </c>
+      <c r="B9" s="32">
         <v>40500</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="32">
         <v>55002</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="32">
         <v>60047</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="32">
         <v>64471</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="32">
         <v>66405</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10" s="28">
-        <v>0</v>
-      </c>
-      <c r="C10" s="28">
-        <v>0</v>
-      </c>
-      <c r="D10" s="28">
-        <v>0</v>
-      </c>
-      <c r="E10" s="28">
-        <v>0</v>
-      </c>
-      <c r="F10" s="28">
+        <v>277</v>
+      </c>
+      <c r="B10" s="32">
+        <v>0</v>
+      </c>
+      <c r="C10" s="32">
+        <v>0</v>
+      </c>
+      <c r="D10" s="32">
+        <v>0</v>
+      </c>
+      <c r="E10" s="32">
+        <v>0</v>
+      </c>
+      <c r="F10" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="B11" s="30">
+      <c r="A11" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="34">
         <f>SUM(B8:B10)</f>
         <v>159434</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="34">
         <f>SUM(C8:C10)</f>
         <v>202005</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="34">
         <f>SUM(D8:D10)</f>
         <v>211460</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="34">
         <f>SUM(E8:E10)</f>
         <v>220426</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="34">
         <f>SUM(F8:F10)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="A13" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="B14" s="26">
+      <c r="A14" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="30">
         <f>B5-B11</f>
         <v>25233</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="30">
         <f>C5-C11</f>
         <v>137792</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="30">
         <f>D5-D11</f>
         <v>215128</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="30">
         <f>E5-E11</f>
         <v>278131</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="30">
         <f>F5-F11</f>
         <v>286475</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B15" s="24">
+        <v>249</v>
+      </c>
+      <c r="B15" s="28">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="28">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.40551379</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="28">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.50429993</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="28">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.55787178</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="28">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.55787178</v>
       </c>
@@ -4153,60 +4313,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>276</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>206</v>
+      <c r="A5" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>282</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -4234,286 +4394,286 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B5" s="38">
+        <v>285</v>
+      </c>
+      <c r="B5" s="42">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>62170</v>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="42">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>199962</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="42">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>415091</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="42">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>693221</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="42">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>979696</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" s="25">
-        <v>0</v>
-      </c>
-      <c r="C6" s="25">
-        <v>0</v>
-      </c>
-      <c r="D6" s="25">
-        <v>0</v>
-      </c>
-      <c r="E6" s="25">
-        <v>0</v>
-      </c>
-      <c r="F6" s="25">
+        <v>286</v>
+      </c>
+      <c r="B6" s="29">
+        <v>0</v>
+      </c>
+      <c r="C6" s="29">
+        <v>0</v>
+      </c>
+      <c r="D6" s="29">
+        <v>0</v>
+      </c>
+      <c r="E6" s="29">
+        <v>0</v>
+      </c>
+      <c r="F6" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B7" s="25">
+        <v>287</v>
+      </c>
+      <c r="B7" s="29">
         <v>5000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="29">
         <v>5000</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>5000</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <v>5000</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <v>5000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B8" s="25">
-        <v>0</v>
-      </c>
-      <c r="C8" s="25">
-        <v>0</v>
-      </c>
-      <c r="D8" s="25">
-        <v>0</v>
-      </c>
-      <c r="E8" s="25">
-        <v>0</v>
-      </c>
-      <c r="F8" s="25">
+        <v>288</v>
+      </c>
+      <c r="B8" s="29">
+        <v>0</v>
+      </c>
+      <c r="C8" s="29">
+        <v>0</v>
+      </c>
+      <c r="D8" s="29">
+        <v>0</v>
+      </c>
+      <c r="E8" s="29">
+        <v>0</v>
+      </c>
+      <c r="F8" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B9" s="30">
+        <v>289</v>
+      </c>
+      <c r="B9" s="34">
         <f>SUM(B5:B8)</f>
         <v>67170</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="34">
         <f>SUM(C5:C8)</f>
         <v>204962</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="34">
         <f>SUM(D5:D8)</f>
         <v>420091</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="34">
         <f>SUM(E5:E8)</f>
         <v>698221</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="34">
         <f>SUM(F5:F8)</f>
         <v>984696</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="A11" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B12" s="25">
-        <v>0</v>
-      </c>
-      <c r="C12" s="25">
-        <v>0</v>
-      </c>
-      <c r="D12" s="25">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25">
-        <v>0</v>
-      </c>
-      <c r="F12" s="25">
+        <v>291</v>
+      </c>
+      <c r="B12" s="29">
+        <v>0</v>
+      </c>
+      <c r="C12" s="29">
+        <v>0</v>
+      </c>
+      <c r="D12" s="29">
+        <v>0</v>
+      </c>
+      <c r="E12" s="29">
+        <v>0</v>
+      </c>
+      <c r="F12" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B13" s="25">
-        <v>0</v>
-      </c>
-      <c r="C13" s="25">
-        <v>0</v>
-      </c>
-      <c r="D13" s="25">
-        <v>0</v>
-      </c>
-      <c r="E13" s="25">
-        <v>0</v>
-      </c>
-      <c r="F13" s="25">
+        <v>292</v>
+      </c>
+      <c r="B13" s="29">
+        <v>0</v>
+      </c>
+      <c r="C13" s="29">
+        <v>0</v>
+      </c>
+      <c r="D13" s="29">
+        <v>0</v>
+      </c>
+      <c r="E13" s="29">
+        <v>0</v>
+      </c>
+      <c r="F13" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B14" s="30" t="str">
+        <v>293</v>
+      </c>
+      <c r="B14" s="34" t="str">
         <f>SUM(B12:B13)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="30" t="str">
+      <c r="C14" s="34" t="str">
         <f>SUM(C12:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="30" t="str">
+      <c r="D14" s="34" t="str">
         <f>SUM(D12:D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="30" t="str">
+      <c r="E14" s="34" t="str">
         <f>SUM(E12:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="30" t="str">
+      <c r="F14" s="34" t="str">
         <f>SUM(F12:F13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="A16" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B17" s="26">
+        <v>295</v>
+      </c>
+      <c r="B17" s="30">
         <f>B9-B14</f>
         <v>67170</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="30">
         <f>C9-C14</f>
         <v>204962</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="30">
         <f>D9-D14</f>
         <v>420091</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="30">
         <f>E9-E14</f>
         <v>698221</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="30">
         <f>F9-F14</f>
         <v>984696</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B19" s="39" t="str">
+        <v>296</v>
+      </c>
+      <c r="B19" s="43" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="39" t="str">
+      <c r="C19" s="43" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="39" t="str">
+      <c r="D19" s="43" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="39" t="str">
+      <c r="E19" s="43" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="39" t="str">
+      <c r="F19" s="43" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -4543,468 +4703,468 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B5" s="25">
+        <v>299</v>
+      </c>
+      <c r="B5" s="29">
         <v>184667</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="29">
         <v>339797</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="29">
         <v>426588</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="29">
         <v>498557</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="29">
         <v>513513</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="25">
+        <v>267</v>
+      </c>
+      <c r="B6" s="29">
         <v>118934</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="29">
         <v>147003</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <v>151413</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="29">
         <v>155955</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="29">
         <v>160634</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B7" s="25">
+        <v>268</v>
+      </c>
+      <c r="B7" s="29">
         <v>40500</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="29">
         <v>55002</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>60047</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <v>64471</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <v>66405</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B8" s="28">
+        <v>300</v>
+      </c>
+      <c r="B8" s="32">
         <f>B5-B6-B7</f>
         <v>25233</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="32">
         <f>C5-C6-C7</f>
         <v>137792</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="32">
         <f>D5-D6-D7</f>
         <v>215128</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="32">
         <f>E5-E6-E7</f>
         <v>278131</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="32">
         <f>F5-F6-F7</f>
         <v>286475</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="25">
-        <v>0</v>
-      </c>
-      <c r="C9" s="25">
-        <v>0</v>
-      </c>
-      <c r="D9" s="25">
-        <v>0</v>
-      </c>
-      <c r="E9" s="25">
-        <v>0</v>
-      </c>
-      <c r="F9" s="25">
+        <v>269</v>
+      </c>
+      <c r="B9" s="29">
+        <v>0</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>296</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>296</v>
-      </c>
-      <c r="D10" s="40" t="s">
-        <v>296</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>296</v>
-      </c>
-      <c r="F10" s="40" t="s">
-        <v>296</v>
+        <v>301</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B13" s="25">
+        <v>304</v>
+      </c>
+      <c r="B13" s="29">
         <v>62170</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="29">
         <v>199962</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="29">
         <v>415091</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="29">
         <v>693221</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="29">
         <v>979696</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B14" s="22">
+        <v>305</v>
+      </c>
+      <c r="B14" s="26">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>142</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="26">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>361</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="26">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>716</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="26">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>1148</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="26">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>1575</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B15" s="29">
+        <v>306</v>
+      </c>
+      <c r="B15" s="33">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>4.7</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="33">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>11.9</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="33">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>23.6</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="33">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>37.7</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="33">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>51.8</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B16" s="24">
+        <v>182</v>
+      </c>
+      <c r="B16" s="28">
         <v>0.48</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="28">
         <v>0.72</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="28">
         <v>0.88</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="28">
         <v>1</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="A18" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B19" s="25">
+        <v>217</v>
+      </c>
+      <c r="B19" s="29">
         <v>15389</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="29">
         <v>18878</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="29">
         <v>19390</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="29">
         <v>19942</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="29">
         <v>20541</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B20" s="25">
+        <v>308</v>
+      </c>
+      <c r="B20" s="29">
         <v>118934</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="29">
         <v>147003</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="29">
         <v>151413</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="29">
         <v>155955</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="29">
         <v>160634</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B21" s="25">
+        <v>309</v>
+      </c>
+      <c r="B21" s="29">
         <v>3375</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="29">
         <v>3056</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="29">
         <v>2729</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="29">
         <v>2579</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="29">
         <v>2656</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B22" s="41">
+        <v>310</v>
+      </c>
+      <c r="B22" s="45">
         <v>10</v>
       </c>
-      <c r="C22" s="41">
+      <c r="C22" s="45">
         <v>10</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="45">
         <v>10</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="45">
         <v>9</v>
       </c>
-      <c r="F22" s="41">
+      <c r="F22" s="45">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="A24" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="F25" s="42" t="s">
-        <v>296</v>
+        <v>312</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B26" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="C26" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="E26" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="F26" s="43" t="s">
-        <v>308</v>
+        <v>313</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="D26" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B27" s="44" t="s">
-        <v>310</v>
-      </c>
-      <c r="C27" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="E27" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="F27" s="43" t="s">
-        <v>308</v>
+        <v>315</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>316</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="D27" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B28" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D28" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="E28" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="F28" s="43" t="s">
-        <v>308</v>
+        <v>317</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="F28" s="47" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B29" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="C29" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="E29" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="F29" s="43" t="s">
-        <v>308</v>
+        <v>318</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="D29" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="F29" s="47" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -5035,69 +5195,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
-        <v>313</v>
-      </c>
-      <c r="B3" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>314</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>105</v>
+      <c r="A3" s="49" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>320</v>
+      </c>
+      <c r="E3" s="49" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B4" s="25">
+        <v>321</v>
+      </c>
+      <c r="B4" s="29">
         <v>20000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E4" s="25">
+        <v>322</v>
+      </c>
+      <c r="E4" s="29">
         <v>15000</v>
       </c>
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="E5" s="25">
+        <v>323</v>
+      </c>
+      <c r="E5" s="29">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B7" s="26">
+        <v>324</v>
+      </c>
+      <c r="B7" s="30">
         <v>20000</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="E7" s="26">
+        <v>325</v>
+      </c>
+      <c r="E7" s="30">
         <v>20000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" s="39">
+        <v>326</v>
+      </c>
+      <c r="B8" s="43">
         <v>0</v>
       </c>
     </row>
@@ -5116,9 +5276,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B29"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5130,134 +5291,174 @@
         <v>64</v>
       </c>
     </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="6" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="12" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="6" t="s">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -5282,322 +5483,322 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
+      <c r="A3" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>323</v>
+      <c r="A4" s="16" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>99</v>
+      <c r="A5" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B6" s="25">
+        <v>299</v>
+      </c>
+      <c r="B6" s="29">
         <v>184667</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="29">
         <v>339797</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <v>426588</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="29">
         <v>498557</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="29">
         <v>513513</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" s="25">
+        <v>246</v>
+      </c>
+      <c r="B7" s="29">
         <v>159434</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="29">
         <v>202005</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>211460</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <v>220426</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <v>227039</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B8" s="26">
+        <v>248</v>
+      </c>
+      <c r="B8" s="30">
         <v>25233</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="30">
         <v>137792</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="30">
         <v>215128</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="30">
         <v>278131</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="30">
         <v>286475</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B9" s="24">
+        <v>249</v>
+      </c>
+      <c r="B9" s="28">
         <v>0.13663808664259927</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="28">
         <v>0.40551379205819943</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="28">
         <v>0.5042999253916937</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="28">
         <v>0.5578717808219178</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="28">
         <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="F10" s="46" t="s">
-        <v>296</v>
+        <v>301</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B11" s="22">
+        <v>310</v>
+      </c>
+      <c r="B11" s="26">
         <v>10</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="26">
         <v>10</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="26">
         <v>10</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="26">
         <v>9</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="26">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="A13" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>325</v>
+      <c r="A14" s="16" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>99</v>
+      <c r="A15" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B16" s="25">
+        <v>299</v>
+      </c>
+      <c r="B16" s="29">
         <v>147733</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="29">
         <v>271838</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="29">
         <v>341270</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="29">
         <v>398845</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="29">
         <v>410811</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B17" s="25">
+        <v>246</v>
+      </c>
+      <c r="B17" s="29">
         <v>159434</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="29">
         <v>202005</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="29">
         <v>211460</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="29">
         <v>220426</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="29">
         <v>227039</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B18" s="26">
+        <v>248</v>
+      </c>
+      <c r="B18" s="30">
         <v>-11701</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="30">
         <v>69833</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="30">
         <v>129811</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="30">
         <v>178419</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="30">
         <v>183772</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B19" s="24">
+        <v>249</v>
+      </c>
+      <c r="B19" s="28">
         <v>-0.07920239169675096</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="28">
         <v>0.2568922400727494</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="28">
         <v>0.38037490673961705</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="28">
         <v>0.4473397260273973</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="28">
         <v>0.44733972602739736</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="C20" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="D20" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="E20" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="F20" s="46" t="s">
-        <v>296</v>
+        <v>301</v>
+      </c>
+      <c r="B20" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B21" s="22">
+        <v>310</v>
+      </c>
+      <c r="B21" s="26">
         <v>12</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="26">
         <v>10</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="26">
         <v>10</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="26">
         <v>10</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="26">
         <v>10</v>
       </c>
     </row>
@@ -5628,22 +5829,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="13"/>
+      <c r="A3" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="17"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -5655,7 +5856,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -5663,7 +5864,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -5687,271 +5888,271 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
+      <c r="A11" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="H12" s="47" t="s">
-        <v>99</v>
+        <v>70</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="51" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D13" s="25">
+        <v>299</v>
+      </c>
+      <c r="D13" s="29">
         <v>184667</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="29">
         <v>339797</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="29">
         <v>426588</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="29">
         <v>498557</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="29">
         <v>513513</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D14" s="25">
+        <v>246</v>
+      </c>
+      <c r="D14" s="29">
         <v>159434</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="29">
         <v>202005</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="29">
         <v>211460</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="29">
         <v>220426</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="29">
         <v>227039</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D15" s="25">
+        <v>248</v>
+      </c>
+      <c r="D15" s="29">
         <v>25233</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="29">
         <v>137792</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="29">
         <v>215128</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="29">
         <v>278131</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="29">
         <v>286475</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="D16" s="25">
+        <v>336</v>
+      </c>
+      <c r="D16" s="29">
         <v>62170</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="29">
         <v>199962</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="29">
         <v>415091</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="29">
         <v>693221</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="29">
         <v>979696</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="D17" s="25">
-        <v>0</v>
-      </c>
-      <c r="E17" s="25">
-        <v>0</v>
-      </c>
-      <c r="F17" s="25">
-        <v>0</v>
-      </c>
-      <c r="G17" s="25">
-        <v>0</v>
-      </c>
-      <c r="H17" s="25">
+        <v>337</v>
+      </c>
+      <c r="D17" s="29">
+        <v>0</v>
+      </c>
+      <c r="E17" s="29">
+        <v>0</v>
+      </c>
+      <c r="F17" s="29">
+        <v>0</v>
+      </c>
+      <c r="G17" s="29">
+        <v>0</v>
+      </c>
+      <c r="H17" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="A19" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="47" t="s">
-        <v>99</v>
+        <v>70</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="51" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D21" s="24">
+        <v>339</v>
+      </c>
+      <c r="D21" s="28">
         <v>0.13663808664259927</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="28">
         <v>0.40551379205819943</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="28">
         <v>0.5042999253916937</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="28">
         <v>0.5578717808219178</v>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="28">
         <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D22" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="E22" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="F22" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="H22" s="46" t="s">
-        <v>296</v>
+        <v>301</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="H22" s="50" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D23" s="24">
+        <v>182</v>
+      </c>
+      <c r="D23" s="28">
         <v>0.48</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="28">
         <v>0.72</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="28">
         <v>0.88</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="28">
         <v>1</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D24" s="22">
+        <v>340</v>
+      </c>
+      <c r="D24" s="26">
         <v>12</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="26">
         <v>18</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="26">
         <v>22</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="26">
         <v>25</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="26">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -5977,6 +6178,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G32"/>
@@ -5990,7 +6192,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -5999,450 +6201,450 @@
       <c r="G2" s="9"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="48" t="s">
-        <v>337</v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
+      <c r="B3" s="52" t="s">
+        <v>343</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>339</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>340</v>
-      </c>
-      <c r="E5" s="49" t="s">
-        <v>341</v>
-      </c>
-      <c r="F5" s="49" t="s">
-        <v>342</v>
-      </c>
-      <c r="G5" s="49" t="s">
-        <v>343</v>
+      <c r="B5" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="C6" s="50">
+        <v>340</v>
+      </c>
+      <c r="C6" s="54">
         <v>12</v>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="54">
         <v>18</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="54">
         <v>22</v>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="54">
         <v>25</v>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="54">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="C7" s="51">
+        <v>299</v>
+      </c>
+      <c r="C7" s="55">
         <v>184666.6666666667</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="55">
         <v>339797</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="55">
         <v>426587.88999999996</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="55">
         <v>498556.69375000003</v>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="55">
         <v>513513.3945625001</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="C8" s="51">
+        <v>267</v>
+      </c>
+      <c r="C8" s="55">
         <v>118934.16666666667</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="55">
         <v>147002.63</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="55">
         <v>151412.7089</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="55">
         <v>155955.090167</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="55">
         <v>160633.74287201</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C9" s="51">
+        <v>268</v>
+      </c>
+      <c r="C9" s="55">
         <v>40500</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="55">
         <v>55002</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="55">
         <v>60046.93999999999</v>
       </c>
-      <c r="F9" s="51">
+      <c r="F9" s="55">
         <v>64470.893</v>
       </c>
-      <c r="G9" s="51">
+      <c r="G9" s="55">
         <v>66405.01979</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C10" s="51">
-        <v>0</v>
-      </c>
-      <c r="D10" s="51">
-        <v>0</v>
-      </c>
-      <c r="E10" s="51">
-        <v>0</v>
-      </c>
-      <c r="F10" s="51">
-        <v>0</v>
-      </c>
-      <c r="G10" s="51">
+        <v>269</v>
+      </c>
+      <c r="C10" s="55">
+        <v>0</v>
+      </c>
+      <c r="D10" s="55">
+        <v>0</v>
+      </c>
+      <c r="E10" s="55">
+        <v>0</v>
+      </c>
+      <c r="F10" s="55">
+        <v>0</v>
+      </c>
+      <c r="G10" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C11" s="52">
+        <v>248</v>
+      </c>
+      <c r="C11" s="56">
         <v>25232.5</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="56">
         <v>137792.37</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="56">
         <v>215128.24109999998</v>
       </c>
-      <c r="F11" s="52">
+      <c r="F11" s="56">
         <v>278130.71058300004</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11" s="56">
         <v>286474.6319004901</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C12" s="52">
+        <v>304</v>
+      </c>
+      <c r="C12" s="56">
         <v>62170</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="56">
         <v>199962.37</v>
       </c>
-      <c r="E12" s="52">
+      <c r="E12" s="56">
         <v>415090.6111</v>
       </c>
-      <c r="F12" s="52">
+      <c r="F12" s="56">
         <v>693221.3216830001</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12" s="56">
         <v>979695.9535834901</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C13" s="53">
+        <v>339</v>
+      </c>
+      <c r="C13" s="57">
         <v>0.13663808664259927</v>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="57">
         <v>0.40551379205819943</v>
       </c>
-      <c r="E13" s="53">
+      <c r="E13" s="57">
         <v>0.5042999253916937</v>
       </c>
-      <c r="F13" s="53">
+      <c r="F13" s="57">
         <v>0.5578717808219178</v>
       </c>
-      <c r="G13" s="53">
+      <c r="G13" s="57">
         <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C14" s="51">
+        <v>217</v>
+      </c>
+      <c r="C14" s="55">
         <v>15388.88888888889</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="55">
         <v>18877.61111111111</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="55">
         <v>19390.358636363635</v>
       </c>
-      <c r="F14" s="51">
+      <c r="F14" s="55">
         <v>19942.267750000003</v>
       </c>
-      <c r="G14" s="51">
+      <c r="G14" s="55">
         <v>20540.535782500006</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C15" s="54">
+        <v>350</v>
+      </c>
+      <c r="C15" s="58">
         <v>0.644047833935018</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="57">
         <v>0.4326189754471052</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="57">
         <v>0.3549390698831137</v>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="57">
         <v>0.3128131506849315</v>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="57">
         <v>0.3128131506849315</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C16" s="53">
+        <v>351</v>
+      </c>
+      <c r="C16" s="57">
         <v>0.06579422382671479</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="57">
         <v>0.048560169748408606</v>
       </c>
-      <c r="E16" s="53">
+      <c r="E16" s="57">
         <v>0.04222830141755781</v>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="57">
         <v>0.0387945205479452</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="57">
         <v>0.0387945205479452</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C17" s="53">
+        <v>352</v>
+      </c>
+      <c r="C17" s="57">
         <v>0.13663808664259935</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="57">
         <v>0.40551379205819943</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="57">
         <v>0.5042999253916934</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="57">
         <v>0.5578717808219178</v>
       </c>
-      <c r="G17" s="53">
+      <c r="G17" s="57">
         <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C18" s="55" t="s">
-        <v>296</v>
-      </c>
-      <c r="D18" s="55" t="s">
-        <v>296</v>
-      </c>
-      <c r="E18" s="55" t="s">
-        <v>296</v>
-      </c>
-      <c r="F18" s="55" t="s">
-        <v>296</v>
-      </c>
-      <c r="G18" s="55" t="s">
-        <v>296</v>
+        <v>301</v>
+      </c>
+      <c r="C18" s="59" t="s">
+        <v>302</v>
+      </c>
+      <c r="D18" s="59" t="s">
+        <v>302</v>
+      </c>
+      <c r="E18" s="59" t="s">
+        <v>302</v>
+      </c>
+      <c r="F18" s="59" t="s">
+        <v>302</v>
+      </c>
+      <c r="G18" s="59" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C19" s="56" t="s">
-        <v>339</v>
-      </c>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
+        <v>353</v>
+      </c>
+      <c r="C19" s="60" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C20" s="56" t="s">
-        <v>349</v>
-      </c>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
+        <v>354</v>
+      </c>
+      <c r="C20" s="60" t="s">
+        <v>355</v>
+      </c>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="G22" s="13"/>
+      <c r="B22" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="G22" s="17"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="35" t="s">
-        <v>354</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>355</v>
-      </c>
-      <c r="D23" s="58" t="s">
-        <v>356</v>
-      </c>
-      <c r="E23" s="58"/>
-      <c r="F23" s="59" t="s">
-        <v>357</v>
-      </c>
-      <c r="G23" s="59"/>
+      <c r="B23" s="39" t="s">
+        <v>360</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="D23" s="62" t="s">
+        <v>362</v>
+      </c>
+      <c r="E23" s="62"/>
+      <c r="F23" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="G23" s="63"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="35" t="s">
-        <v>358</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>355</v>
-      </c>
-      <c r="D24" s="58" t="s">
-        <v>359</v>
-      </c>
-      <c r="E24" s="58"/>
-      <c r="F24" s="59" t="s">
-        <v>360</v>
-      </c>
-      <c r="G24" s="59"/>
+      <c r="B24" s="39" t="s">
+        <v>364</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="D24" s="62" t="s">
+        <v>365</v>
+      </c>
+      <c r="E24" s="62"/>
+      <c r="F24" s="63" t="s">
+        <v>366</v>
+      </c>
+      <c r="G24" s="63"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="C25" s="61" t="s">
         <v>361</v>
       </c>
-      <c r="C25" s="57" t="s">
-        <v>355</v>
-      </c>
-      <c r="D25" s="58" t="s">
-        <v>362</v>
-      </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="59" t="s">
-        <v>363</v>
-      </c>
-      <c r="G25" s="59"/>
+      <c r="D25" s="62" t="s">
+        <v>368</v>
+      </c>
+      <c r="E25" s="62"/>
+      <c r="F25" s="63" t="s">
+        <v>369</v>
+      </c>
+      <c r="G25" s="63"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="35" t="s">
-        <v>364</v>
-      </c>
-      <c r="C26" s="57" t="s">
-        <v>355</v>
-      </c>
-      <c r="D26" s="58" t="s">
-        <v>365</v>
-      </c>
-      <c r="E26" s="58"/>
-      <c r="F26" s="59" t="s">
-        <v>366</v>
-      </c>
-      <c r="G26" s="59"/>
+      <c r="B26" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="C26" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="D26" s="62" t="s">
+        <v>371</v>
+      </c>
+      <c r="E26" s="62"/>
+      <c r="F26" s="63" t="s">
+        <v>372</v>
+      </c>
+      <c r="G26" s="63"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="35" t="s">
-        <v>367</v>
-      </c>
-      <c r="C27" s="57" t="s">
-        <v>355</v>
-      </c>
-      <c r="D27" s="58" t="s">
-        <v>368</v>
-      </c>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59" t="s">
-        <v>369</v>
-      </c>
-      <c r="G27" s="59"/>
+      <c r="B27" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>374</v>
+      </c>
+      <c r="E27" s="62"/>
+      <c r="F27" s="63" t="s">
+        <v>375</v>
+      </c>
+      <c r="G27" s="63"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="35" t="s">
-        <v>370</v>
-      </c>
-      <c r="C28" s="57" t="s">
-        <v>355</v>
-      </c>
-      <c r="D28" s="58" t="s">
-        <v>371</v>
-      </c>
-      <c r="E28" s="58"/>
-      <c r="F28" s="59" t="s">
-        <v>372</v>
-      </c>
-      <c r="G28" s="59"/>
+      <c r="B28" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="D28" s="62" t="s">
+        <v>377</v>
+      </c>
+      <c r="E28" s="62"/>
+      <c r="F28" s="63" t="s">
+        <v>378</v>
+      </c>
+      <c r="G28" s="63"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="35" t="s">
-        <v>373</v>
+      <c r="B30" s="39" t="s">
+        <v>379</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="60" t="s">
-        <v>375</v>
-      </c>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
+      <c r="B32" s="64" t="s">
+        <v>381</v>
+      </c>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -6467,6 +6669,72 @@
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="B32:G32"/>
   </mergeCells>
+  <conditionalFormatting sqref="C11:G11">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C11&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C11&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C11&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C13&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C13&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -6489,37 +6757,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>88</v>
+      <c r="A2" s="16" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="A4" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
     </row>
@@ -6527,7 +6795,7 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6535,7 +6803,7 @@
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="18" t="s">
         <v>7</v>
       </c>
     </row>
@@ -6543,23 +6811,23 @@
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>91</v>
+        <v>96</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="18" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6567,523 +6835,523 @@
       <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="18" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="14">
+        <v>98</v>
+      </c>
+      <c r="B12" s="18">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" s="14">
+        <v>99</v>
+      </c>
+      <c r="B13" s="18">
         <v>25</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
+      <c r="A15" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>99</v>
+      <c r="A16" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="16">
+        <v>106</v>
+      </c>
+      <c r="B17" s="20">
         <v>12</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="20">
         <v>18</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="20">
         <v>22</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="20">
         <v>25</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="20">
         <v>25</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+      <c r="A19" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>106</v>
+      <c r="A20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="17">
+        <v>115</v>
+      </c>
+      <c r="D21" s="21">
         <v>12000</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="17">
+        <v>115</v>
+      </c>
+      <c r="D22" s="21">
         <v>250</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="17">
+        <v>115</v>
+      </c>
+      <c r="D23" s="21">
         <v>7000</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" s="17">
+        <v>121</v>
+      </c>
+      <c r="D24" s="21">
         <v>5000</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="17">
+        <v>124</v>
+      </c>
+      <c r="D25" s="21">
         <v>10</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
+      <c r="A27" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>125</v>
+      <c r="A28" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" s="19">
+        <v>134</v>
+      </c>
+      <c r="D29" s="23">
         <v>1</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="21">
         <v>55000</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="22">
         <v>0.2</v>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="22">
         <v>0.0765</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="19">
+        <v>134</v>
+      </c>
+      <c r="D30" s="23">
         <v>1</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="21">
         <v>45000</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="22">
         <v>0.2</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="22">
         <v>0.0765</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" s="19">
+        <v>138</v>
+      </c>
+      <c r="D31" s="23">
         <v>0.5</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="21">
         <v>28000</v>
       </c>
-      <c r="F31" s="18">
-        <v>0</v>
-      </c>
-      <c r="G31" s="18">
+      <c r="F31" s="22">
+        <v>0</v>
+      </c>
+      <c r="G31" s="22">
         <v>0.0765</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
+      <c r="A33" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>106</v>
+      <c r="A34" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" s="17">
+        <v>142</v>
+      </c>
+      <c r="D35" s="21">
         <v>2500</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" s="17">
+        <v>142</v>
+      </c>
+      <c r="D36" s="21">
         <v>300</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" s="17">
+        <v>121</v>
+      </c>
+      <c r="D37" s="21">
         <v>2400</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D38" s="17">
+        <v>115</v>
+      </c>
+      <c r="D38" s="21">
         <v>500</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" s="17">
+        <v>115</v>
+      </c>
+      <c r="D39" s="21">
         <v>300</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" s="17">
+        <v>121</v>
+      </c>
+      <c r="D40" s="21">
         <v>3000</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
+      <c r="A42" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>147</v>
+      <c r="A43" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" s="17">
+        <v>155</v>
+      </c>
+      <c r="C44" s="21">
         <v>30000</v>
       </c>
-      <c r="D44" s="18">
+      <c r="D44" s="22">
         <v>0.06</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
+      <c r="A46" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B47" s="18">
+        <v>157</v>
+      </c>
+      <c r="B47" s="22">
         <v>0.03</v>
       </c>
-      <c r="C47" s="20" t="s">
-        <v>152</v>
+      <c r="C47" s="24" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B48" s="18">
+        <v>159</v>
+      </c>
+      <c r="B48" s="22">
         <v>0.03</v>
       </c>
-      <c r="C48" s="20" t="s">
-        <v>154</v>
+      <c r="C48" s="24" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B49" s="19">
+        <v>161</v>
+      </c>
+      <c r="B49" s="23">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B50" s="17">
+        <v>162</v>
+      </c>
+      <c r="B50" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>158</v>
+        <v>163</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -7111,17 +7379,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="15"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7142,10 +7410,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7158,7 +7426,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7166,66 +7434,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -7253,111 +7521,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="A5" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="21">
+        <v>106</v>
+      </c>
+      <c r="B6" s="25">
         <v>12</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="25">
         <v>18</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="25">
         <v>22</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="25">
         <v>25</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="25">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="22">
+        <v>99</v>
+      </c>
+      <c r="B7" s="26">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B8" s="23">
+        <v>182</v>
+      </c>
+      <c r="B8" s="27">
         <v>0.48</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="27">
         <v>0.72</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="27">
         <v>0.88</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="27">
         <v>1</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" s="24">
+        <v>184</v>
+      </c>
+      <c r="C10" s="28">
         <v>0.5</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="28">
         <v>0.2222222222222222</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="28">
         <v>0.13636363636363635</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="28">
         <v>0</v>
       </c>
     </row>
@@ -7386,166 +7654,166 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="25">
+        <v>187</v>
+      </c>
+      <c r="B5" s="29">
         <v>144000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="29">
         <v>222480</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="29">
         <v>280078</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="29">
         <v>327818</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="29">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" s="25">
+        <v>188</v>
+      </c>
+      <c r="B6" s="29">
         <v>3000</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="29">
         <v>4635</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <v>5835</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="29">
         <v>6830</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="29">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B7" s="25">
+        <v>189</v>
+      </c>
+      <c r="B7" s="29">
         <v>84000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="29">
         <v>129780</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>163379</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <v>191227</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <v>196964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B8" s="25">
+        <v>190</v>
+      </c>
+      <c r="B8" s="29">
         <v>5000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="29">
         <v>5150</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="29">
         <v>5305</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="29">
         <v>5464</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="29">
         <v>5628</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B9" s="25">
+        <v>191</v>
+      </c>
+      <c r="B9" s="29">
         <v>-10</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="29">
         <v>-10</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="29">
         <v>-11</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="29">
         <v>-11</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="29">
         <v>-11</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="A10" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="30">
         <f>SUM(B5:B9)</f>
         <v>221600</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="30">
         <f>SUM(C5:C9)</f>
         <v>339797</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="30">
         <f>SUM(D5:D9)</f>
         <v>426588</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="30">
         <f>SUM(E5:E9)</f>
         <v>498557</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="30">
         <f>SUM(F5:F9)</f>
         <v>513513</v>
       </c>
@@ -7579,196 +7847,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>188</v>
+      <c r="A3" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="27">
+        <v>133</v>
+      </c>
+      <c r="C4" s="31">
         <v>1</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="29">
         <v>55000</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="28">
         <v>0.2</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="28">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="32">
         <v>70208</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="27">
+        <v>136</v>
+      </c>
+      <c r="C5" s="31">
         <v>1</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="29">
         <v>45000</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="28">
         <v>0.2</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="28">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="32">
         <v>57443</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="27">
+        <v>136</v>
+      </c>
+      <c r="C6" s="31">
         <v>0.5</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <v>28000</v>
       </c>
-      <c r="E6" s="24">
-        <v>0</v>
-      </c>
-      <c r="F6" s="24">
+      <c r="E6" s="28">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="32">
         <v>15071</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="A8" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>99</v>
+      <c r="A9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B10" s="26">
+        <v>196</v>
+      </c>
+      <c r="B10" s="30">
         <v>118934</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="30">
         <v>147003</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="30">
         <v>151413</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="30">
         <v>155955</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="30">
         <v>160634</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="24">
+        <v>197</v>
+      </c>
+      <c r="B11" s="28">
         <v>0.5367065282791817</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="28">
         <v>0.4326189754471052</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="28">
         <v>0.3549390698831137</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="28">
         <v>0.3128131506849315</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="28">
         <v>0.3128131506849315</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="29">
+        <v>198</v>
+      </c>
+      <c r="B12" s="33">
         <v>4.8</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="33">
         <v>7.2</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <v>8.8</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="33">
         <v>10</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="33">
         <v>10</v>
       </c>
     </row>
@@ -7797,316 +8065,316 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>99</v>
+      <c r="A3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B5" s="25">
+        <v>200</v>
+      </c>
+      <c r="B5" s="29">
         <v>6000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="29">
         <v>9270</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="29">
         <v>11670</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="29">
         <v>13659</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="29">
         <v>14069</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B6" s="30">
+        <v>201</v>
+      </c>
+      <c r="B6" s="34">
         <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="34">
         <f>SUM(C5:C5)</f>
         <v>9270</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="34">
         <f>SUM(D5:D5)</f>
         <v>11670</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="34">
         <f>SUM(E5:E5)</f>
         <v>13659</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="34">
         <f>SUM(F5:F5)</f>
         <v>14069</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="A7" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B8" s="25">
+        <v>202</v>
+      </c>
+      <c r="B8" s="29">
         <v>3600</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="29">
         <v>5562</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="29">
         <v>7002</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="29">
         <v>8195</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="29">
         <v>8441</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B9" s="30">
+        <v>203</v>
+      </c>
+      <c r="B9" s="34">
         <f>SUM(B8:B8)</f>
         <v>3600</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="34">
         <f>SUM(C8:C8)</f>
         <v>5562</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="34">
         <f>SUM(D8:D8)</f>
         <v>7002</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="34">
         <f>SUM(E8:E8)</f>
         <v>8195</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="34">
         <f>SUM(F8:F8)</f>
         <v>8441</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="A10" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B11" s="25">
+        <v>204</v>
+      </c>
+      <c r="B11" s="29">
         <v>30000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="29">
         <v>30900</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="29">
         <v>31827</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="29">
         <v>32782</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="29">
         <v>33765</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="25">
+        <v>205</v>
+      </c>
+      <c r="B12" s="29">
         <v>3600</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="29">
         <v>3708</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="29">
         <v>3819</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="29">
         <v>3934</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="29">
         <v>4052</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="25">
+        <v>206</v>
+      </c>
+      <c r="B13" s="29">
         <v>2400</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="29">
         <v>2472</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="29">
         <v>2546</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="29">
         <v>2623</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="29">
         <v>2701</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="30">
+        <v>207</v>
+      </c>
+      <c r="B14" s="34">
         <f>SUM(B11:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="34">
         <f>SUM(C11:C13)</f>
         <v>37080</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="34">
         <f>SUM(D11:D13)</f>
         <v>38192</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="34">
         <f>SUM(E11:E13)</f>
         <v>39338</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="34">
         <f>SUM(F11:F13)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="A15" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B16" s="25">
+        <v>208</v>
+      </c>
+      <c r="B16" s="29">
         <v>3000</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="29">
         <v>3090</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="29">
         <v>3183</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="29">
         <v>3278</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="29">
         <v>3377</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B17" s="30">
+        <v>209</v>
+      </c>
+      <c r="B17" s="34">
         <f>SUM(B16:B16)</f>
         <v>3000</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="34">
         <f>SUM(C16:C16)</f>
         <v>3090</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="34">
         <f>SUM(D16:D16)</f>
         <v>3183</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="34">
         <f>SUM(E16:E16)</f>
         <v>3278</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="34">
         <f>SUM(F16:F16)</f>
         <v>3377</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="B19" s="26">
+      <c r="A19" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B19" s="30">
         <f>B6+B9+B14+B17</f>
         <v>48600</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="30">
         <f>C6+C9+C14+C17</f>
         <v>55002</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="30">
         <f>D6+D9+D14+D17</f>
         <v>60047</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="30">
         <f>E6+E9+E14+E17</f>
         <v>64471</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="30">
         <f>F6+F9+F14+F17</f>
         <v>66405</v>
       </c>
@@ -8137,68 +8405,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>206</v>
+      <c r="A3" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="17">
+        <v>155</v>
+      </c>
+      <c r="C4" s="21">
         <v>30000</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="28">
         <v>0.06</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="26">
         <v>5</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="32">
         <v>6960</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F6" s="26">
+        <v>213</v>
+      </c>
+      <c r="F6" s="30">
         <v>6960</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F7" s="30">
+        <v>214</v>
+      </c>
+      <c r="F7" s="34">
         <v>30000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -4,8 +4,8 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Cover" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Cover" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Assumptions" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Program Profile" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Enrollment Drivers" state="visible" r:id="rId8"/>
@@ -34,6 +34,96 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="382">
   <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Bright Horizons Microschool</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026 · llc_single</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Tabs 5-9: Drivers &amp; inputs</t>
+  </si>
+  <si>
+    <t>Tabs 10-13: Forecasts &amp; budgets</t>
+  </si>
+  <si>
+    <t>Tabs 14-17: Financial statements</t>
+  </si>
+  <si>
+    <t>Tabs 18-22: Analysis, underwriting &amp; dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
     <t>SchoolStack Budget</t>
   </si>
   <si>
@@ -43,9 +133,6 @@
     <t>School Name</t>
   </si>
   <si>
-    <t>Bright Horizons Microschool</t>
-  </si>
-  <si>
     <t>School Type</t>
   </si>
   <si>
@@ -94,15 +181,15 @@
     <t>1.</t>
   </si>
   <si>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <t>2.</t>
+  </si>
+  <si>
     <t>Cover</t>
   </si>
   <si>
-    <t>2.</t>
-  </si>
-  <si>
-    <t>Instructions</t>
-  </si>
-  <si>
     <t>3.</t>
   </si>
   <si>
@@ -224,93 +311,6 @@
   </si>
   <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
-  </si>
-  <si>
-    <t>How to Use This Workbook</t>
-  </si>
-  <si>
-    <t>Generated March 26, 2026 · llc_single</t>
-  </si>
-  <si>
-    <t>Cell Color Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>Tabs 5-9: Drivers &amp; inputs</t>
-  </si>
-  <si>
-    <t>Tabs 10-13: Forecasts &amp; budgets</t>
-  </si>
-  <si>
-    <t>Tabs 14-17: Financial statements</t>
-  </si>
-  <si>
-    <t>Tabs 18-22: Analysis, underwriting &amp; dashboard</t>
-  </si>
-  <si>
-    <t>Debt Service Convention</t>
-  </si>
-  <si>
-    <t>operating expense on the Operating Statement. This is a standard</t>
-  </si>
-  <si>
-    <t>simplification used in school financial underwriting that ensures internal</t>
-  </si>
-  <si>
-    <t>consistency across all tabs.</t>
-  </si>
-  <si>
-    <t>Tips</t>
-  </si>
-  <si>
-    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
-  </si>
-  <si>
-    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
-  </si>
-  <si>
-    <t>Next Steps</t>
-  </si>
-  <si>
-    <t>2. Verify enrollment and revenue projections match your plan.</t>
-  </si>
-  <si>
-    <t>3. Check the Financial Health dashboard for risk signals.</t>
-  </si>
-  <si>
-    <t>4. Share this workbook with your lender or financial advisor.</t>
-  </si>
-  <si>
-    <t>5. Update inputs as your school's plan evolves.</t>
-  </si>
-  <si>
-    <t>Disclaimer</t>
-  </si>
-  <si>
-    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
-  </si>
-  <si>
-    <t>user-provided assumptions and should be independently verified.</t>
   </si>
   <si>
     <t>Bright Horizons Microschool - Assumptions</t>
@@ -1196,45 +1196,6 @@
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF328555"/>
-      <sz val="22"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="13"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF328555"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF999999"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1263,6 +1224,45 @@
     </font>
     <font>
       <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF328555"/>
+      <sz val="22"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="13"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF328555"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF999999"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1398,59 +1398,59 @@
   </cellStyleXfs>
   <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1461,37 +1461,37 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1967,6 +1967,3196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:B37"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="35">
+        <v>12</v>
+      </c>
+      <c r="C4" s="35">
+        <v>18</v>
+      </c>
+      <c r="D4" s="35">
+        <v>22</v>
+      </c>
+      <c r="E4" s="35">
+        <v>25</v>
+      </c>
+      <c r="F4" s="35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="29">
+        <v>144000</v>
+      </c>
+      <c r="C7" s="29">
+        <v>222480</v>
+      </c>
+      <c r="D7" s="29">
+        <v>280078</v>
+      </c>
+      <c r="E7" s="29">
+        <v>327818</v>
+      </c>
+      <c r="F7" s="29">
+        <v>337653</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="29">
+        <v>3000</v>
+      </c>
+      <c r="C8" s="29">
+        <v>4635</v>
+      </c>
+      <c r="D8" s="29">
+        <v>5835</v>
+      </c>
+      <c r="E8" s="29">
+        <v>6830</v>
+      </c>
+      <c r="F8" s="29">
+        <v>7034</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="29">
+        <v>84000</v>
+      </c>
+      <c r="C9" s="29">
+        <v>129780</v>
+      </c>
+      <c r="D9" s="29">
+        <v>163379</v>
+      </c>
+      <c r="E9" s="29">
+        <v>191227</v>
+      </c>
+      <c r="F9" s="29">
+        <v>196964</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="29">
+        <v>5000</v>
+      </c>
+      <c r="C10" s="29">
+        <v>5150</v>
+      </c>
+      <c r="D10" s="29">
+        <v>5305</v>
+      </c>
+      <c r="E10" s="29">
+        <v>5464</v>
+      </c>
+      <c r="F10" s="29">
+        <v>5628</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="29">
+        <v>-10</v>
+      </c>
+      <c r="C11" s="29">
+        <v>-10</v>
+      </c>
+      <c r="D11" s="29">
+        <v>-11</v>
+      </c>
+      <c r="E11" s="29">
+        <v>-11</v>
+      </c>
+      <c r="F11" s="29">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="30">
+        <f>SUM(B7:B11)</f>
+        <v>221600</v>
+      </c>
+      <c r="C12" s="30">
+        <f>SUM(C7:C11)</f>
+        <v>339797</v>
+      </c>
+      <c r="D12" s="30">
+        <f>SUM(D7:D11)</f>
+        <v>426588</v>
+      </c>
+      <c r="E12" s="30">
+        <f>SUM(E7:E11)</f>
+        <v>498557</v>
+      </c>
+      <c r="F12" s="30">
+        <f>SUM(F7:F11)</f>
+        <v>513513</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="29">
+        <v>18467</v>
+      </c>
+      <c r="C14" s="29">
+        <v>18878</v>
+      </c>
+      <c r="D14" s="29">
+        <v>19390</v>
+      </c>
+      <c r="E14" s="29">
+        <v>19942</v>
+      </c>
+      <c r="F14" s="29">
+        <v>20541</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="29">
+        <v>47869</v>
+      </c>
+      <c r="C5" s="29">
+        <v>59166</v>
+      </c>
+      <c r="D5" s="29">
+        <v>60941</v>
+      </c>
+      <c r="E5" s="29">
+        <v>62769</v>
+      </c>
+      <c r="F5" s="29">
+        <v>64652</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="29">
+        <v>12559</v>
+      </c>
+      <c r="C6" s="29">
+        <v>15523</v>
+      </c>
+      <c r="D6" s="29">
+        <v>15989</v>
+      </c>
+      <c r="E6" s="29">
+        <v>16468</v>
+      </c>
+      <c r="F6" s="29">
+        <v>16963</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" s="34">
+        <f>SUM(B5:B6)</f>
+        <v>60428</v>
+      </c>
+      <c r="C7" s="34">
+        <f>SUM(C5:C6)</f>
+        <v>74689</v>
+      </c>
+      <c r="D7" s="34">
+        <f>SUM(D5:D6)</f>
+        <v>76930</v>
+      </c>
+      <c r="E7" s="34">
+        <f>SUM(E5:E6)</f>
+        <v>79237</v>
+      </c>
+      <c r="F7" s="34">
+        <f>SUM(F5:F6)</f>
+        <v>81615</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="29">
+        <v>58506</v>
+      </c>
+      <c r="C9" s="29">
+        <v>72314</v>
+      </c>
+      <c r="D9" s="29">
+        <v>74483</v>
+      </c>
+      <c r="E9" s="29">
+        <v>76718</v>
+      </c>
+      <c r="F9" s="29">
+        <v>79019</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="34">
+        <f>SUM(B9:B9)</f>
+        <v>58506</v>
+      </c>
+      <c r="C10" s="34">
+        <f>SUM(C9:C9)</f>
+        <v>72314</v>
+      </c>
+      <c r="D10" s="34">
+        <f>SUM(D9:D9)</f>
+        <v>74483</v>
+      </c>
+      <c r="E10" s="34">
+        <f>SUM(E9:E9)</f>
+        <v>76718</v>
+      </c>
+      <c r="F10" s="34">
+        <f>SUM(F9:F9)</f>
+        <v>79019</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="30">
+        <f>B7+B10</f>
+        <v>118934</v>
+      </c>
+      <c r="C12" s="30">
+        <f>C7+C10</f>
+        <v>147003</v>
+      </c>
+      <c r="D12" s="30">
+        <f>D7+D10</f>
+        <v>151413</v>
+      </c>
+      <c r="E12" s="30">
+        <f>E7+E10</f>
+        <v>155955</v>
+      </c>
+      <c r="F12" s="30">
+        <f>F7+F10</f>
+        <v>160634</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="29">
+        <v>120000</v>
+      </c>
+      <c r="C5" s="29">
+        <v>222480</v>
+      </c>
+      <c r="D5" s="29">
+        <v>280078</v>
+      </c>
+      <c r="E5" s="29">
+        <v>327818</v>
+      </c>
+      <c r="F5" s="29">
+        <v>337653</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="29">
+        <v>2500</v>
+      </c>
+      <c r="C6" s="29">
+        <v>4635</v>
+      </c>
+      <c r="D6" s="29">
+        <v>5835</v>
+      </c>
+      <c r="E6" s="29">
+        <v>6830</v>
+      </c>
+      <c r="F6" s="29">
+        <v>7034</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="29">
+        <v>70000</v>
+      </c>
+      <c r="C7" s="29">
+        <v>129780</v>
+      </c>
+      <c r="D7" s="29">
+        <v>163379</v>
+      </c>
+      <c r="E7" s="29">
+        <v>191227</v>
+      </c>
+      <c r="F7" s="29">
+        <v>196964</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="29">
+        <v>4167</v>
+      </c>
+      <c r="C8" s="29">
+        <v>5150</v>
+      </c>
+      <c r="D8" s="29">
+        <v>5305</v>
+      </c>
+      <c r="E8" s="29">
+        <v>5464</v>
+      </c>
+      <c r="F8" s="29">
+        <v>5628</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="29">
+        <v>-8</v>
+      </c>
+      <c r="C9" s="29">
+        <v>-10</v>
+      </c>
+      <c r="D9" s="29">
+        <v>-11</v>
+      </c>
+      <c r="E9" s="29">
+        <v>-11</v>
+      </c>
+      <c r="F9" s="29">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="34">
+        <f>SUM(B5:B9)</f>
+        <v>184667</v>
+      </c>
+      <c r="C10" s="34">
+        <f>SUM(C5:C9)</f>
+        <v>339797</v>
+      </c>
+      <c r="D10" s="34">
+        <f>SUM(D5:D9)</f>
+        <v>426588</v>
+      </c>
+      <c r="E10" s="34">
+        <f>SUM(E5:E9)</f>
+        <v>498557</v>
+      </c>
+      <c r="F10" s="34">
+        <f>SUM(F5:F9)</f>
+        <v>513513</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="29">
+        <v>58506</v>
+      </c>
+      <c r="C13" s="29">
+        <v>72314</v>
+      </c>
+      <c r="D13" s="29">
+        <v>74483</v>
+      </c>
+      <c r="E13" s="29">
+        <v>76718</v>
+      </c>
+      <c r="F13" s="29">
+        <v>79019</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" s="29">
+        <v>47869</v>
+      </c>
+      <c r="C14" s="29">
+        <v>59166</v>
+      </c>
+      <c r="D14" s="29">
+        <v>60941</v>
+      </c>
+      <c r="E14" s="29">
+        <v>62769</v>
+      </c>
+      <c r="F14" s="29">
+        <v>64652</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="29">
+        <v>12559</v>
+      </c>
+      <c r="C15" s="29">
+        <v>15523</v>
+      </c>
+      <c r="D15" s="29">
+        <v>15989</v>
+      </c>
+      <c r="E15" s="29">
+        <v>16468</v>
+      </c>
+      <c r="F15" s="29">
+        <v>16963</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="34">
+        <f>SUM(B13:B15)</f>
+        <v>118934</v>
+      </c>
+      <c r="C16" s="34">
+        <f>SUM(C13:C15)</f>
+        <v>147003</v>
+      </c>
+      <c r="D16" s="34">
+        <f>SUM(D13:D15)</f>
+        <v>151413</v>
+      </c>
+      <c r="E16" s="34">
+        <f>SUM(E13:E15)</f>
+        <v>155955</v>
+      </c>
+      <c r="F16" s="34">
+        <f>SUM(F13:F15)</f>
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B20" s="29">
+        <v>5000</v>
+      </c>
+      <c r="C20" s="29">
+        <v>9270</v>
+      </c>
+      <c r="D20" s="29">
+        <v>11670</v>
+      </c>
+      <c r="E20" s="29">
+        <v>13659</v>
+      </c>
+      <c r="F20" s="29">
+        <v>14069</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B22" s="29">
+        <v>3000</v>
+      </c>
+      <c r="C22" s="29">
+        <v>5562</v>
+      </c>
+      <c r="D22" s="29">
+        <v>7002</v>
+      </c>
+      <c r="E22" s="29">
+        <v>8195</v>
+      </c>
+      <c r="F22" s="29">
+        <v>8441</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" s="29">
+        <v>25000</v>
+      </c>
+      <c r="C24" s="29">
+        <v>30900</v>
+      </c>
+      <c r="D24" s="29">
+        <v>31827</v>
+      </c>
+      <c r="E24" s="29">
+        <v>32782</v>
+      </c>
+      <c r="F24" s="29">
+        <v>33765</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B25" s="29">
+        <v>3000</v>
+      </c>
+      <c r="C25" s="29">
+        <v>3708</v>
+      </c>
+      <c r="D25" s="29">
+        <v>3819</v>
+      </c>
+      <c r="E25" s="29">
+        <v>3934</v>
+      </c>
+      <c r="F25" s="29">
+        <v>4052</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B26" s="29">
+        <v>2000</v>
+      </c>
+      <c r="C26" s="29">
+        <v>2472</v>
+      </c>
+      <c r="D26" s="29">
+        <v>2546</v>
+      </c>
+      <c r="E26" s="29">
+        <v>2623</v>
+      </c>
+      <c r="F26" s="29">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B27" s="34">
+        <f>SUM(B24:B26)</f>
+        <v>30000</v>
+      </c>
+      <c r="C27" s="34">
+        <f>SUM(C24:C26)</f>
+        <v>37080</v>
+      </c>
+      <c r="D27" s="34">
+        <f>SUM(D24:D26)</f>
+        <v>38192</v>
+      </c>
+      <c r="E27" s="34">
+        <f>SUM(E24:E26)</f>
+        <v>39338</v>
+      </c>
+      <c r="F27" s="34">
+        <f>SUM(F24:F26)</f>
+        <v>40518</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="36" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" s="29">
+        <v>2500</v>
+      </c>
+      <c r="C29" s="29">
+        <v>3090</v>
+      </c>
+      <c r="D29" s="29">
+        <v>3183</v>
+      </c>
+      <c r="E29" s="29">
+        <v>3278</v>
+      </c>
+      <c r="F29" s="29">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="34">
+        <f>B20+B22+B27+B29</f>
+        <v>40500</v>
+      </c>
+      <c r="C30" s="34">
+        <f>C20+C22+C27+C29</f>
+        <v>55002</v>
+      </c>
+      <c r="D30" s="34">
+        <f>D20+D22+D27+D29</f>
+        <v>60047</v>
+      </c>
+      <c r="E30" s="34">
+        <f>E20+E22+E27+E29</f>
+        <v>64471</v>
+      </c>
+      <c r="F30" s="34">
+        <f>F20+F22+F27+F29</f>
+        <v>66405</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="B33" s="34" t="str">
+        <f>SUM(B33:B32)</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="34" t="str">
+        <f>SUM(C33:C32)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="34" t="str">
+        <f>SUM(D33:D32)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="34" t="str">
+        <f>SUM(E33:E32)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="34" t="str">
+        <f>SUM(F33:F32)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="32">
+        <f>'Budget Detail'!B10</f>
+        <v>184667</v>
+      </c>
+      <c r="C4" s="32">
+        <f>'Budget Detail'!C10</f>
+        <v>339797</v>
+      </c>
+      <c r="D4" s="32">
+        <f>'Budget Detail'!D10</f>
+        <v>426588</v>
+      </c>
+      <c r="E4" s="32">
+        <f>'Budget Detail'!E10</f>
+        <v>498557</v>
+      </c>
+      <c r="F4" s="32">
+        <f>'Budget Detail'!F10</f>
+        <v>513513</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="32">
+        <f>'Budget Detail'!B16</f>
+        <v>118934</v>
+      </c>
+      <c r="C5" s="32">
+        <f>'Budget Detail'!C16</f>
+        <v>147003</v>
+      </c>
+      <c r="D5" s="32">
+        <f>'Budget Detail'!D16</f>
+        <v>151413</v>
+      </c>
+      <c r="E5" s="32">
+        <f>'Budget Detail'!E16</f>
+        <v>155955</v>
+      </c>
+      <c r="F5" s="32">
+        <f>'Budget Detail'!F16</f>
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="32">
+        <f>'Budget Detail'!B30</f>
+        <v>40500</v>
+      </c>
+      <c r="C6" s="32">
+        <f>'Budget Detail'!C30</f>
+        <v>55002</v>
+      </c>
+      <c r="D6" s="32">
+        <f>'Budget Detail'!D30</f>
+        <v>60047</v>
+      </c>
+      <c r="E6" s="32">
+        <f>'Budget Detail'!E30</f>
+        <v>64471</v>
+      </c>
+      <c r="F6" s="32">
+        <f>'Budget Detail'!F30</f>
+        <v>66405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="32" t="str">
+        <f>'Budget Detail'!B33</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="32" t="str">
+        <f>'Budget Detail'!C33</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="32" t="str">
+        <f>'Budget Detail'!D33</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="32" t="str">
+        <f>'Budget Detail'!E33</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="32" t="str">
+        <f>'Budget Detail'!F33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="34">
+        <f>SUM(B5:B7)</f>
+        <v>159434</v>
+      </c>
+      <c r="C8" s="34">
+        <f>SUM(C5:C7)</f>
+        <v>202005</v>
+      </c>
+      <c r="D8" s="34">
+        <f>SUM(D5:D7)</f>
+        <v>211460</v>
+      </c>
+      <c r="E8" s="34">
+        <f>SUM(E5:E7)</f>
+        <v>220426</v>
+      </c>
+      <c r="F8" s="34">
+        <f>SUM(F5:F7)</f>
+        <v>227039</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="30">
+        <f>B4-B8</f>
+        <v>25233</v>
+      </c>
+      <c r="C11" s="30">
+        <f>C4-C8</f>
+        <v>137792</v>
+      </c>
+      <c r="D11" s="30">
+        <f>D4-D8</f>
+        <v>215128</v>
+      </c>
+      <c r="E11" s="30">
+        <f>E4-E8</f>
+        <v>278131</v>
+      </c>
+      <c r="F11" s="30">
+        <f>F4-F8</f>
+        <v>286475</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="28">
+        <f>IF(B4=0,0,B11/B4)</f>
+        <v>0.13663809</v>
+      </c>
+      <c r="C12" s="28">
+        <f>IF(C4=0,0,C11/C4)</f>
+        <v>0.40551379</v>
+      </c>
+      <c r="D12" s="28">
+        <f>IF(D4=0,0,D11/D4)</f>
+        <v>0.50429993</v>
+      </c>
+      <c r="E12" s="28">
+        <f>IF(E4=0,0,E11/E4)</f>
+        <v>0.55787178</v>
+      </c>
+      <c r="F12" s="28">
+        <f>IF(F4=0,0,F11/F4)</f>
+        <v>0.55787178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="29">
+        <v>25233</v>
+      </c>
+      <c r="C13" s="29">
+        <v>163025</v>
+      </c>
+      <c r="D13" s="29">
+        <v>378153</v>
+      </c>
+      <c r="E13" s="29">
+        <v>656284</v>
+      </c>
+      <c r="F13" s="29">
+        <v>942758</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="29">
+        <v>15389</v>
+      </c>
+      <c r="C14" s="29">
+        <v>18878</v>
+      </c>
+      <c r="D14" s="29">
+        <v>19390</v>
+      </c>
+      <c r="E14" s="29">
+        <v>19942</v>
+      </c>
+      <c r="F14" s="29">
+        <v>20541</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B15" s="29">
+        <v>13286</v>
+      </c>
+      <c r="C15" s="29">
+        <v>11222</v>
+      </c>
+      <c r="D15" s="29">
+        <v>9612</v>
+      </c>
+      <c r="E15" s="29">
+        <v>8817</v>
+      </c>
+      <c r="F15" s="29">
+        <v>9082</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="34">
+        <v>9150</v>
+      </c>
+      <c r="C4" s="34">
+        <v>22110</v>
+      </c>
+      <c r="D4" s="34">
+        <v>22110</v>
+      </c>
+      <c r="E4" s="34">
+        <v>22110</v>
+      </c>
+      <c r="F4" s="34">
+        <v>22110</v>
+      </c>
+      <c r="G4" s="34">
+        <v>22110</v>
+      </c>
+      <c r="H4" s="34">
+        <v>22110</v>
+      </c>
+      <c r="I4" s="34">
+        <v>22110</v>
+      </c>
+      <c r="J4" s="34">
+        <v>22110</v>
+      </c>
+      <c r="K4" s="34">
+        <v>22110</v>
+      </c>
+      <c r="L4" s="34">
+        <v>13210</v>
+      </c>
+      <c r="M4" s="34">
+        <v>250</v>
+      </c>
+      <c r="N4" s="34">
+        <f>SUM(B4:M4)</f>
+        <v>221600</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="C7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="D7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="E7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="F7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="G7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="H7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="I7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="J7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="K7" s="29">
+        <v>11893</v>
+      </c>
+      <c r="L7" s="29">
+        <v>0</v>
+      </c>
+      <c r="M7" s="29">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
+        <f>SUM(B7:M7)</f>
+        <v>118934</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="C8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="D8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="E8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="F8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="G8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="H8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="I8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="J8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="K8" s="29">
+        <v>4050</v>
+      </c>
+      <c r="L8" s="29">
+        <v>0</v>
+      </c>
+      <c r="M8" s="29">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
+        <f>SUM(B8:M8)</f>
+        <v>40500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="29">
+        <v>0</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29">
+        <v>0</v>
+      </c>
+      <c r="G9" s="29">
+        <v>0</v>
+      </c>
+      <c r="H9" s="29">
+        <v>0</v>
+      </c>
+      <c r="I9" s="29">
+        <v>0</v>
+      </c>
+      <c r="J9" s="29">
+        <v>0</v>
+      </c>
+      <c r="K9" s="29">
+        <v>0</v>
+      </c>
+      <c r="L9" s="29">
+        <v>0</v>
+      </c>
+      <c r="M9" s="29">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29" t="str">
+        <f>SUM(B9:M9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B12" s="32">
+        <f>B7+B8+B9</f>
+        <v>15943</v>
+      </c>
+      <c r="C12" s="32">
+        <f>C7+C8+C9</f>
+        <v>15943</v>
+      </c>
+      <c r="D12" s="32">
+        <f>D7+D8+D9</f>
+        <v>15943</v>
+      </c>
+      <c r="E12" s="32">
+        <f>E7+E8+E9</f>
+        <v>15943</v>
+      </c>
+      <c r="F12" s="32">
+        <f>F7+F8+F9</f>
+        <v>15943</v>
+      </c>
+      <c r="G12" s="32">
+        <f>G7+G8+G9</f>
+        <v>15943</v>
+      </c>
+      <c r="H12" s="32">
+        <f>H7+H8+H9</f>
+        <v>15943</v>
+      </c>
+      <c r="I12" s="32">
+        <f>I7+I8+I9</f>
+        <v>15943</v>
+      </c>
+      <c r="J12" s="32">
+        <f>J7+J8+J9</f>
+        <v>15943</v>
+      </c>
+      <c r="K12" s="32">
+        <f>K7+K8+K9</f>
+        <v>15943</v>
+      </c>
+      <c r="L12" s="32" t="str">
+        <f>L7+L8+L9</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="32" t="str">
+        <f>M7+M8+M9</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="32">
+        <f>SUM(B12:M12)</f>
+        <v>159430</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="32">
+        <f>B4-B12</f>
+        <v>-6793</v>
+      </c>
+      <c r="C13" s="32">
+        <f>C4-C12</f>
+        <v>6167</v>
+      </c>
+      <c r="D13" s="32">
+        <f>D4-D12</f>
+        <v>6167</v>
+      </c>
+      <c r="E13" s="32">
+        <f>E4-E12</f>
+        <v>6167</v>
+      </c>
+      <c r="F13" s="32">
+        <f>F4-F12</f>
+        <v>6167</v>
+      </c>
+      <c r="G13" s="32">
+        <f>G4-G12</f>
+        <v>6167</v>
+      </c>
+      <c r="H13" s="32">
+        <f>H4-H12</f>
+        <v>6167</v>
+      </c>
+      <c r="I13" s="32">
+        <f>I4-I12</f>
+        <v>6167</v>
+      </c>
+      <c r="J13" s="32">
+        <f>J4-J12</f>
+        <v>6167</v>
+      </c>
+      <c r="K13" s="32">
+        <f>K4-K12</f>
+        <v>6167</v>
+      </c>
+      <c r="L13" s="32">
+        <f>L4-L12</f>
+        <v>13210</v>
+      </c>
+      <c r="M13" s="32">
+        <f>M4-M12</f>
+        <v>250</v>
+      </c>
+      <c r="N13" s="32">
+        <f>SUM(B13:M13)</f>
+        <v>62170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B14" s="37">
+        <f>B17+B13</f>
+        <v>-6793</v>
+      </c>
+      <c r="C14" s="37">
+        <f>B14+C13</f>
+        <v>-626</v>
+      </c>
+      <c r="D14" s="37">
+        <f>C14+D13</f>
+        <v>5541</v>
+      </c>
+      <c r="E14" s="37">
+        <f>D14+E13</f>
+        <v>11708</v>
+      </c>
+      <c r="F14" s="37">
+        <f>E14+F13</f>
+        <v>17875</v>
+      </c>
+      <c r="G14" s="37">
+        <f>F14+G13</f>
+        <v>24042</v>
+      </c>
+      <c r="H14" s="37">
+        <f>G14+H13</f>
+        <v>30209</v>
+      </c>
+      <c r="I14" s="37">
+        <f>H14+I13</f>
+        <v>36376</v>
+      </c>
+      <c r="J14" s="37">
+        <f>I14+J13</f>
+        <v>42543</v>
+      </c>
+      <c r="K14" s="37">
+        <f>J14+K13</f>
+        <v>48710</v>
+      </c>
+      <c r="L14" s="37">
+        <f>K14+L13</f>
+        <v>61920</v>
+      </c>
+      <c r="M14" s="37">
+        <f>L14+M13</f>
+        <v>62170</v>
+      </c>
+      <c r="N14" s="30">
+        <f>M14</f>
+        <v>62170</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="B18" s="37">
+        <f>M14</f>
+        <v>62170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="B19" s="29">
+        <f>MIN(B14:M14)</f>
+        <v>-6793</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="34">
+        <v>184667</v>
+      </c>
+      <c r="C5" s="34">
+        <v>339797</v>
+      </c>
+      <c r="D5" s="34">
+        <v>426588</v>
+      </c>
+      <c r="E5" s="34">
+        <v>498557</v>
+      </c>
+      <c r="F5" s="34">
+        <v>513513</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="32">
+        <v>118934</v>
+      </c>
+      <c r="C8" s="32">
+        <v>147003</v>
+      </c>
+      <c r="D8" s="32">
+        <v>151413</v>
+      </c>
+      <c r="E8" s="32">
+        <v>155955</v>
+      </c>
+      <c r="F8" s="32">
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B9" s="32">
+        <v>40500</v>
+      </c>
+      <c r="C9" s="32">
+        <v>55002</v>
+      </c>
+      <c r="D9" s="32">
+        <v>60047</v>
+      </c>
+      <c r="E9" s="32">
+        <v>64471</v>
+      </c>
+      <c r="F9" s="32">
+        <v>66405</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="32">
+        <v>0</v>
+      </c>
+      <c r="C10" s="32">
+        <v>0</v>
+      </c>
+      <c r="D10" s="32">
+        <v>0</v>
+      </c>
+      <c r="E10" s="32">
+        <v>0</v>
+      </c>
+      <c r="F10" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="34">
+        <f>SUM(B8:B10)</f>
+        <v>159434</v>
+      </c>
+      <c r="C11" s="34">
+        <f>SUM(C8:C10)</f>
+        <v>202005</v>
+      </c>
+      <c r="D11" s="34">
+        <f>SUM(D8:D10)</f>
+        <v>211460</v>
+      </c>
+      <c r="E11" s="34">
+        <f>SUM(E8:E10)</f>
+        <v>220426</v>
+      </c>
+      <c r="F11" s="34">
+        <f>SUM(F8:F10)</f>
+        <v>227039</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="30">
+        <f>B5-B11</f>
+        <v>25233</v>
+      </c>
+      <c r="C14" s="30">
+        <f>C5-C11</f>
+        <v>137792</v>
+      </c>
+      <c r="D14" s="30">
+        <f>D5-D11</f>
+        <v>215128</v>
+      </c>
+      <c r="E14" s="30">
+        <f>E5-E11</f>
+        <v>278131</v>
+      </c>
+      <c r="F14" s="30">
+        <f>F5-F11</f>
+        <v>286475</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B15" s="28">
+        <f>IF(B5=0,0,B14/B5)</f>
+        <v>0.13663809</v>
+      </c>
+      <c r="C15" s="28">
+        <f>IF(C5=0,0,C14/C5)</f>
+        <v>0.40551379</v>
+      </c>
+      <c r="D15" s="28">
+        <f>IF(D5=0,0,D14/D5)</f>
+        <v>0.50429993</v>
+      </c>
+      <c r="E15" s="28">
+        <f>IF(E5=0,0,E14/E5)</f>
+        <v>0.55787178</v>
+      </c>
+      <c r="F15" s="28">
+        <f>IF(F5=0,0,F14/F5)</f>
+        <v>0.55787178</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>282</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5" s="42">
+        <f>'Monthly Cash Flow Y1'!M14</f>
+        <v>62170</v>
+      </c>
+      <c r="C5" s="42">
+        <f>B5+'5-Year Operating Stmt'!C14</f>
+        <v>199962</v>
+      </c>
+      <c r="D5" s="42">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
+        <v>415091</v>
+      </c>
+      <c r="E5" s="42">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
+        <v>693221</v>
+      </c>
+      <c r="F5" s="42">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
+        <v>979696</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B6" s="29">
+        <v>0</v>
+      </c>
+      <c r="C6" s="29">
+        <v>0</v>
+      </c>
+      <c r="D6" s="29">
+        <v>0</v>
+      </c>
+      <c r="E6" s="29">
+        <v>0</v>
+      </c>
+      <c r="F6" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" s="29">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="29">
+        <v>5000</v>
+      </c>
+      <c r="D7" s="29">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="29">
+        <v>5000</v>
+      </c>
+      <c r="F7" s="29">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="29">
+        <v>0</v>
+      </c>
+      <c r="C8" s="29">
+        <v>0</v>
+      </c>
+      <c r="D8" s="29">
+        <v>0</v>
+      </c>
+      <c r="E8" s="29">
+        <v>0</v>
+      </c>
+      <c r="F8" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" s="34">
+        <f>SUM(B5:B8)</f>
+        <v>67170</v>
+      </c>
+      <c r="C9" s="34">
+        <f>SUM(C5:C8)</f>
+        <v>204962</v>
+      </c>
+      <c r="D9" s="34">
+        <f>SUM(D5:D8)</f>
+        <v>420091</v>
+      </c>
+      <c r="E9" s="34">
+        <f>SUM(E5:E8)</f>
+        <v>698221</v>
+      </c>
+      <c r="F9" s="34">
+        <f>SUM(F5:F8)</f>
+        <v>984696</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" s="29">
+        <v>0</v>
+      </c>
+      <c r="C12" s="29">
+        <v>0</v>
+      </c>
+      <c r="D12" s="29">
+        <v>0</v>
+      </c>
+      <c r="E12" s="29">
+        <v>0</v>
+      </c>
+      <c r="F12" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="B13" s="29">
+        <v>0</v>
+      </c>
+      <c r="C13" s="29">
+        <v>0</v>
+      </c>
+      <c r="D13" s="29">
+        <v>0</v>
+      </c>
+      <c r="E13" s="29">
+        <v>0</v>
+      </c>
+      <c r="F13" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="B14" s="34" t="str">
+        <f>SUM(B12:B13)</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="34" t="str">
+        <f>SUM(C12:C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="34" t="str">
+        <f>SUM(D12:D13)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="34" t="str">
+        <f>SUM(E12:E13)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="34" t="str">
+        <f>SUM(F12:F13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B17" s="30">
+        <f>B9-B14</f>
+        <v>67170</v>
+      </c>
+      <c r="C17" s="30">
+        <f>C9-C14</f>
+        <v>204962</v>
+      </c>
+      <c r="D17" s="30">
+        <f>D9-D14</f>
+        <v>420091</v>
+      </c>
+      <c r="E17" s="30">
+        <f>E9-E14</f>
+        <v>698221</v>
+      </c>
+      <c r="F17" s="30">
+        <f>F9-F14</f>
+        <v>984696</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="B19" s="43" t="str">
+        <f>B9-B14-B17</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="43" t="str">
+        <f>C9-C14-C17</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="43" t="str">
+        <f>D9-D14-D17</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="43" t="str">
+        <f>E9-E14-E17</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="43" t="str">
+        <f>F9-F14-F17</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="B5" s="29">
+        <v>184667</v>
+      </c>
+      <c r="C5" s="29">
+        <v>339797</v>
+      </c>
+      <c r="D5" s="29">
+        <v>426588</v>
+      </c>
+      <c r="E5" s="29">
+        <v>498557</v>
+      </c>
+      <c r="F5" s="29">
+        <v>513513</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="29">
+        <v>118934</v>
+      </c>
+      <c r="C6" s="29">
+        <v>147003</v>
+      </c>
+      <c r="D6" s="29">
+        <v>151413</v>
+      </c>
+      <c r="E6" s="29">
+        <v>155955</v>
+      </c>
+      <c r="F6" s="29">
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B7" s="29">
+        <v>40500</v>
+      </c>
+      <c r="C7" s="29">
+        <v>55002</v>
+      </c>
+      <c r="D7" s="29">
+        <v>60047</v>
+      </c>
+      <c r="E7" s="29">
+        <v>64471</v>
+      </c>
+      <c r="F7" s="29">
+        <v>66405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8" s="32">
+        <f>B5-B6-B7</f>
+        <v>25233</v>
+      </c>
+      <c r="C8" s="32">
+        <f>C5-C6-C7</f>
+        <v>137792</v>
+      </c>
+      <c r="D8" s="32">
+        <f>D5-D6-D7</f>
+        <v>215128</v>
+      </c>
+      <c r="E8" s="32">
+        <f>E5-E6-E7</f>
+        <v>278131</v>
+      </c>
+      <c r="F8" s="32">
+        <f>F5-F6-F7</f>
+        <v>286475</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="29">
+        <v>0</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" s="29">
+        <v>62170</v>
+      </c>
+      <c r="C13" s="29">
+        <v>199962</v>
+      </c>
+      <c r="D13" s="29">
+        <v>415091</v>
+      </c>
+      <c r="E13" s="29">
+        <v>693221</v>
+      </c>
+      <c r="F13" s="29">
+        <v>979696</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B14" s="26">
+        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
+        <v>142</v>
+      </c>
+      <c r="C14" s="26">
+        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
+        <v>361</v>
+      </c>
+      <c r="D14" s="26">
+        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
+        <v>716</v>
+      </c>
+      <c r="E14" s="26">
+        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
+        <v>1148</v>
+      </c>
+      <c r="F14" s="26">
+        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="B15" s="33">
+        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
+        <v>4.7</v>
+      </c>
+      <c r="C15" s="33">
+        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
+        <v>11.9</v>
+      </c>
+      <c r="D15" s="33">
+        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
+        <v>23.6</v>
+      </c>
+      <c r="E15" s="33">
+        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
+        <v>37.7</v>
+      </c>
+      <c r="F15" s="33">
+        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="28">
+        <v>0.48</v>
+      </c>
+      <c r="C16" s="28">
+        <v>0.72</v>
+      </c>
+      <c r="D16" s="28">
+        <v>0.88</v>
+      </c>
+      <c r="E16" s="28">
+        <v>1</v>
+      </c>
+      <c r="F16" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="29">
+        <v>15389</v>
+      </c>
+      <c r="C19" s="29">
+        <v>18878</v>
+      </c>
+      <c r="D19" s="29">
+        <v>19390</v>
+      </c>
+      <c r="E19" s="29">
+        <v>19942</v>
+      </c>
+      <c r="F19" s="29">
+        <v>20541</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B20" s="29">
+        <v>118934</v>
+      </c>
+      <c r="C20" s="29">
+        <v>147003</v>
+      </c>
+      <c r="D20" s="29">
+        <v>151413</v>
+      </c>
+      <c r="E20" s="29">
+        <v>155955</v>
+      </c>
+      <c r="F20" s="29">
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="B21" s="29">
+        <v>3375</v>
+      </c>
+      <c r="C21" s="29">
+        <v>3056</v>
+      </c>
+      <c r="D21" s="29">
+        <v>2729</v>
+      </c>
+      <c r="E21" s="29">
+        <v>2579</v>
+      </c>
+      <c r="F21" s="29">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B22" s="45">
+        <v>10</v>
+      </c>
+      <c r="C22" s="45">
+        <v>10</v>
+      </c>
+      <c r="D22" s="45">
+        <v>10</v>
+      </c>
+      <c r="E22" s="45">
+        <v>9</v>
+      </c>
+      <c r="F22" s="45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="D26" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>316</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="D27" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="F28" s="47" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="D29" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="F29" s="47" t="s">
+        <v>314</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>320</v>
+      </c>
+      <c r="E3" s="49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="B4" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="E4" s="29">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D5" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" s="29">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B7" s="30">
+        <v>20000</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="E7" s="30">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="B8" s="43">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B3:C43"/>
@@ -1978,268 +5168,268 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1"/>
+      <c r="B3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="8"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="9"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>5</v>
+      <c r="B9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>7</v>
+      <c r="B10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>9</v>
+      <c r="B11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>11</v>
+      <c r="B12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>13</v>
+      <c r="B13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>15</v>
+      <c r="B14" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>17</v>
+      <c r="B15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="5"/>
+      <c r="B18" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="12"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>20</v>
+        <v>48</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>24</v>
+        <v>52</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>26</v>
+        <v>54</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>28</v>
+        <v>56</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>30</v>
+        <v>58</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>32</v>
+        <v>60</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>34</v>
+        <v>62</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>36</v>
+        <v>64</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>38</v>
+        <v>66</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>40</v>
+        <v>68</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>42</v>
+        <v>70</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>44</v>
+        <v>72</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>46</v>
+        <v>74</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>48</v>
+        <v>76</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>50</v>
+        <v>78</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>52</v>
+        <v>80</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>54</v>
+        <v>82</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>56</v>
+        <v>84</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>60</v>
+        <v>88</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>62</v>
+        <v>90</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="8"/>
+      <c r="B43" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2249,8 +5439,8 @@
     <mergeCell ref="B43:C43"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C19" r:id="rId1" location="#'Cover'!A1"/>
-    <hyperlink ref="C20" r:id="rId2" location="#'Instructions'!A1"/>
+    <hyperlink ref="C19" r:id="rId1" location="#'Instructions'!A1"/>
+    <hyperlink ref="C20" r:id="rId2" location="#'Cover'!A1"/>
     <hyperlink ref="C21" r:id="rId3" location="#'Assumptions'!A1"/>
     <hyperlink ref="C22" r:id="rId4" location="#'Program Profile'!A1"/>
     <hyperlink ref="C23" r:id="rId5" location="#'Enrollment Drivers'!A1"/>
@@ -2280,3196 +5470,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="35">
-        <v>12</v>
-      </c>
-      <c r="C4" s="35">
-        <v>18</v>
-      </c>
-      <c r="D4" s="35">
-        <v>22</v>
-      </c>
-      <c r="E4" s="35">
-        <v>25</v>
-      </c>
-      <c r="F4" s="35">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="29">
-        <v>144000</v>
-      </c>
-      <c r="C7" s="29">
-        <v>222480</v>
-      </c>
-      <c r="D7" s="29">
-        <v>280078</v>
-      </c>
-      <c r="E7" s="29">
-        <v>327818</v>
-      </c>
-      <c r="F7" s="29">
-        <v>337653</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="29">
-        <v>3000</v>
-      </c>
-      <c r="C8" s="29">
-        <v>4635</v>
-      </c>
-      <c r="D8" s="29">
-        <v>5835</v>
-      </c>
-      <c r="E8" s="29">
-        <v>6830</v>
-      </c>
-      <c r="F8" s="29">
-        <v>7034</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="29">
-        <v>84000</v>
-      </c>
-      <c r="C9" s="29">
-        <v>129780</v>
-      </c>
-      <c r="D9" s="29">
-        <v>163379</v>
-      </c>
-      <c r="E9" s="29">
-        <v>191227</v>
-      </c>
-      <c r="F9" s="29">
-        <v>196964</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="29">
-        <v>5000</v>
-      </c>
-      <c r="C10" s="29">
-        <v>5150</v>
-      </c>
-      <c r="D10" s="29">
-        <v>5305</v>
-      </c>
-      <c r="E10" s="29">
-        <v>5464</v>
-      </c>
-      <c r="F10" s="29">
-        <v>5628</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="29">
-        <v>-10</v>
-      </c>
-      <c r="C11" s="29">
-        <v>-10</v>
-      </c>
-      <c r="D11" s="29">
-        <v>-11</v>
-      </c>
-      <c r="E11" s="29">
-        <v>-11</v>
-      </c>
-      <c r="F11" s="29">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="30">
-        <f>SUM(B7:B11)</f>
-        <v>221600</v>
-      </c>
-      <c r="C12" s="30">
-        <f>SUM(C7:C11)</f>
-        <v>339797</v>
-      </c>
-      <c r="D12" s="30">
-        <f>SUM(D7:D11)</f>
-        <v>426588</v>
-      </c>
-      <c r="E12" s="30">
-        <f>SUM(E7:E11)</f>
-        <v>498557</v>
-      </c>
-      <c r="F12" s="30">
-        <f>SUM(F7:F11)</f>
-        <v>513513</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B14" s="29">
-        <v>18467</v>
-      </c>
-      <c r="C14" s="29">
-        <v>18878</v>
-      </c>
-      <c r="D14" s="29">
-        <v>19390</v>
-      </c>
-      <c r="E14" s="29">
-        <v>19942</v>
-      </c>
-      <c r="F14" s="29">
-        <v>20541</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" s="29">
-        <v>47869</v>
-      </c>
-      <c r="C5" s="29">
-        <v>59166</v>
-      </c>
-      <c r="D5" s="29">
-        <v>60941</v>
-      </c>
-      <c r="E5" s="29">
-        <v>62769</v>
-      </c>
-      <c r="F5" s="29">
-        <v>64652</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B6" s="29">
-        <v>12559</v>
-      </c>
-      <c r="C6" s="29">
-        <v>15523</v>
-      </c>
-      <c r="D6" s="29">
-        <v>15989</v>
-      </c>
-      <c r="E6" s="29">
-        <v>16468</v>
-      </c>
-      <c r="F6" s="29">
-        <v>16963</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" s="34">
-        <f>SUM(B5:B6)</f>
-        <v>60428</v>
-      </c>
-      <c r="C7" s="34">
-        <f>SUM(C5:C6)</f>
-        <v>74689</v>
-      </c>
-      <c r="D7" s="34">
-        <f>SUM(D5:D6)</f>
-        <v>76930</v>
-      </c>
-      <c r="E7" s="34">
-        <f>SUM(E5:E6)</f>
-        <v>79237</v>
-      </c>
-      <c r="F7" s="34">
-        <f>SUM(F5:F6)</f>
-        <v>81615</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B9" s="29">
-        <v>58506</v>
-      </c>
-      <c r="C9" s="29">
-        <v>72314</v>
-      </c>
-      <c r="D9" s="29">
-        <v>74483</v>
-      </c>
-      <c r="E9" s="29">
-        <v>76718</v>
-      </c>
-      <c r="F9" s="29">
-        <v>79019</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B10" s="34">
-        <f>SUM(B9:B9)</f>
-        <v>58506</v>
-      </c>
-      <c r="C10" s="34">
-        <f>SUM(C9:C9)</f>
-        <v>72314</v>
-      </c>
-      <c r="D10" s="34">
-        <f>SUM(D9:D9)</f>
-        <v>74483</v>
-      </c>
-      <c r="E10" s="34">
-        <f>SUM(E9:E9)</f>
-        <v>76718</v>
-      </c>
-      <c r="F10" s="34">
-        <f>SUM(F9:F9)</f>
-        <v>79019</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="B12" s="30">
-        <f>B7+B10</f>
-        <v>118934</v>
-      </c>
-      <c r="C12" s="30">
-        <f>C7+C10</f>
-        <v>147003</v>
-      </c>
-      <c r="D12" s="30">
-        <f>D7+D10</f>
-        <v>151413</v>
-      </c>
-      <c r="E12" s="30">
-        <f>E7+E10</f>
-        <v>155955</v>
-      </c>
-      <c r="F12" s="30">
-        <f>F7+F10</f>
-        <v>160634</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="29">
-        <v>120000</v>
-      </c>
-      <c r="C5" s="29">
-        <v>222480</v>
-      </c>
-      <c r="D5" s="29">
-        <v>280078</v>
-      </c>
-      <c r="E5" s="29">
-        <v>327818</v>
-      </c>
-      <c r="F5" s="29">
-        <v>337653</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="29">
-        <v>2500</v>
-      </c>
-      <c r="C6" s="29">
-        <v>4635</v>
-      </c>
-      <c r="D6" s="29">
-        <v>5835</v>
-      </c>
-      <c r="E6" s="29">
-        <v>6830</v>
-      </c>
-      <c r="F6" s="29">
-        <v>7034</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="29">
-        <v>70000</v>
-      </c>
-      <c r="C7" s="29">
-        <v>129780</v>
-      </c>
-      <c r="D7" s="29">
-        <v>163379</v>
-      </c>
-      <c r="E7" s="29">
-        <v>191227</v>
-      </c>
-      <c r="F7" s="29">
-        <v>196964</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" s="29">
-        <v>4167</v>
-      </c>
-      <c r="C8" s="29">
-        <v>5150</v>
-      </c>
-      <c r="D8" s="29">
-        <v>5305</v>
-      </c>
-      <c r="E8" s="29">
-        <v>5464</v>
-      </c>
-      <c r="F8" s="29">
-        <v>5628</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B9" s="29">
-        <v>-8</v>
-      </c>
-      <c r="C9" s="29">
-        <v>-10</v>
-      </c>
-      <c r="D9" s="29">
-        <v>-11</v>
-      </c>
-      <c r="E9" s="29">
-        <v>-11</v>
-      </c>
-      <c r="F9" s="29">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B10" s="34">
-        <f>SUM(B5:B9)</f>
-        <v>184667</v>
-      </c>
-      <c r="C10" s="34">
-        <f>SUM(C5:C9)</f>
-        <v>339797</v>
-      </c>
-      <c r="D10" s="34">
-        <f>SUM(D5:D9)</f>
-        <v>426588</v>
-      </c>
-      <c r="E10" s="34">
-        <f>SUM(E5:E9)</f>
-        <v>498557</v>
-      </c>
-      <c r="F10" s="34">
-        <f>SUM(F5:F9)</f>
-        <v>513513</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="29">
-        <v>58506</v>
-      </c>
-      <c r="C13" s="29">
-        <v>72314</v>
-      </c>
-      <c r="D13" s="29">
-        <v>74483</v>
-      </c>
-      <c r="E13" s="29">
-        <v>76718</v>
-      </c>
-      <c r="F13" s="29">
-        <v>79019</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B14" s="29">
-        <v>47869</v>
-      </c>
-      <c r="C14" s="29">
-        <v>59166</v>
-      </c>
-      <c r="D14" s="29">
-        <v>60941</v>
-      </c>
-      <c r="E14" s="29">
-        <v>62769</v>
-      </c>
-      <c r="F14" s="29">
-        <v>64652</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B15" s="29">
-        <v>12559</v>
-      </c>
-      <c r="C15" s="29">
-        <v>15523</v>
-      </c>
-      <c r="D15" s="29">
-        <v>15989</v>
-      </c>
-      <c r="E15" s="29">
-        <v>16468</v>
-      </c>
-      <c r="F15" s="29">
-        <v>16963</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="34">
-        <f>SUM(B13:B15)</f>
-        <v>118934</v>
-      </c>
-      <c r="C16" s="34">
-        <f>SUM(C13:C15)</f>
-        <v>147003</v>
-      </c>
-      <c r="D16" s="34">
-        <f>SUM(D13:D15)</f>
-        <v>151413</v>
-      </c>
-      <c r="E16" s="34">
-        <f>SUM(E13:E15)</f>
-        <v>155955</v>
-      </c>
-      <c r="F16" s="34">
-        <f>SUM(F13:F15)</f>
-        <v>160634</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B20" s="29">
-        <v>5000</v>
-      </c>
-      <c r="C20" s="29">
-        <v>9270</v>
-      </c>
-      <c r="D20" s="29">
-        <v>11670</v>
-      </c>
-      <c r="E20" s="29">
-        <v>13659</v>
-      </c>
-      <c r="F20" s="29">
-        <v>14069</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B22" s="29">
-        <v>3000</v>
-      </c>
-      <c r="C22" s="29">
-        <v>5562</v>
-      </c>
-      <c r="D22" s="29">
-        <v>7002</v>
-      </c>
-      <c r="E22" s="29">
-        <v>8195</v>
-      </c>
-      <c r="F22" s="29">
-        <v>8441</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B24" s="29">
-        <v>25000</v>
-      </c>
-      <c r="C24" s="29">
-        <v>30900</v>
-      </c>
-      <c r="D24" s="29">
-        <v>31827</v>
-      </c>
-      <c r="E24" s="29">
-        <v>32782</v>
-      </c>
-      <c r="F24" s="29">
-        <v>33765</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B25" s="29">
-        <v>3000</v>
-      </c>
-      <c r="C25" s="29">
-        <v>3708</v>
-      </c>
-      <c r="D25" s="29">
-        <v>3819</v>
-      </c>
-      <c r="E25" s="29">
-        <v>3934</v>
-      </c>
-      <c r="F25" s="29">
-        <v>4052</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B26" s="29">
-        <v>2000</v>
-      </c>
-      <c r="C26" s="29">
-        <v>2472</v>
-      </c>
-      <c r="D26" s="29">
-        <v>2546</v>
-      </c>
-      <c r="E26" s="29">
-        <v>2623</v>
-      </c>
-      <c r="F26" s="29">
-        <v>2701</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B27" s="34">
-        <f>SUM(B24:B26)</f>
-        <v>30000</v>
-      </c>
-      <c r="C27" s="34">
-        <f>SUM(C24:C26)</f>
-        <v>37080</v>
-      </c>
-      <c r="D27" s="34">
-        <f>SUM(D24:D26)</f>
-        <v>38192</v>
-      </c>
-      <c r="E27" s="34">
-        <f>SUM(E24:E26)</f>
-        <v>39338</v>
-      </c>
-      <c r="F27" s="34">
-        <f>SUM(F24:F26)</f>
-        <v>40518</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B29" s="29">
-        <v>2500</v>
-      </c>
-      <c r="C29" s="29">
-        <v>3090</v>
-      </c>
-      <c r="D29" s="29">
-        <v>3183</v>
-      </c>
-      <c r="E29" s="29">
-        <v>3278</v>
-      </c>
-      <c r="F29" s="29">
-        <v>3377</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B30" s="34">
-        <f>B20+B22+B27+B29</f>
-        <v>40500</v>
-      </c>
-      <c r="C30" s="34">
-        <f>C20+C22+C27+C29</f>
-        <v>55002</v>
-      </c>
-      <c r="D30" s="34">
-        <f>D20+D22+D27+D29</f>
-        <v>60047</v>
-      </c>
-      <c r="E30" s="34">
-        <f>E20+E22+E27+E29</f>
-        <v>64471</v>
-      </c>
-      <c r="F30" s="34">
-        <f>F20+F22+F27+F29</f>
-        <v>66405</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B33" s="34" t="str">
-        <f>SUM(B33:B32)</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="34" t="str">
-        <f>SUM(C33:C32)</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="34" t="str">
-        <f>SUM(D33:D32)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="34" t="str">
-        <f>SUM(E33:E32)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="34" t="str">
-        <f>SUM(F33:F32)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B4" s="32">
-        <f>'Budget Detail'!B10</f>
-        <v>184667</v>
-      </c>
-      <c r="C4" s="32">
-        <f>'Budget Detail'!C10</f>
-        <v>339797</v>
-      </c>
-      <c r="D4" s="32">
-        <f>'Budget Detail'!D10</f>
-        <v>426588</v>
-      </c>
-      <c r="E4" s="32">
-        <f>'Budget Detail'!E10</f>
-        <v>498557</v>
-      </c>
-      <c r="F4" s="32">
-        <f>'Budget Detail'!F10</f>
-        <v>513513</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="32">
-        <f>'Budget Detail'!B16</f>
-        <v>118934</v>
-      </c>
-      <c r="C5" s="32">
-        <f>'Budget Detail'!C16</f>
-        <v>147003</v>
-      </c>
-      <c r="D5" s="32">
-        <f>'Budget Detail'!D16</f>
-        <v>151413</v>
-      </c>
-      <c r="E5" s="32">
-        <f>'Budget Detail'!E16</f>
-        <v>155955</v>
-      </c>
-      <c r="F5" s="32">
-        <f>'Budget Detail'!F16</f>
-        <v>160634</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B6" s="32">
-        <f>'Budget Detail'!B30</f>
-        <v>40500</v>
-      </c>
-      <c r="C6" s="32">
-        <f>'Budget Detail'!C30</f>
-        <v>55002</v>
-      </c>
-      <c r="D6" s="32">
-        <f>'Budget Detail'!D30</f>
-        <v>60047</v>
-      </c>
-      <c r="E6" s="32">
-        <f>'Budget Detail'!E30</f>
-        <v>64471</v>
-      </c>
-      <c r="F6" s="32">
-        <f>'Budget Detail'!F30</f>
-        <v>66405</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B7" s="32" t="str">
-        <f>'Budget Detail'!B33</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="str">
-        <f>'Budget Detail'!C33</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="32" t="str">
-        <f>'Budget Detail'!D33</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="32" t="str">
-        <f>'Budget Detail'!E33</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="32" t="str">
-        <f>'Budget Detail'!F33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B8" s="34">
-        <f>SUM(B5:B7)</f>
-        <v>159434</v>
-      </c>
-      <c r="C8" s="34">
-        <f>SUM(C5:C7)</f>
-        <v>202005</v>
-      </c>
-      <c r="D8" s="34">
-        <f>SUM(D5:D7)</f>
-        <v>211460</v>
-      </c>
-      <c r="E8" s="34">
-        <f>SUM(E5:E7)</f>
-        <v>220426</v>
-      </c>
-      <c r="F8" s="34">
-        <f>SUM(F5:F7)</f>
-        <v>227039</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B11" s="30">
-        <f>B4-B8</f>
-        <v>25233</v>
-      </c>
-      <c r="C11" s="30">
-        <f>C4-C8</f>
-        <v>137792</v>
-      </c>
-      <c r="D11" s="30">
-        <f>D4-D8</f>
-        <v>215128</v>
-      </c>
-      <c r="E11" s="30">
-        <f>E4-E8</f>
-        <v>278131</v>
-      </c>
-      <c r="F11" s="30">
-        <f>F4-F8</f>
-        <v>286475</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="28">
-        <f>IF(B4=0,0,B11/B4)</f>
-        <v>0.13663809</v>
-      </c>
-      <c r="C12" s="28">
-        <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.40551379</v>
-      </c>
-      <c r="D12" s="28">
-        <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.50429993</v>
-      </c>
-      <c r="E12" s="28">
-        <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.55787178</v>
-      </c>
-      <c r="F12" s="28">
-        <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.55787178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" s="29">
-        <v>25233</v>
-      </c>
-      <c r="C13" s="29">
-        <v>163025</v>
-      </c>
-      <c r="D13" s="29">
-        <v>378153</v>
-      </c>
-      <c r="E13" s="29">
-        <v>656284</v>
-      </c>
-      <c r="F13" s="29">
-        <v>942758</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B14" s="29">
-        <v>15389</v>
-      </c>
-      <c r="C14" s="29">
-        <v>18878</v>
-      </c>
-      <c r="D14" s="29">
-        <v>19390</v>
-      </c>
-      <c r="E14" s="29">
-        <v>19942</v>
-      </c>
-      <c r="F14" s="29">
-        <v>20541</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="B15" s="29">
-        <v>13286</v>
-      </c>
-      <c r="C15" s="29">
-        <v>11222</v>
-      </c>
-      <c r="D15" s="29">
-        <v>9612</v>
-      </c>
-      <c r="E15" s="29">
-        <v>8817</v>
-      </c>
-      <c r="F15" s="29">
-        <v>9082</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="M2" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B4" s="34">
-        <v>9150</v>
-      </c>
-      <c r="C4" s="34">
-        <v>22110</v>
-      </c>
-      <c r="D4" s="34">
-        <v>22110</v>
-      </c>
-      <c r="E4" s="34">
-        <v>22110</v>
-      </c>
-      <c r="F4" s="34">
-        <v>22110</v>
-      </c>
-      <c r="G4" s="34">
-        <v>22110</v>
-      </c>
-      <c r="H4" s="34">
-        <v>22110</v>
-      </c>
-      <c r="I4" s="34">
-        <v>22110</v>
-      </c>
-      <c r="J4" s="34">
-        <v>22110</v>
-      </c>
-      <c r="K4" s="34">
-        <v>22110</v>
-      </c>
-      <c r="L4" s="34">
-        <v>13210</v>
-      </c>
-      <c r="M4" s="34">
-        <v>250</v>
-      </c>
-      <c r="N4" s="34">
-        <f>SUM(B4:M4)</f>
-        <v>221600</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="C7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="D7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="E7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="F7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="G7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="H7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="I7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="J7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="K7" s="29">
-        <v>11893</v>
-      </c>
-      <c r="L7" s="29">
-        <v>0</v>
-      </c>
-      <c r="M7" s="29">
-        <v>0</v>
-      </c>
-      <c r="N7" s="29">
-        <f>SUM(B7:M7)</f>
-        <v>118934</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="C8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="D8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="E8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="F8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="G8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="H8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="I8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="J8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="K8" s="29">
-        <v>4050</v>
-      </c>
-      <c r="L8" s="29">
-        <v>0</v>
-      </c>
-      <c r="M8" s="29">
-        <v>0</v>
-      </c>
-      <c r="N8" s="29">
-        <f>SUM(B8:M8)</f>
-        <v>40500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="29">
-        <v>0</v>
-      </c>
-      <c r="C9" s="29">
-        <v>0</v>
-      </c>
-      <c r="D9" s="29">
-        <v>0</v>
-      </c>
-      <c r="E9" s="29">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29">
-        <v>0</v>
-      </c>
-      <c r="G9" s="29">
-        <v>0</v>
-      </c>
-      <c r="H9" s="29">
-        <v>0</v>
-      </c>
-      <c r="I9" s="29">
-        <v>0</v>
-      </c>
-      <c r="J9" s="29">
-        <v>0</v>
-      </c>
-      <c r="K9" s="29">
-        <v>0</v>
-      </c>
-      <c r="L9" s="29">
-        <v>0</v>
-      </c>
-      <c r="M9" s="29">
-        <v>0</v>
-      </c>
-      <c r="N9" s="29" t="str">
-        <f>SUM(B9:M9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B12" s="32">
-        <f>B7+B8+B9</f>
-        <v>15943</v>
-      </c>
-      <c r="C12" s="32">
-        <f>C7+C8+C9</f>
-        <v>15943</v>
-      </c>
-      <c r="D12" s="32">
-        <f>D7+D8+D9</f>
-        <v>15943</v>
-      </c>
-      <c r="E12" s="32">
-        <f>E7+E8+E9</f>
-        <v>15943</v>
-      </c>
-      <c r="F12" s="32">
-        <f>F7+F8+F9</f>
-        <v>15943</v>
-      </c>
-      <c r="G12" s="32">
-        <f>G7+G8+G9</f>
-        <v>15943</v>
-      </c>
-      <c r="H12" s="32">
-        <f>H7+H8+H9</f>
-        <v>15943</v>
-      </c>
-      <c r="I12" s="32">
-        <f>I7+I8+I9</f>
-        <v>15943</v>
-      </c>
-      <c r="J12" s="32">
-        <f>J7+J8+J9</f>
-        <v>15943</v>
-      </c>
-      <c r="K12" s="32">
-        <f>K7+K8+K9</f>
-        <v>15943</v>
-      </c>
-      <c r="L12" s="32" t="str">
-        <f>L7+L8+L9</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="32" t="str">
-        <f>M7+M8+M9</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="32">
-        <f>SUM(B12:M12)</f>
-        <v>159430</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B13" s="32">
-        <f>B4-B12</f>
-        <v>-6793</v>
-      </c>
-      <c r="C13" s="32">
-        <f>C4-C12</f>
-        <v>6167</v>
-      </c>
-      <c r="D13" s="32">
-        <f>D4-D12</f>
-        <v>6167</v>
-      </c>
-      <c r="E13" s="32">
-        <f>E4-E12</f>
-        <v>6167</v>
-      </c>
-      <c r="F13" s="32">
-        <f>F4-F12</f>
-        <v>6167</v>
-      </c>
-      <c r="G13" s="32">
-        <f>G4-G12</f>
-        <v>6167</v>
-      </c>
-      <c r="H13" s="32">
-        <f>H4-H12</f>
-        <v>6167</v>
-      </c>
-      <c r="I13" s="32">
-        <f>I4-I12</f>
-        <v>6167</v>
-      </c>
-      <c r="J13" s="32">
-        <f>J4-J12</f>
-        <v>6167</v>
-      </c>
-      <c r="K13" s="32">
-        <f>K4-K12</f>
-        <v>6167</v>
-      </c>
-      <c r="L13" s="32">
-        <f>L4-L12</f>
-        <v>13210</v>
-      </c>
-      <c r="M13" s="32">
-        <f>M4-M12</f>
-        <v>250</v>
-      </c>
-      <c r="N13" s="32">
-        <f>SUM(B13:M13)</f>
-        <v>62170</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B14" s="37">
-        <f>B17+B13</f>
-        <v>-6793</v>
-      </c>
-      <c r="C14" s="37">
-        <f>B14+C13</f>
-        <v>-626</v>
-      </c>
-      <c r="D14" s="37">
-        <f>C14+D13</f>
-        <v>5541</v>
-      </c>
-      <c r="E14" s="37">
-        <f>D14+E13</f>
-        <v>11708</v>
-      </c>
-      <c r="F14" s="37">
-        <f>E14+F13</f>
-        <v>17875</v>
-      </c>
-      <c r="G14" s="37">
-        <f>F14+G13</f>
-        <v>24042</v>
-      </c>
-      <c r="H14" s="37">
-        <f>G14+H13</f>
-        <v>30209</v>
-      </c>
-      <c r="I14" s="37">
-        <f>H14+I13</f>
-        <v>36376</v>
-      </c>
-      <c r="J14" s="37">
-        <f>I14+J13</f>
-        <v>42543</v>
-      </c>
-      <c r="K14" s="37">
-        <f>J14+K13</f>
-        <v>48710</v>
-      </c>
-      <c r="L14" s="37">
-        <f>K14+L13</f>
-        <v>61920</v>
-      </c>
-      <c r="M14" s="37">
-        <f>L14+M13</f>
-        <v>62170</v>
-      </c>
-      <c r="N14" s="30">
-        <f>M14</f>
-        <v>62170</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B18" s="37">
-        <f>M14</f>
-        <v>62170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B19" s="29">
-        <f>MIN(B14:M14)</f>
-        <v>-6793</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="B5" s="34">
-        <v>184667</v>
-      </c>
-      <c r="C5" s="34">
-        <v>339797</v>
-      </c>
-      <c r="D5" s="34">
-        <v>426588</v>
-      </c>
-      <c r="E5" s="34">
-        <v>498557</v>
-      </c>
-      <c r="F5" s="34">
-        <v>513513</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B8" s="32">
-        <v>118934</v>
-      </c>
-      <c r="C8" s="32">
-        <v>147003</v>
-      </c>
-      <c r="D8" s="32">
-        <v>151413</v>
-      </c>
-      <c r="E8" s="32">
-        <v>155955</v>
-      </c>
-      <c r="F8" s="32">
-        <v>160634</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B9" s="32">
-        <v>40500</v>
-      </c>
-      <c r="C9" s="32">
-        <v>55002</v>
-      </c>
-      <c r="D9" s="32">
-        <v>60047</v>
-      </c>
-      <c r="E9" s="32">
-        <v>64471</v>
-      </c>
-      <c r="F9" s="32">
-        <v>66405</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" s="32">
-        <v>0</v>
-      </c>
-      <c r="C10" s="32">
-        <v>0</v>
-      </c>
-      <c r="D10" s="32">
-        <v>0</v>
-      </c>
-      <c r="E10" s="32">
-        <v>0</v>
-      </c>
-      <c r="F10" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="34">
-        <f>SUM(B8:B10)</f>
-        <v>159434</v>
-      </c>
-      <c r="C11" s="34">
-        <f>SUM(C8:C10)</f>
-        <v>202005</v>
-      </c>
-      <c r="D11" s="34">
-        <f>SUM(D8:D10)</f>
-        <v>211460</v>
-      </c>
-      <c r="E11" s="34">
-        <f>SUM(E8:E10)</f>
-        <v>220426</v>
-      </c>
-      <c r="F11" s="34">
-        <f>SUM(F8:F10)</f>
-        <v>227039</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="B14" s="30">
-        <f>B5-B11</f>
-        <v>25233</v>
-      </c>
-      <c r="C14" s="30">
-        <f>C5-C11</f>
-        <v>137792</v>
-      </c>
-      <c r="D14" s="30">
-        <f>D5-D11</f>
-        <v>215128</v>
-      </c>
-      <c r="E14" s="30">
-        <f>E5-E11</f>
-        <v>278131</v>
-      </c>
-      <c r="F14" s="30">
-        <f>F5-F11</f>
-        <v>286475</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B15" s="28">
-        <f>IF(B5=0,0,B14/B5)</f>
-        <v>0.13663809</v>
-      </c>
-      <c r="C15" s="28">
-        <f>IF(C5=0,0,C14/C5)</f>
-        <v>0.40551379</v>
-      </c>
-      <c r="D15" s="28">
-        <f>IF(D5=0,0,D14/D5)</f>
-        <v>0.50429993</v>
-      </c>
-      <c r="E15" s="28">
-        <f>IF(E5=0,0,E14/E5)</f>
-        <v>0.55787178</v>
-      </c>
-      <c r="F15" s="28">
-        <f>IF(F5=0,0,F14/F5)</f>
-        <v>0.55787178</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>212</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B5" s="42">
-        <f>'Monthly Cash Flow Y1'!M14</f>
-        <v>62170</v>
-      </c>
-      <c r="C5" s="42">
-        <f>B5+'5-Year Operating Stmt'!C14</f>
-        <v>199962</v>
-      </c>
-      <c r="D5" s="42">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
-        <v>415091</v>
-      </c>
-      <c r="E5" s="42">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
-        <v>693221</v>
-      </c>
-      <c r="F5" s="42">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
-        <v>979696</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B6" s="29">
-        <v>0</v>
-      </c>
-      <c r="C6" s="29">
-        <v>0</v>
-      </c>
-      <c r="D6" s="29">
-        <v>0</v>
-      </c>
-      <c r="E6" s="29">
-        <v>0</v>
-      </c>
-      <c r="F6" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B7" s="29">
-        <v>5000</v>
-      </c>
-      <c r="C7" s="29">
-        <v>5000</v>
-      </c>
-      <c r="D7" s="29">
-        <v>5000</v>
-      </c>
-      <c r="E7" s="29">
-        <v>5000</v>
-      </c>
-      <c r="F7" s="29">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B8" s="29">
-        <v>0</v>
-      </c>
-      <c r="C8" s="29">
-        <v>0</v>
-      </c>
-      <c r="D8" s="29">
-        <v>0</v>
-      </c>
-      <c r="E8" s="29">
-        <v>0</v>
-      </c>
-      <c r="F8" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="34">
-        <f>SUM(B5:B8)</f>
-        <v>67170</v>
-      </c>
-      <c r="C9" s="34">
-        <f>SUM(C5:C8)</f>
-        <v>204962</v>
-      </c>
-      <c r="D9" s="34">
-        <f>SUM(D5:D8)</f>
-        <v>420091</v>
-      </c>
-      <c r="E9" s="34">
-        <f>SUM(E5:E8)</f>
-        <v>698221</v>
-      </c>
-      <c r="F9" s="34">
-        <f>SUM(F5:F8)</f>
-        <v>984696</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12" s="29">
-        <v>0</v>
-      </c>
-      <c r="C12" s="29">
-        <v>0</v>
-      </c>
-      <c r="D12" s="29">
-        <v>0</v>
-      </c>
-      <c r="E12" s="29">
-        <v>0</v>
-      </c>
-      <c r="F12" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B13" s="29">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14" s="34" t="str">
-        <f>SUM(B12:B13)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="34" t="str">
-        <f>SUM(C12:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="34" t="str">
-        <f>SUM(D12:D13)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="34" t="str">
-        <f>SUM(E12:E13)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="34" t="str">
-        <f>SUM(F12:F13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B17" s="30">
-        <f>B9-B14</f>
-        <v>67170</v>
-      </c>
-      <c r="C17" s="30">
-        <f>C9-C14</f>
-        <v>204962</v>
-      </c>
-      <c r="D17" s="30">
-        <f>D9-D14</f>
-        <v>420091</v>
-      </c>
-      <c r="E17" s="30">
-        <f>E9-E14</f>
-        <v>698221</v>
-      </c>
-      <c r="F17" s="30">
-        <f>F9-F14</f>
-        <v>984696</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="43" t="str">
-        <f>B9-B14-B17</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="43" t="str">
-        <f>C9-C14-C17</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="43" t="str">
-        <f>D9-D14-D17</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="43" t="str">
-        <f>E9-E14-E17</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="43" t="str">
-        <f>F9-F14-F17</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B5" s="29">
-        <v>184667</v>
-      </c>
-      <c r="C5" s="29">
-        <v>339797</v>
-      </c>
-      <c r="D5" s="29">
-        <v>426588</v>
-      </c>
-      <c r="E5" s="29">
-        <v>498557</v>
-      </c>
-      <c r="F5" s="29">
-        <v>513513</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="29">
-        <v>118934</v>
-      </c>
-      <c r="C6" s="29">
-        <v>147003</v>
-      </c>
-      <c r="D6" s="29">
-        <v>151413</v>
-      </c>
-      <c r="E6" s="29">
-        <v>155955</v>
-      </c>
-      <c r="F6" s="29">
-        <v>160634</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B7" s="29">
-        <v>40500</v>
-      </c>
-      <c r="C7" s="29">
-        <v>55002</v>
-      </c>
-      <c r="D7" s="29">
-        <v>60047</v>
-      </c>
-      <c r="E7" s="29">
-        <v>64471</v>
-      </c>
-      <c r="F7" s="29">
-        <v>66405</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B8" s="32">
-        <f>B5-B6-B7</f>
-        <v>25233</v>
-      </c>
-      <c r="C8" s="32">
-        <f>C5-C6-C7</f>
-        <v>137792</v>
-      </c>
-      <c r="D8" s="32">
-        <f>D5-D6-D7</f>
-        <v>215128</v>
-      </c>
-      <c r="E8" s="32">
-        <f>E5-E6-E7</f>
-        <v>278131</v>
-      </c>
-      <c r="F8" s="32">
-        <f>F5-F6-F7</f>
-        <v>286475</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="29">
-        <v>0</v>
-      </c>
-      <c r="C9" s="29">
-        <v>0</v>
-      </c>
-      <c r="D9" s="29">
-        <v>0</v>
-      </c>
-      <c r="E9" s="29">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B13" s="29">
-        <v>62170</v>
-      </c>
-      <c r="C13" s="29">
-        <v>199962</v>
-      </c>
-      <c r="D13" s="29">
-        <v>415091</v>
-      </c>
-      <c r="E13" s="29">
-        <v>693221</v>
-      </c>
-      <c r="F13" s="29">
-        <v>979696</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B14" s="26">
-        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
-        <v>142</v>
-      </c>
-      <c r="C14" s="26">
-        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
-        <v>361</v>
-      </c>
-      <c r="D14" s="26">
-        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
-        <v>716</v>
-      </c>
-      <c r="E14" s="26">
-        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
-        <v>1148</v>
-      </c>
-      <c r="F14" s="26">
-        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B15" s="33">
-        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
-        <v>4.7</v>
-      </c>
-      <c r="C15" s="33">
-        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
-        <v>11.9</v>
-      </c>
-      <c r="D15" s="33">
-        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
-        <v>23.6</v>
-      </c>
-      <c r="E15" s="33">
-        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
-        <v>37.7</v>
-      </c>
-      <c r="F15" s="33">
-        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
-        <v>51.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B16" s="28">
-        <v>0.48</v>
-      </c>
-      <c r="C16" s="28">
-        <v>0.72</v>
-      </c>
-      <c r="D16" s="28">
-        <v>0.88</v>
-      </c>
-      <c r="E16" s="28">
-        <v>1</v>
-      </c>
-      <c r="F16" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B19" s="29">
-        <v>15389</v>
-      </c>
-      <c r="C19" s="29">
-        <v>18878</v>
-      </c>
-      <c r="D19" s="29">
-        <v>19390</v>
-      </c>
-      <c r="E19" s="29">
-        <v>19942</v>
-      </c>
-      <c r="F19" s="29">
-        <v>20541</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B20" s="29">
-        <v>118934</v>
-      </c>
-      <c r="C20" s="29">
-        <v>147003</v>
-      </c>
-      <c r="D20" s="29">
-        <v>151413</v>
-      </c>
-      <c r="E20" s="29">
-        <v>155955</v>
-      </c>
-      <c r="F20" s="29">
-        <v>160634</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B21" s="29">
-        <v>3375</v>
-      </c>
-      <c r="C21" s="29">
-        <v>3056</v>
-      </c>
-      <c r="D21" s="29">
-        <v>2729</v>
-      </c>
-      <c r="E21" s="29">
-        <v>2579</v>
-      </c>
-      <c r="F21" s="29">
-        <v>2656</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B22" s="45">
-        <v>10</v>
-      </c>
-      <c r="C22" s="45">
-        <v>10</v>
-      </c>
-      <c r="D22" s="45">
-        <v>10</v>
-      </c>
-      <c r="E22" s="45">
-        <v>9</v>
-      </c>
-      <c r="F22" s="45">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B25" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="C25" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="D25" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="E25" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="F25" s="46" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="F26" s="47" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B27" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="C27" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="D27" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="E27" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="F27" s="47" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B28" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="D28" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="F28" s="47" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B29" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="C29" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="D29" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="F29" s="47" t="s">
-        <v>314</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
-        <v>319</v>
-      </c>
-      <c r="B3" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>320</v>
-      </c>
-      <c r="E3" s="49" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B4" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="E4" s="29">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="5" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="E5" s="29">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B7" s="30">
-        <v>20000</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="E7" s="30">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B8" s="43">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF328555"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B2:B37"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
@@ -5509,7 +5509,7 @@
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>101</v>
@@ -5528,7 +5528,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="11" t="s">
         <v>299</v>
       </c>
       <c r="B6" s="29">
@@ -5548,7 +5548,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="11" t="s">
         <v>246</v>
       </c>
       <c r="B7" s="29">
@@ -5568,7 +5568,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="10" t="s">
         <v>248</v>
       </c>
       <c r="B8" s="30">
@@ -5588,7 +5588,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="11" t="s">
         <v>249</v>
       </c>
       <c r="B9" s="28">
@@ -5608,7 +5608,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="11" t="s">
         <v>301</v>
       </c>
       <c r="B10" s="50" t="s">
@@ -5628,7 +5628,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="11" t="s">
         <v>310</v>
       </c>
       <c r="B11" s="26">
@@ -5664,7 +5664,7 @@
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>101</v>
@@ -5683,7 +5683,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="11" t="s">
         <v>299</v>
       </c>
       <c r="B16" s="29">
@@ -5703,7 +5703,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="11" t="s">
         <v>246</v>
       </c>
       <c r="B17" s="29">
@@ -5723,7 +5723,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="10" t="s">
         <v>248</v>
       </c>
       <c r="B18" s="30">
@@ -5743,7 +5743,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="11" t="s">
         <v>249</v>
       </c>
       <c r="B19" s="28">
@@ -5763,7 +5763,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="11" t="s">
         <v>301</v>
       </c>
       <c r="B20" s="50" t="s">
@@ -5783,7 +5783,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="11" t="s">
         <v>310</v>
       </c>
       <c r="B21" s="26">
@@ -5847,51 +5847,51 @@
       <c r="B3" s="17"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
+      <c r="A4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
+      <c r="B5" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
+      <c r="B6" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
+      <c r="A7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
+      <c r="A8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>17</v>
+      <c r="B9" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5908,13 +5908,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D12" s="51" t="s">
         <v>101</v>
@@ -5933,7 +5933,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="11" t="s">
         <v>299</v>
       </c>
       <c r="D13" s="29">
@@ -5953,7 +5953,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="11" t="s">
         <v>246</v>
       </c>
       <c r="D14" s="29">
@@ -5973,7 +5973,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="11" t="s">
         <v>248</v>
       </c>
       <c r="D15" s="29">
@@ -5993,7 +5993,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="11" t="s">
         <v>336</v>
       </c>
       <c r="D16" s="29">
@@ -6013,7 +6013,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="11" t="s">
         <v>337</v>
       </c>
       <c r="D17" s="29">
@@ -6046,13 +6046,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D20" s="51" t="s">
         <v>101</v>
@@ -6071,7 +6071,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="11" t="s">
         <v>339</v>
       </c>
       <c r="D21" s="28">
@@ -6091,7 +6091,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="11" t="s">
         <v>301</v>
       </c>
       <c r="D22" s="50" t="s">
@@ -6111,7 +6111,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D23" s="28">
@@ -6131,7 +6131,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="11" t="s">
         <v>340</v>
       </c>
       <c r="D24" s="26">
@@ -6151,16 +6151,16 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6191,14 +6191,14 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="52" t="s">
@@ -6231,7 +6231,7 @@
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="11" t="s">
         <v>340</v>
       </c>
       <c r="C6" s="54">
@@ -6251,7 +6251,7 @@
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="11" t="s">
         <v>299</v>
       </c>
       <c r="C7" s="55">
@@ -6271,7 +6271,7 @@
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="11" t="s">
         <v>267</v>
       </c>
       <c r="C8" s="55">
@@ -6291,7 +6291,7 @@
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="11" t="s">
         <v>268</v>
       </c>
       <c r="C9" s="55">
@@ -6311,7 +6311,7 @@
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="11" t="s">
         <v>269</v>
       </c>
       <c r="C10" s="55">
@@ -6331,7 +6331,7 @@
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="10" t="s">
         <v>248</v>
       </c>
       <c r="C11" s="56">
@@ -6351,7 +6351,7 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="10" t="s">
         <v>304</v>
       </c>
       <c r="C12" s="56">
@@ -6371,7 +6371,7 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="10" t="s">
         <v>339</v>
       </c>
       <c r="C13" s="57">
@@ -6391,7 +6391,7 @@
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="10" t="s">
         <v>217</v>
       </c>
       <c r="C14" s="55">
@@ -6411,7 +6411,7 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="10" t="s">
         <v>350</v>
       </c>
       <c r="C15" s="58">
@@ -6431,7 +6431,7 @@
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="10" t="s">
         <v>351</v>
       </c>
       <c r="C16" s="57">
@@ -6451,7 +6451,7 @@
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="10" t="s">
         <v>352</v>
       </c>
       <c r="C17" s="57">
@@ -6471,7 +6471,7 @@
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="10" t="s">
         <v>301</v>
       </c>
       <c r="C18" s="59" t="s">
@@ -6491,7 +6491,7 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="10" t="s">
         <v>353</v>
       </c>
       <c r="C19" s="60" t="s">
@@ -6503,7 +6503,7 @@
       <c r="G19" s="60"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="10" t="s">
         <v>354</v>
       </c>
       <c r="C20" s="60" t="s">
@@ -6630,11 +6630,11 @@
       <c r="B30" s="39" t="s">
         <v>379</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="64" t="s">
@@ -6784,39 +6784,39 @@
       <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>2</v>
+      <c r="A5" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
+      <c r="A6" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
+      <c r="A7" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>8</v>
+      <c r="A8" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="11" t="s">
         <v>96</v>
       </c>
       <c r="B9" s="18" t="s">
@@ -6824,23 +6824,23 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>14</v>
+      <c r="A10" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>16</v>
+      <c r="A11" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="11" t="s">
         <v>98</v>
       </c>
       <c r="B12" s="18">
@@ -6848,7 +6848,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="11" t="s">
         <v>99</v>
       </c>
       <c r="B13" s="18">
@@ -6868,7 +6868,7 @@
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>101</v>
@@ -6887,7 +6887,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="11" t="s">
         <v>106</v>
       </c>
       <c r="B17" s="20">
@@ -6935,13 +6935,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D21" s="21">
@@ -6952,13 +6952,13 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D22" s="21">
@@ -6969,13 +6969,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D23" s="21">
@@ -6986,13 +6986,13 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D24" s="21">
@@ -7003,13 +7003,13 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="11" t="s">
         <v>124</v>
       </c>
       <c r="D25" s="21">
@@ -7054,13 +7054,13 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="11" t="s">
         <v>134</v>
       </c>
       <c r="D29" s="23">
@@ -7077,13 +7077,13 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="11" t="s">
         <v>134</v>
       </c>
       <c r="D30" s="23">
@@ -7100,13 +7100,13 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="11" t="s">
         <v>138</v>
       </c>
       <c r="D31" s="23">
@@ -7151,13 +7151,13 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="11" t="s">
         <v>142</v>
       </c>
       <c r="D35" s="21">
@@ -7168,13 +7168,13 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="11" t="s">
         <v>142</v>
       </c>
       <c r="D36" s="21">
@@ -7185,13 +7185,13 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D37" s="21">
@@ -7202,13 +7202,13 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D38" s="21">
@@ -7219,13 +7219,13 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D39" s="21">
@@ -7236,13 +7236,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D40" s="21">
@@ -7281,10 +7281,10 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="11" t="s">
         <v>155</v>
       </c>
       <c r="C44" s="21">
@@ -7309,7 +7309,7 @@
       <c r="G46" s="17"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="11" t="s">
         <v>157</v>
       </c>
       <c r="B47" s="22">
@@ -7320,7 +7320,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="11" t="s">
         <v>159</v>
       </c>
       <c r="B48" s="22">
@@ -7331,7 +7331,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B49" s="23">
@@ -7339,7 +7339,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="11" t="s">
         <v>162</v>
       </c>
       <c r="B50" s="21">
@@ -7347,7 +7347,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="11" t="s">
         <v>163</v>
       </c>
       <c r="B51" s="18" t="s">
@@ -7380,119 +7380,119 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="B1" s="15"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="11" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
+      <c r="A4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
+      <c r="A5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="11" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
+      <c r="A7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>17</v>
+      <c r="B8" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="11" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="11" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="11" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="11" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="11" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="11" t="s">
         <v>180</v>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7533,7 +7533,7 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>101</v>
@@ -7562,7 +7562,7 @@
       <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="10" t="s">
         <v>106</v>
       </c>
       <c r="B6" s="25">
@@ -7582,7 +7582,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="11" t="s">
         <v>99</v>
       </c>
       <c r="B7" s="26">
@@ -7590,7 +7590,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="11" t="s">
         <v>182</v>
       </c>
       <c r="B8" s="27">
@@ -7610,10 +7610,10 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="11" t="s">
         <v>184</v>
       </c>
       <c r="C10" s="28">
@@ -7665,7 +7665,7 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>101</v>
@@ -7694,7 +7694,7 @@
       <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="11" t="s">
         <v>187</v>
       </c>
       <c r="B5" s="29">
@@ -7714,7 +7714,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="11" t="s">
         <v>188</v>
       </c>
       <c r="B6" s="29">
@@ -7734,7 +7734,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="11" t="s">
         <v>189</v>
       </c>
       <c r="B7" s="29">
@@ -7754,7 +7754,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="11" t="s">
         <v>190</v>
       </c>
       <c r="B8" s="29">
@@ -7774,7 +7774,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="11" t="s">
         <v>191</v>
       </c>
       <c r="B9" s="29">
@@ -7848,7 +7848,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7881,10 +7881,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="11" t="s">
         <v>133</v>
       </c>
       <c r="C4" s="31">
@@ -7904,10 +7904,10 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="11" t="s">
         <v>136</v>
       </c>
       <c r="C5" s="31">
@@ -7927,10 +7927,10 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="11" t="s">
         <v>136</v>
       </c>
       <c r="C6" s="31">
@@ -7962,7 +7962,7 @@
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>101</v>
@@ -7981,7 +7981,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="10" t="s">
         <v>196</v>
       </c>
       <c r="B10" s="30">
@@ -8001,7 +8001,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="11" t="s">
         <v>197</v>
       </c>
       <c r="B11" s="28">
@@ -8021,7 +8021,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="11" t="s">
         <v>198</v>
       </c>
       <c r="B12" s="33">
@@ -8076,7 +8076,7 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>101</v>
@@ -8105,7 +8105,7 @@
       <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="11" t="s">
         <v>200</v>
       </c>
       <c r="B5" s="29">
@@ -8125,7 +8125,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="10" t="s">
         <v>201</v>
       </c>
       <c r="B6" s="34">
@@ -8160,7 +8160,7 @@
       <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="11" t="s">
         <v>202</v>
       </c>
       <c r="B8" s="29">
@@ -8180,7 +8180,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="10" t="s">
         <v>203</v>
       </c>
       <c r="B9" s="34">
@@ -8215,7 +8215,7 @@
       <c r="F10" s="17"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="11" t="s">
         <v>204</v>
       </c>
       <c r="B11" s="29">
@@ -8235,7 +8235,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="11" t="s">
         <v>205</v>
       </c>
       <c r="B12" s="29">
@@ -8255,7 +8255,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="11" t="s">
         <v>206</v>
       </c>
       <c r="B13" s="29">
@@ -8275,7 +8275,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="10" t="s">
         <v>207</v>
       </c>
       <c r="B14" s="34">
@@ -8310,7 +8310,7 @@
       <c r="F15" s="17"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="11" t="s">
         <v>208</v>
       </c>
       <c r="B16" s="29">
@@ -8330,7 +8330,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="10" t="s">
         <v>209</v>
       </c>
       <c r="B17" s="34">
@@ -8435,10 +8435,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="11" t="s">
         <v>155</v>
       </c>
       <c r="C4" s="21">
@@ -8455,7 +8455,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="10" t="s">
         <v>213</v>
       </c>
       <c r="F6" s="30">
@@ -8463,7 +8463,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="10" t="s">
         <v>214</v>
       </c>
       <c r="F7" s="34">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="382">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1396,7 +1396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1419,6 +1419,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2184,22 +2185,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2207,49 +2208,49 @@
       <c r="A4" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="36">
         <v>12</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="36">
         <v>18</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="36">
         <v>22</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="36">
         <v>25</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="36">
         <v>25</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>144000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>222480</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>280078</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>327818</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>337653</v>
       </c>
     </row>
@@ -2257,19 +2258,19 @@
       <c r="A8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>3000</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>4635</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>5835</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>6830</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>7034</v>
       </c>
     </row>
@@ -2277,19 +2278,19 @@
       <c r="A9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>84000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>129780</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>163379</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>191227</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>196964</v>
       </c>
     </row>
@@ -2297,19 +2298,19 @@
       <c r="A10" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <v>5000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>5150</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>5305</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>5464</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>5628</v>
       </c>
     </row>
@@ -2317,43 +2318,43 @@
       <c r="A11" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <v>-10</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>-10</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>-11</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>-11</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>-11</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>SUM(B7:B11)</f>
         <v>221600</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>SUM(C7:C11)</f>
         <v>339797</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>SUM(D7:D11)</f>
         <v>426588</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>SUM(E7:E11)</f>
         <v>498557</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>SUM(F7:F11)</f>
         <v>513513</v>
       </c>
@@ -2362,19 +2363,19 @@
       <c r="A14" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>18467</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>18878</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>19390</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>19942</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>20541</v>
       </c>
     </row>
@@ -2413,52 +2414,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>47869</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>59166</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>60941</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>62769</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>64652</v>
       </c>
     </row>
@@ -2466,19 +2467,19 @@
       <c r="A6" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>12559</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>15523</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>15989</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>16468</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>16963</v>
       </c>
     </row>
@@ -2486,54 +2487,54 @@
       <c r="A7" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="35">
         <f>SUM(B5:B6)</f>
         <v>60428</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="35">
         <f>SUM(C5:C6)</f>
         <v>74689</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="35">
         <f>SUM(D5:D6)</f>
         <v>76930</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="35">
         <f>SUM(E5:E6)</f>
         <v>79237</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="35">
         <f>SUM(F5:F6)</f>
         <v>81615</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>58506</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>72314</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>74483</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>76718</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>79019</v>
       </c>
     </row>
@@ -2541,48 +2542,48 @@
       <c r="A10" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>SUM(B9:B9)</f>
         <v>58506</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>SUM(C9:C9)</f>
         <v>72314</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="35">
         <f>SUM(D9:D9)</f>
         <v>74483</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="35">
         <f>SUM(E9:E9)</f>
         <v>76718</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <f>SUM(F9:F9)</f>
         <v>79019</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>B7+B10</f>
         <v>118934</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>C7+C10</f>
         <v>147003</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>D7+D10</f>
         <v>151413</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>E7+E10</f>
         <v>155955</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>F7+F10</f>
         <v>160634</v>
       </c>
@@ -2622,52 +2623,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>120000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>222480</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>280078</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>327818</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>337653</v>
       </c>
     </row>
@@ -2675,19 +2676,19 @@
       <c r="A6" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>2500</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>4635</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>5835</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>6830</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>7034</v>
       </c>
     </row>
@@ -2695,19 +2696,19 @@
       <c r="A7" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>70000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>129780</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>163379</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>191227</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>196964</v>
       </c>
     </row>
@@ -2715,19 +2716,19 @@
       <c r="A8" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>4167</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>5150</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>5305</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>5464</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>5628</v>
       </c>
     </row>
@@ -2735,19 +2736,19 @@
       <c r="A9" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>-8</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>-10</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>-11</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>-11</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>-11</v>
       </c>
     </row>
@@ -2755,54 +2756,54 @@
       <c r="A10" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>SUM(B5:B9)</f>
         <v>184667</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>SUM(C5:C9)</f>
         <v>339797</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="35">
         <f>SUM(D5:D9)</f>
         <v>426588</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="35">
         <f>SUM(E5:E9)</f>
         <v>498557</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <f>SUM(F5:F9)</f>
         <v>513513</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <v>58506</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>72314</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>74483</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>76718</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>79019</v>
       </c>
     </row>
@@ -2810,19 +2811,19 @@
       <c r="A14" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>47869</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>59166</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>60941</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>62769</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>64652</v>
       </c>
     </row>
@@ -2830,19 +2831,19 @@
       <c r="A15" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>12559</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>15523</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>15989</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>16468</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>16963</v>
       </c>
     </row>
@@ -2850,39 +2851,39 @@
       <c r="A16" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="35">
         <f>SUM(B13:B15)</f>
         <v>118934</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="35">
         <f>SUM(C13:C15)</f>
         <v>147003</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="35">
         <f>SUM(D13:D15)</f>
         <v>151413</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="35">
         <f>SUM(E13:E15)</f>
         <v>155955</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="35">
         <f>SUM(F13:F15)</f>
         <v>160634</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="37" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2890,24 +2891,24 @@
       <c r="A20" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <v>5000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>9270</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>11670</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>13659</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>14069</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="37" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2915,24 +2916,24 @@
       <c r="A22" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <v>3000</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>5562</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>7002</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>8195</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>8441</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="37" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2940,19 +2941,19 @@
       <c r="A24" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="30">
         <v>25000</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>30900</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>31827</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>32782</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>33765</v>
       </c>
     </row>
@@ -2960,19 +2961,19 @@
       <c r="A25" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="30">
         <v>3000</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>3708</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>3819</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>3934</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>4052</v>
       </c>
     </row>
@@ -2980,19 +2981,19 @@
       <c r="A26" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="30">
         <v>2000</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <v>2472</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <v>2546</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <v>2623</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <v>2701</v>
       </c>
     </row>
@@ -3000,29 +3001,29 @@
       <c r="A27" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B27" s="34">
+      <c r="B27" s="35">
         <f>SUM(B24:B26)</f>
         <v>30000</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <f>SUM(C24:C26)</f>
         <v>37080</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="35">
         <f>SUM(D24:D26)</f>
         <v>38192</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <f>SUM(E24:E26)</f>
         <v>39338</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="35">
         <f>SUM(F24:F26)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="37" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3030,19 +3031,19 @@
       <c r="A29" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="30">
         <v>2500</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>3090</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>3183</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <v>3278</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <v>3377</v>
       </c>
     </row>
@@ -3050,58 +3051,58 @@
       <c r="A30" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="35">
         <f>B20+B22+B27+B29</f>
         <v>40500</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <f>C20+C22+C27+C29</f>
         <v>55002</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <f>D20+D22+D27+D29</f>
         <v>60047</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="35">
         <f>E20+E22+E27+E29</f>
         <v>64471</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <f>F20+F22+F27+F29</f>
         <v>66405</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B33" s="34" t="str">
+      <c r="B33" s="35" t="str">
         <f>SUM(B33:B32)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="34" t="str">
+      <c r="C33" s="35" t="str">
         <f>SUM(C33:C32)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="34" t="str">
+      <c r="D33" s="35" t="str">
         <f>SUM(D33:D32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="34" t="str">
+      <c r="E33" s="35" t="str">
         <f>SUM(E33:E32)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="34" t="str">
+      <c r="F33" s="35" t="str">
         <f>SUM(F33:F32)</f>
         <v>0</v>
       </c>
@@ -3141,22 +3142,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3164,23 +3165,23 @@
       <c r="A4" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="33">
         <f>'Budget Detail'!B10</f>
         <v>184667</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="33">
         <f>'Budget Detail'!C10</f>
         <v>339797</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="33">
         <f>'Budget Detail'!D10</f>
         <v>426588</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="33">
         <f>'Budget Detail'!E10</f>
         <v>498557</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="33">
         <f>'Budget Detail'!F10</f>
         <v>513513</v>
       </c>
@@ -3189,23 +3190,23 @@
       <c r="A5" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="33">
         <f>'Budget Detail'!B16</f>
         <v>118934</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="33">
         <f>'Budget Detail'!C16</f>
         <v>147003</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="33">
         <f>'Budget Detail'!D16</f>
         <v>151413</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="33">
         <f>'Budget Detail'!E16</f>
         <v>155955</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="33">
         <f>'Budget Detail'!F16</f>
         <v>160634</v>
       </c>
@@ -3214,23 +3215,23 @@
       <c r="A6" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="33">
         <f>'Budget Detail'!B30</f>
         <v>40500</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <f>'Budget Detail'!C30</f>
         <v>55002</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="33">
         <f>'Budget Detail'!D30</f>
         <v>60047</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="33">
         <f>'Budget Detail'!E30</f>
         <v>64471</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="33">
         <f>'Budget Detail'!F30</f>
         <v>66405</v>
       </c>
@@ -3239,23 +3240,23 @@
       <c r="A7" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="32" t="str">
+      <c r="B7" s="33" t="str">
         <f>'Budget Detail'!B33</f>
         <v>0</v>
       </c>
-      <c r="C7" s="32" t="str">
+      <c r="C7" s="33" t="str">
         <f>'Budget Detail'!C33</f>
         <v>0</v>
       </c>
-      <c r="D7" s="32" t="str">
+      <c r="D7" s="33" t="str">
         <f>'Budget Detail'!D33</f>
         <v>0</v>
       </c>
-      <c r="E7" s="32" t="str">
+      <c r="E7" s="33" t="str">
         <f>'Budget Detail'!E33</f>
         <v>0</v>
       </c>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="33" t="str">
         <f>'Budget Detail'!F33</f>
         <v>0</v>
       </c>
@@ -3264,58 +3265,58 @@
       <c r="A8" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="35">
         <f>SUM(B5:B7)</f>
         <v>159434</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <f>SUM(C5:C7)</f>
         <v>202005</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="35">
         <f>SUM(D5:D7)</f>
         <v>211460</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="35">
         <f>SUM(E5:E7)</f>
         <v>220426</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="35">
         <f>SUM(F5:F7)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>B4-B8</f>
         <v>25233</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>C4-C8</f>
         <v>137792</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>D4-D8</f>
         <v>215128</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>E4-E8</f>
         <v>278131</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>F4-F8</f>
         <v>286475</v>
       </c>
@@ -3324,23 +3325,23 @@
       <c r="A12" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.40551379</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.50429993</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.55787178</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.55787178</v>
       </c>
@@ -3349,19 +3350,19 @@
       <c r="A13" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <v>25233</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>163025</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>378153</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>656284</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>942758</v>
       </c>
     </row>
@@ -3369,19 +3370,19 @@
       <c r="A14" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>15389</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>18878</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>19390</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>19942</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>20541</v>
       </c>
     </row>
@@ -3389,19 +3390,19 @@
       <c r="A15" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>13286</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>11222</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>9612</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>8817</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>9082</v>
       </c>
     </row>
@@ -3449,171 +3450,171 @@
       <c r="N1" s="15"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="20" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="35">
         <v>9150</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="35">
         <v>22110</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="35">
         <v>22110</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="35">
         <v>22110</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="35">
         <v>22110</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="35">
         <v>22110</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="35">
         <v>22110</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="35">
         <v>22110</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="35">
         <v>22110</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="35">
         <v>22110</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="35">
         <v>13210</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="35">
         <v>250</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="35">
         <f>SUM(B4:M4)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>11893</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>11893</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>11893</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>11893</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>11893</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <v>11893</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="30">
         <v>11893</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="30">
         <v>11893</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="30">
         <v>11893</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="30">
         <v>11893</v>
       </c>
-      <c r="L7" s="29">
-        <v>0</v>
-      </c>
-      <c r="M7" s="29">
-        <v>0</v>
-      </c>
-      <c r="N7" s="29">
+      <c r="L7" s="30">
+        <v>0</v>
+      </c>
+      <c r="M7" s="30">
+        <v>0</v>
+      </c>
+      <c r="N7" s="30">
         <f>SUM(B7:M7)</f>
         <v>118934</v>
       </c>
@@ -3622,43 +3623,43 @@
       <c r="A8" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>4050</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>4050</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>4050</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>4050</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>4050</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="30">
         <v>4050</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="30">
         <v>4050</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="30">
         <v>4050</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="30">
         <v>4050</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="30">
         <v>4050</v>
       </c>
-      <c r="L8" s="29">
-        <v>0</v>
-      </c>
-      <c r="M8" s="29">
-        <v>0</v>
-      </c>
-      <c r="N8" s="29">
+      <c r="L8" s="30">
+        <v>0</v>
+      </c>
+      <c r="M8" s="30">
+        <v>0</v>
+      </c>
+      <c r="N8" s="30">
         <f>SUM(B8:M8)</f>
         <v>40500</v>
       </c>
@@ -3667,118 +3668,118 @@
       <c r="A9" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B9" s="29">
-        <v>0</v>
-      </c>
-      <c r="C9" s="29">
-        <v>0</v>
-      </c>
-      <c r="D9" s="29">
-        <v>0</v>
-      </c>
-      <c r="E9" s="29">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29">
-        <v>0</v>
-      </c>
-      <c r="G9" s="29">
-        <v>0</v>
-      </c>
-      <c r="H9" s="29">
-        <v>0</v>
-      </c>
-      <c r="I9" s="29">
-        <v>0</v>
-      </c>
-      <c r="J9" s="29">
-        <v>0</v>
-      </c>
-      <c r="K9" s="29">
-        <v>0</v>
-      </c>
-      <c r="L9" s="29">
-        <v>0</v>
-      </c>
-      <c r="M9" s="29">
-        <v>0</v>
-      </c>
-      <c r="N9" s="29" t="str">
+      <c r="B9" s="30">
+        <v>0</v>
+      </c>
+      <c r="C9" s="30">
+        <v>0</v>
+      </c>
+      <c r="D9" s="30">
+        <v>0</v>
+      </c>
+      <c r="E9" s="30">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30">
+        <v>0</v>
+      </c>
+      <c r="G9" s="30">
+        <v>0</v>
+      </c>
+      <c r="H9" s="30">
+        <v>0</v>
+      </c>
+      <c r="I9" s="30">
+        <v>0</v>
+      </c>
+      <c r="J9" s="30">
+        <v>0</v>
+      </c>
+      <c r="K9" s="30">
+        <v>0</v>
+      </c>
+      <c r="L9" s="30">
+        <v>0</v>
+      </c>
+      <c r="M9" s="30">
+        <v>0</v>
+      </c>
+      <c r="N9" s="30" t="str">
         <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>B7+B8+B9</f>
         <v>15943</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>C7+C8+C9</f>
         <v>15943</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <f>D7+D8+D9</f>
         <v>15943</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>E7+E8+E9</f>
         <v>15943</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <f>F7+F8+F9</f>
         <v>15943</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="33">
         <f>G7+G8+G9</f>
         <v>15943</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="33">
         <f>H7+H8+H9</f>
         <v>15943</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="33">
         <f>I7+I8+I9</f>
         <v>15943</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="33">
         <f>J7+J8+J9</f>
         <v>15943</v>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="33">
         <f>K7+K8+K9</f>
         <v>15943</v>
       </c>
-      <c r="L12" s="32" t="str">
+      <c r="L12" s="33" t="str">
         <f>L7+L8+L9</f>
         <v>0</v>
       </c>
-      <c r="M12" s="32" t="str">
+      <c r="M12" s="33" t="str">
         <f>M7+M8+M9</f>
         <v>0</v>
       </c>
-      <c r="N12" s="32">
+      <c r="N12" s="33">
         <f>SUM(B12:M12)</f>
         <v>159430</v>
       </c>
@@ -3787,55 +3788,55 @@
       <c r="A13" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>B4-B12</f>
         <v>-6793</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>C4-C12</f>
         <v>6167</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>D4-D12</f>
         <v>6167</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>E4-E12</f>
         <v>6167</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>F4-F12</f>
         <v>6167</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="33">
         <f>G4-G12</f>
         <v>6167</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="33">
         <f>H4-H12</f>
         <v>6167</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="33">
         <f>I4-I12</f>
         <v>6167</v>
       </c>
-      <c r="J13" s="32">
+      <c r="J13" s="33">
         <f>J4-J12</f>
         <v>6167</v>
       </c>
-      <c r="K13" s="32">
+      <c r="K13" s="33">
         <f>K4-K12</f>
         <v>6167</v>
       </c>
-      <c r="L13" s="32">
+      <c r="L13" s="33">
         <f>L4-L12</f>
         <v>13210</v>
       </c>
-      <c r="M13" s="32">
+      <c r="M13" s="33">
         <f>M4-M12</f>
         <v>250</v>
       </c>
-      <c r="N13" s="32">
+      <c r="N13" s="33">
         <f>SUM(B13:M13)</f>
         <v>62170</v>
       </c>
@@ -3844,71 +3845,71 @@
       <c r="A14" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="38">
         <f>B17+B13</f>
         <v>-6793</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="38">
         <f>B14+C13</f>
         <v>-626</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="38">
         <f>C14+D13</f>
         <v>5541</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="38">
         <f>D14+E13</f>
         <v>11708</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="38">
         <f>E14+F13</f>
         <v>17875</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="38">
         <f>F14+G13</f>
         <v>24042</v>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="38">
         <f>G14+H13</f>
         <v>30209</v>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="38">
         <f>H14+I13</f>
         <v>36376</v>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="38">
         <f>I14+J13</f>
         <v>42543</v>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="38">
         <f>J14+K13</f>
         <v>48710</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="38">
         <f>K14+L13</f>
         <v>61920</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="38">
         <f>L14+M13</f>
         <v>62170</v>
       </c>
-      <c r="N14" s="30">
+      <c r="N14" s="31">
         <f>M14</f>
         <v>62170</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="22">
         <v>0</v>
       </c>
     </row>
@@ -3916,7 +3917,7 @@
       <c r="A18" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="38">
         <f>M14</f>
         <v>62170</v>
       </c>
@@ -3925,7 +3926,7 @@
       <c r="A19" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <f>MIN(B14:M14)</f>
         <v>-6793</v>
       </c>
@@ -3965,82 +3966,82 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="35">
         <v>184667</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="35">
         <v>339797</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="35">
         <v>426588</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="35">
         <v>498557</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <v>513513</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="33">
         <v>118934</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <v>147003</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <v>151413</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <v>155955</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <v>160634</v>
       </c>
     </row>
@@ -4048,19 +4049,19 @@
       <c r="A9" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <v>40500</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <v>55002</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <v>60047</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <v>64471</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <v>66405</v>
       </c>
     </row>
@@ -4068,78 +4069,78 @@
       <c r="A10" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="B10" s="32">
-        <v>0</v>
-      </c>
-      <c r="C10" s="32">
-        <v>0</v>
-      </c>
-      <c r="D10" s="32">
-        <v>0</v>
-      </c>
-      <c r="E10" s="32">
-        <v>0</v>
-      </c>
-      <c r="F10" s="32">
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33">
+        <v>0</v>
+      </c>
+      <c r="D10" s="33">
+        <v>0</v>
+      </c>
+      <c r="E10" s="33">
+        <v>0</v>
+      </c>
+      <c r="F10" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <f>SUM(B8:B10)</f>
         <v>159434</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="35">
         <f>SUM(C8:C10)</f>
         <v>202005</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="35">
         <f>SUM(D8:D10)</f>
         <v>211460</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="35">
         <f>SUM(E8:E10)</f>
         <v>220426</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="35">
         <f>SUM(F8:F10)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <f>B5-B11</f>
         <v>25233</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>C5-C11</f>
         <v>137792</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>D5-D11</f>
         <v>215128</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>E5-E11</f>
         <v>278131</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>F5-F11</f>
         <v>286475</v>
       </c>
@@ -4148,23 +4149,23 @@
       <c r="A15" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="29">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.40551379</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.50429993</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.55787178</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.55787178</v>
       </c>
@@ -4204,49 +4205,49 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="41" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4285,56 +4286,56 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="43">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>62170</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>199962</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>415091</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>693221</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>979696</v>
       </c>
@@ -4343,19 +4344,19 @@
       <c r="A6" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B6" s="29">
-        <v>0</v>
-      </c>
-      <c r="C6" s="29">
-        <v>0</v>
-      </c>
-      <c r="D6" s="29">
-        <v>0</v>
-      </c>
-      <c r="E6" s="29">
-        <v>0</v>
-      </c>
-      <c r="F6" s="29">
+      <c r="B6" s="30">
+        <v>0</v>
+      </c>
+      <c r="C6" s="30">
+        <v>0</v>
+      </c>
+      <c r="D6" s="30">
+        <v>0</v>
+      </c>
+      <c r="E6" s="30">
+        <v>0</v>
+      </c>
+      <c r="F6" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4363,19 +4364,19 @@
       <c r="A7" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>5000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>5000</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>5000</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>5000</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>5000</v>
       </c>
     </row>
@@ -4383,19 +4384,19 @@
       <c r="A8" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B8" s="29">
-        <v>0</v>
-      </c>
-      <c r="C8" s="29">
-        <v>0</v>
-      </c>
-      <c r="D8" s="29">
-        <v>0</v>
-      </c>
-      <c r="E8" s="29">
-        <v>0</v>
-      </c>
-      <c r="F8" s="29">
+      <c r="B8" s="30">
+        <v>0</v>
+      </c>
+      <c r="C8" s="30">
+        <v>0</v>
+      </c>
+      <c r="D8" s="30">
+        <v>0</v>
+      </c>
+      <c r="E8" s="30">
+        <v>0</v>
+      </c>
+      <c r="F8" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4403,54 +4404,54 @@
       <c r="A9" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="35">
         <f>SUM(B5:B8)</f>
         <v>67170</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <f>SUM(C5:C8)</f>
         <v>204962</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="35">
         <f>SUM(D5:D8)</f>
         <v>420091</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="35">
         <f>SUM(E5:E8)</f>
         <v>698221</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>SUM(F5:F8)</f>
         <v>984696</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B12" s="29">
-        <v>0</v>
-      </c>
-      <c r="C12" s="29">
-        <v>0</v>
-      </c>
-      <c r="D12" s="29">
-        <v>0</v>
-      </c>
-      <c r="E12" s="29">
-        <v>0</v>
-      </c>
-      <c r="F12" s="29">
+      <c r="B12" s="30">
+        <v>0</v>
+      </c>
+      <c r="C12" s="30">
+        <v>0</v>
+      </c>
+      <c r="D12" s="30">
+        <v>0</v>
+      </c>
+      <c r="E12" s="30">
+        <v>0</v>
+      </c>
+      <c r="F12" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4458,19 +4459,19 @@
       <c r="A13" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B13" s="29">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29">
+      <c r="B13" s="30">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4478,58 +4479,58 @@
       <c r="A14" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="34" t="str">
+      <c r="B14" s="35" t="str">
         <f>SUM(B12:B13)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="34" t="str">
+      <c r="C14" s="35" t="str">
         <f>SUM(C12:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="34" t="str">
+      <c r="D14" s="35" t="str">
         <f>SUM(D12:D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="34" t="str">
+      <c r="E14" s="35" t="str">
         <f>SUM(E12:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="34" t="str">
+      <c r="F14" s="35" t="str">
         <f>SUM(F12:F13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <f>B9-B14</f>
         <v>67170</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>C9-C14</f>
         <v>204962</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>D9-D14</f>
         <v>420091</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>E9-E14</f>
         <v>698221</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>F9-F14</f>
         <v>984696</v>
       </c>
@@ -4538,23 +4539,23 @@
       <c r="A19" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="B19" s="43" t="str">
+      <c r="B19" s="44" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="43" t="str">
+      <c r="C19" s="44" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="43" t="str">
+      <c r="D19" s="44" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="43" t="str">
+      <c r="E19" s="44" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="43" t="str">
+      <c r="F19" s="44" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -4594,52 +4595,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>184667</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>339797</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>426588</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>498557</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>513513</v>
       </c>
     </row>
@@ -4647,19 +4648,19 @@
       <c r="A6" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>118934</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>147003</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>151413</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>155955</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>160634</v>
       </c>
     </row>
@@ -4667,19 +4668,19 @@
       <c r="A7" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>40500</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>55002</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>60047</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>64471</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>66405</v>
       </c>
     </row>
@@ -4687,23 +4688,23 @@
       <c r="A8" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="33">
         <f>B5-B6-B7</f>
         <v>25233</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <f>C5-C6-C7</f>
         <v>137792</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <f>D5-D6-D7</f>
         <v>215128</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <f>E5-E6-E7</f>
         <v>278131</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <f>F5-F6-F7</f>
         <v>286475</v>
       </c>
@@ -4712,19 +4713,19 @@
       <c r="A9" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B9" s="29">
-        <v>0</v>
-      </c>
-      <c r="C9" s="29">
-        <v>0</v>
-      </c>
-      <c r="D9" s="29">
-        <v>0</v>
-      </c>
-      <c r="E9" s="29">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29">
+      <c r="B9" s="30">
+        <v>0</v>
+      </c>
+      <c r="C9" s="30">
+        <v>0</v>
+      </c>
+      <c r="D9" s="30">
+        <v>0</v>
+      </c>
+      <c r="E9" s="30">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30">
         <v>0</v>
       </c>
     </row>
@@ -4732,49 +4733,49 @@
       <c r="A10" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="45" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>303</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <v>62170</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>199962</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>415091</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>693221</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>979696</v>
       </c>
     </row>
@@ -4782,23 +4783,23 @@
       <c r="A14" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>142</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>361</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>716</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>1148</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>1575</v>
       </c>
@@ -4807,23 +4808,23 @@
       <c r="A15" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="34">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>4.7</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>11.9</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="34">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>23.6</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>37.7</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="34">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>51.8</v>
       </c>
@@ -4832,49 +4833,49 @@
       <c r="A16" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <v>0.48</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <v>0.72</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <v>0.88</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <v>1</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>307</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <v>15389</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>18878</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>19390</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>19942</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>20541</v>
       </c>
     </row>
@@ -4882,19 +4883,19 @@
       <c r="A20" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <v>118934</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>147003</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>151413</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>155955</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>160634</v>
       </c>
     </row>
@@ -4902,19 +4903,19 @@
       <c r="A21" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="30">
         <v>3375</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>3056</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>2729</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>2579</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>2656</v>
       </c>
     </row>
@@ -4922,49 +4923,49 @@
       <c r="A22" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B22" s="45">
+      <c r="B22" s="46">
         <v>10</v>
       </c>
-      <c r="C22" s="45">
+      <c r="C22" s="46">
         <v>10</v>
       </c>
-      <c r="D22" s="45">
+      <c r="D22" s="46">
         <v>10</v>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="46">
         <v>9</v>
       </c>
-      <c r="F22" s="45">
+      <c r="F22" s="46">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="F25" s="47" t="s">
         <v>302</v>
       </c>
     </row>
@@ -4972,19 +4973,19 @@
       <c r="A26" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="E26" s="47" t="s">
+      <c r="E26" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="48" t="s">
         <v>314</v>
       </c>
     </row>
@@ -4992,19 +4993,19 @@
       <c r="A27" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="49" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="D27" s="47" t="s">
+      <c r="D27" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="E27" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="48" t="s">
         <v>314</v>
       </c>
     </row>
@@ -5012,19 +5013,19 @@
       <c r="A28" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="D28" s="47" t="s">
+      <c r="D28" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="E28" s="47" t="s">
+      <c r="E28" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="48" t="s">
         <v>314</v>
       </c>
     </row>
@@ -5032,19 +5033,19 @@
       <c r="A29" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="47" t="s">
+      <c r="E29" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="F29" s="47" t="s">
+      <c r="F29" s="48" t="s">
         <v>314</v>
       </c>
     </row>
@@ -5085,16 +5086,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>319</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="50" t="s">
         <v>320</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>111</v>
       </c>
     </row>
@@ -5102,13 +5103,13 @@
       <c r="A4" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <v>20000</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>15000</v>
       </c>
     </row>
@@ -5116,7 +5117,7 @@
       <c r="D5" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>5000</v>
       </c>
     </row>
@@ -5124,13 +5125,13 @@
       <c r="A7" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>20000</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>20000</v>
       </c>
     </row>
@@ -5138,7 +5139,7 @@
       <c r="A8" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="44">
         <v>0</v>
       </c>
     </row>
@@ -5493,37 +5494,37 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>328</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5531,19 +5532,19 @@
       <c r="A6" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>184667</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>339797</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>426588</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>498557</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>513513</v>
       </c>
     </row>
@@ -5551,19 +5552,19 @@
       <c r="A7" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>159434</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>202005</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>211460</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>220426</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>227039</v>
       </c>
     </row>
@@ -5571,19 +5572,19 @@
       <c r="A8" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>25233</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>137792</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>215128</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>278131</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>286475</v>
       </c>
     </row>
@@ -5591,19 +5592,19 @@
       <c r="A9" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="29">
         <v>0.13663808664259927</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <v>0.40551379205819943</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>0.5042999253916937</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>0.5578717808219178</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>0.5578717808219178</v>
       </c>
     </row>
@@ -5611,19 +5612,19 @@
       <c r="A10" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="51" t="s">
         <v>302</v>
       </c>
     </row>
@@ -5631,54 +5632,54 @@
       <c r="A11" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <v>10</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <v>10</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <v>10</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <v>9</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5686,19 +5687,19 @@
       <c r="A16" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <v>147733</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>271838</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>341270</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>398845</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>410811</v>
       </c>
     </row>
@@ -5706,19 +5707,19 @@
       <c r="A17" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <v>159434</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>202005</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>211460</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>220426</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>227039</v>
       </c>
     </row>
@@ -5726,19 +5727,19 @@
       <c r="A18" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <v>-11701</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>69833</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>129811</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>178419</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>183772</v>
       </c>
     </row>
@@ -5746,19 +5747,19 @@
       <c r="A19" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="29">
         <v>-0.07920239169675096</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <v>0.2568922400727494</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <v>0.38037490673961705</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="29">
         <v>0.4473397260273973</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="29">
         <v>0.44733972602739736</v>
       </c>
     </row>
@@ -5766,19 +5767,19 @@
       <c r="A20" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="D20" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="51" t="s">
         <v>302</v>
       </c>
     </row>
@@ -5786,19 +5787,19 @@
       <c r="A21" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <v>12</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <v>10</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <v>10</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <v>10</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <v>10</v>
       </c>
     </row>
@@ -5841,10 +5842,10 @@
       <c r="H1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -5895,16 +5896,16 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -5916,19 +5917,19 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="51" t="s">
+      <c r="F12" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="51" t="s">
+      <c r="G12" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="51" t="s">
+      <c r="H12" s="52" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5936,19 +5937,19 @@
       <c r="A13" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>184667</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>339797</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>426588</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <v>498557</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <v>513513</v>
       </c>
     </row>
@@ -5956,19 +5957,19 @@
       <c r="A14" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>159434</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>202005</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>211460</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <v>220426</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <v>227039</v>
       </c>
     </row>
@@ -5976,19 +5977,19 @@
       <c r="A15" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>25233</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>137792</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>215128</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="30">
         <v>278131</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="30">
         <v>286475</v>
       </c>
     </row>
@@ -5996,19 +5997,19 @@
       <c r="A16" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>62170</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>199962</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>415091</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <v>693221</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="30">
         <v>979696</v>
       </c>
     </row>
@@ -6016,33 +6017,33 @@
       <c r="A17" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="D17" s="29">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29">
+      <c r="D17" s="30">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -6054,19 +6055,19 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="51" t="s">
+      <c r="E20" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="51" t="s">
+      <c r="G20" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="51" t="s">
+      <c r="H20" s="52" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6074,19 +6075,19 @@
       <c r="A21" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <v>0.13663808664259927</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <v>0.40551379205819943</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <v>0.5042999253916937</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <v>0.5578717808219178</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <v>0.5578717808219178</v>
       </c>
     </row>
@@ -6094,19 +6095,19 @@
       <c r="A22" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="D22" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="G22" s="50" t="s">
+      <c r="G22" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="H22" s="50" t="s">
+      <c r="H22" s="51" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6114,19 +6115,19 @@
       <c r="A23" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <v>0.48</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <v>0.72</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <v>0.88</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <v>1</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <v>1</v>
       </c>
     </row>
@@ -6134,19 +6135,19 @@
       <c r="A24" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="27">
         <v>12</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <v>18</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="27">
         <v>22</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="27">
         <v>25</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="27">
         <v>25</v>
       </c>
     </row>
@@ -6201,32 +6202,32 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="53" t="s">
         <v>343</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="54" t="s">
         <v>345</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="54" t="s">
         <v>346</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="54" t="s">
         <v>347</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="54" t="s">
         <v>348</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="G5" s="54" t="s">
         <v>349</v>
       </c>
     </row>
@@ -6234,19 +6235,19 @@
       <c r="B6" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="55">
         <v>12</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="55">
         <v>18</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="55">
         <v>22</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="55">
         <v>25</v>
       </c>
-      <c r="G6" s="54">
+      <c r="G6" s="55">
         <v>25</v>
       </c>
     </row>
@@ -6254,19 +6255,19 @@
       <c r="B7" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="56">
         <v>184666.6666666667</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="56">
         <v>339797</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="56">
         <v>426587.88999999996</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="56">
         <v>498556.69375000003</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="56">
         <v>513513.3945625001</v>
       </c>
     </row>
@@ -6274,19 +6275,19 @@
       <c r="B8" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="56">
         <v>118934.16666666667</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="56">
         <v>147002.63</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="56">
         <v>151412.7089</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="56">
         <v>155955.090167</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="56">
         <v>160633.74287201</v>
       </c>
     </row>
@@ -6294,19 +6295,19 @@
       <c r="B9" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="56">
         <v>40500</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="56">
         <v>55002</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="56">
         <v>60046.93999999999</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="56">
         <v>64470.893</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="56">
         <v>66405.01979</v>
       </c>
     </row>
@@ -6314,19 +6315,19 @@
       <c r="B10" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C10" s="55">
-        <v>0</v>
-      </c>
-      <c r="D10" s="55">
-        <v>0</v>
-      </c>
-      <c r="E10" s="55">
-        <v>0</v>
-      </c>
-      <c r="F10" s="55">
-        <v>0</v>
-      </c>
-      <c r="G10" s="55">
+      <c r="C10" s="56">
+        <v>0</v>
+      </c>
+      <c r="D10" s="56">
+        <v>0</v>
+      </c>
+      <c r="E10" s="56">
+        <v>0</v>
+      </c>
+      <c r="F10" s="56">
+        <v>0</v>
+      </c>
+      <c r="G10" s="56">
         <v>0</v>
       </c>
     </row>
@@ -6334,19 +6335,19 @@
       <c r="B11" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="57">
         <v>25232.5</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="57">
         <v>137792.37</v>
       </c>
-      <c r="E11" s="56">
+      <c r="E11" s="57">
         <v>215128.24109999998</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="57">
         <v>278130.71058300004</v>
       </c>
-      <c r="G11" s="56">
+      <c r="G11" s="57">
         <v>286474.6319004901</v>
       </c>
     </row>
@@ -6354,19 +6355,19 @@
       <c r="B12" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="57">
         <v>62170</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="57">
         <v>199962.37</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="57">
         <v>415090.6111</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="57">
         <v>693221.3216830001</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="57">
         <v>979695.9535834901</v>
       </c>
     </row>
@@ -6374,19 +6375,19 @@
       <c r="B13" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="58">
         <v>0.13663808664259927</v>
       </c>
-      <c r="D13" s="57">
+      <c r="D13" s="58">
         <v>0.40551379205819943</v>
       </c>
-      <c r="E13" s="57">
+      <c r="E13" s="58">
         <v>0.5042999253916937</v>
       </c>
-      <c r="F13" s="57">
+      <c r="F13" s="58">
         <v>0.5578717808219178</v>
       </c>
-      <c r="G13" s="57">
+      <c r="G13" s="58">
         <v>0.5578717808219178</v>
       </c>
     </row>
@@ -6394,19 +6395,19 @@
       <c r="B14" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="56">
         <v>15388.88888888889</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="56">
         <v>18877.61111111111</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="56">
         <v>19390.358636363635</v>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="56">
         <v>19942.267750000003</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="56">
         <v>20540.535782500006</v>
       </c>
     </row>
@@ -6414,19 +6415,19 @@
       <c r="B15" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="C15" s="58">
+      <c r="C15" s="59">
         <v>0.644047833935018</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="58">
         <v>0.4326189754471052</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="58">
         <v>0.3549390698831137</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F15" s="58">
         <v>0.3128131506849315</v>
       </c>
-      <c r="G15" s="57">
+      <c r="G15" s="58">
         <v>0.3128131506849315</v>
       </c>
     </row>
@@ -6434,19 +6435,19 @@
       <c r="B16" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="58">
         <v>0.06579422382671479</v>
       </c>
-      <c r="D16" s="57">
+      <c r="D16" s="58">
         <v>0.048560169748408606</v>
       </c>
-      <c r="E16" s="57">
+      <c r="E16" s="58">
         <v>0.04222830141755781</v>
       </c>
-      <c r="F16" s="57">
+      <c r="F16" s="58">
         <v>0.0387945205479452</v>
       </c>
-      <c r="G16" s="57">
+      <c r="G16" s="58">
         <v>0.0387945205479452</v>
       </c>
     </row>
@@ -6454,19 +6455,19 @@
       <c r="B17" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="58">
         <v>0.13663808664259935</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="58">
         <v>0.40551379205819943</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E17" s="58">
         <v>0.5042999253916934</v>
       </c>
-      <c r="F17" s="57">
+      <c r="F17" s="58">
         <v>0.5578717808219178</v>
       </c>
-      <c r="G17" s="57">
+      <c r="G17" s="58">
         <v>0.5578717808219178</v>
       </c>
     </row>
@@ -6474,19 +6475,19 @@
       <c r="B18" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="60" t="s">
         <v>302</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="60" t="s">
         <v>302</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="60" t="s">
         <v>302</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="60" t="s">
         <v>302</v>
       </c>
-      <c r="G18" s="59" t="s">
+      <c r="G18" s="60" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6494,140 +6495,140 @@
       <c r="B19" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="C19" s="60" t="s">
+      <c r="C19" s="61" t="s">
         <v>345</v>
       </c>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="61" t="s">
         <v>355</v>
       </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="18" t="s">
         <v>358</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17" t="s">
+      <c r="E22" s="18"/>
+      <c r="F22" s="18" t="s">
         <v>359</v>
       </c>
-      <c r="G22" s="17"/>
+      <c r="G22" s="18"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="40" t="s">
         <v>360</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="62" t="s">
         <v>361</v>
       </c>
-      <c r="D23" s="62" t="s">
+      <c r="D23" s="63" t="s">
         <v>362</v>
       </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="63" t="s">
+      <c r="E23" s="63"/>
+      <c r="F23" s="64" t="s">
         <v>363</v>
       </c>
-      <c r="G23" s="63"/>
+      <c r="G23" s="64"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="62" t="s">
         <v>361</v>
       </c>
-      <c r="D24" s="62" t="s">
+      <c r="D24" s="63" t="s">
         <v>365</v>
       </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="63" t="s">
+      <c r="E24" s="63"/>
+      <c r="F24" s="64" t="s">
         <v>366</v>
       </c>
-      <c r="G24" s="63"/>
+      <c r="G24" s="64"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="40" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="62" t="s">
         <v>361</v>
       </c>
-      <c r="D25" s="62" t="s">
+      <c r="D25" s="63" t="s">
         <v>368</v>
       </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63" t="s">
+      <c r="E25" s="63"/>
+      <c r="F25" s="64" t="s">
         <v>369</v>
       </c>
-      <c r="G25" s="63"/>
+      <c r="G25" s="64"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="40" t="s">
         <v>370</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="62" t="s">
         <v>361</v>
       </c>
-      <c r="D26" s="62" t="s">
+      <c r="D26" s="63" t="s">
         <v>371</v>
       </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63" t="s">
+      <c r="E26" s="63"/>
+      <c r="F26" s="64" t="s">
         <v>372</v>
       </c>
-      <c r="G26" s="63"/>
+      <c r="G26" s="64"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="40" t="s">
         <v>373</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="62" t="s">
         <v>361</v>
       </c>
-      <c r="D27" s="62" t="s">
+      <c r="D27" s="63" t="s">
         <v>374</v>
       </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63" t="s">
+      <c r="E27" s="63"/>
+      <c r="F27" s="64" t="s">
         <v>375</v>
       </c>
-      <c r="G27" s="63"/>
+      <c r="G27" s="64"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="62" t="s">
         <v>361</v>
       </c>
-      <c r="D28" s="62" t="s">
+      <c r="D28" s="63" t="s">
         <v>377</v>
       </c>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63" t="s">
+      <c r="E28" s="63"/>
+      <c r="F28" s="64" t="s">
         <v>378</v>
       </c>
-      <c r="G28" s="63"/>
+      <c r="G28" s="64"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="40" t="s">
         <v>379</v>
       </c>
       <c r="C30" s="10" t="s">
@@ -6637,14 +6638,14 @@
       <c r="E30" s="10"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="64" t="s">
+      <c r="B32" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="C32" s="64"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -6767,27 +6768,30 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6795,7 +6799,7 @@
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6803,7 +6807,7 @@
       <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6811,7 +6815,7 @@
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6819,7 +6823,7 @@
       <c r="A9" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>97</v>
       </c>
     </row>
@@ -6827,7 +6831,7 @@
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6835,7 +6839,7 @@
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6843,7 +6847,7 @@
       <c r="A12" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>7</v>
       </c>
     </row>
@@ -6851,38 +6855,38 @@
       <c r="A13" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>25</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6890,47 +6894,47 @@
       <c r="A17" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="21">
         <v>12</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <v>18</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <v>22</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <v>25</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>25</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="20" t="s">
         <v>112</v>
       </c>
     </row>
@@ -6944,10 +6948,10 @@
       <c r="C21" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="22">
         <v>12000</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <v>0</v>
       </c>
     </row>
@@ -6961,10 +6965,10 @@
       <c r="C22" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <v>250</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="23">
         <v>0</v>
       </c>
     </row>
@@ -6978,10 +6982,10 @@
       <c r="C23" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="22">
         <v>7000</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="23">
         <v>0</v>
       </c>
     </row>
@@ -6995,10 +6999,10 @@
       <c r="C24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="22">
         <v>5000</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7012,44 +7016,44 @@
       <c r="C25" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="22">
         <v>10</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="20" t="s">
         <v>131</v>
       </c>
     </row>
@@ -7063,16 +7067,16 @@
       <c r="C29" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="24">
         <v>1</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="22">
         <v>55000</v>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="23">
         <v>0.2</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -7086,16 +7090,16 @@
       <c r="C30" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="24">
         <v>1</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="22">
         <v>45000</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="23">
         <v>0.2</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -7109,44 +7113,44 @@
       <c r="C31" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="24">
         <v>0.5</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="22">
         <v>28000</v>
       </c>
-      <c r="F31" s="22">
-        <v>0</v>
-      </c>
-      <c r="G31" s="22">
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
+      <c r="G31" s="23">
         <v>0.0765</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="20" t="s">
         <v>112</v>
       </c>
     </row>
@@ -7160,10 +7164,10 @@
       <c r="C35" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D35" s="21">
+      <c r="D35" s="22">
         <v>2500</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="23">
         <v>0.03</v>
       </c>
     </row>
@@ -7177,10 +7181,10 @@
       <c r="C36" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="21">
+      <c r="D36" s="22">
         <v>300</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7194,10 +7198,10 @@
       <c r="C37" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D37" s="21">
+      <c r="D37" s="22">
         <v>2400</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E37" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7211,10 +7215,10 @@
       <c r="C38" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D38" s="21">
+      <c r="D38" s="22">
         <v>500</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7228,10 +7232,10 @@
       <c r="C39" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="22">
         <v>300</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7245,38 +7249,38 @@
       <c r="C40" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="22">
         <v>3000</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="19" t="s">
+      <c r="A43" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="E43" s="20" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7287,35 +7291,35 @@
       <c r="B44" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C44" s="21">
+      <c r="C44" s="22">
         <v>30000</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="23">
         <v>0.06</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B47" s="22">
+      <c r="B47" s="23">
         <v>0.03</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="25" t="s">
         <v>158</v>
       </c>
     </row>
@@ -7323,10 +7327,10 @@
       <c r="A48" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B48" s="22">
+      <c r="B48" s="23">
         <v>0.03</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="25" t="s">
         <v>160</v>
       </c>
     </row>
@@ -7334,7 +7338,7 @@
       <c r="A49" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B49" s="24">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -7342,7 +7346,7 @@
       <c r="A50" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B50" s="21">
+      <c r="B50" s="22">
         <v>0</v>
       </c>
     </row>
@@ -7350,7 +7354,7 @@
       <c r="A51" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="19" t="s">
         <v>164</v>
       </c>
     </row>
@@ -7532,52 +7536,52 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <v>12</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>18</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>22</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>25</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>25</v>
       </c>
     </row>
@@ -7585,7 +7589,7 @@
       <c r="A7" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <v>25</v>
       </c>
     </row>
@@ -7593,19 +7597,19 @@
       <c r="A8" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <v>0.48</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <v>0.72</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <v>0.88</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <v>1</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <v>1</v>
       </c>
     </row>
@@ -7616,16 +7620,16 @@
       <c r="B10" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <v>0.5</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <v>0.2222222222222222</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <v>0.13636363636363635</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <v>0</v>
       </c>
     </row>
@@ -7664,52 +7668,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>144000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>222480</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>280078</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>327818</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>337653</v>
       </c>
     </row>
@@ -7717,19 +7721,19 @@
       <c r="A6" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>3000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>4635</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>5835</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>6830</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>7034</v>
       </c>
     </row>
@@ -7737,19 +7741,19 @@
       <c r="A7" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>84000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>129780</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>163379</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>191227</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>196964</v>
       </c>
     </row>
@@ -7757,19 +7761,19 @@
       <c r="A8" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>5000</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>5150</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>5305</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>5464</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>5628</v>
       </c>
     </row>
@@ -7777,43 +7781,43 @@
       <c r="A9" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>-10</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>-10</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>-11</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>-11</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>-11</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <f>SUM(B5:B9)</f>
         <v>221600</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>SUM(C5:C9)</f>
         <v>339797</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>SUM(D5:D9)</f>
         <v>426588</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>SUM(E5:E9)</f>
         <v>498557</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>SUM(F5:F9)</f>
         <v>513513</v>
       </c>
@@ -7858,25 +7862,25 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="20" t="s">
         <v>194</v>
       </c>
     </row>
@@ -7887,19 +7891,19 @@
       <c r="B4" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="32">
         <v>1</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>55000</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="29">
         <v>0.2</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="33">
         <v>70208</v>
       </c>
     </row>
@@ -7910,19 +7914,19 @@
       <c r="B5" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <v>1</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>45000</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <v>0.2</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="33">
         <v>57443</v>
       </c>
     </row>
@@ -7933,50 +7937,50 @@
       <c r="B6" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <v>0.5</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>28000</v>
       </c>
-      <c r="E6" s="28">
-        <v>0</v>
-      </c>
-      <c r="F6" s="28">
+      <c r="E6" s="29">
+        <v>0</v>
+      </c>
+      <c r="F6" s="29">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="33">
         <v>15071</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -7984,19 +7988,19 @@
       <c r="A10" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>118934</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>147003</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>151413</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>155955</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>160634</v>
       </c>
     </row>
@@ -8004,19 +8008,19 @@
       <c r="A11" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="29">
         <v>0.5367065282791817</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <v>0.4326189754471052</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <v>0.3549390698831137</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <v>0.3128131506849315</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="29">
         <v>0.3128131506849315</v>
       </c>
     </row>
@@ -8024,19 +8028,19 @@
       <c r="A12" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <v>4.8</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <v>7.2</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <v>8.8</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <v>10</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <v>10</v>
       </c>
     </row>
@@ -8075,52 +8079,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>6000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>9270</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>11670</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>13659</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>14069</v>
       </c>
     </row>
@@ -8128,54 +8132,54 @@
       <c r="A6" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="35">
         <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="35">
         <f>SUM(C5:C5)</f>
         <v>9270</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="35">
         <f>SUM(D5:D5)</f>
         <v>11670</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="35">
         <f>SUM(E5:E5)</f>
         <v>13659</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="35">
         <f>SUM(F5:F5)</f>
         <v>14069</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>3600</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>5562</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>7002</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>8195</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>8441</v>
       </c>
     </row>
@@ -8183,54 +8187,54 @@
       <c r="A9" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="35">
         <f>SUM(B8:B8)</f>
         <v>3600</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <f>SUM(C8:C8)</f>
         <v>5562</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="35">
         <f>SUM(D8:D8)</f>
         <v>7002</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="35">
         <f>SUM(E8:E8)</f>
         <v>8195</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>SUM(F8:F8)</f>
         <v>8441</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <v>30000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>30900</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>31827</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>32782</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>33765</v>
       </c>
     </row>
@@ -8238,19 +8242,19 @@
       <c r="A12" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <v>3600</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>3708</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>3819</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>3934</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>4052</v>
       </c>
     </row>
@@ -8258,19 +8262,19 @@
       <c r="A13" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <v>2400</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>2472</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>2546</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>2623</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>2701</v>
       </c>
     </row>
@@ -8278,54 +8282,54 @@
       <c r="A14" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>SUM(B11:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>SUM(C11:C13)</f>
         <v>37080</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="35">
         <f>SUM(D11:D13)</f>
         <v>38192</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <f>SUM(E11:E13)</f>
         <v>39338</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>SUM(F11:F13)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <v>3000</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>3090</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>3183</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>3278</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>3377</v>
       </c>
     </row>
@@ -8333,48 +8337,48 @@
       <c r="A17" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="35">
         <f>SUM(B16:B16)</f>
         <v>3000</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="35">
         <f>SUM(C16:C16)</f>
         <v>3090</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="35">
         <f>SUM(D16:D16)</f>
         <v>3183</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="35">
         <f>SUM(E16:E16)</f>
         <v>3278</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="35">
         <f>SUM(F16:F16)</f>
         <v>3377</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>B6+B9+B14+B17</f>
         <v>48600</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>C6+C9+C14+C17</f>
         <v>55002</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>D6+D9+D14+D17</f>
         <v>60047</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>E6+E9+E14+E17</f>
         <v>64471</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>F6+F9+F14+F17</f>
         <v>66405</v>
       </c>
@@ -8415,22 +8419,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>212</v>
       </c>
     </row>
@@ -8441,16 +8445,16 @@
       <c r="B4" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="22">
         <v>30000</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <v>0.06</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>5</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="33">
         <v>6960</v>
       </c>
     </row>
@@ -8458,7 +8462,7 @@
       <c r="A6" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>6960</v>
       </c>
     </row>
@@ -8466,7 +8470,7 @@
       <c r="A7" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="35">
         <v>30000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="385">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -592,97 +592,106 @@
     <t>Tuition &amp; Funding Drivers</t>
   </si>
   <si>
-    <t>REVENUE BY LINE ITEM</t>
-  </si>
-  <si>
-    <t>Tuition (Tuition &amp; Fees)</t>
-  </si>
-  <si>
-    <t>Registration Fee (Tuition &amp; Fees)</t>
-  </si>
-  <si>
-    <t>AZ ESA Funds (School Choice)</t>
-  </si>
-  <si>
-    <t>Annual Fundraising (Philanthropy)</t>
-  </si>
-  <si>
-    <t>Scholarship Discount (Tuition Offsets)</t>
+    <t>TUITION &amp; FEES</t>
+  </si>
+  <si>
+    <t>Total Tuition &amp; Fees</t>
+  </si>
+  <si>
+    <t>TUITION OFFSETS</t>
+  </si>
+  <si>
+    <t>Total Tuition Offsets</t>
+  </si>
+  <si>
+    <t>SCHOOL CHOICE</t>
+  </si>
+  <si>
+    <t>Total School Choice</t>
+  </si>
+  <si>
+    <t>PHILANTHROPY</t>
+  </si>
+  <si>
+    <t>Total Philanthropy</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL REVENUE</t>
+  </si>
+  <si>
+    <t>Base Rate</t>
+  </si>
+  <si>
+    <t>Loaded Cost</t>
+  </si>
+  <si>
+    <t>5-YEAR TOTAL PERSONNEL COST</t>
+  </si>
+  <si>
+    <t>Total Personnel</t>
+  </si>
+  <si>
+    <t>Personnel as % of Revenue</t>
+  </si>
+  <si>
+    <t>Students per FTE</t>
+  </si>
+  <si>
+    <t>Operating Expense Drivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Curriculum &amp; Materials</t>
+  </si>
+  <si>
+    <t>Total Instructional / Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Technology</t>
+  </si>
+  <si>
+    <t>Total Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Insurance</t>
+  </si>
+  <si>
+    <t>Total Occupancy / Facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Marketing</t>
+  </si>
+  <si>
+    <t>Total Administrative / General</t>
+  </si>
+  <si>
+    <t>TOTAL OPERATING EXPENSES</t>
+  </si>
+  <si>
+    <t>Capital Stack &amp; Loan Terms</t>
+  </si>
+  <si>
+    <t>Annual Payment</t>
+  </si>
+  <si>
+    <t>Total Annual Debt Service</t>
+  </si>
+  <si>
+    <t>Total Loan Principal</t>
+  </si>
+  <si>
+    <t>Enrollment &amp; Tuition Forecast</t>
+  </si>
+  <si>
+    <t>REVENUE FORECAST</t>
   </si>
   <si>
     <t>TOTAL REVENUE</t>
-  </si>
-  <si>
-    <t>Base Rate</t>
-  </si>
-  <si>
-    <t>Loaded Cost</t>
-  </si>
-  <si>
-    <t>5-YEAR TOTAL PERSONNEL COST</t>
-  </si>
-  <si>
-    <t>Total Personnel</t>
-  </si>
-  <si>
-    <t>Personnel as % of Revenue</t>
-  </si>
-  <si>
-    <t>Students per FTE</t>
-  </si>
-  <si>
-    <t>Operating Expense Drivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Curriculum &amp; Materials</t>
-  </si>
-  <si>
-    <t>Total Instructional / Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Technology</t>
-  </si>
-  <si>
-    <t>Total Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Rent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Insurance</t>
-  </si>
-  <si>
-    <t>Total Occupancy / Facility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Marketing</t>
-  </si>
-  <si>
-    <t>Total Administrative / General</t>
-  </si>
-  <si>
-    <t>TOTAL OPERATING EXPENSES</t>
-  </si>
-  <si>
-    <t>Capital Stack &amp; Loan Terms</t>
-  </si>
-  <si>
-    <t>Annual Payment</t>
-  </si>
-  <si>
-    <t>Total Annual Debt Service</t>
-  </si>
-  <si>
-    <t>Total Loan Principal</t>
-  </si>
-  <si>
-    <t>Enrollment &amp; Tuition Forecast</t>
-  </si>
-  <si>
-    <t>REVENUE FORECAST</t>
   </si>
   <si>
     <t>Revenue per Student</t>
@@ -1432,15 +1441,15 @@
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2176,7 +2185,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2226,7 +2235,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2238,19 +2247,19 @@
       <c r="A7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>144000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>222480</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>280078</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>327818</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>337653</v>
       </c>
     </row>
@@ -2258,19 +2267,19 @@
       <c r="A8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>3000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>4635</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>5835</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>6830</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>7034</v>
       </c>
     </row>
@@ -2278,19 +2287,19 @@
       <c r="A9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>84000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>129780</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>163379</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>191227</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>196964</v>
       </c>
     </row>
@@ -2298,19 +2307,19 @@
       <c r="A10" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="29">
         <v>5000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="29">
         <v>5150</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="29">
         <v>5305</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <v>5464</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="29">
         <v>5628</v>
       </c>
     </row>
@@ -2318,25 +2327,25 @@
       <c r="A11" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>-10</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>-10</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>-11</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>-11</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="29">
         <v>-11</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B7:B11)</f>
@@ -2361,21 +2370,21 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B14" s="30">
+        <v>220</v>
+      </c>
+      <c r="B14" s="29">
         <v>18467</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="29">
         <v>18878</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>19390</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>19942</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>20541</v>
       </c>
     </row>
@@ -2405,7 +2414,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2445,65 +2454,65 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" s="30">
+        <v>222</v>
+      </c>
+      <c r="B5" s="29">
         <v>47869</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>59166</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>60941</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>62769</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>64652</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="B6" s="30">
+        <v>223</v>
+      </c>
+      <c r="B6" s="29">
         <v>12559</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>15523</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>15989</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>16468</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>16963</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" s="35">
+        <v>224</v>
+      </c>
+      <c r="B7" s="30">
         <f>SUM(B5:B6)</f>
         <v>60428</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="30">
         <f>SUM(C5:C6)</f>
         <v>74689</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="30">
         <f>SUM(D5:D6)</f>
         <v>76930</v>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="30">
         <f>SUM(E5:E6)</f>
         <v>79237</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="30">
         <f>SUM(F5:F6)</f>
         <v>81615</v>
       </c>
@@ -2520,52 +2529,52 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B9" s="30">
+        <v>225</v>
+      </c>
+      <c r="B9" s="29">
         <v>58506</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>72314</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>74483</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>76718</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>79019</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="B10" s="35">
+        <v>226</v>
+      </c>
+      <c r="B10" s="30">
         <f>SUM(B9:B9)</f>
         <v>58506</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="30">
         <f>SUM(C9:C9)</f>
         <v>72314</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="30">
         <f>SUM(D9:D9)</f>
         <v>74483</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="30">
         <f>SUM(E9:E9)</f>
         <v>76718</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="30">
         <f>SUM(F9:F9)</f>
         <v>79019</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B12" s="31">
         <f>B7+B10</f>
@@ -2614,7 +2623,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2644,7 +2653,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -2654,132 +2663,132 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="30">
+        <v>230</v>
+      </c>
+      <c r="B5" s="29">
         <v>120000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>222480</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>280078</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>327818</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="30">
+        <v>231</v>
+      </c>
+      <c r="B6" s="29">
         <v>2500</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>4635</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>5835</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>6830</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="30">
+        <v>232</v>
+      </c>
+      <c r="B7" s="29">
         <v>70000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>129780</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>163379</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>191227</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>196964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" s="30">
+        <v>233</v>
+      </c>
+      <c r="B8" s="29">
         <v>4167</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>5150</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>5305</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>5464</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>5628</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="B9" s="30">
+        <v>234</v>
+      </c>
+      <c r="B9" s="29">
         <v>-8</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>-10</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>-11</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>-11</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>-11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B10" s="35">
+        <v>235</v>
+      </c>
+      <c r="B10" s="30">
         <f>SUM(B5:B9)</f>
         <v>184667</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="30">
         <f>SUM(C5:C9)</f>
         <v>339797</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="30">
         <f>SUM(D5:D9)</f>
         <v>426588</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="30">
         <f>SUM(E5:E9)</f>
         <v>498557</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="30">
         <f>SUM(F5:F9)</f>
         <v>513513</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -2789,85 +2798,85 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="30">
+        <v>225</v>
+      </c>
+      <c r="B13" s="29">
         <v>58506</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <v>72314</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>74483</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>76718</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>79019</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B14" s="30">
+        <v>222</v>
+      </c>
+      <c r="B14" s="29">
         <v>47869</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="29">
         <v>59166</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>60941</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>62769</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>64652</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="B15" s="30">
+        <v>223</v>
+      </c>
+      <c r="B15" s="29">
         <v>12559</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <v>15523</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>15989</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>16468</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>16963</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="35">
+        <v>198</v>
+      </c>
+      <c r="B16" s="30">
         <f>SUM(B13:B15)</f>
         <v>118934</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="30">
         <f>SUM(C13:C15)</f>
         <v>147003</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="30">
         <f>SUM(D13:D15)</f>
         <v>151413</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="30">
         <f>SUM(E13:E15)</f>
         <v>155955</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="30">
         <f>SUM(F13:F15)</f>
         <v>160634</v>
       </c>
@@ -2889,21 +2898,21 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B20" s="30">
+        <v>237</v>
+      </c>
+      <c r="B20" s="29">
         <v>5000</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="29">
         <v>9270</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="29">
         <v>11670</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>13659</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="29">
         <v>14069</v>
       </c>
     </row>
@@ -2914,21 +2923,21 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="B22" s="30">
+        <v>238</v>
+      </c>
+      <c r="B22" s="29">
         <v>3000</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="29">
         <v>5562</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="29">
         <v>7002</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="29">
         <v>8195</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="29">
         <v>8441</v>
       </c>
     </row>
@@ -2939,85 +2948,85 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="B24" s="30">
+        <v>239</v>
+      </c>
+      <c r="B24" s="29">
         <v>25000</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="29">
         <v>30900</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="29">
         <v>31827</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="29">
         <v>32782</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="29">
         <v>33765</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B25" s="30">
+        <v>240</v>
+      </c>
+      <c r="B25" s="29">
         <v>3000</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="29">
         <v>3708</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="29">
         <v>3819</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="29">
         <v>3934</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="29">
         <v>4052</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B26" s="30">
+        <v>241</v>
+      </c>
+      <c r="B26" s="29">
         <v>2000</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="29">
         <v>2472</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="29">
         <v>2546</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="29">
         <v>2623</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="29">
         <v>2701</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="B27" s="35">
+        <v>242</v>
+      </c>
+      <c r="B27" s="30">
         <f>SUM(B24:B26)</f>
         <v>30000</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="30">
         <f>SUM(C24:C26)</f>
         <v>37080</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="30">
         <f>SUM(D24:D26)</f>
         <v>38192</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="30">
         <f>SUM(E24:E26)</f>
         <v>39338</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="30">
         <f>SUM(F24:F26)</f>
         <v>40518</v>
       </c>
@@ -3029,52 +3038,52 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B29" s="30">
+        <v>243</v>
+      </c>
+      <c r="B29" s="29">
         <v>2500</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="29">
         <v>3090</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="29">
         <v>3183</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="29">
         <v>3278</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="29">
         <v>3377</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="B30" s="35">
+        <v>244</v>
+      </c>
+      <c r="B30" s="30">
         <f>B20+B22+B27+B29</f>
         <v>40500</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="30">
         <f>C20+C22+C27+C29</f>
         <v>55002</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="30">
         <f>D20+D22+D27+D29</f>
         <v>60047</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="30">
         <f>E20+E22+E27+E29</f>
         <v>64471</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="30">
         <f>F20+F22+F27+F29</f>
         <v>66405</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -3084,25 +3093,25 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="B33" s="35" t="str">
+        <v>246</v>
+      </c>
+      <c r="B33" s="30" t="str">
         <f>SUM(B33:B32)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="35" t="str">
+      <c r="C33" s="30" t="str">
         <f>SUM(C33:C32)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="35" t="str">
+      <c r="D33" s="30" t="str">
         <f>SUM(D33:D32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="35" t="str">
+      <c r="E33" s="30" t="str">
         <f>SUM(E33:E32)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="35" t="str">
+      <c r="F33" s="30" t="str">
         <f>SUM(F33:F32)</f>
         <v>0</v>
       </c>
@@ -3133,7 +3142,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3163,7 +3172,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B4" s="33">
         <f>'Budget Detail'!B10</f>
@@ -3188,7 +3197,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B5" s="33">
         <f>'Budget Detail'!B16</f>
@@ -3213,7 +3222,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B6" s="33">
         <f>'Budget Detail'!B30</f>
@@ -3238,7 +3247,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B7" s="33" t="str">
         <f>'Budget Detail'!B33</f>
@@ -3263,32 +3272,32 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B8" s="35">
+        <v>249</v>
+      </c>
+      <c r="B8" s="30">
         <f>SUM(B5:B7)</f>
         <v>159434</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="30">
         <f>SUM(C5:C7)</f>
         <v>202005</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="30">
         <f>SUM(D5:D7)</f>
         <v>211460</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="30">
         <f>SUM(E5:E7)</f>
         <v>220426</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="30">
         <f>SUM(F5:F7)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -3298,7 +3307,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B11" s="31">
         <f>B4-B8</f>
@@ -3323,86 +3332,86 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="29">
+        <v>252</v>
+      </c>
+      <c r="B12" s="28">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="28">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.40551379</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="28">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.50429993</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="28">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.55787178</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="28">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.55787178</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" s="30">
+        <v>253</v>
+      </c>
+      <c r="B13" s="29">
         <v>25233</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <v>163025</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>378153</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>656284</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>942758</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B14" s="30">
+        <v>220</v>
+      </c>
+      <c r="B14" s="29">
         <v>15389</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="29">
         <v>18878</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>19390</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>19942</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>20541</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="B15" s="30">
+        <v>254</v>
+      </c>
+      <c r="B15" s="29">
         <v>13286</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <v>11222</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>9612</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>8817</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>9082</v>
       </c>
     </row>
@@ -3433,7 +3442,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3454,48 +3463,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -3513,52 +3522,52 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B4" s="35">
+        <v>235</v>
+      </c>
+      <c r="B4" s="30">
         <v>9150</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="30">
         <v>22110</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="30">
         <v>22110</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="30">
         <v>22110</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="30">
         <v>22110</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="30">
         <v>22110</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="30">
         <v>22110</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="30">
         <v>22110</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="30">
         <v>22110</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="30">
         <v>22110</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="30">
         <v>13210</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="30">
         <v>250</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="30">
         <f>SUM(B4:M4)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -3576,142 +3585,142 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B7" s="30">
+        <v>270</v>
+      </c>
+      <c r="B7" s="29">
         <v>11893</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>11893</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>11893</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>11893</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>11893</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="29">
         <v>11893</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="29">
         <v>11893</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="29">
         <v>11893</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="29">
         <v>11893</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="29">
         <v>11893</v>
       </c>
-      <c r="L7" s="30">
-        <v>0</v>
-      </c>
-      <c r="M7" s="30">
-        <v>0</v>
-      </c>
-      <c r="N7" s="30">
+      <c r="L7" s="29">
+        <v>0</v>
+      </c>
+      <c r="M7" s="29">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="30">
+        <v>271</v>
+      </c>
+      <c r="B8" s="29">
         <v>4050</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>4050</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>4050</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>4050</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>4050</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="29">
         <v>4050</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="29">
         <v>4050</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="29">
         <v>4050</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="29">
         <v>4050</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="29">
         <v>4050</v>
       </c>
-      <c r="L8" s="30">
-        <v>0</v>
-      </c>
-      <c r="M8" s="30">
-        <v>0</v>
-      </c>
-      <c r="N8" s="30">
+      <c r="L8" s="29">
+        <v>0</v>
+      </c>
+      <c r="M8" s="29">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="30">
-        <v>0</v>
-      </c>
-      <c r="C9" s="30">
-        <v>0</v>
-      </c>
-      <c r="D9" s="30">
-        <v>0</v>
-      </c>
-      <c r="E9" s="30">
-        <v>0</v>
-      </c>
-      <c r="F9" s="30">
-        <v>0</v>
-      </c>
-      <c r="G9" s="30">
-        <v>0</v>
-      </c>
-      <c r="H9" s="30">
-        <v>0</v>
-      </c>
-      <c r="I9" s="30">
-        <v>0</v>
-      </c>
-      <c r="J9" s="30">
-        <v>0</v>
-      </c>
-      <c r="K9" s="30">
-        <v>0</v>
-      </c>
-      <c r="L9" s="30">
-        <v>0</v>
-      </c>
-      <c r="M9" s="30">
-        <v>0</v>
-      </c>
-      <c r="N9" s="30" t="str">
+        <v>272</v>
+      </c>
+      <c r="B9" s="29">
+        <v>0</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29">
+        <v>0</v>
+      </c>
+      <c r="G9" s="29">
+        <v>0</v>
+      </c>
+      <c r="H9" s="29">
+        <v>0</v>
+      </c>
+      <c r="I9" s="29">
+        <v>0</v>
+      </c>
+      <c r="J9" s="29">
+        <v>0</v>
+      </c>
+      <c r="K9" s="29">
+        <v>0</v>
+      </c>
+      <c r="L9" s="29">
+        <v>0</v>
+      </c>
+      <c r="M9" s="29">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29" t="str">
         <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -3729,7 +3738,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B12" s="33">
         <f>B7+B8+B9</f>
@@ -3786,7 +3795,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B13" s="33">
         <f>B4-B12</f>
@@ -3843,7 +3852,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
@@ -3900,7 +3909,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -3915,7 +3924,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
@@ -3924,9 +3933,9 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="B19" s="30">
+        <v>278</v>
+      </c>
+      <c r="B19" s="29">
         <f>MIN(B14:M14)</f>
         <v>-6793</v>
       </c>
@@ -3957,7 +3966,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3987,7 +3996,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -3997,27 +4006,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="B5" s="35">
+        <v>235</v>
+      </c>
+      <c r="B5" s="30">
         <v>184667</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="30">
         <v>339797</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="30">
         <v>426588</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="30">
         <v>498557</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="30">
         <v>513513</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -4027,7 +4036,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B8" s="33">
         <v>118934</v>
@@ -4047,7 +4056,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B9" s="33">
         <v>40500</v>
@@ -4067,7 +4076,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B10" s="33">
         <v>0</v>
@@ -4087,32 +4096,32 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="35">
+        <v>249</v>
+      </c>
+      <c r="B11" s="30">
         <f>SUM(B8:B10)</f>
         <v>159434</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="30">
         <f>SUM(C8:C10)</f>
         <v>202005</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="30">
         <f>SUM(D8:D10)</f>
         <v>211460</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="30">
         <f>SUM(E8:E10)</f>
         <v>220426</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="30">
         <f>SUM(F8:F10)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -4122,7 +4131,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B14" s="31">
         <f>B5-B11</f>
@@ -4147,25 +4156,25 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B15" s="29">
+        <v>252</v>
+      </c>
+      <c r="B15" s="28">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="28">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.40551379</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="28">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.50429993</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="28">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.55787178</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="28">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.55787178</v>
       </c>
@@ -4226,7 +4235,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4236,19 +4245,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B5" s="41" t="s">
         <v>152</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4277,7 +4286,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4307,7 +4316,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4317,7 +4326,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B5" s="43">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -4342,92 +4351,92 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="B6" s="30">
-        <v>0</v>
-      </c>
-      <c r="C6" s="30">
-        <v>0</v>
-      </c>
-      <c r="D6" s="30">
-        <v>0</v>
-      </c>
-      <c r="E6" s="30">
-        <v>0</v>
-      </c>
-      <c r="F6" s="30">
+        <v>289</v>
+      </c>
+      <c r="B6" s="29">
+        <v>0</v>
+      </c>
+      <c r="C6" s="29">
+        <v>0</v>
+      </c>
+      <c r="D6" s="29">
+        <v>0</v>
+      </c>
+      <c r="E6" s="29">
+        <v>0</v>
+      </c>
+      <c r="F6" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="B7" s="30">
+        <v>290</v>
+      </c>
+      <c r="B7" s="29">
         <v>5000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>5000</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>5000</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>5000</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>5000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B8" s="30">
-        <v>0</v>
-      </c>
-      <c r="C8" s="30">
-        <v>0</v>
-      </c>
-      <c r="D8" s="30">
-        <v>0</v>
-      </c>
-      <c r="E8" s="30">
-        <v>0</v>
-      </c>
-      <c r="F8" s="30">
+        <v>291</v>
+      </c>
+      <c r="B8" s="29">
+        <v>0</v>
+      </c>
+      <c r="C8" s="29">
+        <v>0</v>
+      </c>
+      <c r="D8" s="29">
+        <v>0</v>
+      </c>
+      <c r="E8" s="29">
+        <v>0</v>
+      </c>
+      <c r="F8" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="35">
+        <v>292</v>
+      </c>
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>67170</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="30">
         <f>SUM(C5:C8)</f>
         <v>204962</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="30">
         <f>SUM(D5:D8)</f>
         <v>420091</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="30">
         <f>SUM(E5:E8)</f>
         <v>698221</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="30">
         <f>SUM(F5:F8)</f>
         <v>984696</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -4437,72 +4446,72 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12" s="30">
-        <v>0</v>
-      </c>
-      <c r="C12" s="30">
-        <v>0</v>
-      </c>
-      <c r="D12" s="30">
-        <v>0</v>
-      </c>
-      <c r="E12" s="30">
-        <v>0</v>
-      </c>
-      <c r="F12" s="30">
+        <v>294</v>
+      </c>
+      <c r="B12" s="29">
+        <v>0</v>
+      </c>
+      <c r="C12" s="29">
+        <v>0</v>
+      </c>
+      <c r="D12" s="29">
+        <v>0</v>
+      </c>
+      <c r="E12" s="29">
+        <v>0</v>
+      </c>
+      <c r="F12" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B13" s="30">
-        <v>0</v>
-      </c>
-      <c r="C13" s="30">
-        <v>0</v>
-      </c>
-      <c r="D13" s="30">
-        <v>0</v>
-      </c>
-      <c r="E13" s="30">
-        <v>0</v>
-      </c>
-      <c r="F13" s="30">
+        <v>295</v>
+      </c>
+      <c r="B13" s="29">
+        <v>0</v>
+      </c>
+      <c r="C13" s="29">
+        <v>0</v>
+      </c>
+      <c r="D13" s="29">
+        <v>0</v>
+      </c>
+      <c r="E13" s="29">
+        <v>0</v>
+      </c>
+      <c r="F13" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14" s="35" t="str">
+        <v>296</v>
+      </c>
+      <c r="B14" s="30" t="str">
         <f>SUM(B12:B13)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="35" t="str">
+      <c r="C14" s="30" t="str">
         <f>SUM(C12:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="35" t="str">
+      <c r="D14" s="30" t="str">
         <f>SUM(D12:D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="35" t="str">
+      <c r="E14" s="30" t="str">
         <f>SUM(E12:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="35" t="str">
+      <c r="F14" s="30" t="str">
         <f>SUM(F12:F13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -4512,7 +4521,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B17" s="31">
         <f>B9-B14</f>
@@ -4537,7 +4546,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B19" s="44" t="str">
         <f>B9-B14-B17</f>
@@ -4586,7 +4595,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4616,7 +4625,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4626,67 +4635,67 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="B5" s="30">
+        <v>302</v>
+      </c>
+      <c r="B5" s="29">
         <v>184667</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>339797</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>426588</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>498557</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>513513</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="30">
+        <v>270</v>
+      </c>
+      <c r="B6" s="29">
         <v>118934</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>147003</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>151413</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>155955</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>160634</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="B7" s="30">
+        <v>271</v>
+      </c>
+      <c r="B7" s="29">
         <v>40500</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>55002</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>60047</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>64471</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>66405</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B8" s="33">
         <f>B5-B6-B7</f>
@@ -4711,47 +4720,47 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="30">
-        <v>0</v>
-      </c>
-      <c r="C9" s="30">
-        <v>0</v>
-      </c>
-      <c r="D9" s="30">
-        <v>0</v>
-      </c>
-      <c r="E9" s="30">
-        <v>0</v>
-      </c>
-      <c r="F9" s="30">
+        <v>272</v>
+      </c>
+      <c r="B9" s="29">
+        <v>0</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F10" s="45" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -4761,52 +4770,52 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="B13" s="30">
+        <v>307</v>
+      </c>
+      <c r="B13" s="29">
         <v>62170</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <v>199962</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>415091</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>693221</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>979696</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="B14" s="27">
+        <v>308</v>
+      </c>
+      <c r="B14" s="35">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>142</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="35">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>361</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="35">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>716</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="35">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>1148</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="35">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>1575</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B15" s="34">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -4833,25 +4842,25 @@
       <c r="A16" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="28">
         <v>0.48</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="28">
         <v>0.72</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="28">
         <v>0.88</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="28">
         <v>1</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -4861,67 +4870,67 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B19" s="30">
+        <v>220</v>
+      </c>
+      <c r="B19" s="29">
         <v>15389</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="29">
         <v>18878</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <v>19390</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>19942</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>20541</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B20" s="30">
+        <v>311</v>
+      </c>
+      <c r="B20" s="29">
         <v>118934</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="29">
         <v>147003</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="29">
         <v>151413</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>155955</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="29">
         <v>160634</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="B21" s="30">
+        <v>312</v>
+      </c>
+      <c r="B21" s="29">
         <v>3375</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="29">
         <v>3056</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="29">
         <v>2729</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>2579</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="29">
         <v>2656</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B22" s="46">
         <v>10</v>
@@ -4941,7 +4950,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -4951,102 +4960,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D25" s="47" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E26" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D27" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E27" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="B28" s="48" t="s">
         <v>317</v>
       </c>
-      <c r="B28" s="48" t="s">
-        <v>314</v>
-      </c>
       <c r="C28" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D28" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D29" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -5087,13 +5096,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B3" s="50" t="s">
         <v>111</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E3" s="50" t="s">
         <v>111</v>
@@ -5101,35 +5110,35 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="B4" s="30">
+        <v>324</v>
+      </c>
+      <c r="B4" s="29">
         <v>20000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="E4" s="30">
+        <v>325</v>
+      </c>
+      <c r="E4" s="29">
         <v>15000</v>
       </c>
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="E5" s="30">
+        <v>326</v>
+      </c>
+      <c r="E5" s="29">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B7" s="31">
         <v>20000</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E7" s="31">
         <v>20000</v>
@@ -5137,7 +5146,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B8" s="44">
         <v>0</v>
@@ -5485,7 +5494,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5495,7 +5504,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -5505,7 +5514,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5530,47 +5539,47 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="B6" s="30">
+        <v>302</v>
+      </c>
+      <c r="B6" s="29">
         <v>184667</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>339797</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>426588</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>498557</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>513513</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B7" s="30">
+        <v>249</v>
+      </c>
+      <c r="B7" s="29">
         <v>159434</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>202005</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>211460</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>220426</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>227039</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B8" s="31">
         <v>25233</v>
@@ -5590,67 +5599,67 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B9" s="29">
+        <v>252</v>
+      </c>
+      <c r="B9" s="28">
         <v>0.13663808664259927</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="28">
         <v>0.40551379205819943</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>0.5042999253916937</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>0.5578717808219178</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B11" s="27">
+        <v>313</v>
+      </c>
+      <c r="B11" s="35">
         <v>10</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="35">
         <v>10</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="35">
         <v>10</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="35">
         <v>9</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="35">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -5660,7 +5669,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5685,47 +5694,47 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="B16" s="30">
+        <v>302</v>
+      </c>
+      <c r="B16" s="29">
         <v>147733</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <v>271838</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>341270</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>398845</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>410811</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B17" s="30">
+        <v>249</v>
+      </c>
+      <c r="B17" s="29">
         <v>159434</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="29">
         <v>202005</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <v>211460</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>220426</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <v>227039</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B18" s="31">
         <v>-11701</v>
@@ -5745,61 +5754,61 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B19" s="29">
+        <v>252</v>
+      </c>
+      <c r="B19" s="28">
         <v>-0.07920239169675096</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="28">
         <v>0.2568922400727494</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="28">
         <v>0.38037490673961705</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="28">
         <v>0.4473397260273973</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="28">
         <v>0.44733972602739736</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B21" s="27">
+        <v>313</v>
+      </c>
+      <c r="B21" s="35">
         <v>12</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="35">
         <v>10</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="35">
         <v>10</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="35">
         <v>10</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="35">
         <v>10</v>
       </c>
     </row>
@@ -5831,7 +5840,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5865,7 +5874,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -5889,7 +5898,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -5897,7 +5906,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -5935,107 +5944,107 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="D13" s="30">
+        <v>302</v>
+      </c>
+      <c r="D13" s="29">
         <v>184667</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>339797</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>426588</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <v>498557</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="29">
         <v>513513</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D14" s="30">
+        <v>249</v>
+      </c>
+      <c r="D14" s="29">
         <v>159434</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>202005</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>211460</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="29">
         <v>220426</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="29">
         <v>227039</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="D15" s="30">
+        <v>251</v>
+      </c>
+      <c r="D15" s="29">
         <v>25233</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>137792</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>215128</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="29">
         <v>278131</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="29">
         <v>286475</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="D16" s="30">
+        <v>339</v>
+      </c>
+      <c r="D16" s="29">
         <v>62170</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>199962</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>415091</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="29">
         <v>693221</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="29">
         <v>979696</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="D17" s="30">
-        <v>0</v>
-      </c>
-      <c r="E17" s="30">
-        <v>0</v>
-      </c>
-      <c r="F17" s="30">
-        <v>0</v>
-      </c>
-      <c r="G17" s="30">
-        <v>0</v>
-      </c>
-      <c r="H17" s="30">
+        <v>340</v>
+      </c>
+      <c r="D17" s="29">
+        <v>0</v>
+      </c>
+      <c r="E17" s="29">
+        <v>0</v>
+      </c>
+      <c r="F17" s="29">
+        <v>0</v>
+      </c>
+      <c r="G17" s="29">
+        <v>0</v>
+      </c>
+      <c r="H17" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -6073,87 +6082,87 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="D21" s="29">
+        <v>342</v>
+      </c>
+      <c r="D21" s="28">
         <v>0.13663808664259927</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="28">
         <v>0.40551379205819943</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="28">
         <v>0.5042999253916937</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="28">
         <v>0.5578717808219178</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="28">
         <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G22" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H22" s="51" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="28">
         <v>0.48</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="28">
         <v>0.72</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="28">
         <v>0.88</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="28">
         <v>1</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="D24" s="27">
+        <v>343</v>
+      </c>
+      <c r="D24" s="35">
         <v>12</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="35">
         <v>18</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="35">
         <v>22</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="35">
         <v>25</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="35">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -6193,7 +6202,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6203,7 +6212,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C3" s="53"/>
       <c r="D3" s="53"/>
@@ -6213,27 +6222,27 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C6" s="55">
         <v>12</v>
@@ -6253,7 +6262,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C7" s="56">
         <v>184666.6666666667</v>
@@ -6273,7 +6282,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C8" s="56">
         <v>118934.16666666667</v>
@@ -6293,7 +6302,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C9" s="56">
         <v>40500</v>
@@ -6313,7 +6322,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C10" s="56">
         <v>0</v>
@@ -6333,7 +6342,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C11" s="57">
         <v>25232.5</v>
@@ -6353,7 +6362,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C12" s="57">
         <v>62170</v>
@@ -6373,7 +6382,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C13" s="58">
         <v>0.13663808664259927</v>
@@ -6393,7 +6402,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C14" s="56">
         <v>15388.88888888889</v>
@@ -6413,7 +6422,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C15" s="59">
         <v>0.644047833935018</v>
@@ -6433,7 +6442,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C16" s="58">
         <v>0.06579422382671479</v>
@@ -6453,7 +6462,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C17" s="58">
         <v>0.13663808664259935</v>
@@ -6473,30 +6482,30 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F18" s="60" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G18" s="60" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D19" s="61"/>
       <c r="E19" s="61"/>
@@ -6505,10 +6514,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D20" s="61"/>
       <c r="E20" s="61"/>
@@ -6517,129 +6526,129 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="18" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G22" s="18"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="40" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C23" s="62" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E23" s="63"/>
       <c r="F23" s="64" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G23" s="64"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="40" t="s">
+        <v>367</v>
+      </c>
+      <c r="C24" s="62" t="s">
         <v>364</v>
       </c>
-      <c r="C24" s="62" t="s">
-        <v>361</v>
-      </c>
       <c r="D24" s="63" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E24" s="63"/>
       <c r="F24" s="64" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G24" s="64"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="40" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C25" s="62" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E25" s="63"/>
       <c r="F25" s="64" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G25" s="64"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C26" s="62" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E26" s="63"/>
       <c r="F26" s="64" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="G26" s="64"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="40" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C27" s="62" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="64" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G27" s="64"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="40" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C28" s="62" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E28" s="63"/>
       <c r="F28" s="64" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G28" s="64"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="40" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="65" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C32" s="65"/>
       <c r="D32" s="65"/>
@@ -7589,7 +7598,7 @@
       <c r="A7" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="21">
         <v>25</v>
       </c>
     </row>
@@ -7597,19 +7606,24 @@
       <c r="A8" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="27">
+        <f>B6/$B$7</f>
         <v>0.48</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="27">
+        <f>C6/$B$7</f>
         <v>0.72</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="27">
+        <f>D6/$B$7</f>
         <v>0.88</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="27">
+        <f>E6/$B$7</f>
         <v>1</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="27">
+        <f>F6/$B$7</f>
         <v>1</v>
       </c>
     </row>
@@ -7620,16 +7634,20 @@
       <c r="B10" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="28">
+        <f>IF(B6=0,0,(C6-B6)/B6)</f>
         <v>0.5</v>
       </c>
-      <c r="D10" s="29">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="E10" s="29">
-        <v>0.13636363636363635</v>
-      </c>
-      <c r="F10" s="29">
+      <c r="D10" s="28">
+        <f>IF(C6=0,0,(D6-C6)/C6)</f>
+        <v>0.22222222</v>
+      </c>
+      <c r="E10" s="28">
+        <f>IF(D6=0,0,(E6-D6)/D6)</f>
+        <v>0.13636364</v>
+      </c>
+      <c r="F10" s="28" t="str">
+        <f>IF(E6=0,0,(F6-E6)/E6)</f>
         <v>0</v>
       </c>
     </row>
@@ -7650,10 +7668,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7699,126 +7717,256 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="30">
+        <v>113</v>
+      </c>
+      <c r="B5" s="29">
         <v>144000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>222480</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>280078</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>327818</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="29">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="29">
+        <v>4635</v>
+      </c>
+      <c r="D6" s="29">
+        <v>5835</v>
+      </c>
+      <c r="E6" s="29">
+        <v>6830</v>
+      </c>
+      <c r="F6" s="29">
+        <v>7034</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="30">
+        <f>SUBTOTAL(9,B5:B6)</f>
+        <v>147000</v>
+      </c>
+      <c r="C7" s="30">
+        <f>SUBTOTAL(9,C5:C6)</f>
+        <v>227115</v>
+      </c>
+      <c r="D7" s="30">
+        <f>SUBTOTAL(9,D5:D6)</f>
+        <v>285913</v>
+      </c>
+      <c r="E7" s="30">
+        <f>SUBTOTAL(9,E5:E6)</f>
+        <v>334648</v>
+      </c>
+      <c r="F7" s="30">
+        <f>SUBTOTAL(9,F5:F6)</f>
+        <v>344687</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="30">
-        <v>3000</v>
-      </c>
-      <c r="C6" s="30">
-        <v>4635</v>
-      </c>
-      <c r="D6" s="30">
-        <v>5835</v>
-      </c>
-      <c r="E6" s="30">
-        <v>6830</v>
-      </c>
-      <c r="F6" s="30">
-        <v>7034</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="30">
-        <v>84000</v>
-      </c>
-      <c r="C7" s="30">
-        <v>129780</v>
-      </c>
-      <c r="D7" s="30">
-        <v>163379</v>
-      </c>
-      <c r="E7" s="30">
-        <v>191227</v>
-      </c>
-      <c r="F7" s="30">
-        <v>196964</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="30">
-        <v>5000</v>
-      </c>
-      <c r="C8" s="30">
-        <v>5150</v>
-      </c>
-      <c r="D8" s="30">
-        <v>5305</v>
-      </c>
-      <c r="E8" s="30">
-        <v>5464</v>
-      </c>
-      <c r="F8" s="30">
-        <v>5628</v>
-      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="29">
+        <v>-10</v>
+      </c>
+      <c r="C9" s="29">
+        <v>-10</v>
+      </c>
+      <c r="D9" s="29">
+        <v>-11</v>
+      </c>
+      <c r="E9" s="29">
+        <v>-11</v>
+      </c>
+      <c r="F9" s="29">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="30">
+        <f>SUBTOTAL(9,B9:B9)</f>
+        <v>-10</v>
+      </c>
+      <c r="C10" s="30">
+        <f>SUBTOTAL(9,C9:C9)</f>
+        <v>-10</v>
+      </c>
+      <c r="D10" s="30">
+        <f>SUBTOTAL(9,D9:D9)</f>
+        <v>-11</v>
+      </c>
+      <c r="E10" s="30">
+        <f>SUBTOTAL(9,E9:E9)</f>
+        <v>-11</v>
+      </c>
+      <c r="F10" s="30">
+        <f>SUBTOTAL(9,F9:F9)</f>
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="29">
+        <v>84000</v>
+      </c>
+      <c r="C12" s="29">
+        <v>129780</v>
+      </c>
+      <c r="D12" s="29">
+        <v>163379</v>
+      </c>
+      <c r="E12" s="29">
+        <v>191227</v>
+      </c>
+      <c r="F12" s="29">
+        <v>196964</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="30">
-        <v>-10</v>
-      </c>
-      <c r="C9" s="30">
-        <v>-10</v>
-      </c>
-      <c r="D9" s="30">
-        <v>-11</v>
-      </c>
-      <c r="E9" s="30">
-        <v>-11</v>
-      </c>
-      <c r="F9" s="30">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="B13" s="30">
+        <f>SUBTOTAL(9,B12:B12)</f>
+        <v>84000</v>
+      </c>
+      <c r="C13" s="30">
+        <f>SUBTOTAL(9,C12:C12)</f>
+        <v>129780</v>
+      </c>
+      <c r="D13" s="30">
+        <f>SUBTOTAL(9,D12:D12)</f>
+        <v>163379</v>
+      </c>
+      <c r="E13" s="30">
+        <f>SUBTOTAL(9,E12:E12)</f>
+        <v>191227</v>
+      </c>
+      <c r="F13" s="30">
+        <f>SUBTOTAL(9,F12:F12)</f>
+        <v>196964</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="B10" s="31">
-        <f>SUM(B5:B9)</f>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="22">
+        <v>5000</v>
+      </c>
+      <c r="C15" s="29">
+        <v>5150</v>
+      </c>
+      <c r="D15" s="29">
+        <v>5305</v>
+      </c>
+      <c r="E15" s="29">
+        <v>5464</v>
+      </c>
+      <c r="F15" s="29">
+        <v>5628</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B16" s="30">
+        <f>SUBTOTAL(9,B15:B15)</f>
+        <v>5000</v>
+      </c>
+      <c r="C16" s="30">
+        <f>SUBTOTAL(9,C15:C15)</f>
+        <v>5150</v>
+      </c>
+      <c r="D16" s="30">
+        <f>SUBTOTAL(9,D15:D15)</f>
+        <v>5305</v>
+      </c>
+      <c r="E16" s="30">
+        <f>SUBTOTAL(9,E15:E15)</f>
+        <v>5464</v>
+      </c>
+      <c r="F16" s="30">
+        <f>SUBTOTAL(9,F15:F15)</f>
+        <v>5628</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="31">
+        <f>SUM(B7,B10,B13,B16)</f>
         <v>221600</v>
       </c>
-      <c r="C10" s="31">
-        <f>SUM(C5:C9)</f>
+      <c r="C18" s="31">
+        <f>SUM(C7,C10,C13,C16)</f>
         <v>339797</v>
       </c>
-      <c r="D10" s="31">
-        <f>SUM(D5:D9)</f>
+      <c r="D18" s="31">
+        <f>SUM(D7,D10,D13,D16)</f>
         <v>426588</v>
       </c>
-      <c r="E10" s="31">
-        <f>SUM(E5:E9)</f>
+      <c r="E18" s="31">
+        <f>SUM(E7,E10,E13,E16)</f>
         <v>498557</v>
       </c>
-      <c r="F10" s="31">
-        <f>SUM(F5:F9)</f>
+      <c r="F18" s="31">
+        <f>SUM(F7,F10,F13,F16)</f>
         <v>513513</v>
       </c>
     </row>
@@ -7872,7 +8020,7 @@
         <v>128</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>130</v>
@@ -7881,7 +8029,7 @@
         <v>131</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7894,13 +8042,13 @@
       <c r="C4" s="32">
         <v>1</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="29">
         <v>55000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="28">
         <v>0.2</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="28">
         <v>0.0765</v>
       </c>
       <c r="G4" s="33">
@@ -7917,13 +8065,13 @@
       <c r="C5" s="32">
         <v>1</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>45000</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="28">
         <v>0.2</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="28">
         <v>0.0765</v>
       </c>
       <c r="G5" s="33">
@@ -7940,13 +8088,13 @@
       <c r="C6" s="32">
         <v>0.5</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>28000</v>
       </c>
-      <c r="E6" s="29">
-        <v>0</v>
-      </c>
-      <c r="F6" s="29">
+      <c r="E6" s="28">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28">
         <v>0.0765</v>
       </c>
       <c r="G6" s="33">
@@ -7955,7 +8103,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -7986,7 +8134,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B10" s="31">
         <v>118934</v>
@@ -8006,27 +8154,27 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="B11" s="29">
+        <v>199</v>
+      </c>
+      <c r="B11" s="28">
         <v>0.5367065282791817</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="28">
         <v>0.4326189754471052</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="28">
         <v>0.3549390698831137</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="28">
         <v>0.3128131506849315</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="28">
         <v>0.3128131506849315</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B12" s="34">
         <v>4.8</v>
@@ -8070,7 +8218,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8110,45 +8258,45 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="30">
+        <v>202</v>
+      </c>
+      <c r="B5" s="29">
         <v>6000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>9270</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>11670</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>13659</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>14069</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="35">
+        <v>203</v>
+      </c>
+      <c r="B6" s="30">
         <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="30">
         <f>SUM(C5:C5)</f>
         <v>9270</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="30">
         <f>SUM(D5:D5)</f>
         <v>11670</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="30">
         <f>SUM(E5:E5)</f>
         <v>13659</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="30">
         <f>SUM(F5:F5)</f>
         <v>14069</v>
       </c>
@@ -8165,45 +8313,45 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="30">
+        <v>204</v>
+      </c>
+      <c r="B8" s="29">
         <v>3600</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>5562</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>7002</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>8195</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>8441</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="35">
+        <v>205</v>
+      </c>
+      <c r="B9" s="30">
         <f>SUM(B8:B8)</f>
         <v>3600</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="30">
         <f>SUM(C8:C8)</f>
         <v>5562</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="30">
         <f>SUM(D8:D8)</f>
         <v>7002</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="30">
         <f>SUM(E8:E8)</f>
         <v>8195</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="30">
         <f>SUM(F8:F8)</f>
         <v>8441</v>
       </c>
@@ -8220,85 +8368,85 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="30">
+        <v>206</v>
+      </c>
+      <c r="B11" s="29">
         <v>30000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>30900</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>31827</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>32782</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="29">
         <v>33765</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="30">
+        <v>207</v>
+      </c>
+      <c r="B12" s="29">
         <v>3600</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <v>3708</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>3819</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>3934</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <v>4052</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="30">
+        <v>208</v>
+      </c>
+      <c r="B13" s="29">
         <v>2400</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <v>2472</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>2546</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>2623</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>2701</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="35">
+        <v>209</v>
+      </c>
+      <c r="B14" s="30">
         <f>SUM(B11:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="30">
         <f>SUM(C11:C13)</f>
         <v>37080</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="30">
         <f>SUM(D11:D13)</f>
         <v>38192</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="30">
         <f>SUM(E11:E13)</f>
         <v>39338</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="30">
         <f>SUM(F11:F13)</f>
         <v>40518</v>
       </c>
@@ -8315,52 +8463,52 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="30">
+        <v>210</v>
+      </c>
+      <c r="B16" s="29">
         <v>3000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <v>3090</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>3183</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>3278</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>3377</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="B17" s="35">
+        <v>211</v>
+      </c>
+      <c r="B17" s="30">
         <f>SUM(B16:B16)</f>
         <v>3000</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="30">
         <f>SUM(C16:C16)</f>
         <v>3090</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="30">
         <f>SUM(D16:D16)</f>
         <v>3183</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="30">
         <f>SUM(E16:E16)</f>
         <v>3278</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="30">
         <f>SUM(F16:F16)</f>
         <v>3377</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B19" s="31">
         <f>B6+B9+B14+B17</f>
@@ -8410,7 +8558,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8435,7 +8583,7 @@
         <v>153</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -8448,10 +8596,10 @@
       <c r="C4" s="22">
         <v>30000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="28">
         <v>0.06</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="35">
         <v>5</v>
       </c>
       <c r="F4" s="33">
@@ -8460,7 +8608,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F6" s="31">
         <v>6960</v>
@@ -8468,9 +8616,9 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="F7" s="35">
+        <v>216</v>
+      </c>
+      <c r="F7" s="30">
         <v>30000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -7760,23 +7760,23 @@
         <v>187</v>
       </c>
       <c r="B7" s="30">
-        <f>SUBTOTAL(9,B5:B6)</f>
+        <f>SUM(B5,B6)</f>
         <v>147000</v>
       </c>
       <c r="C7" s="30">
-        <f>SUBTOTAL(9,C5:C6)</f>
+        <f>SUM(C5,C6)</f>
         <v>227115</v>
       </c>
       <c r="D7" s="30">
-        <f>SUBTOTAL(9,D5:D6)</f>
+        <f>SUM(D5,D6)</f>
         <v>285913</v>
       </c>
       <c r="E7" s="30">
-        <f>SUBTOTAL(9,E5:E6)</f>
+        <f>SUM(E5,E6)</f>
         <v>334648</v>
       </c>
       <c r="F7" s="30">
-        <f>SUBTOTAL(9,F5:F6)</f>
+        <f>SUM(F5,F6)</f>
         <v>344687</v>
       </c>
     </row>
@@ -7815,23 +7815,23 @@
         <v>189</v>
       </c>
       <c r="B10" s="30">
-        <f>SUBTOTAL(9,B9:B9)</f>
+        <f>SUM(B9)</f>
         <v>-10</v>
       </c>
       <c r="C10" s="30">
-        <f>SUBTOTAL(9,C9:C9)</f>
+        <f>SUM(C9)</f>
         <v>-10</v>
       </c>
       <c r="D10" s="30">
-        <f>SUBTOTAL(9,D9:D9)</f>
+        <f>SUM(D9)</f>
         <v>-11</v>
       </c>
       <c r="E10" s="30">
-        <f>SUBTOTAL(9,E9:E9)</f>
+        <f>SUM(E9)</f>
         <v>-11</v>
       </c>
       <c r="F10" s="30">
-        <f>SUBTOTAL(9,F9:F9)</f>
+        <f>SUM(F9)</f>
         <v>-11</v>
       </c>
     </row>
@@ -7870,23 +7870,23 @@
         <v>191</v>
       </c>
       <c r="B13" s="30">
-        <f>SUBTOTAL(9,B12:B12)</f>
+        <f>SUM(B12)</f>
         <v>84000</v>
       </c>
       <c r="C13" s="30">
-        <f>SUBTOTAL(9,C12:C12)</f>
+        <f>SUM(C12)</f>
         <v>129780</v>
       </c>
       <c r="D13" s="30">
-        <f>SUBTOTAL(9,D12:D12)</f>
+        <f>SUM(D12)</f>
         <v>163379</v>
       </c>
       <c r="E13" s="30">
-        <f>SUBTOTAL(9,E12:E12)</f>
+        <f>SUM(E12)</f>
         <v>191227</v>
       </c>
       <c r="F13" s="30">
-        <f>SUBTOTAL(9,F12:F12)</f>
+        <f>SUM(F12)</f>
         <v>196964</v>
       </c>
     </row>
@@ -7925,23 +7925,23 @@
         <v>193</v>
       </c>
       <c r="B16" s="30">
-        <f>SUBTOTAL(9,B15:B15)</f>
+        <f>SUM(B15)</f>
         <v>5000</v>
       </c>
       <c r="C16" s="30">
-        <f>SUBTOTAL(9,C15:C15)</f>
+        <f>SUM(C15)</f>
         <v>5150</v>
       </c>
       <c r="D16" s="30">
-        <f>SUBTOTAL(9,D15:D15)</f>
+        <f>SUM(D15)</f>
         <v>5305</v>
       </c>
       <c r="E16" s="30">
-        <f>SUBTOTAL(9,E15:E15)</f>
+        <f>SUM(E15)</f>
         <v>5464</v>
       </c>
       <c r="F16" s="30">
-        <f>SUBTOTAL(9,F15:F15)</f>
+        <f>SUM(F15)</f>
         <v>5628</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="386">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -316,7 +316,10 @@
     <t>Bright Horizons Microschool - Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs. All other cells are formulas.</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -1330,7 +1333,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1349,6 +1352,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
@@ -1363,7 +1371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1381,6 +1389,15 @@
       <top style="thin">
         <color rgb="FFD0D0D0"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
       </bottom>
@@ -1430,9 +1447,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1440,26 +1458,25 @@
     <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1470,13 +1487,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1485,16 +1502,16 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2185,7 +2202,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2194,197 +2211,197 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="36">
+        <v>107</v>
+      </c>
+      <c r="B4" s="35">
         <v>12</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="35">
         <v>18</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="35">
         <v>22</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="35">
         <v>25</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="35">
         <v>25</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="A6" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="29">
+        <v>114</v>
+      </c>
+      <c r="B7" s="30">
         <v>144000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>222480</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>280078</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>327818</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>337653</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="29">
+        <v>117</v>
+      </c>
+      <c r="B8" s="30">
         <v>3000</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>4635</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>5835</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>6830</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>7034</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="29">
+        <v>118</v>
+      </c>
+      <c r="B9" s="30">
         <v>84000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>129780</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>163379</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>191227</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>196964</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="29">
+        <v>120</v>
+      </c>
+      <c r="B10" s="30">
         <v>5000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>5150</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>5305</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>5464</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>5628</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="29">
+        <v>123</v>
+      </c>
+      <c r="B11" s="30">
         <v>-10</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>-10</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>-11</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>-11</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>-11</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="31">
+      <c r="A12" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="32">
         <f>SUM(B7:B11)</f>
         <v>221600</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>SUM(C7:C11)</f>
         <v>339797</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>SUM(D7:D11)</f>
         <v>426588</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>SUM(E7:E11)</f>
         <v>498557</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>SUM(F7:F11)</f>
         <v>513513</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="B14" s="29">
+        <v>221</v>
+      </c>
+      <c r="B14" s="30">
         <v>18467</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>18878</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>19390</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>19942</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>20541</v>
       </c>
     </row>
@@ -2414,7 +2431,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2423,176 +2440,176 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="29">
+        <v>223</v>
+      </c>
+      <c r="B5" s="30">
         <v>47869</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>59166</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>60941</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>62769</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>64652</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B6" s="29">
+        <v>224</v>
+      </c>
+      <c r="B6" s="30">
         <v>12559</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>15523</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>15989</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>16468</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>16963</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="B7" s="30">
+        <v>225</v>
+      </c>
+      <c r="B7" s="31">
         <f>SUM(B5:B6)</f>
         <v>60428</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>SUM(C5:C6)</f>
         <v>74689</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>SUM(D5:D6)</f>
         <v>76930</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>SUM(E5:E6)</f>
         <v>79237</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>SUM(F5:F6)</f>
         <v>81615</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B9" s="29">
+        <v>226</v>
+      </c>
+      <c r="B9" s="30">
         <v>58506</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>72314</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>74483</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>76718</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>79019</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="B10" s="30">
+        <v>227</v>
+      </c>
+      <c r="B10" s="31">
         <f>SUM(B9:B9)</f>
         <v>58506</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>SUM(C9:C9)</f>
         <v>72314</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>SUM(D9:D9)</f>
         <v>74483</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>SUM(E9:E9)</f>
         <v>76718</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>SUM(F9:F9)</f>
         <v>79019</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B12" s="31">
+      <c r="A12" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="32">
         <f>B7+B10</f>
         <v>118934</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>C7+C10</f>
         <v>147003</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>D7+D10</f>
         <v>151413</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>E7+E10</f>
         <v>155955</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>F7+F10</f>
         <v>160634</v>
       </c>
@@ -2623,7 +2640,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2632,486 +2649,486 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B5" s="29">
+        <v>231</v>
+      </c>
+      <c r="B5" s="30">
         <v>120000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>222480</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>280078</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>327818</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="B6" s="29">
+        <v>232</v>
+      </c>
+      <c r="B6" s="30">
         <v>2500</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>4635</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>5835</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>6830</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B7" s="29">
+        <v>233</v>
+      </c>
+      <c r="B7" s="30">
         <v>70000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>129780</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>163379</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>191227</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>196964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B8" s="29">
+        <v>234</v>
+      </c>
+      <c r="B8" s="30">
         <v>4167</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>5150</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>5305</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>5464</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>5628</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B9" s="29">
+        <v>235</v>
+      </c>
+      <c r="B9" s="30">
         <v>-8</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>-10</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>-11</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>-11</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>-11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="B10" s="30">
+        <v>236</v>
+      </c>
+      <c r="B10" s="31">
         <f>SUM(B5:B9)</f>
         <v>184667</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>SUM(C5:C9)</f>
         <v>339797</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>SUM(D5:D9)</f>
         <v>426588</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>SUM(E5:E9)</f>
         <v>498557</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>SUM(F5:F9)</f>
         <v>513513</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B13" s="29">
+        <v>226</v>
+      </c>
+      <c r="B13" s="30">
         <v>58506</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>72314</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>74483</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>76718</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>79019</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B14" s="29">
+        <v>223</v>
+      </c>
+      <c r="B14" s="30">
         <v>47869</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>59166</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>60941</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>62769</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>64652</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B15" s="29">
+        <v>224</v>
+      </c>
+      <c r="B15" s="30">
         <v>12559</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>15523</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>15989</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>16468</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>16963</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B16" s="30">
+        <v>199</v>
+      </c>
+      <c r="B16" s="31">
         <f>SUM(B13:B15)</f>
         <v>118934</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>SUM(C13:C15)</f>
         <v>147003</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <f>SUM(D13:D15)</f>
         <v>151413</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <f>SUM(E13:E15)</f>
         <v>155955</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f>SUM(F13:F15)</f>
         <v>160634</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
-        <v>146</v>
+      <c r="A19" s="36" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B20" s="29">
+        <v>238</v>
+      </c>
+      <c r="B20" s="30">
         <v>5000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>9270</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>11670</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>13659</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>14069</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
-        <v>147</v>
+      <c r="A21" s="36" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B22" s="29">
+        <v>239</v>
+      </c>
+      <c r="B22" s="30">
         <v>3000</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>5562</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>7002</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>8195</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>8441</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>141</v>
+      <c r="A23" s="36" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B24" s="29">
+        <v>240</v>
+      </c>
+      <c r="B24" s="30">
         <v>25000</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>30900</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>31827</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>32782</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>33765</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B25" s="29">
+        <v>241</v>
+      </c>
+      <c r="B25" s="30">
         <v>3000</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>3708</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>3819</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>3934</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>4052</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B26" s="29">
+        <v>242</v>
+      </c>
+      <c r="B26" s="30">
         <v>2000</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <v>2472</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <v>2546</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <v>2623</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <v>2701</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="B27" s="30">
+        <v>243</v>
+      </c>
+      <c r="B27" s="31">
         <f>SUM(B24:B26)</f>
         <v>30000</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <f>SUM(C24:C26)</f>
         <v>37080</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <f>SUM(D24:D26)</f>
         <v>38192</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <f>SUM(E24:E26)</f>
         <v>39338</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <f>SUM(F24:F26)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="37" t="s">
-        <v>149</v>
+      <c r="A28" s="36" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B29" s="29">
+        <v>244</v>
+      </c>
+      <c r="B29" s="30">
         <v>2500</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>3090</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>3183</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <v>3278</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <v>3377</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="B30" s="30">
+        <v>245</v>
+      </c>
+      <c r="B30" s="31">
         <f>B20+B22+B27+B29</f>
         <v>40500</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <f>C20+C22+C27+C29</f>
         <v>55002</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="31">
         <f>D20+D22+D27+D29</f>
         <v>60047</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="31">
         <f>E20+E22+E27+E29</f>
         <v>64471</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="31">
         <f>F20+F22+F27+F29</f>
         <v>66405</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
+      <c r="A32" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B33" s="30" t="str">
+        <v>247</v>
+      </c>
+      <c r="B33" s="31" t="str">
         <f>SUM(B33:B32)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="30" t="str">
+      <c r="C33" s="31" t="str">
         <f>SUM(C33:C32)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="30" t="str">
+      <c r="D33" s="31" t="str">
         <f>SUM(D33:D32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="30" t="str">
+      <c r="E33" s="31" t="str">
         <f>SUM(E33:E32)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="30" t="str">
+      <c r="F33" s="31" t="str">
         <f>SUM(F33:F32)</f>
         <v>0</v>
       </c>
@@ -3142,7 +3159,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3151,28 +3168,28 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B4" s="33">
         <f>'Budget Detail'!B10</f>
@@ -3197,7 +3214,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B5" s="33">
         <f>'Budget Detail'!B16</f>
@@ -3222,7 +3239,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B6" s="33">
         <f>'Budget Detail'!B30</f>
@@ -3247,7 +3264,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B7" s="33" t="str">
         <f>'Budget Detail'!B33</f>
@@ -3272,146 +3289,146 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B8" s="30">
+        <v>250</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v>159434</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
         <v>202005</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v>211460</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v>220426</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B11" s="31">
+        <v>252</v>
+      </c>
+      <c r="B11" s="32">
         <f>B4-B8</f>
         <v>25233</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>C4-C8</f>
         <v>137792</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>D4-D8</f>
         <v>215128</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>E4-E8</f>
         <v>278131</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>F4-F8</f>
         <v>286475</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B12" s="28">
+        <v>253</v>
+      </c>
+      <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.40551379</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.50429993</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.55787178</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.55787178</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="B13" s="29">
+        <v>254</v>
+      </c>
+      <c r="B13" s="30">
         <v>25233</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>163025</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>378153</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>656284</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>942758</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="B14" s="29">
+        <v>221</v>
+      </c>
+      <c r="B14" s="30">
         <v>15389</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>18878</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>19390</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>19942</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>20541</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="B15" s="29">
+        <v>255</v>
+      </c>
+      <c r="B15" s="30">
         <v>13286</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>11222</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>9612</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>8817</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>9082</v>
       </c>
     </row>
@@ -3442,7 +3459,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3459,286 +3476,286 @@
       <c r="N1" s="15"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="L2" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="M2" s="21" t="s">
         <v>268</v>
       </c>
+      <c r="N2" s="21" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="B4" s="30">
+        <v>236</v>
+      </c>
+      <c r="B4" s="31">
         <v>9150</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <v>22110</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>22110</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>22110</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>22110</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>22110</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="31">
         <v>22110</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="31">
         <v>22110</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="31">
         <v>22110</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="31">
         <v>22110</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="31">
         <v>13210</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="31">
         <v>250</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="31">
         <f>SUM(B4:M4)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
+      <c r="A6" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B7" s="29">
+        <v>271</v>
+      </c>
+      <c r="B7" s="30">
         <v>11893</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>11893</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>11893</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>11893</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>11893</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <v>11893</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="30">
         <v>11893</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="30">
         <v>11893</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="30">
         <v>11893</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="30">
         <v>11893</v>
       </c>
-      <c r="L7" s="29">
-        <v>0</v>
-      </c>
-      <c r="M7" s="29">
-        <v>0</v>
-      </c>
-      <c r="N7" s="29">
+      <c r="L7" s="30">
+        <v>0</v>
+      </c>
+      <c r="M7" s="30">
+        <v>0</v>
+      </c>
+      <c r="N7" s="30">
         <f>SUM(B7:M7)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="29">
+        <v>272</v>
+      </c>
+      <c r="B8" s="30">
         <v>4050</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>4050</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>4050</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>4050</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>4050</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="30">
         <v>4050</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="30">
         <v>4050</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="30">
         <v>4050</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="30">
         <v>4050</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="30">
         <v>4050</v>
       </c>
-      <c r="L8" s="29">
-        <v>0</v>
-      </c>
-      <c r="M8" s="29">
-        <v>0</v>
-      </c>
-      <c r="N8" s="29">
+      <c r="L8" s="30">
+        <v>0</v>
+      </c>
+      <c r="M8" s="30">
+        <v>0</v>
+      </c>
+      <c r="N8" s="30">
         <f>SUM(B8:M8)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B9" s="29">
-        <v>0</v>
-      </c>
-      <c r="C9" s="29">
-        <v>0</v>
-      </c>
-      <c r="D9" s="29">
-        <v>0</v>
-      </c>
-      <c r="E9" s="29">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29">
-        <v>0</v>
-      </c>
-      <c r="G9" s="29">
-        <v>0</v>
-      </c>
-      <c r="H9" s="29">
-        <v>0</v>
-      </c>
-      <c r="I9" s="29">
-        <v>0</v>
-      </c>
-      <c r="J9" s="29">
-        <v>0</v>
-      </c>
-      <c r="K9" s="29">
-        <v>0</v>
-      </c>
-      <c r="L9" s="29">
-        <v>0</v>
-      </c>
-      <c r="M9" s="29">
-        <v>0</v>
-      </c>
-      <c r="N9" s="29" t="str">
+        <v>273</v>
+      </c>
+      <c r="B9" s="30">
+        <v>0</v>
+      </c>
+      <c r="C9" s="30">
+        <v>0</v>
+      </c>
+      <c r="D9" s="30">
+        <v>0</v>
+      </c>
+      <c r="E9" s="30">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30">
+        <v>0</v>
+      </c>
+      <c r="G9" s="30">
+        <v>0</v>
+      </c>
+      <c r="H9" s="30">
+        <v>0</v>
+      </c>
+      <c r="I9" s="30">
+        <v>0</v>
+      </c>
+      <c r="J9" s="30">
+        <v>0</v>
+      </c>
+      <c r="K9" s="30">
+        <v>0</v>
+      </c>
+      <c r="L9" s="30">
+        <v>0</v>
+      </c>
+      <c r="M9" s="30">
+        <v>0</v>
+      </c>
+      <c r="N9" s="30" t="str">
         <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B12" s="33">
         <f>B7+B8+B9</f>
@@ -3795,7 +3812,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B13" s="33">
         <f>B4-B12</f>
@@ -3852,90 +3869,90 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="B14" s="38">
+        <v>276</v>
+      </c>
+      <c r="B14" s="37">
         <f>B17+B13</f>
         <v>-6793</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="37">
         <f>B14+C13</f>
         <v>-626</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="37">
         <f>C14+D13</f>
         <v>5541</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="37">
         <f>D14+E13</f>
         <v>11708</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="37">
         <f>E14+F13</f>
         <v>17875</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="37">
         <f>F14+G13</f>
         <v>24042</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="37">
         <f>G14+H13</f>
         <v>30209</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="37">
         <f>H14+I13</f>
         <v>36376</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14" s="37">
         <f>I14+J13</f>
         <v>42543</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14" s="37">
         <f>J14+K13</f>
         <v>48710</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14" s="37">
         <f>K14+L13</f>
         <v>61920</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14" s="37">
         <f>L14+M13</f>
         <v>62170</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="32">
         <f>M14</f>
         <v>62170</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="22">
+        <v>163</v>
+      </c>
+      <c r="B17" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B18" s="38">
+        <v>278</v>
+      </c>
+      <c r="B18" s="37">
         <f>M14</f>
         <v>62170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="B19" s="29">
+        <v>279</v>
+      </c>
+      <c r="B19" s="30">
         <f>MIN(B14:M14)</f>
         <v>-6793</v>
       </c>
@@ -3966,7 +3983,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3975,68 +3992,68 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="B5" s="30">
+      <c r="A5" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="B5" s="31">
         <v>184667</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>339797</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>426588</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>498557</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>513513</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B8" s="33">
         <v>118934</v>
@@ -4056,7 +4073,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B9" s="33">
         <v>40500</v>
@@ -4076,7 +4093,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B10" s="33">
         <v>0</v>
@@ -4095,86 +4112,86 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="B11" s="30">
+      <c r="A11" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
         <v>159434</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUM(C8:C10)</f>
         <v>202005</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUM(D8:D10)</f>
         <v>211460</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUM(E8:E10)</f>
         <v>220426</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>SUM(F8:F10)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="B14" s="31">
+      <c r="A14" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="B14" s="32">
         <f>B5-B11</f>
         <v>25233</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>C5-C11</f>
         <v>137792</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>D5-D11</f>
         <v>215128</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>E5-E11</f>
         <v>278131</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>F5-F11</f>
         <v>286475</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B15" s="28">
+        <v>253</v>
+      </c>
+      <c r="B15" s="29">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.40551379</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.50429993</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.55787178</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.55787178</v>
       </c>
@@ -4214,50 +4231,50 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="B5" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="42" t="s">
+      <c r="A5" s="39" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="B5" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="E5" s="41" t="s">
-        <v>214</v>
+      <c r="D5" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -4286,7 +4303,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4295,276 +4312,276 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B5" s="43">
+        <v>289</v>
+      </c>
+      <c r="B5" s="42">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>62170</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="42">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>199962</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="42">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>415091</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="42">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>693221</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="42">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>979696</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="B6" s="29">
-        <v>0</v>
-      </c>
-      <c r="C6" s="29">
-        <v>0</v>
-      </c>
-      <c r="D6" s="29">
-        <v>0</v>
-      </c>
-      <c r="E6" s="29">
-        <v>0</v>
-      </c>
-      <c r="F6" s="29">
+        <v>290</v>
+      </c>
+      <c r="B6" s="30">
+        <v>0</v>
+      </c>
+      <c r="C6" s="30">
+        <v>0</v>
+      </c>
+      <c r="D6" s="30">
+        <v>0</v>
+      </c>
+      <c r="E6" s="30">
+        <v>0</v>
+      </c>
+      <c r="F6" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="B7" s="29">
+        <v>291</v>
+      </c>
+      <c r="B7" s="30">
         <v>5000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>5000</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>5000</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>5000</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>5000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B8" s="29">
-        <v>0</v>
-      </c>
-      <c r="C8" s="29">
-        <v>0</v>
-      </c>
-      <c r="D8" s="29">
-        <v>0</v>
-      </c>
-      <c r="E8" s="29">
-        <v>0</v>
-      </c>
-      <c r="F8" s="29">
+        <v>292</v>
+      </c>
+      <c r="B8" s="30">
+        <v>0</v>
+      </c>
+      <c r="C8" s="30">
+        <v>0</v>
+      </c>
+      <c r="D8" s="30">
+        <v>0</v>
+      </c>
+      <c r="E8" s="30">
+        <v>0</v>
+      </c>
+      <c r="F8" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="B9" s="30">
+        <v>293</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
         <v>67170</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
         <v>204962</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
         <v>420091</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
         <v>698221</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
         <v>984696</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B12" s="29">
-        <v>0</v>
-      </c>
-      <c r="C12" s="29">
-        <v>0</v>
-      </c>
-      <c r="D12" s="29">
-        <v>0</v>
-      </c>
-      <c r="E12" s="29">
-        <v>0</v>
-      </c>
-      <c r="F12" s="29">
+        <v>295</v>
+      </c>
+      <c r="B12" s="30">
+        <v>0</v>
+      </c>
+      <c r="C12" s="30">
+        <v>0</v>
+      </c>
+      <c r="D12" s="30">
+        <v>0</v>
+      </c>
+      <c r="E12" s="30">
+        <v>0</v>
+      </c>
+      <c r="F12" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="B13" s="29">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29">
+        <v>296</v>
+      </c>
+      <c r="B13" s="30">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="B14" s="30" t="str">
+        <v>297</v>
+      </c>
+      <c r="B14" s="31" t="str">
         <f>SUM(B12:B13)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="30" t="str">
+      <c r="C14" s="31" t="str">
         <f>SUM(C12:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="30" t="str">
+      <c r="D14" s="31" t="str">
         <f>SUM(D12:D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="30" t="str">
+      <c r="E14" s="31" t="str">
         <f>SUM(E12:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="30" t="str">
+      <c r="F14" s="31" t="str">
         <f>SUM(F12:F13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="B17" s="31">
+        <v>299</v>
+      </c>
+      <c r="B17" s="32">
         <f>B9-B14</f>
         <v>67170</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>C9-C14</f>
         <v>204962</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>D9-D14</f>
         <v>420091</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>E9-E14</f>
         <v>698221</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>F9-F14</f>
         <v>984696</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="B19" s="44" t="str">
+        <v>300</v>
+      </c>
+      <c r="B19" s="43" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="44" t="str">
+      <c r="C19" s="43" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="44" t="str">
+      <c r="D19" s="43" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="44" t="str">
+      <c r="E19" s="43" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="44" t="str">
+      <c r="F19" s="43" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -4595,7 +4612,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4604,98 +4621,98 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="B5" s="29">
+        <v>303</v>
+      </c>
+      <c r="B5" s="30">
         <v>184667</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>339797</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>426588</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>498557</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>513513</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B6" s="29">
+        <v>271</v>
+      </c>
+      <c r="B6" s="30">
         <v>118934</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>147003</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>151413</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>155955</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>160634</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="29">
+        <v>272</v>
+      </c>
+      <c r="B7" s="30">
         <v>40500</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>55002</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>60047</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>64471</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>66405</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B8" s="33">
         <f>B5-B6-B7</f>
@@ -4720,102 +4737,102 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B9" s="29">
-        <v>0</v>
-      </c>
-      <c r="C9" s="29">
-        <v>0</v>
-      </c>
-      <c r="D9" s="29">
-        <v>0</v>
-      </c>
-      <c r="E9" s="29">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29">
+        <v>273</v>
+      </c>
+      <c r="B9" s="30">
+        <v>0</v>
+      </c>
+      <c r="C9" s="30">
+        <v>0</v>
+      </c>
+      <c r="D9" s="30">
+        <v>0</v>
+      </c>
+      <c r="E9" s="30">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="B10" s="45" t="s">
         <v>305</v>
       </c>
-      <c r="C10" s="45" t="s">
-        <v>305</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>305</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>305</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>305</v>
+      <c r="B10" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="B13" s="29">
+        <v>308</v>
+      </c>
+      <c r="B13" s="30">
         <v>62170</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>199962</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>415091</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>693221</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>979696</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B14" s="35">
+        <v>309</v>
+      </c>
+      <c r="B14" s="45">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>142</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="45">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>361</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="45">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>716</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="45">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>1148</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="45">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>1575</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B15" s="34">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -4840,97 +4857,97 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B16" s="28">
+        <v>183</v>
+      </c>
+      <c r="B16" s="29">
         <v>0.48</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <v>0.72</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <v>0.88</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <v>1</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="29">
+        <v>221</v>
+      </c>
+      <c r="B19" s="30">
         <v>15389</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>18878</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>19390</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>19942</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>20541</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="B20" s="29">
+        <v>312</v>
+      </c>
+      <c r="B20" s="30">
         <v>118934</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>147003</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>151413</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>155955</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>160634</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="B21" s="29">
+        <v>313</v>
+      </c>
+      <c r="B21" s="30">
         <v>3375</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>3056</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>2729</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>2579</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>2656</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B22" s="46">
         <v>10</v>
@@ -4949,113 +4966,113 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="A24" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D25" s="47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E26" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>320</v>
+      </c>
+      <c r="C27" s="48" t="s">
         <v>318</v>
       </c>
-      <c r="B27" s="49" t="s">
-        <v>319</v>
-      </c>
-      <c r="C27" s="48" t="s">
-        <v>317</v>
-      </c>
       <c r="D27" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E27" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D28" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D29" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -5096,59 +5113,59 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="B4" s="29">
+        <v>325</v>
+      </c>
+      <c r="B4" s="30">
         <v>20000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="E4" s="29">
+        <v>326</v>
+      </c>
+      <c r="E4" s="30">
         <v>15000</v>
       </c>
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="E5" s="29">
+        <v>327</v>
+      </c>
+      <c r="E5" s="30">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="B7" s="31">
+        <v>328</v>
+      </c>
+      <c r="B7" s="32">
         <v>20000</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="E7" s="31">
+        <v>329</v>
+      </c>
+      <c r="E7" s="32">
         <v>20000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="B8" s="44">
+        <v>330</v>
+      </c>
+      <c r="B8" s="43">
         <v>0</v>
       </c>
     </row>
@@ -5494,7 +5511,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5503,312 +5520,312 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="B6" s="29">
+        <v>303</v>
+      </c>
+      <c r="B6" s="30">
         <v>184667</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>339797</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>426588</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>498557</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>513513</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B7" s="29">
+        <v>250</v>
+      </c>
+      <c r="B7" s="30">
         <v>159434</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>202005</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>211460</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>220426</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>227039</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B8" s="31">
+        <v>252</v>
+      </c>
+      <c r="B8" s="32">
         <v>25233</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <v>137792</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <v>215128</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <v>278131</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <v>286475</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B9" s="28">
+        <v>253</v>
+      </c>
+      <c r="B9" s="29">
         <v>0.13663808664259927</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <v>0.40551379205819943</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>0.5042999253916937</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>0.5578717808219178</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B11" s="35">
+        <v>314</v>
+      </c>
+      <c r="B11" s="45">
         <v>10</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="45">
         <v>10</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="45">
         <v>10</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="45">
         <v>9</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="45">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="B16" s="29">
+        <v>303</v>
+      </c>
+      <c r="B16" s="30">
         <v>147733</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>271838</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>341270</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>398845</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>410811</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B17" s="29">
+        <v>250</v>
+      </c>
+      <c r="B17" s="30">
         <v>159434</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>202005</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>211460</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>220426</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>227039</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B18" s="31">
+        <v>252</v>
+      </c>
+      <c r="B18" s="32">
         <v>-11701</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <v>69833</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <v>129811</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <v>178419</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <v>183772</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B19" s="28">
+        <v>253</v>
+      </c>
+      <c r="B19" s="29">
         <v>-0.07920239169675096</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <v>0.2568922400727494</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <v>0.38037490673961705</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="29">
         <v>0.4473397260273973</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="29">
         <v>0.44733972602739736</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B21" s="35">
+        <v>314</v>
+      </c>
+      <c r="B21" s="45">
         <v>12</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="45">
         <v>10</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="45">
         <v>10</v>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="45">
         <v>10</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="45">
         <v>10</v>
       </c>
     </row>
@@ -5840,7 +5857,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5851,10 +5868,10 @@
       <c r="H1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -5866,7 +5883,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -5874,7 +5891,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -5898,23 +5915,23 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -5927,132 +5944,132 @@
         <v>7</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="D13" s="29">
+        <v>303</v>
+      </c>
+      <c r="D13" s="30">
         <v>184667</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>339797</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>426588</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <v>498557</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <v>513513</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D14" s="29">
+        <v>250</v>
+      </c>
+      <c r="D14" s="30">
         <v>159434</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>202005</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>211460</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <v>220426</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <v>227039</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="D15" s="29">
+        <v>252</v>
+      </c>
+      <c r="D15" s="30">
         <v>25233</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>137792</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>215128</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="30">
         <v>278131</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="30">
         <v>286475</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="D16" s="29">
+        <v>340</v>
+      </c>
+      <c r="D16" s="30">
         <v>62170</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>199962</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>415091</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <v>693221</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="30">
         <v>979696</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="D17" s="29">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29">
+        <v>341</v>
+      </c>
+      <c r="D17" s="30">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="A19" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -6065,104 +6082,104 @@
         <v>7</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" s="52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H20" s="52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="D21" s="28">
+        <v>343</v>
+      </c>
+      <c r="D21" s="29">
         <v>0.13663808664259927</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <v>0.40551379205819943</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <v>0.5042999253916937</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <v>0.5578717808219178</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <v>0.5578717808219178</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G22" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H22" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D23" s="28">
+        <v>183</v>
+      </c>
+      <c r="D23" s="29">
         <v>0.48</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <v>0.72</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <v>0.88</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <v>1</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="D24" s="35">
+        <v>344</v>
+      </c>
+      <c r="D24" s="45">
         <v>12</v>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="45">
         <v>18</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="45">
         <v>22</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="45">
         <v>25</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="45">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -6202,7 +6219,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6212,7 +6229,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C3" s="53"/>
       <c r="D3" s="53"/>
@@ -6221,28 +6238,28 @@
       <c r="G3" s="53"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>347</v>
+      <c r="B5" s="19" t="s">
+        <v>348</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C6" s="55">
         <v>12</v>
@@ -6262,7 +6279,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C7" s="56">
         <v>184666.6666666667</v>
@@ -6282,7 +6299,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C8" s="56">
         <v>118934.16666666667</v>
@@ -6302,7 +6319,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C9" s="56">
         <v>40500</v>
@@ -6322,7 +6339,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C10" s="56">
         <v>0</v>
@@ -6342,7 +6359,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C11" s="57">
         <v>25232.5</v>
@@ -6362,7 +6379,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C12" s="57">
         <v>62170</v>
@@ -6382,7 +6399,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C13" s="58">
         <v>0.13663808664259927</v>
@@ -6402,7 +6419,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C14" s="56">
         <v>15388.88888888889</v>
@@ -6422,7 +6439,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C15" s="59">
         <v>0.644047833935018</v>
@@ -6442,7 +6459,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C16" s="58">
         <v>0.06579422382671479</v>
@@ -6462,7 +6479,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C17" s="58">
         <v>0.13663808664259935</v>
@@ -6482,30 +6499,30 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F18" s="60" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G18" s="60" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D19" s="61"/>
       <c r="E19" s="61"/>
@@ -6514,10 +6531,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D20" s="61"/>
       <c r="E20" s="61"/>
@@ -6525,130 +6542,130 @@
       <c r="G20" s="61"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="C22" s="18" t="s">
+      <c r="B22" s="19" t="s">
         <v>360</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="C22" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="G22" s="18"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="40" t="s">
-        <v>363</v>
+      <c r="B23" s="39" t="s">
+        <v>364</v>
       </c>
       <c r="C23" s="62" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E23" s="63"/>
       <c r="F23" s="64" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G23" s="64"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="40" t="s">
-        <v>367</v>
+      <c r="B24" s="39" t="s">
+        <v>368</v>
       </c>
       <c r="C24" s="62" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E24" s="63"/>
       <c r="F24" s="64" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G24" s="64"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="40" t="s">
-        <v>370</v>
+      <c r="B25" s="39" t="s">
+        <v>371</v>
       </c>
       <c r="C25" s="62" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E25" s="63"/>
       <c r="F25" s="64" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G25" s="64"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="40" t="s">
-        <v>373</v>
+      <c r="B26" s="39" t="s">
+        <v>374</v>
       </c>
       <c r="C26" s="62" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E26" s="63"/>
       <c r="F26" s="64" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G26" s="64"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
-        <v>376</v>
+      <c r="B27" s="39" t="s">
+        <v>377</v>
       </c>
       <c r="C27" s="62" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="64" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G27" s="64"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="40" t="s">
-        <v>379</v>
+      <c r="B28" s="39" t="s">
+        <v>380</v>
       </c>
       <c r="C28" s="62" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E28" s="63"/>
       <c r="F28" s="64" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G28" s="64"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="40" t="s">
-        <v>382</v>
+      <c r="B30" s="39" t="s">
+        <v>383</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="65" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C32" s="65"/>
       <c r="D32" s="65"/>
@@ -6777,30 +6794,36 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>94</v>
       </c>
+      <c r="D2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6808,7 +6831,7 @@
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6816,7 +6839,7 @@
       <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6824,23 +6847,23 @@
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="19" t="s">
         <v>97</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6848,523 +6871,523 @@
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="19">
+        <v>99</v>
+      </c>
+      <c r="B12" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="19">
+        <v>100</v>
+      </c>
+      <c r="B13" s="20">
         <v>25</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
+      <c r="A15" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="D16" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="E16" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="21">
+        <v>107</v>
+      </c>
+      <c r="B17" s="22">
         <v>12</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <v>18</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="22">
         <v>22</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="22">
         <v>25</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="22">
         <v>25</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
+      <c r="A19" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="B20" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="C20" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="D20" s="21" t="s">
         <v>112</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="22">
+        <v>116</v>
+      </c>
+      <c r="D21" s="23">
         <v>12000</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <v>250</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="22">
+        <v>116</v>
+      </c>
+      <c r="D23" s="23">
         <v>7000</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="22">
+        <v>122</v>
+      </c>
+      <c r="D24" s="23">
         <v>5000</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" s="22">
+        <v>125</v>
+      </c>
+      <c r="D25" s="23">
         <v>10</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
+      <c r="A27" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="20" t="s">
+      <c r="A28" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="B28" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="D28" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="E28" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="G28" s="20" t="s">
+      <c r="F28" s="21" t="s">
         <v>131</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="24">
+        <v>135</v>
+      </c>
+      <c r="D29" s="25">
         <v>1</v>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="23">
         <v>55000</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="24">
         <v>0.2</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" s="24">
+      <c r="D30" s="25">
         <v>1</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="23">
         <v>45000</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="24">
         <v>0.2</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>136</v>
-      </c>
       <c r="C31" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D31" s="24">
+        <v>139</v>
+      </c>
+      <c r="D31" s="25">
         <v>0.5</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <v>28000</v>
       </c>
-      <c r="F31" s="23">
-        <v>0</v>
-      </c>
-      <c r="G31" s="23">
+      <c r="F31" s="24">
+        <v>0</v>
+      </c>
+      <c r="G31" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
+      <c r="A33" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B34" s="20" t="s">
+      <c r="A34" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="B34" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="C34" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="D34" s="21" t="s">
         <v>112</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D35" s="22">
+        <v>143</v>
+      </c>
+      <c r="D35" s="23">
         <v>2500</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="24">
         <v>0.03</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D36" s="22">
+      <c r="D36" s="23">
         <v>300</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D37" s="22">
+        <v>122</v>
+      </c>
+      <c r="D37" s="23">
         <v>2400</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" s="22">
+        <v>116</v>
+      </c>
+      <c r="D38" s="23">
         <v>500</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" s="22">
+        <v>116</v>
+      </c>
+      <c r="D39" s="23">
         <v>300</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D40" s="22">
+        <v>122</v>
+      </c>
+      <c r="D40" s="23">
         <v>3000</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
+      <c r="A42" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" s="20" t="s">
+      <c r="A43" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="D43" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" s="20" t="s">
+      <c r="B43" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>153</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C44" s="22">
+        <v>156</v>
+      </c>
+      <c r="C44" s="23">
         <v>30000</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="24">
         <v>0.06</v>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
+      <c r="A46" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B47" s="23">
+        <v>158</v>
+      </c>
+      <c r="B47" s="24">
         <v>0.03</v>
       </c>
-      <c r="C47" s="25" t="s">
-        <v>158</v>
+      <c r="C47" s="26" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B48" s="23">
+        <v>160</v>
+      </c>
+      <c r="B48" s="24">
         <v>0.03</v>
       </c>
-      <c r="C48" s="25" t="s">
-        <v>160</v>
+      <c r="C48" s="26" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B49" s="24">
+        <v>162</v>
+      </c>
+      <c r="B49" s="25">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B50" s="22">
+        <v>163</v>
+      </c>
+      <c r="B50" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="B51" s="19" t="s">
         <v>164</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -7399,10 +7422,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7423,10 +7446,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7439,7 +7462,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -7447,66 +7470,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -7545,108 +7568,108 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="A5" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="26">
+        <v>107</v>
+      </c>
+      <c r="B6" s="27">
         <v>12</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>18</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <v>22</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>25</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="21">
+        <v>100</v>
+      </c>
+      <c r="B7" s="22">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B8" s="27">
+        <v>183</v>
+      </c>
+      <c r="B8" s="28">
         <f>B6/$B$7</f>
         <v>0.48</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>C6/$B$7</f>
         <v>0.72</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>D6/$B$7</f>
         <v>0.88</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>E6/$B$7</f>
         <v>1</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>F6/$B$7</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="C10" s="28">
+        <v>185</v>
+      </c>
+      <c r="C10" s="29">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
         <v>0.5</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>IF(C6=0,0,(D6-C6)/C6)</f>
         <v>0.22222222</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>IF(D6=0,0,(E6-D6)/D6)</f>
         <v>0.13636364</v>
       </c>
-      <c r="F10" s="28" t="str">
+      <c r="F10" s="29" t="str">
         <f>IF(E6=0,0,(F6-E6)/E6)</f>
         <v>0</v>
       </c>
@@ -7677,7 +7700,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7686,286 +7709,286 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="29">
+        <v>114</v>
+      </c>
+      <c r="B5" s="30">
         <v>144000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>222480</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>280078</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>327818</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="29">
+        <v>117</v>
+      </c>
+      <c r="B6" s="30">
         <v>3000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>4635</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>5835</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>6830</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B7" s="30">
+        <v>188</v>
+      </c>
+      <c r="B7" s="31">
         <f>SUM(B5,B6)</f>
         <v>147000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>SUM(C5,C6)</f>
         <v>227115</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>SUM(D5,D6)</f>
         <v>285913</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>SUM(E5,E6)</f>
         <v>334648</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>SUM(F5,F6)</f>
         <v>344687</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="29">
+        <v>123</v>
+      </c>
+      <c r="B9" s="30">
         <v>-10</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>-10</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>-11</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>-11</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>-11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B10" s="30">
+        <v>190</v>
+      </c>
+      <c r="B10" s="31">
         <f>SUM(B9)</f>
         <v>-10</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>SUM(C9)</f>
         <v>-10</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>SUM(D9)</f>
         <v>-11</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>SUM(E9)</f>
         <v>-11</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>SUM(F9)</f>
         <v>-11</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="29">
+        <v>118</v>
+      </c>
+      <c r="B12" s="30">
         <v>84000</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>129780</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>163379</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>191227</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>196964</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="B13" s="30">
+        <v>192</v>
+      </c>
+      <c r="B13" s="31">
         <f>SUM(B12)</f>
         <v>84000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>SUM(C12)</f>
         <v>129780</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>SUM(D12)</f>
         <v>163379</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>SUM(E12)</f>
         <v>191227</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>SUM(F12)</f>
         <v>196964</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="22">
+        <v>120</v>
+      </c>
+      <c r="B15" s="23">
         <v>5000</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>5150</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>5305</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>5464</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>5628</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" s="30">
+        <v>194</v>
+      </c>
+      <c r="B16" s="31">
         <f>SUM(B15)</f>
         <v>5000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>SUM(C15)</f>
         <v>5150</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <f>SUM(D15)</f>
         <v>5305</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <f>SUM(E15)</f>
         <v>5464</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f>SUM(F15)</f>
         <v>5628</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="B18" s="31">
+      <c r="A18" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" s="32">
         <f>SUM(B7,B10,B13,B16)</f>
         <v>221600</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <f>SUM(C7,C10,C13,C16)</f>
         <v>339797</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <f>SUM(D7,D10,D13,D16)</f>
         <v>426588</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <f>SUM(E7,E10,E13,E16)</f>
         <v>498557</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <f>SUM(F7,F10,F13,F16)</f>
         <v>513513</v>
       </c>
@@ -8010,45 +8033,45 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="20" t="s">
+      <c r="A3" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>196</v>
+      <c r="F3" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="32">
+        <v>134</v>
+      </c>
+      <c r="C4" s="25">
         <v>1</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="23">
         <v>55000</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="24">
         <v>0.2</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="24">
         <v>0.0765</v>
       </c>
       <c r="G4" s="33">
@@ -8057,21 +8080,21 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="32">
+        <v>137</v>
+      </c>
+      <c r="C5" s="25">
         <v>1</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="23">
         <v>45000</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="24">
         <v>0.2</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="24">
         <v>0.0765</v>
       </c>
       <c r="G5" s="33">
@@ -8080,21 +8103,21 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="32">
+      <c r="C6" s="25">
         <v>0.5</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="23">
         <v>28000</v>
       </c>
-      <c r="E6" s="28">
-        <v>0</v>
-      </c>
-      <c r="F6" s="28">
+      <c r="E6" s="24">
+        <v>0</v>
+      </c>
+      <c r="F6" s="24">
         <v>0.0765</v>
       </c>
       <c r="G6" s="33">
@@ -8102,79 +8125,79 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
+      <c r="A8" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="20" t="s">
+      <c r="B9" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="C9" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="D9" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B10" s="31">
+        <v>199</v>
+      </c>
+      <c r="B10" s="32">
         <v>118934</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <v>147003</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <v>151413</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <v>155955</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <v>160634</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B11" s="28">
+        <v>200</v>
+      </c>
+      <c r="B11" s="29">
         <v>0.5367065282791817</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <v>0.4326189754471052</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <v>0.3549390698831137</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <v>0.3128131506849315</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="29">
         <v>0.3128131506849315</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B12" s="34">
         <v>4.8</v>
@@ -8218,7 +8241,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8227,306 +8250,306 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="B5" s="29">
+        <v>203</v>
+      </c>
+      <c r="B5" s="30">
         <v>6000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>9270</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>11670</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>13659</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>14069</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B6" s="30">
+        <v>204</v>
+      </c>
+      <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>SUM(C5:C5)</f>
         <v>9270</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>SUM(D5:D5)</f>
         <v>11670</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>SUM(E5:E5)</f>
         <v>13659</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>SUM(F5:F5)</f>
         <v>14069</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B8" s="29">
+        <v>205</v>
+      </c>
+      <c r="B8" s="30">
         <v>3600</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>5562</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>7002</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>8195</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>8441</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="30">
+        <v>206</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
         <v>3600</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUM(C8:C8)</f>
         <v>5562</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUM(D8:D8)</f>
         <v>7002</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUM(E8:E8)</f>
         <v>8195</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>SUM(F8:F8)</f>
         <v>8441</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="29">
+        <v>207</v>
+      </c>
+      <c r="B11" s="30">
         <v>30000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>30900</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>31827</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>32782</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>33765</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B12" s="29">
+        <v>208</v>
+      </c>
+      <c r="B12" s="30">
         <v>3600</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>3708</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>3819</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>3934</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>4052</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="29">
+        <v>209</v>
+      </c>
+      <c r="B13" s="30">
         <v>2400</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>2472</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>2546</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <v>2623</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <v>2701</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="B14" s="30">
+        <v>210</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B11:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>SUM(C11:C13)</f>
         <v>37080</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>SUM(D11:D13)</f>
         <v>38192</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>SUM(E11:E13)</f>
         <v>39338</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>SUM(F11:F13)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="A15" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="B16" s="29">
+        <v>211</v>
+      </c>
+      <c r="B16" s="30">
         <v>3000</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>3090</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>3183</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>3278</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>3377</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="B17" s="30">
+        <v>212</v>
+      </c>
+      <c r="B17" s="31">
         <f>SUM(B16:B16)</f>
         <v>3000</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>SUM(C16:C16)</f>
         <v>3090</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>SUM(D16:D16)</f>
         <v>3183</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>SUM(E16:E16)</f>
         <v>3278</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>SUM(F16:F16)</f>
         <v>3377</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="B19" s="31">
+      <c r="A19" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="32">
         <f>B6+B9+B14+B17</f>
         <v>48600</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>C6+C9+C14+C17</f>
         <v>55002</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="32">
         <f>D6+D9+D14+D17</f>
         <v>60047</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="32">
         <f>E6+E9+E14+E17</f>
         <v>64471</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="32">
         <f>F6+F9+F14+F17</f>
         <v>66405</v>
       </c>
@@ -8558,7 +8581,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8567,39 +8590,39 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="B3" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>214</v>
+      <c r="D3" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="22">
+        <v>156</v>
+      </c>
+      <c r="C4" s="23">
         <v>30000</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="24">
         <v>0.06</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="22">
         <v>5</v>
       </c>
       <c r="F4" s="33">
@@ -8608,17 +8631,17 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="F6" s="31">
+        <v>216</v>
+      </c>
+      <c r="F6" s="32">
         <v>6960</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F7" s="30">
+        <v>217</v>
+      </c>
+      <c r="F7" s="31">
         <v>30000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="396">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1078,6 +1078,15 @@
     <t>Generated March 26, 2026</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -1096,13 +1105,34 @@
     <t>Year 5</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
     <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
   </si>
   <si>
     <t>Break-even Year</t>
@@ -1203,7 +1233,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1327,6 +1357,18 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <color rgb="FF9CA3AF"/>
       <sz val="11"/>
@@ -1422,7 +1464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1493,6 +1535,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1508,9 +1553,14 @@
     <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1524,14 +1574,35 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6205,19 +6276,20 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>346</v>
       </c>
@@ -6226,8 +6298,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
         <v>347</v>
       </c>
@@ -6236,530 +6309,602 @@
       <c r="E3" s="53"/>
       <c r="F3" s="53"/>
       <c r="G3" s="53"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="H3" s="53"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="54" t="s">
         <v>348</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="D4" s="55" t="s">
         <v>349</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="F4" s="56" t="s">
         <v>350</v>
       </c>
-      <c r="E5" s="54" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
         <v>351</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="C6" s="57" t="s">
         <v>352</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="D6" s="57" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="C6" s="55">
-        <v>12</v>
-      </c>
-      <c r="D6" s="55">
-        <v>18</v>
-      </c>
-      <c r="E6" s="55">
-        <v>22</v>
-      </c>
-      <c r="F6" s="55">
-        <v>25</v>
-      </c>
-      <c r="G6" s="55">
-        <v>25</v>
+      <c r="E6" s="57" t="s">
+        <v>354</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>356</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="C7" s="56">
-        <v>184666.6666666667</v>
-      </c>
-      <c r="D7" s="56">
-        <v>339797</v>
-      </c>
-      <c r="E7" s="56">
-        <v>426587.88999999996</v>
-      </c>
-      <c r="F7" s="56">
-        <v>498556.69375000003</v>
-      </c>
-      <c r="G7" s="56">
-        <v>513513.3945625001</v>
+        <v>344</v>
+      </c>
+      <c r="C7" s="58">
+        <v>12</v>
+      </c>
+      <c r="D7" s="58">
+        <v>18</v>
+      </c>
+      <c r="E7" s="58">
+        <v>22</v>
+      </c>
+      <c r="F7" s="58">
+        <v>25</v>
+      </c>
+      <c r="G7" s="58">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="56">
-        <v>118934.16666666667</v>
-      </c>
-      <c r="D8" s="56">
-        <v>147002.63</v>
-      </c>
-      <c r="E8" s="56">
-        <v>151412.7089</v>
-      </c>
-      <c r="F8" s="56">
-        <v>155955.090167</v>
-      </c>
-      <c r="G8" s="56">
-        <v>160633.74287201</v>
+        <v>303</v>
+      </c>
+      <c r="C8" s="59">
+        <v>184666.6666666667</v>
+      </c>
+      <c r="D8" s="59">
+        <v>339797</v>
+      </c>
+      <c r="E8" s="59">
+        <v>426587.88999999996</v>
+      </c>
+      <c r="F8" s="59">
+        <v>498556.69375000003</v>
+      </c>
+      <c r="G8" s="59">
+        <v>513513.3945625001</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="C9" s="56">
-        <v>40500</v>
-      </c>
-      <c r="D9" s="56">
-        <v>55002</v>
-      </c>
-      <c r="E9" s="56">
-        <v>60046.93999999999</v>
-      </c>
-      <c r="F9" s="56">
-        <v>64470.893</v>
-      </c>
-      <c r="G9" s="56">
-        <v>66405.01979</v>
+        <v>271</v>
+      </c>
+      <c r="C9" s="59">
+        <v>118934.16666666667</v>
+      </c>
+      <c r="D9" s="59">
+        <v>147002.63</v>
+      </c>
+      <c r="E9" s="59">
+        <v>151412.7089</v>
+      </c>
+      <c r="F9" s="59">
+        <v>155955.090167</v>
+      </c>
+      <c r="G9" s="59">
+        <v>160633.74287201</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="59">
+        <v>40500</v>
+      </c>
+      <c r="D10" s="59">
+        <v>55002</v>
+      </c>
+      <c r="E10" s="59">
+        <v>60046.93999999999</v>
+      </c>
+      <c r="F10" s="59">
+        <v>64470.893</v>
+      </c>
+      <c r="G10" s="59">
+        <v>66405.01979</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="C10" s="56">
-        <v>0</v>
-      </c>
-      <c r="D10" s="56">
-        <v>0</v>
-      </c>
-      <c r="E10" s="56">
-        <v>0</v>
-      </c>
-      <c r="F10" s="56">
-        <v>0</v>
-      </c>
-      <c r="G10" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="C11" s="57">
-        <v>25232.5</v>
-      </c>
-      <c r="D11" s="57">
-        <v>137792.37</v>
-      </c>
-      <c r="E11" s="57">
-        <v>215128.24109999998</v>
-      </c>
-      <c r="F11" s="57">
-        <v>278130.71058300004</v>
-      </c>
-      <c r="G11" s="57">
-        <v>286474.6319004901</v>
+      <c r="C11" s="59">
+        <v>0</v>
+      </c>
+      <c r="D11" s="59">
+        <v>0</v>
+      </c>
+      <c r="E11" s="59">
+        <v>0</v>
+      </c>
+      <c r="F11" s="59">
+        <v>0</v>
+      </c>
+      <c r="G11" s="59">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="C12" s="57">
-        <v>62170</v>
-      </c>
-      <c r="D12" s="57">
-        <v>199962.37</v>
-      </c>
-      <c r="E12" s="57">
-        <v>415090.6111</v>
-      </c>
-      <c r="F12" s="57">
-        <v>693221.3216830001</v>
-      </c>
-      <c r="G12" s="57">
-        <v>979695.9535834901</v>
+        <v>252</v>
+      </c>
+      <c r="C12" s="60">
+        <v>25232.5</v>
+      </c>
+      <c r="D12" s="60">
+        <v>137792.37</v>
+      </c>
+      <c r="E12" s="60">
+        <v>215128.24109999998</v>
+      </c>
+      <c r="F12" s="60">
+        <v>278130.71058300004</v>
+      </c>
+      <c r="G12" s="60">
+        <v>286474.6319004901</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="C13" s="58">
-        <v>0.13663808664259927</v>
-      </c>
-      <c r="D13" s="58">
-        <v>0.40551379205819943</v>
-      </c>
-      <c r="E13" s="58">
-        <v>0.5042999253916937</v>
-      </c>
-      <c r="F13" s="58">
-        <v>0.5578717808219178</v>
-      </c>
-      <c r="G13" s="58">
-        <v>0.5578717808219178</v>
+        <v>308</v>
+      </c>
+      <c r="C13" s="60">
+        <v>62170</v>
+      </c>
+      <c r="D13" s="60">
+        <v>199962.37</v>
+      </c>
+      <c r="E13" s="60">
+        <v>415090.6111</v>
+      </c>
+      <c r="F13" s="60">
+        <v>693221.3216830001</v>
+      </c>
+      <c r="G13" s="60">
+        <v>979695.9535834901</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C14" s="61">
+        <v>0.13663808664259927</v>
+      </c>
+      <c r="D14" s="61">
+        <v>0.40551379205819943</v>
+      </c>
+      <c r="E14" s="61">
+        <v>0.5042999253916937</v>
+      </c>
+      <c r="F14" s="61">
+        <v>0.5578717808219178</v>
+      </c>
+      <c r="G14" s="61">
+        <v>0.5578717808219178</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="56">
+      <c r="C15" s="62">
         <v>15388.88888888889</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D15" s="62">
         <v>18877.61111111111</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E15" s="62">
         <v>19390.358636363635</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F15" s="62">
         <v>19942.267750000003</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G15" s="62">
         <v>20540.535782500006</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C15" s="59">
+      <c r="H15" s="63" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C16" s="64">
         <v>0.644047833935018</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D16" s="61">
         <v>0.4326189754471052</v>
       </c>
-      <c r="E15" s="58">
+      <c r="E16" s="61">
         <v>0.3549390698831137</v>
       </c>
-      <c r="F15" s="58">
+      <c r="F16" s="61">
         <v>0.3128131506849315</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G16" s="61">
         <v>0.3128131506849315</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="C16" s="58">
+      <c r="H16" s="63" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="C17" s="61">
         <v>0.06579422382671479</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D17" s="61">
         <v>0.048560169748408606</v>
       </c>
-      <c r="E16" s="58">
+      <c r="E17" s="61">
         <v>0.04222830141755781</v>
       </c>
-      <c r="F16" s="58">
+      <c r="F17" s="61">
         <v>0.0387945205479452</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G17" s="61">
         <v>0.0387945205479452</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="C17" s="58">
+      <c r="H17" s="63" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C18" s="61">
         <v>0.13663808664259935</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D18" s="61">
         <v>0.40551379205819943</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E18" s="61">
         <v>0.5042999253916934</v>
       </c>
-      <c r="F17" s="58">
+      <c r="F18" s="61">
         <v>0.5578717808219178</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G18" s="61">
         <v>0.5578717808219178</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
+      <c r="H18" s="63" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="C19" s="65">
+        <v>1</v>
+      </c>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="63" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="C18" s="60" t="s">
+      <c r="C20" s="66" t="s">
         <v>306</v>
       </c>
-      <c r="D18" s="60" t="s">
+      <c r="D20" s="66" t="s">
         <v>306</v>
       </c>
-      <c r="E18" s="60" t="s">
+      <c r="E20" s="66" t="s">
         <v>306</v>
       </c>
-      <c r="F18" s="60" t="s">
+      <c r="F20" s="66" t="s">
         <v>306</v>
       </c>
-      <c r="G18" s="60" t="s">
+      <c r="G20" s="66" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="C19" s="61" t="s">
-        <v>349</v>
-      </c>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="C20" s="61" t="s">
-        <v>359</v>
-      </c>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="39" t="s">
-        <v>364</v>
-      </c>
-      <c r="C23" s="62" t="s">
-        <v>365</v>
-      </c>
-      <c r="D23" s="63" t="s">
-        <v>366</v>
-      </c>
-      <c r="E23" s="63"/>
-      <c r="F23" s="64" t="s">
+      <c r="H20" s="63" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="G23" s="64"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="39" t="s">
+      <c r="C21" s="67" t="s">
+        <v>352</v>
+      </c>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="63" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="C24" s="62" t="s">
-        <v>365</v>
-      </c>
-      <c r="D24" s="63" t="s">
+      <c r="C22" s="67" t="s">
         <v>369</v>
       </c>
-      <c r="E24" s="63"/>
-      <c r="F24" s="64" t="s">
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="63" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="G24" s="64"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C24" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="39" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25" s="62" t="s">
-        <v>365</v>
-      </c>
-      <c r="D25" s="63" t="s">
-        <v>372</v>
-      </c>
-      <c r="E25" s="63"/>
-      <c r="F25" s="64" t="s">
-        <v>373</v>
-      </c>
-      <c r="G25" s="64"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+      <c r="C25" s="68" t="s">
+        <v>375</v>
+      </c>
+      <c r="D25" s="69" t="s">
+        <v>376</v>
+      </c>
+      <c r="E25" s="69"/>
+      <c r="F25" s="70" t="s">
+        <v>377</v>
+      </c>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="C26" s="62" t="s">
-        <v>365</v>
-      </c>
-      <c r="D26" s="63" t="s">
+        <v>378</v>
+      </c>
+      <c r="C26" s="68" t="s">
         <v>375</v>
       </c>
-      <c r="E26" s="63"/>
-      <c r="F26" s="64" t="s">
-        <v>376</v>
-      </c>
-      <c r="G26" s="64"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D26" s="69" t="s">
+        <v>379</v>
+      </c>
+      <c r="E26" s="69"/>
+      <c r="F26" s="70" t="s">
+        <v>380</v>
+      </c>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="39" t="s">
-        <v>377</v>
-      </c>
-      <c r="C27" s="62" t="s">
-        <v>365</v>
-      </c>
-      <c r="D27" s="63" t="s">
-        <v>378</v>
-      </c>
-      <c r="E27" s="63"/>
-      <c r="F27" s="64" t="s">
-        <v>379</v>
-      </c>
-      <c r="G27" s="64"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>375</v>
+      </c>
+      <c r="D27" s="69" t="s">
+        <v>382</v>
+      </c>
+      <c r="E27" s="69"/>
+      <c r="F27" s="70" t="s">
+        <v>383</v>
+      </c>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>365</v>
-      </c>
-      <c r="D28" s="63" t="s">
-        <v>381</v>
-      </c>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64" t="s">
-        <v>382</v>
-      </c>
-      <c r="G28" s="64"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+      <c r="C28" s="68" t="s">
+        <v>375</v>
+      </c>
+      <c r="D28" s="69" t="s">
+        <v>385</v>
+      </c>
+      <c r="E28" s="69"/>
+      <c r="F28" s="70" t="s">
+        <v>386</v>
+      </c>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="C29" s="68" t="s">
+        <v>375</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>388</v>
+      </c>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70" t="s">
+        <v>389</v>
+      </c>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="39" t="s">
-        <v>383</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="65" t="s">
-        <v>385</v>
-      </c>
-      <c r="C32" s="65"/>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
+        <v>390</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>375</v>
+      </c>
+      <c r="D30" s="69" t="s">
+        <v>391</v>
+      </c>
+      <c r="E30" s="69"/>
+      <c r="F30" s="70" t="s">
+        <v>392</v>
+      </c>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="71" t="s">
+        <v>395</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="21">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="B34:H34"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="398">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -881,6 +881,12 @@
   </si>
   <si>
     <t>BOTTOM LINE</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>LOAN TERMS</t>
@@ -1328,6 +1334,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF328555"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1347,12 +1359,6 @@
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1464,7 +1470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1512,21 +1518,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1534,8 +1546,8 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1556,22 +1568,19 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4045,7 +4054,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4265,6 +4274,51 @@
       <c r="F15" s="29">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.55787178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B16" s="33">
+        <f>B14</f>
+        <v>25233</v>
+      </c>
+      <c r="C16" s="33">
+        <f>B16+C14</f>
+        <v>163025</v>
+      </c>
+      <c r="D16" s="33">
+        <f>C16+D14</f>
+        <v>378153</v>
+      </c>
+      <c r="E16" s="33">
+        <f>D16+E14</f>
+        <v>656284</v>
+      </c>
+      <c r="F16" s="33">
+        <f>E16+F14</f>
+        <v>942758</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4323,7 +4377,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4332,19 +4386,19 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
-        <v>284</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>286</v>
-      </c>
-      <c r="E5" s="40" t="s">
+      <c r="C5" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="E5" s="42" t="s">
         <v>215</v>
       </c>
     </row>
@@ -4374,7 +4428,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4404,7 +4458,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4414,32 +4468,32 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="B5" s="42">
+        <v>291</v>
+      </c>
+      <c r="B5" s="44">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>62170</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="44">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>199962</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="44">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>415091</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="44">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>693221</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="44">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>979696</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B6" s="30">
         <v>0</v>
@@ -4459,7 +4513,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B7" s="30">
         <v>5000</v>
@@ -4479,7 +4533,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B8" s="30">
         <v>0</v>
@@ -4499,7 +4553,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
@@ -4524,7 +4578,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4534,7 +4588,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B12" s="30">
         <v>0</v>
@@ -4554,7 +4608,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B13" s="30">
         <v>0</v>
@@ -4574,7 +4628,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B14" s="31" t="str">
         <f>SUM(B12:B13)</f>
@@ -4599,7 +4653,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4609,7 +4663,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B17" s="32">
         <f>B9-B14</f>
@@ -4634,25 +4688,25 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="B19" s="43" t="str">
+        <v>302</v>
+      </c>
+      <c r="B19" s="45" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="43" t="str">
+      <c r="C19" s="45" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="43" t="str">
+      <c r="D19" s="45" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="43" t="str">
+      <c r="E19" s="45" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="43" t="str">
+      <c r="F19" s="45" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -4683,7 +4737,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4713,7 +4767,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4723,7 +4777,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B5" s="30">
         <v>184667</v>
@@ -4783,7 +4837,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B8" s="33">
         <f>B5-B6-B7</f>
@@ -4828,27 +4882,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>306</v>
+        <v>307</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -4858,7 +4912,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B13" s="30">
         <v>62170</v>
@@ -4878,32 +4932,32 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="B14" s="45">
+        <v>311</v>
+      </c>
+      <c r="B14" s="47">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>142</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="47">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>361</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="47">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>716</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="47">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>1148</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="47">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>1575</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B15" s="34">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -4948,7 +5002,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -4978,7 +5032,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B20" s="30">
         <v>118934</v>
@@ -4998,7 +5052,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B21" s="30">
         <v>3375</v>
@@ -5018,27 +5072,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="B22" s="46">
+        <v>316</v>
+      </c>
+      <c r="B22" s="48">
         <v>10</v>
       </c>
-      <c r="C22" s="46">
+      <c r="C22" s="48">
         <v>10</v>
       </c>
-      <c r="D22" s="46">
+      <c r="D22" s="48">
         <v>10</v>
       </c>
-      <c r="E22" s="46">
+      <c r="E22" s="48">
         <v>9</v>
       </c>
-      <c r="F22" s="46">
+      <c r="F22" s="48">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -5048,102 +5102,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="B25" s="47" t="s">
-        <v>306</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>306</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>306</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>306</v>
-      </c>
-      <c r="F25" s="47" t="s">
-        <v>306</v>
+        <v>318</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>308</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>308</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>308</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>308</v>
+      </c>
+      <c r="F25" s="49" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B26" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="D26" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>318</v>
+        <v>319</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="F26" s="50" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B27" s="49" t="s">
+        <v>321</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="C27" s="50" t="s">
         <v>320</v>
       </c>
-      <c r="C27" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="D27" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="E27" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="F27" s="48" t="s">
-        <v>318</v>
+      <c r="D27" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="B28" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="C28" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="D28" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="E28" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="F28" s="48" t="s">
-        <v>318</v>
+        <v>323</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="D28" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="F28" s="50" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="B29" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="D29" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="E29" s="48" t="s">
-        <v>318</v>
-      </c>
-      <c r="F29" s="48" t="s">
-        <v>318</v>
+        <v>324</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -5183,28 +5237,28 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="B3" s="50" t="s">
+      <c r="A3" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="B3" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="50" t="s">
-        <v>324</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="52" t="s">
+        <v>326</v>
+      </c>
+      <c r="E3" s="52" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B4" s="30">
         <v>20000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E4" s="30">
         <v>15000</v>
@@ -5212,7 +5266,7 @@
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E5" s="30">
         <v>5000</v>
@@ -5220,13 +5274,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B7" s="32">
         <v>20000</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E7" s="32">
         <v>20000</v>
@@ -5234,9 +5288,9 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="B8" s="43">
+        <v>332</v>
+      </c>
+      <c r="B8" s="45">
         <v>0</v>
       </c>
     </row>
@@ -5582,7 +5636,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5592,7 +5646,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -5602,7 +5656,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5627,7 +5681,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B6" s="30">
         <v>184667</v>
@@ -5707,47 +5761,47 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="B10" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>306</v>
+        <v>307</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B11" s="45">
+        <v>316</v>
+      </c>
+      <c r="B11" s="47">
         <v>10</v>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="47">
         <v>10</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="47">
         <v>10</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="47">
         <v>9</v>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="47">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -5757,7 +5811,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5782,7 +5836,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B16" s="30">
         <v>147733</v>
@@ -5862,41 +5916,41 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="B20" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>306</v>
+        <v>307</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B21" s="45">
+        <v>316</v>
+      </c>
+      <c r="B21" s="47">
         <v>12</v>
       </c>
-      <c r="C21" s="45">
+      <c r="C21" s="47">
         <v>10</v>
       </c>
-      <c r="D21" s="45">
+      <c r="D21" s="47">
         <v>10</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="47">
         <v>10</v>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="47">
         <v>10</v>
       </c>
     </row>
@@ -5928,7 +5982,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5962,7 +6016,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -5986,7 +6040,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -5994,7 +6048,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6014,25 +6068,25 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="54" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D13" s="30">
         <v>184667</v>
@@ -6092,7 +6146,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D16" s="30">
         <v>62170</v>
@@ -6112,7 +6166,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D17" s="30">
         <v>0</v>
@@ -6132,7 +6186,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -6152,25 +6206,25 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D20" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="52" t="s">
+      <c r="F20" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="52" t="s">
+      <c r="G20" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="54" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D21" s="29">
         <v>0.13663808664259927</v>
@@ -6190,22 +6244,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="D22" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="E22" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="F22" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="G22" s="51" t="s">
-        <v>306</v>
-      </c>
-      <c r="H22" s="51" t="s">
-        <v>306</v>
+        <v>307</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="G22" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="H22" s="53" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6230,27 +6284,27 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="D24" s="45">
+        <v>346</v>
+      </c>
+      <c r="D24" s="47">
         <v>12</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E24" s="47">
         <v>18</v>
       </c>
-      <c r="F24" s="45">
+      <c r="F24" s="47">
         <v>22</v>
       </c>
-      <c r="G24" s="45">
+      <c r="G24" s="47">
         <v>25</v>
       </c>
-      <c r="H24" s="45">
+      <c r="H24" s="47">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -6291,7 +6345,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6301,87 +6355,87 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
+      <c r="B3" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="54" t="s">
-        <v>348</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>349</v>
-      </c>
-      <c r="F4" s="56" t="s">
+      <c r="B4" s="56" t="s">
         <v>350</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>351</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>352</v>
-      </c>
-      <c r="D6" s="57" t="s">
         <v>353</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="C6" s="59" t="s">
         <v>354</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="D6" s="59" t="s">
         <v>355</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="E6" s="59" t="s">
         <v>356</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="F6" s="59" t="s">
         <v>357</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="C7" s="58">
+        <v>346</v>
+      </c>
+      <c r="C7" s="60">
         <v>12</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="60">
         <v>18</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="60">
         <v>22</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="60">
         <v>25</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="60">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="C8" s="59">
+        <v>305</v>
+      </c>
+      <c r="C8" s="61">
         <v>184666.6666666667</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="61">
         <v>339797</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="61">
         <v>426587.88999999996</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="61">
         <v>498556.69375000003</v>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="61">
         <v>513513.3945625001</v>
       </c>
     </row>
@@ -6389,19 +6443,19 @@
       <c r="B9" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="61">
         <v>118934.16666666667</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="61">
         <v>147002.63</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="61">
         <v>151412.7089</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="61">
         <v>155955.090167</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="61">
         <v>160633.74287201</v>
       </c>
     </row>
@@ -6409,19 +6463,19 @@
       <c r="B10" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="61">
         <v>40500</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="61">
         <v>55002</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="61">
         <v>60046.93999999999</v>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="61">
         <v>64470.893</v>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="61">
         <v>66405.01979</v>
       </c>
     </row>
@@ -6429,19 +6483,19 @@
       <c r="B11" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="C11" s="59">
-        <v>0</v>
-      </c>
-      <c r="D11" s="59">
-        <v>0</v>
-      </c>
-      <c r="E11" s="59">
-        <v>0</v>
-      </c>
-      <c r="F11" s="59">
-        <v>0</v>
-      </c>
-      <c r="G11" s="59">
+      <c r="C11" s="61">
+        <v>0</v>
+      </c>
+      <c r="D11" s="61">
+        <v>0</v>
+      </c>
+      <c r="E11" s="61">
+        <v>0</v>
+      </c>
+      <c r="F11" s="61">
+        <v>0</v>
+      </c>
+      <c r="G11" s="61">
         <v>0</v>
       </c>
     </row>
@@ -6449,59 +6503,59 @@
       <c r="B12" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="C12" s="60">
+      <c r="C12" s="62">
         <v>25232.5</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="62">
         <v>137792.37</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E12" s="62">
         <v>215128.24109999998</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F12" s="62">
         <v>278130.71058300004</v>
       </c>
-      <c r="G12" s="60">
+      <c r="G12" s="62">
         <v>286474.6319004901</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="C13" s="60">
+        <v>310</v>
+      </c>
+      <c r="C13" s="62">
         <v>62170</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="62">
         <v>199962.37</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="62">
         <v>415090.6111</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F13" s="62">
         <v>693221.3216830001</v>
       </c>
-      <c r="G13" s="60">
+      <c r="G13" s="62">
         <v>979695.9535834901</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="C14" s="61">
+        <v>345</v>
+      </c>
+      <c r="C14" s="63">
         <v>0.13663808664259927</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="63">
         <v>0.40551379205819943</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="63">
         <v>0.5042999253916937</v>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="63">
         <v>0.5578717808219178</v>
       </c>
-      <c r="G14" s="61">
+      <c r="G14" s="63">
         <v>0.5578717808219178</v>
       </c>
     </row>
@@ -6509,302 +6563,302 @@
       <c r="B15" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C15" s="62">
+      <c r="C15" s="64">
         <v>15388.88888888889</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="64">
         <v>18877.61111111111</v>
       </c>
-      <c r="E15" s="62">
+      <c r="E15" s="64">
         <v>19390.358636363635</v>
       </c>
-      <c r="F15" s="62">
+      <c r="F15" s="64">
         <v>19942.267750000003</v>
       </c>
-      <c r="G15" s="62">
+      <c r="G15" s="64">
         <v>20540.535782500006</v>
       </c>
-      <c r="H15" s="63" t="s">
-        <v>358</v>
+      <c r="H15" s="65" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="C16" s="64">
+        <v>361</v>
+      </c>
+      <c r="C16" s="66">
         <v>0.644047833935018</v>
       </c>
-      <c r="D16" s="61">
+      <c r="D16" s="63">
         <v>0.4326189754471052</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="63">
         <v>0.3549390698831137</v>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="63">
         <v>0.3128131506849315</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G16" s="63">
         <v>0.3128131506849315</v>
       </c>
-      <c r="H16" s="63" t="s">
-        <v>360</v>
+      <c r="H16" s="65" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="C17" s="61">
+        <v>363</v>
+      </c>
+      <c r="C17" s="63">
         <v>0.06579422382671479</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="63">
         <v>0.048560169748408606</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="63">
         <v>0.04222830141755781</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="63">
         <v>0.0387945205479452</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="63">
         <v>0.0387945205479452</v>
       </c>
-      <c r="H17" s="63" t="s">
-        <v>362</v>
+      <c r="H17" s="65" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C18" s="61">
+        <v>365</v>
+      </c>
+      <c r="C18" s="63">
         <v>0.13663808664259935</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D18" s="63">
         <v>0.40551379205819943</v>
       </c>
-      <c r="E18" s="61">
+      <c r="E18" s="63">
         <v>0.5042999253916934</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="63">
         <v>0.5578717808219178</v>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="63">
         <v>0.5578717808219178</v>
       </c>
-      <c r="H18" s="63" t="s">
-        <v>364</v>
+      <c r="H18" s="65" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="C19" s="65">
-        <v>1</v>
-      </c>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="63" t="s">
-        <v>366</v>
+        <v>367</v>
+      </c>
+      <c r="C19" s="67">
+        <v>3</v>
+      </c>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="65" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="C20" s="66" t="s">
-        <v>306</v>
-      </c>
-      <c r="D20" s="66" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="66" t="s">
-        <v>306</v>
-      </c>
-      <c r="F20" s="66" t="s">
-        <v>306</v>
-      </c>
-      <c r="G20" s="66" t="s">
-        <v>306</v>
-      </c>
-      <c r="H20" s="63" t="s">
-        <v>306</v>
+        <v>307</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="E20" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="G20" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="H20" s="65" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="C21" s="67" t="s">
-        <v>352</v>
-      </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="63" t="s">
-        <v>352</v>
+        <v>369</v>
+      </c>
+      <c r="C21" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="65" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="C22" s="67" t="s">
-        <v>369</v>
-      </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="63" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="C22" s="69" t="s">
+        <v>371</v>
+      </c>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="65" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="C25" s="68" t="s">
-        <v>375</v>
-      </c>
-      <c r="D25" s="69" t="s">
+      <c r="B25" s="41" t="s">
         <v>376</v>
       </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="70" t="s">
+      <c r="C25" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
+      <c r="D25" s="70" t="s">
+        <v>378</v>
+      </c>
+      <c r="E25" s="70"/>
+      <c r="F25" s="71" t="s">
+        <v>379</v>
+      </c>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="C26" s="68" t="s">
-        <v>375</v>
-      </c>
-      <c r="D26" s="69" t="s">
-        <v>379</v>
-      </c>
-      <c r="E26" s="69"/>
-      <c r="F26" s="70" t="s">
+      <c r="B26" s="41" t="s">
         <v>380</v>
       </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
+      <c r="C26" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="D26" s="70" t="s">
+        <v>381</v>
+      </c>
+      <c r="E26" s="70"/>
+      <c r="F26" s="71" t="s">
+        <v>382</v>
+      </c>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="C27" s="68" t="s">
-        <v>375</v>
-      </c>
-      <c r="D27" s="69" t="s">
-        <v>382</v>
-      </c>
-      <c r="E27" s="69"/>
-      <c r="F27" s="70" t="s">
+      <c r="B27" s="41" t="s">
         <v>383</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
+      <c r="C27" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="D27" s="70" t="s">
+        <v>384</v>
+      </c>
+      <c r="E27" s="70"/>
+      <c r="F27" s="71" t="s">
+        <v>385</v>
+      </c>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="39" t="s">
-        <v>384</v>
-      </c>
-      <c r="C28" s="68" t="s">
-        <v>375</v>
-      </c>
-      <c r="D28" s="69" t="s">
-        <v>385</v>
-      </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="70" t="s">
+      <c r="B28" s="41" t="s">
         <v>386</v>
       </c>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
+      <c r="C28" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="D28" s="70" t="s">
+        <v>387</v>
+      </c>
+      <c r="E28" s="70"/>
+      <c r="F28" s="71" t="s">
+        <v>388</v>
+      </c>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="39" t="s">
-        <v>387</v>
-      </c>
-      <c r="C29" s="68" t="s">
-        <v>375</v>
-      </c>
-      <c r="D29" s="69" t="s">
-        <v>388</v>
-      </c>
-      <c r="E29" s="69"/>
-      <c r="F29" s="70" t="s">
+      <c r="B29" s="41" t="s">
         <v>389</v>
       </c>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
+      <c r="C29" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="D29" s="70" t="s">
+        <v>390</v>
+      </c>
+      <c r="E29" s="70"/>
+      <c r="F29" s="71" t="s">
+        <v>391</v>
+      </c>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="39" t="s">
-        <v>390</v>
-      </c>
-      <c r="C30" s="68" t="s">
-        <v>375</v>
-      </c>
-      <c r="D30" s="69" t="s">
-        <v>391</v>
-      </c>
-      <c r="E30" s="69"/>
-      <c r="F30" s="70" t="s">
+      <c r="B30" s="41" t="s">
         <v>392</v>
       </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
+      <c r="C30" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>393</v>
+      </c>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71" t="s">
+        <v>394</v>
+      </c>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="39" t="s">
-        <v>393</v>
+      <c r="B32" s="41" t="s">
+        <v>395</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="71" t="s">
-        <v>395</v>
-      </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="B34" s="72" t="s">
+        <v>397</v>
+      </c>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="21">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="398">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1470,7 +1470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1575,6 +1575,9 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6693,13 +6696,26 @@
       <c r="B21" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="C21" s="69" t="s">
-        <v>354</v>
-      </c>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
+      <c r="C21" s="39" t="str">
+        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="69" t="str">
+        <f>IF('5-Year Operating Stmt'!C16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="69" t="str">
+        <f>IF('5-Year Operating Stmt'!D16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="69" t="str">
+        <f>IF('5-Year Operating Stmt'!E16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="69" t="str">
+        <f>IF('5-Year Operating Stmt'!F16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="65" t="s">
         <v>354</v>
       </c>
@@ -6708,13 +6724,13 @@
       <c r="B22" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="70" t="s">
         <v>371</v>
       </c>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
       <c r="H22" s="65" t="s">
         <v>371</v>
       </c>
@@ -6743,15 +6759,15 @@
       <c r="C25" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="71" t="s">
         <v>378</v>
       </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71" t="s">
+      <c r="E25" s="71"/>
+      <c r="F25" s="72" t="s">
         <v>379</v>
       </c>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="41" t="s">
@@ -6760,15 +6776,15 @@
       <c r="C26" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D26" s="70" t="s">
+      <c r="D26" s="71" t="s">
         <v>381</v>
       </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71" t="s">
+      <c r="E26" s="71"/>
+      <c r="F26" s="72" t="s">
         <v>382</v>
       </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="41" t="s">
@@ -6777,15 +6793,15 @@
       <c r="C27" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D27" s="70" t="s">
+      <c r="D27" s="71" t="s">
         <v>384</v>
       </c>
-      <c r="E27" s="70"/>
-      <c r="F27" s="71" t="s">
+      <c r="E27" s="71"/>
+      <c r="F27" s="72" t="s">
         <v>385</v>
       </c>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="41" t="s">
@@ -6794,15 +6810,15 @@
       <c r="C28" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D28" s="70" t="s">
+      <c r="D28" s="71" t="s">
         <v>387</v>
       </c>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71" t="s">
+      <c r="E28" s="71"/>
+      <c r="F28" s="72" t="s">
         <v>388</v>
       </c>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="41" t="s">
@@ -6811,15 +6827,15 @@
       <c r="C29" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D29" s="70" t="s">
+      <c r="D29" s="71" t="s">
         <v>390</v>
       </c>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71" t="s">
+      <c r="E29" s="71"/>
+      <c r="F29" s="72" t="s">
         <v>391</v>
       </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="41" t="s">
@@ -6828,15 +6844,15 @@
       <c r="C30" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D30" s="70" t="s">
+      <c r="D30" s="71" t="s">
         <v>393</v>
       </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71" t="s">
+      <c r="E30" s="71"/>
+      <c r="F30" s="72" t="s">
         <v>394</v>
       </c>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="41" t="s">
@@ -6850,22 +6866,21 @@
       <c r="F32" s="10"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="72" t="s">
+      <c r="B34" s="73" t="s">
         <v>397</v>
       </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="73"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -6944,10 +6959,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="398">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1144,10 +1144,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1381,7 +1381,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1416,6 +1416,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1470,7 +1475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1572,14 +1577,21 @@
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -6661,10 +6673,18 @@
       <c r="C19" s="67">
         <v>3</v>
       </c>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
+      <c r="D19" s="67">
+        <v>3</v>
+      </c>
+      <c r="E19" s="67">
+        <v>3</v>
+      </c>
+      <c r="F19" s="67">
+        <v>3</v>
+      </c>
+      <c r="G19" s="67">
+        <v>3</v>
+      </c>
       <c r="H19" s="65" t="s">
         <v>368</v>
       </c>
@@ -6701,19 +6721,19 @@
         <v>✓ Break-even</v>
       </c>
       <c r="D21" s="69" t="str">
-        <f>IF('5-Year Operating Stmt'!C16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="69" t="str">
-        <f>IF('5-Year Operating Stmt'!D16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="69" t="str">
-        <f>IF('5-Year Operating Stmt'!E16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="69" t="str">
-        <f>IF('5-Year Operating Stmt'!F16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="65" t="s">
@@ -6724,13 +6744,21 @@
       <c r="B22" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="C22" s="70" t="s">
-        <v>371</v>
-      </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
+      <c r="C22" s="70">
+        <v>5</v>
+      </c>
+      <c r="D22" s="71">
+        <v>12</v>
+      </c>
+      <c r="E22" s="67">
+        <v>24</v>
+      </c>
+      <c r="F22" s="67">
+        <v>38</v>
+      </c>
+      <c r="G22" s="67">
+        <v>52</v>
+      </c>
       <c r="H22" s="65" t="s">
         <v>371</v>
       </c>
@@ -6759,15 +6787,15 @@
       <c r="C25" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="D25" s="72" t="s">
         <v>378</v>
       </c>
-      <c r="E25" s="71"/>
-      <c r="F25" s="72" t="s">
+      <c r="E25" s="72"/>
+      <c r="F25" s="73" t="s">
         <v>379</v>
       </c>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="41" t="s">
@@ -6776,15 +6804,15 @@
       <c r="C26" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="72" t="s">
         <v>381</v>
       </c>
-      <c r="E26" s="71"/>
-      <c r="F26" s="72" t="s">
+      <c r="E26" s="72"/>
+      <c r="F26" s="73" t="s">
         <v>382</v>
       </c>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="41" t="s">
@@ -6793,15 +6821,15 @@
       <c r="C27" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D27" s="71" t="s">
+      <c r="D27" s="72" t="s">
         <v>384</v>
       </c>
-      <c r="E27" s="71"/>
-      <c r="F27" s="72" t="s">
+      <c r="E27" s="72"/>
+      <c r="F27" s="73" t="s">
         <v>385</v>
       </c>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="41" t="s">
@@ -6810,15 +6838,15 @@
       <c r="C28" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="72" t="s">
         <v>387</v>
       </c>
-      <c r="E28" s="71"/>
-      <c r="F28" s="72" t="s">
+      <c r="E28" s="72"/>
+      <c r="F28" s="73" t="s">
         <v>388</v>
       </c>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="41" t="s">
@@ -6827,15 +6855,15 @@
       <c r="C29" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="72" t="s">
         <v>390</v>
       </c>
-      <c r="E29" s="71"/>
-      <c r="F29" s="72" t="s">
+      <c r="E29" s="72"/>
+      <c r="F29" s="73" t="s">
         <v>391</v>
       </c>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="41" t="s">
@@ -6844,15 +6872,15 @@
       <c r="C30" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="D30" s="71" t="s">
+      <c r="D30" s="72" t="s">
         <v>393</v>
       </c>
-      <c r="E30" s="71"/>
-      <c r="F30" s="72" t="s">
+      <c r="E30" s="72"/>
+      <c r="F30" s="73" t="s">
         <v>394</v>
       </c>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="41" t="s">
@@ -6866,22 +6894,20 @@
       <c r="F32" s="10"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="73" t="s">
+      <c r="B34" s="74" t="s">
         <v>397</v>
       </c>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="73"/>
-      <c r="H34" s="73"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -1195,7 +1195,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 8% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -6624,20 +6624,20 @@
       <c r="B17" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="C17" s="63">
-        <v>0.06579422382671479</v>
+      <c r="C17" s="66">
+        <v>0.19494584837545123</v>
       </c>
       <c r="D17" s="63">
-        <v>0.048560169748408606</v>
+        <v>0.10912397696271597</v>
       </c>
       <c r="E17" s="63">
-        <v>0.04222830141755781</v>
+        <v>0.0895299676697339</v>
       </c>
       <c r="F17" s="63">
-        <v>0.0387945205479452</v>
+        <v>0.0789041095890411</v>
       </c>
       <c r="G17" s="63">
-        <v>0.0387945205479452</v>
+        <v>0.0789041095890411</v>
       </c>
       <c r="H17" s="65" t="s">
         <v>364</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -40,7 +40,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · llc_single</t>
+    <t>Generated March 27, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -160,7 +160,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1081,7 +1081,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="401">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -703,49 +703,58 @@
     <t>Staffing Costs Forecast</t>
   </si>
   <si>
+    <t xml:space="preserve">  Lead Teacher [1 FTE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Teaching Assistant [0.5 FTE]</t>
+  </si>
+  <si>
+    <t>Total Instructional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder / Head of School [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total School Leadership</t>
+  </si>
+  <si>
+    <t>TOTAL PERSONNEL</t>
+  </si>
+  <si>
+    <t>Bright Horizons Microschool - Budget Detail</t>
+  </si>
+  <si>
+    <t>REVENUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Tuition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Registration Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AZ ESA Funds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Annual Fundraising</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Scholarship Discount</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>PERSONNEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder / Head of School</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Lead Teacher</t>
   </si>
   <si>
     <t xml:space="preserve">  Teaching Assistant</t>
-  </si>
-  <si>
-    <t>Total Instructional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Founder / Head of School</t>
-  </si>
-  <si>
-    <t>Total School Leadership</t>
-  </si>
-  <si>
-    <t>TOTAL PERSONNEL</t>
-  </si>
-  <si>
-    <t>Bright Horizons Microschool - Budget Detail</t>
-  </si>
-  <si>
-    <t>REVENUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Tuition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Registration Fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  AZ ESA Funds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Annual Fundraising</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Scholarship Discount</t>
-  </si>
-  <si>
-    <t>Total Revenue</t>
-  </si>
-  <si>
-    <t>PERSONNEL</t>
   </si>
   <si>
     <t xml:space="preserve">    Curriculum &amp; Materials</t>
@@ -2910,7 +2919,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B13" s="30">
         <v>58506</v>
@@ -2930,7 +2939,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="B14" s="30">
         <v>47869</v>
@@ -2950,7 +2959,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B15" s="30">
         <v>12559</v>
@@ -3010,7 +3019,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B20" s="30">
         <v>5000</v>
@@ -3035,7 +3044,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B22" s="30">
         <v>3000</v>
@@ -3060,7 +3069,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B24" s="30">
         <v>25000</v>
@@ -3080,7 +3089,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B25" s="30">
         <v>3000</v>
@@ -3100,7 +3109,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B26" s="30">
         <v>2000</v>
@@ -3120,7 +3129,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B27" s="31">
         <f>SUM(B24:B26)</f>
@@ -3150,7 +3159,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B29" s="30">
         <v>2500</v>
@@ -3170,7 +3179,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B30" s="31">
         <f>B20+B22+B27+B29</f>
@@ -3195,7 +3204,7 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
@@ -3205,7 +3214,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B33" s="31" t="str">
         <f>SUM(B33:B32)</f>
@@ -3254,7 +3263,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3334,7 +3343,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B6" s="33">
         <f>'Budget Detail'!B30</f>
@@ -3359,7 +3368,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B7" s="33" t="str">
         <f>'Budget Detail'!B33</f>
@@ -3384,7 +3393,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -3409,7 +3418,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3419,7 +3428,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B11" s="32">
         <f>B4-B8</f>
@@ -3444,7 +3453,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3469,7 +3478,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B13" s="30">
         <v>25233</v>
@@ -3509,7 +3518,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B15" s="30">
         <v>13286</v>
@@ -3554,7 +3563,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3575,43 +3584,43 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3679,7 +3688,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -3697,7 +3706,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B7" s="30">
         <v>11893</v>
@@ -3742,7 +3751,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B8" s="30">
         <v>4050</v>
@@ -3787,7 +3796,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B9" s="30">
         <v>0</v>
@@ -3832,7 +3841,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -3850,7 +3859,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B12" s="33">
         <f>B7+B8+B9</f>
@@ -3907,7 +3916,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B13" s="33">
         <f>B4-B12</f>
@@ -3964,7 +3973,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B14" s="37">
         <f>B17+B13</f>
@@ -4021,7 +4030,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4036,7 +4045,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B18" s="37">
         <f>M14</f>
@@ -4045,7 +4054,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B19" s="30">
         <f>MIN(B14:M14)</f>
@@ -4078,7 +4087,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4138,7 +4147,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4148,7 +4157,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B8" s="33">
         <v>118934</v>
@@ -4168,7 +4177,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B9" s="33">
         <v>40500</v>
@@ -4188,7 +4197,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B10" s="33">
         <v>0</v>
@@ -4208,7 +4217,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
@@ -4233,7 +4242,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -4243,7 +4252,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="38" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B14" s="32">
         <f>B5-B11</f>
@@ -4268,7 +4277,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B15" s="29">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4293,7 +4302,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B16" s="33">
         <f>B14</f>
@@ -4318,10 +4327,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C17" s="40" t="s">
         <v>7</v>
@@ -4392,7 +4401,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4402,16 +4411,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B5" s="42" t="s">
         <v>153</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E5" s="42" t="s">
         <v>215</v>
@@ -4443,7 +4452,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4473,7 +4482,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4483,7 +4492,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B5" s="44">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -4508,7 +4517,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B6" s="30">
         <v>0</v>
@@ -4528,7 +4537,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B7" s="30">
         <v>5000</v>
@@ -4548,7 +4557,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B8" s="30">
         <v>0</v>
@@ -4568,7 +4577,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
@@ -4593,7 +4602,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4603,7 +4612,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B12" s="30">
         <v>0</v>
@@ -4623,7 +4632,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B13" s="30">
         <v>0</v>
@@ -4643,7 +4652,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B14" s="31" t="str">
         <f>SUM(B12:B13)</f>
@@ -4668,7 +4677,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4678,7 +4687,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B17" s="32">
         <f>B9-B14</f>
@@ -4703,7 +4712,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B19" s="45" t="str">
         <f>B9-B14-B17</f>
@@ -4752,7 +4761,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4782,7 +4791,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4792,7 +4801,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B5" s="30">
         <v>184667</v>
@@ -4812,7 +4821,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B6" s="30">
         <v>118934</v>
@@ -4832,7 +4841,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B7" s="30">
         <v>40500</v>
@@ -4852,7 +4861,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B8" s="33">
         <f>B5-B6-B7</f>
@@ -4877,7 +4886,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B9" s="30">
         <v>0</v>
@@ -4897,27 +4906,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -4927,7 +4936,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B13" s="30">
         <v>62170</v>
@@ -4947,7 +4956,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B14" s="47">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -4972,7 +4981,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B15" s="34">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5017,7 +5026,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -5047,7 +5056,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B20" s="30">
         <v>118934</v>
@@ -5067,7 +5076,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B21" s="30">
         <v>3375</v>
@@ -5087,7 +5096,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B22" s="48">
         <v>10</v>
@@ -5107,7 +5116,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -5117,102 +5126,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E25" s="49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F25" s="49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="B28" s="50" t="s">
         <v>323</v>
       </c>
-      <c r="B28" s="50" t="s">
-        <v>320</v>
-      </c>
       <c r="C28" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -5253,13 +5262,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B3" s="52" t="s">
         <v>112</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E3" s="52" t="s">
         <v>112</v>
@@ -5267,13 +5276,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B4" s="30">
         <v>20000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E4" s="30">
         <v>15000</v>
@@ -5281,7 +5290,7 @@
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E5" s="30">
         <v>5000</v>
@@ -5289,13 +5298,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B7" s="32">
         <v>20000</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E7" s="32">
         <v>20000</v>
@@ -5303,7 +5312,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B8" s="45">
         <v>0</v>
@@ -5651,7 +5660,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5661,7 +5670,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -5671,7 +5680,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5696,7 +5705,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B6" s="30">
         <v>184667</v>
@@ -5716,7 +5725,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B7" s="30">
         <v>159434</v>
@@ -5736,7 +5745,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B8" s="32">
         <v>25233</v>
@@ -5756,7 +5765,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B9" s="29">
         <v>0.13663808664259927</v>
@@ -5776,27 +5785,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B11" s="47">
         <v>10</v>
@@ -5816,7 +5825,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -5826,7 +5835,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5851,7 +5860,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B16" s="30">
         <v>147733</v>
@@ -5871,7 +5880,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B17" s="30">
         <v>159434</v>
@@ -5891,7 +5900,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B18" s="32">
         <v>-11701</v>
@@ -5911,7 +5920,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B19" s="29">
         <v>-0.07920239169675096</v>
@@ -5931,27 +5940,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B21" s="47">
         <v>12</v>
@@ -5997,7 +6006,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6031,7 +6040,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6055,7 +6064,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6063,7 +6072,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6101,7 +6110,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D13" s="30">
         <v>184667</v>
@@ -6121,7 +6130,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D14" s="30">
         <v>159434</v>
@@ -6141,7 +6150,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D15" s="30">
         <v>25233</v>
@@ -6161,7 +6170,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D16" s="30">
         <v>62170</v>
@@ -6181,7 +6190,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D17" s="30">
         <v>0</v>
@@ -6201,7 +6210,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -6239,7 +6248,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D21" s="29">
         <v>0.13663808664259927</v>
@@ -6259,22 +6268,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G22" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H22" s="53" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6299,7 +6308,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D24" s="47">
         <v>12</v>
@@ -6319,7 +6328,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -6360,7 +6369,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6371,7 +6380,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="55" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="55"/>
@@ -6382,41 +6391,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="56" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C7" s="60">
         <v>12</v>
@@ -6436,7 +6445,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C8" s="61">
         <v>184666.6666666667</v>
@@ -6456,7 +6465,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C9" s="61">
         <v>118934.16666666667</v>
@@ -6476,7 +6485,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C10" s="61">
         <v>40500</v>
@@ -6496,7 +6505,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C11" s="61">
         <v>0</v>
@@ -6516,7 +6525,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C12" s="62">
         <v>25232.5</v>
@@ -6536,7 +6545,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C13" s="62">
         <v>62170</v>
@@ -6556,7 +6565,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C14" s="63">
         <v>0.13663808664259927</v>
@@ -6594,12 +6603,12 @@
         <v>20540.535782500006</v>
       </c>
       <c r="H15" s="65" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C16" s="66">
         <v>0.644047833935018</v>
@@ -6617,12 +6626,12 @@
         <v>0.3128131506849315</v>
       </c>
       <c r="H16" s="65" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C17" s="66">
         <v>0.19494584837545123</v>
@@ -6640,12 +6649,12 @@
         <v>0.0789041095890411</v>
       </c>
       <c r="H17" s="65" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C18" s="63">
         <v>0.13663808664259935</v>
@@ -6663,12 +6672,12 @@
         <v>0.5578717808219178</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C19" s="67">
         <v>3</v>
@@ -6686,35 +6695,35 @@
         <v>3</v>
       </c>
       <c r="H19" s="65" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D20" s="68" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F20" s="68" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G20" s="68" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C21" s="39" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
@@ -6737,12 +6746,12 @@
         <v>0</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C22" s="70">
         <v>5</v>
@@ -6760,134 +6769,134 @@
         <v>52</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="41" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D25" s="72" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E25" s="72"/>
       <c r="F25" s="73" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G25" s="73"/>
       <c r="H25" s="73"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="C26" s="39" t="s">
         <v>380</v>
       </c>
-      <c r="C26" s="39" t="s">
-        <v>377</v>
-      </c>
       <c r="D26" s="72" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E26" s="72"/>
       <c r="F26" s="73" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="G26" s="73"/>
       <c r="H26" s="73"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="41" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D27" s="72" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E27" s="72"/>
       <c r="F27" s="73" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G27" s="73"/>
       <c r="H27" s="73"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="41" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D28" s="72" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E28" s="72"/>
       <c r="F28" s="73" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G28" s="73"/>
       <c r="H28" s="73"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="41" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E29" s="72"/>
       <c r="F29" s="73" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G29" s="73"/>
       <c r="H29" s="73"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="41" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D30" s="72" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E30" s="72"/>
       <c r="F30" s="73" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G30" s="73"/>
       <c r="H30" s="73"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="41" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
@@ -6895,7 +6904,7 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="74" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C34" s="74"/>
       <c r="D34" s="74"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="402">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1157,6 +1157,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -6357,7 +6360,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6772,153 +6775,174 @@
         <v>374</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C23" s="67">
+        <v>142</v>
+      </c>
+      <c r="D23" s="67">
+        <v>361</v>
+      </c>
+      <c r="E23" s="67">
+        <v>716</v>
+      </c>
+      <c r="F23" s="67">
+        <v>1148</v>
+      </c>
+      <c r="G23" s="67">
+        <v>1575</v>
+      </c>
+      <c r="H23" s="65" t="s">
         <v>375</v>
       </c>
-      <c r="C24" s="19" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
         <v>376</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="C25" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="D25" s="19" t="s">
         <v>378</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="41" t="s">
+      <c r="E25" s="19"/>
+      <c r="F25" s="19" t="s">
         <v>379</v>
       </c>
-      <c r="C25" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="D25" s="72" t="s">
-        <v>381</v>
-      </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73" t="s">
-        <v>382</v>
-      </c>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="41" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D26" s="72" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E26" s="72"/>
       <c r="F26" s="73" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G26" s="73"/>
       <c r="H26" s="73"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="41" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D27" s="72" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E27" s="72"/>
       <c r="F27" s="73" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G27" s="73"/>
       <c r="H27" s="73"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="41" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D28" s="72" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E28" s="72"/>
       <c r="F28" s="73" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G28" s="73"/>
       <c r="H28" s="73"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="41" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E29" s="72"/>
       <c r="F29" s="73" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G29" s="73"/>
       <c r="H29" s="73"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="41" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D30" s="72" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E30" s="72"/>
       <c r="F30" s="73" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G30" s="73"/>
       <c r="H30" s="73"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="41" t="s">
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="41" t="s">
+        <v>396</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>381</v>
+      </c>
+      <c r="D31" s="72" t="s">
+        <v>397</v>
+      </c>
+      <c r="E31" s="72"/>
+      <c r="F31" s="73" t="s">
         <v>398</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="41" t="s">
         <v>399</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="74" t="s">
+      <c r="C33" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="74"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="74" t="s">
+        <v>401</v>
+      </c>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -6931,8 +6955,10 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="406">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1124,6 +1124,18 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1487,7 +1499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1586,6 +1598,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6360,7 +6381,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6609,356 +6630,439 @@
         <v>363</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="66">
+        <v>13286.180555555557</v>
+      </c>
+      <c r="D16" s="66">
+        <v>11222.479444444445</v>
+      </c>
+      <c r="E16" s="66">
+        <v>9611.802222727272</v>
+      </c>
+      <c r="F16" s="66">
+        <v>8817.03932668</v>
+      </c>
+      <c r="G16" s="66">
+        <v>9081.550506480402</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="C16" s="66">
-        <v>0.644047833935018</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.4326189754471052</v>
-      </c>
-      <c r="E16" s="63">
-        <v>0.3549390698831137</v>
-      </c>
-      <c r="F16" s="63">
-        <v>0.3128131506849315</v>
-      </c>
-      <c r="G16" s="63">
-        <v>0.3128131506849315</v>
-      </c>
-      <c r="H16" s="65" t="s">
+      <c r="C17" s="61">
+        <v>500</v>
+      </c>
+      <c r="D17" s="61">
+        <v>515</v>
+      </c>
+      <c r="E17" s="61">
+        <v>530.4499999999999</v>
+      </c>
+      <c r="F17" s="61">
+        <v>546.3635</v>
+      </c>
+      <c r="G17" s="61">
+        <v>562.754405</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="67">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="67">
+        <v>2060</v>
+      </c>
+      <c r="E18" s="64">
+        <v>1736.0181818181816</v>
+      </c>
+      <c r="F18" s="64">
+        <v>1573.52688</v>
+      </c>
+      <c r="G18" s="64">
+        <v>1620.7326864000001</v>
+      </c>
+      <c r="H18" s="65" t="s">
         <v>366</v>
       </c>
-      <c r="C17" s="66">
-        <v>0.19494584837545123</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.10912397696271597</v>
-      </c>
-      <c r="E17" s="63">
-        <v>0.0895299676697339</v>
-      </c>
-      <c r="F17" s="63">
-        <v>0.0789041095890411</v>
-      </c>
-      <c r="G17" s="63">
-        <v>0.0789041095890411</v>
-      </c>
-      <c r="H17" s="65" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="C18" s="63">
-        <v>0.13663808664259935</v>
-      </c>
-      <c r="D18" s="63">
-        <v>0.40551379205819943</v>
-      </c>
-      <c r="E18" s="63">
-        <v>0.5042999253916934</v>
-      </c>
-      <c r="F18" s="63">
-        <v>0.5578717808219178</v>
-      </c>
-      <c r="G18" s="63">
-        <v>0.5578717808219178</v>
-      </c>
-      <c r="H18" s="65" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="C19" s="67">
-        <v>3</v>
-      </c>
-      <c r="D19" s="67">
-        <v>3</v>
-      </c>
-      <c r="E19" s="67">
-        <v>3</v>
-      </c>
-      <c r="F19" s="67">
-        <v>3</v>
-      </c>
-      <c r="G19" s="67">
-        <v>3</v>
-      </c>
-      <c r="H19" s="65" t="s">
-        <v>371</v>
+      <c r="C19" s="68">
+        <v>2102.7083333333335</v>
+      </c>
+      <c r="D19" s="68">
+        <v>7655.131666666666</v>
+      </c>
+      <c r="E19" s="68">
+        <v>9778.556413636363</v>
+      </c>
+      <c r="F19" s="68">
+        <v>11125.22842332</v>
+      </c>
+      <c r="G19" s="68">
+        <v>11458.985276019603</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="C20" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="D20" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="F20" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="G20" s="68" t="s">
-        <v>311</v>
+        <v>368</v>
+      </c>
+      <c r="C20" s="69">
+        <v>0.644047833935018</v>
+      </c>
+      <c r="D20" s="63">
+        <v>0.4326189754471052</v>
+      </c>
+      <c r="E20" s="63">
+        <v>0.3549390698831137</v>
+      </c>
+      <c r="F20" s="63">
+        <v>0.3128131506849315</v>
+      </c>
+      <c r="G20" s="63">
+        <v>0.3128131506849315</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>311</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C21" s="69">
+        <v>0.19494584837545123</v>
+      </c>
+      <c r="D21" s="63">
+        <v>0.10912397696271597</v>
+      </c>
+      <c r="E21" s="63">
+        <v>0.0895299676697339</v>
+      </c>
+      <c r="F21" s="63">
+        <v>0.0789041095890411</v>
+      </c>
+      <c r="G21" s="63">
+        <v>0.0789041095890411</v>
+      </c>
+      <c r="H21" s="65" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="C21" s="39" t="str">
+      <c r="C22" s="63">
+        <v>0.13663808664259935</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.40551379205819943</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0.5042999253916934</v>
+      </c>
+      <c r="F22" s="63">
+        <v>0.5578717808219178</v>
+      </c>
+      <c r="G22" s="63">
+        <v>0.5578717808219178</v>
+      </c>
+      <c r="H22" s="65" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="C23" s="70">
+        <v>3</v>
+      </c>
+      <c r="D23" s="70">
+        <v>3</v>
+      </c>
+      <c r="E23" s="70">
+        <v>3</v>
+      </c>
+      <c r="F23" s="70">
+        <v>3</v>
+      </c>
+      <c r="G23" s="70">
+        <v>3</v>
+      </c>
+      <c r="H23" s="65" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="D24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="E24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="F24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="G24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="39" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="69" t="str">
+      <c r="D25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="69" t="str">
+      <c r="E25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="69" t="str">
+      <c r="F25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="69" t="str">
+      <c r="G25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H25" s="65" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="C22" s="70">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="C26" s="73">
         <v>5</v>
       </c>
-      <c r="D22" s="71">
+      <c r="D26" s="74">
         <v>12</v>
       </c>
-      <c r="E22" s="67">
+      <c r="E26" s="70">
         <v>24</v>
       </c>
-      <c r="F22" s="67">
+      <c r="F26" s="70">
         <v>38</v>
       </c>
-      <c r="G22" s="67">
+      <c r="G26" s="70">
         <v>52</v>
       </c>
-      <c r="H22" s="65" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
+      <c r="H26" s="65" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="C23" s="67">
+      <c r="C27" s="70">
         <v>142</v>
       </c>
-      <c r="D23" s="67">
+      <c r="D27" s="70">
         <v>361</v>
       </c>
-      <c r="E23" s="67">
+      <c r="E27" s="70">
         <v>716</v>
       </c>
-      <c r="F23" s="67">
+      <c r="F27" s="70">
         <v>1148</v>
       </c>
-      <c r="G23" s="67">
+      <c r="G27" s="70">
         <v>1575</v>
       </c>
-      <c r="H23" s="65" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19" t="s">
+      <c r="H27" s="65" t="s">
         <v>379</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="41" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C29" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="D26" s="72" t="s">
+      <c r="D29" s="19" t="s">
         <v>382</v>
       </c>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="41" t="s">
-        <v>384</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="D27" s="72" t="s">
-        <v>385</v>
-      </c>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73" t="s">
-        <v>386</v>
-      </c>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="41" t="s">
-        <v>387</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="D28" s="72" t="s">
-        <v>388</v>
-      </c>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73" t="s">
-        <v>389</v>
-      </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="41" t="s">
-        <v>390</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="D29" s="72" t="s">
-        <v>391</v>
-      </c>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73" t="s">
-        <v>392</v>
-      </c>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="41" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>394</v>
-      </c>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73" t="s">
-        <v>395</v>
-      </c>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
+        <v>385</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>386</v>
+      </c>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
+        <v>387</v>
+      </c>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="41" t="s">
+        <v>388</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>389</v>
+      </c>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
+        <v>390</v>
+      </c>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="41" t="s">
+        <v>391</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D32" s="75" t="s">
+        <v>392</v>
+      </c>
+      <c r="E32" s="75"/>
+      <c r="F32" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="41" t="s">
+        <v>394</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D33" s="75" t="s">
+        <v>395</v>
+      </c>
+      <c r="E33" s="75"/>
+      <c r="F33" s="76" t="s">
         <v>396</v>
       </c>
-      <c r="C31" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="D31" s="72" t="s">
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="41" t="s">
         <v>397</v>
       </c>
-      <c r="E31" s="72"/>
-      <c r="F31" s="73" t="s">
+      <c r="C34" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D34" s="75" t="s">
         <v>398</v>
       </c>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="41" t="s">
+      <c r="E34" s="75"/>
+      <c r="F34" s="76" t="s">
         <v>399</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="41" t="s">
         <v>400</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="74" t="s">
+      <c r="C35" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D35" s="75" t="s">
         <v>401</v>
       </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76" t="s">
+        <v>402</v>
+      </c>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="41" t="s">
+        <v>403</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="77" t="s">
+        <v>405</v>
+      </c>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7004,37 +7108,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="401">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1126,18 +1126,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1169,9 +1157,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1499,7 +1484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1598,15 +1583,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6381,7 +6357,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6630,439 +6606,333 @@
         <v>363</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>258</v>
+        <v>364</v>
       </c>
       <c r="C16" s="66">
-        <v>13286.180555555557</v>
-      </c>
-      <c r="D16" s="66">
-        <v>11222.479444444445</v>
-      </c>
-      <c r="E16" s="66">
-        <v>9611.802222727272</v>
-      </c>
-      <c r="F16" s="66">
-        <v>8817.03932668</v>
-      </c>
-      <c r="G16" s="66">
-        <v>9081.550506480402</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="C17" s="61">
-        <v>500</v>
-      </c>
-      <c r="D17" s="61">
-        <v>515</v>
-      </c>
-      <c r="E17" s="61">
-        <v>530.4499999999999</v>
-      </c>
-      <c r="F17" s="61">
-        <v>546.3635</v>
-      </c>
-      <c r="G17" s="61">
-        <v>562.754405</v>
+        <v>0.644047833935018</v>
+      </c>
+      <c r="D16" s="63">
+        <v>0.4326189754471052</v>
+      </c>
+      <c r="E16" s="63">
+        <v>0.3549390698831137</v>
+      </c>
+      <c r="F16" s="63">
+        <v>0.3128131506849315</v>
+      </c>
+      <c r="G16" s="63">
+        <v>0.3128131506849315</v>
+      </c>
+      <c r="H16" s="65" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C17" s="66">
+        <v>0.19494584837545123</v>
+      </c>
+      <c r="D17" s="63">
+        <v>0.10912397696271597</v>
+      </c>
+      <c r="E17" s="63">
+        <v>0.0895299676697339</v>
+      </c>
+      <c r="F17" s="63">
+        <v>0.0789041095890411</v>
+      </c>
+      <c r="G17" s="63">
+        <v>0.0789041095890411</v>
+      </c>
+      <c r="H17" s="65" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="C18" s="67">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="67">
-        <v>2060</v>
-      </c>
-      <c r="E18" s="64">
-        <v>1736.0181818181816</v>
-      </c>
-      <c r="F18" s="64">
-        <v>1573.52688</v>
-      </c>
-      <c r="G18" s="64">
-        <v>1620.7326864000001</v>
+      <c r="B18" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="C18" s="63">
+        <v>0.13663808664259935</v>
+      </c>
+      <c r="D18" s="63">
+        <v>0.40551379205819943</v>
+      </c>
+      <c r="E18" s="63">
+        <v>0.5042999253916934</v>
+      </c>
+      <c r="F18" s="63">
+        <v>0.5578717808219178</v>
+      </c>
+      <c r="G18" s="63">
+        <v>0.5578717808219178</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="C19" s="68">
-        <v>2102.7083333333335</v>
-      </c>
-      <c r="D19" s="68">
-        <v>7655.131666666666</v>
-      </c>
-      <c r="E19" s="68">
-        <v>9778.556413636363</v>
-      </c>
-      <c r="F19" s="68">
-        <v>11125.22842332</v>
-      </c>
-      <c r="G19" s="68">
-        <v>11458.985276019603</v>
+        <v>370</v>
+      </c>
+      <c r="C19" s="67">
+        <v>3</v>
+      </c>
+      <c r="D19" s="67">
+        <v>3</v>
+      </c>
+      <c r="E19" s="67">
+        <v>3</v>
+      </c>
+      <c r="F19" s="67">
+        <v>3</v>
+      </c>
+      <c r="G19" s="67">
+        <v>3</v>
+      </c>
+      <c r="H19" s="65" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="C20" s="69">
-        <v>0.644047833935018</v>
-      </c>
-      <c r="D20" s="63">
-        <v>0.4326189754471052</v>
-      </c>
-      <c r="E20" s="63">
-        <v>0.3549390698831137</v>
-      </c>
-      <c r="F20" s="63">
-        <v>0.3128131506849315</v>
-      </c>
-      <c r="G20" s="63">
-        <v>0.3128131506849315</v>
+        <v>310</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E20" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="G20" s="68" t="s">
+        <v>311</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>369</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="C21" s="69">
-        <v>0.19494584837545123</v>
-      </c>
-      <c r="D21" s="63">
-        <v>0.10912397696271597</v>
-      </c>
-      <c r="E21" s="63">
-        <v>0.0895299676697339</v>
-      </c>
-      <c r="F21" s="63">
-        <v>0.0789041095890411</v>
-      </c>
-      <c r="G21" s="63">
-        <v>0.0789041095890411</v>
+        <v>372</v>
+      </c>
+      <c r="C21" s="39" t="str">
+        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="69" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="69" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="69" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="69" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="C22" s="63">
-        <v>0.13663808664259935</v>
-      </c>
-      <c r="D22" s="63">
-        <v>0.40551379205819943</v>
-      </c>
-      <c r="E22" s="63">
-        <v>0.5042999253916934</v>
-      </c>
-      <c r="F22" s="63">
-        <v>0.5578717808219178</v>
-      </c>
-      <c r="G22" s="63">
-        <v>0.5578717808219178</v>
+        <v>373</v>
+      </c>
+      <c r="C22" s="70">
+        <v>5</v>
+      </c>
+      <c r="D22" s="71">
+        <v>12</v>
+      </c>
+      <c r="E22" s="67">
+        <v>24</v>
+      </c>
+      <c r="F22" s="67">
+        <v>38</v>
+      </c>
+      <c r="G22" s="67">
+        <v>52</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="70">
-        <v>3</v>
-      </c>
-      <c r="D23" s="70">
-        <v>3</v>
-      </c>
-      <c r="E23" s="70">
-        <v>3</v>
-      </c>
-      <c r="F23" s="70">
-        <v>3</v>
-      </c>
-      <c r="G23" s="70">
-        <v>3</v>
-      </c>
-      <c r="H23" s="65" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="C24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="D24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="E24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="F24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="G24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="H24" s="65" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
+      <c r="C24" s="19" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="39" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="65" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
+      <c r="D24" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="C26" s="73">
-        <v>5</v>
-      </c>
-      <c r="D26" s="74">
-        <v>12</v>
-      </c>
-      <c r="E26" s="70">
-        <v>24</v>
-      </c>
-      <c r="F26" s="70">
-        <v>38</v>
-      </c>
-      <c r="G26" s="70">
-        <v>52</v>
-      </c>
-      <c r="H26" s="65" t="s">
+      <c r="E24" s="19"/>
+      <c r="F24" s="19" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="C27" s="70">
-        <v>142</v>
-      </c>
-      <c r="D27" s="70">
-        <v>361</v>
-      </c>
-      <c r="E27" s="70">
-        <v>716</v>
-      </c>
-      <c r="F27" s="70">
-        <v>1148</v>
-      </c>
-      <c r="G27" s="70">
-        <v>1575</v>
-      </c>
-      <c r="H27" s="65" t="s">
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="41" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="19" t="s">
+      <c r="C25" s="39" t="s">
         <v>380</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="D25" s="72" t="s">
         <v>381</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="E25" s="72"/>
+      <c r="F25" s="73" t="s">
         <v>382</v>
       </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19" t="s">
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="41" t="s">
         <v>383</v>
       </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
+      <c r="C26" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="D26" s="72" t="s">
+        <v>384</v>
+      </c>
+      <c r="E26" s="72"/>
+      <c r="F26" s="73" t="s">
+        <v>385</v>
+      </c>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="41" t="s">
+        <v>386</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="D27" s="72" t="s">
+        <v>387</v>
+      </c>
+      <c r="E27" s="72"/>
+      <c r="F27" s="73" t="s">
+        <v>388</v>
+      </c>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="D28" s="72" t="s">
+        <v>390</v>
+      </c>
+      <c r="E28" s="72"/>
+      <c r="F28" s="73" t="s">
+        <v>391</v>
+      </c>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="41" t="s">
+        <v>392</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="D29" s="72" t="s">
+        <v>393</v>
+      </c>
+      <c r="E29" s="72"/>
+      <c r="F29" s="73" t="s">
+        <v>394</v>
+      </c>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="41" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>386</v>
-      </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
-        <v>387</v>
-      </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="41" t="s">
-        <v>388</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D31" s="75" t="s">
-        <v>389</v>
-      </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
-        <v>390</v>
-      </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+      <c r="D30" s="72" t="s">
+        <v>396</v>
+      </c>
+      <c r="E30" s="72"/>
+      <c r="F30" s="73" t="s">
+        <v>397</v>
+      </c>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="41" t="s">
-        <v>391</v>
-      </c>
-      <c r="C32" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D32" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="41" t="s">
-        <v>394</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D33" s="75" t="s">
-        <v>395</v>
-      </c>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76" t="s">
-        <v>396</v>
-      </c>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="41" t="s">
-        <v>397</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D34" s="75" t="s">
         <v>398</v>
       </c>
-      <c r="E34" s="75"/>
-      <c r="F34" s="76" t="s">
+      <c r="C32" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="41" t="s">
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="74" t="s">
         <v>400</v>
       </c>
-      <c r="C35" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D35" s="75" t="s">
-        <v>401</v>
-      </c>
-      <c r="E35" s="75"/>
-      <c r="F35" s="76" t="s">
-        <v>402</v>
-      </c>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="41" t="s">
-        <v>403</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="77" t="s">
-        <v>405</v>
-      </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7108,37 +6978,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="406">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1126,6 +1126,18 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1157,6 +1169,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1484,7 +1499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1583,6 +1598,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6357,7 +6381,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6606,333 +6630,439 @@
         <v>363</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="66">
+        <v>13286.180555555557</v>
+      </c>
+      <c r="D16" s="66">
+        <v>11222.479444444445</v>
+      </c>
+      <c r="E16" s="66">
+        <v>9611.802222727272</v>
+      </c>
+      <c r="F16" s="66">
+        <v>8817.03932668</v>
+      </c>
+      <c r="G16" s="66">
+        <v>9081.550506480402</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="C16" s="66">
-        <v>0.644047833935018</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.4326189754471052</v>
-      </c>
-      <c r="E16" s="63">
-        <v>0.3549390698831137</v>
-      </c>
-      <c r="F16" s="63">
-        <v>0.3128131506849315</v>
-      </c>
-      <c r="G16" s="63">
-        <v>0.3128131506849315</v>
-      </c>
-      <c r="H16" s="65" t="s">
+      <c r="C17" s="61">
+        <v>500</v>
+      </c>
+      <c r="D17" s="61">
+        <v>515</v>
+      </c>
+      <c r="E17" s="61">
+        <v>530.4499999999999</v>
+      </c>
+      <c r="F17" s="61">
+        <v>546.3635</v>
+      </c>
+      <c r="G17" s="61">
+        <v>562.754405</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="67">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="67">
+        <v>2060</v>
+      </c>
+      <c r="E18" s="64">
+        <v>1736.0181818181816</v>
+      </c>
+      <c r="F18" s="64">
+        <v>1573.52688</v>
+      </c>
+      <c r="G18" s="64">
+        <v>1620.7326864000001</v>
+      </c>
+      <c r="H18" s="65" t="s">
         <v>366</v>
       </c>
-      <c r="C17" s="66">
-        <v>0.19494584837545123</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.10912397696271597</v>
-      </c>
-      <c r="E17" s="63">
-        <v>0.0895299676697339</v>
-      </c>
-      <c r="F17" s="63">
-        <v>0.0789041095890411</v>
-      </c>
-      <c r="G17" s="63">
-        <v>0.0789041095890411</v>
-      </c>
-      <c r="H17" s="65" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="C18" s="63">
-        <v>0.13663808664259935</v>
-      </c>
-      <c r="D18" s="63">
-        <v>0.40551379205819943</v>
-      </c>
-      <c r="E18" s="63">
-        <v>0.5042999253916934</v>
-      </c>
-      <c r="F18" s="63">
-        <v>0.5578717808219178</v>
-      </c>
-      <c r="G18" s="63">
-        <v>0.5578717808219178</v>
-      </c>
-      <c r="H18" s="65" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="C19" s="67">
-        <v>3</v>
-      </c>
-      <c r="D19" s="67">
-        <v>3</v>
-      </c>
-      <c r="E19" s="67">
-        <v>3</v>
-      </c>
-      <c r="F19" s="67">
-        <v>3</v>
-      </c>
-      <c r="G19" s="67">
-        <v>3</v>
-      </c>
-      <c r="H19" s="65" t="s">
-        <v>371</v>
+      <c r="C19" s="68">
+        <v>2102.7083333333335</v>
+      </c>
+      <c r="D19" s="68">
+        <v>7655.131666666666</v>
+      </c>
+      <c r="E19" s="68">
+        <v>9778.556413636363</v>
+      </c>
+      <c r="F19" s="68">
+        <v>11125.22842332</v>
+      </c>
+      <c r="G19" s="68">
+        <v>11458.985276019603</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="C20" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="D20" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="F20" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="G20" s="68" t="s">
-        <v>311</v>
+        <v>368</v>
+      </c>
+      <c r="C20" s="69">
+        <v>0.644047833935018</v>
+      </c>
+      <c r="D20" s="63">
+        <v>0.4326189754471052</v>
+      </c>
+      <c r="E20" s="63">
+        <v>0.3549390698831137</v>
+      </c>
+      <c r="F20" s="63">
+        <v>0.3128131506849315</v>
+      </c>
+      <c r="G20" s="63">
+        <v>0.3128131506849315</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>311</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C21" s="69">
+        <v>0.19494584837545123</v>
+      </c>
+      <c r="D21" s="63">
+        <v>0.10912397696271597</v>
+      </c>
+      <c r="E21" s="63">
+        <v>0.0895299676697339</v>
+      </c>
+      <c r="F21" s="63">
+        <v>0.0789041095890411</v>
+      </c>
+      <c r="G21" s="63">
+        <v>0.0789041095890411</v>
+      </c>
+      <c r="H21" s="65" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="C21" s="39" t="str">
+      <c r="C22" s="63">
+        <v>0.13663808664259935</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.40551379205819943</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0.5042999253916934</v>
+      </c>
+      <c r="F22" s="63">
+        <v>0.5578717808219178</v>
+      </c>
+      <c r="G22" s="63">
+        <v>0.5578717808219178</v>
+      </c>
+      <c r="H22" s="65" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="C23" s="70">
+        <v>3</v>
+      </c>
+      <c r="D23" s="70">
+        <v>3</v>
+      </c>
+      <c r="E23" s="70">
+        <v>3</v>
+      </c>
+      <c r="F23" s="70">
+        <v>3</v>
+      </c>
+      <c r="G23" s="70">
+        <v>3</v>
+      </c>
+      <c r="H23" s="65" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="D24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="E24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="F24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="G24" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="39" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="69" t="str">
+      <c r="D25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="69" t="str">
+      <c r="E25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="69" t="str">
+      <c r="F25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="69" t="str">
+      <c r="G25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H25" s="65" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="C22" s="70">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="C26" s="73">
         <v>5</v>
       </c>
-      <c r="D22" s="71">
+      <c r="D26" s="74">
         <v>12</v>
       </c>
-      <c r="E22" s="67">
+      <c r="E26" s="70">
         <v>24</v>
       </c>
-      <c r="F22" s="67">
+      <c r="F26" s="70">
         <v>38</v>
       </c>
-      <c r="G22" s="67">
+      <c r="G26" s="70">
         <v>52</v>
       </c>
-      <c r="H22" s="65" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="H26" s="65" t="s">
         <v>378</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="41" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C27" s="70">
+        <v>142</v>
+      </c>
+      <c r="D27" s="70">
+        <v>361</v>
+      </c>
+      <c r="E27" s="70">
+        <v>716</v>
+      </c>
+      <c r="F27" s="70">
+        <v>1148</v>
+      </c>
+      <c r="G27" s="70">
+        <v>1575</v>
+      </c>
+      <c r="H27" s="65" t="s">
         <v>379</v>
       </c>
-      <c r="C25" s="39" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="D25" s="72" t="s">
+      <c r="C29" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73" t="s">
+      <c r="D29" s="19" t="s">
         <v>382</v>
       </c>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="41" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="C26" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="D26" s="72" t="s">
-        <v>384</v>
-      </c>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73" t="s">
-        <v>385</v>
-      </c>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="41" t="s">
-        <v>386</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="D27" s="72" t="s">
-        <v>387</v>
-      </c>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73" t="s">
-        <v>388</v>
-      </c>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="41" t="s">
-        <v>389</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="D28" s="72" t="s">
-        <v>390</v>
-      </c>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73" t="s">
-        <v>391</v>
-      </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="41" t="s">
-        <v>392</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="D29" s="72" t="s">
-        <v>393</v>
-      </c>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73" t="s">
-        <v>394</v>
-      </c>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="41" t="s">
+        <v>384</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>386</v>
+      </c>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
+        <v>387</v>
+      </c>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="41" t="s">
+        <v>388</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>389</v>
+      </c>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
+        <v>390</v>
+      </c>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="41" t="s">
+        <v>391</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D32" s="75" t="s">
+        <v>392</v>
+      </c>
+      <c r="E32" s="75"/>
+      <c r="F32" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="41" t="s">
+        <v>394</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D33" s="75" t="s">
         <v>395</v>
       </c>
-      <c r="C30" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="D30" s="72" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="76" t="s">
         <v>396</v>
       </c>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73" t="s">
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="41" t="s">
         <v>397</v>
       </c>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="41" t="s">
+      <c r="C34" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D34" s="75" t="s">
         <v>398</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="E34" s="75"/>
+      <c r="F34" s="76" t="s">
         <v>399</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="74" t="s">
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="41" t="s">
         <v>400</v>
       </c>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="74"/>
+      <c r="C35" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D35" s="75" t="s">
+        <v>401</v>
+      </c>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76" t="s">
+        <v>402</v>
+      </c>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="41" t="s">
+        <v>403</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="77" t="s">
+        <v>405</v>
+      </c>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6978,37 +7108,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -26,13 +26,15 @@
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="444">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -40,7 +42,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · llc_single</t>
+    <t>Generated April 29, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -160,7 +162,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -310,6 +312,12 @@
     <t>Financial Health</t>
   </si>
   <si>
+    <t>23.</t>
+  </si>
+  <si>
+    <t>Budget Narrative</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -376,6 +384,9 @@
     <t>Escalation %</t>
   </si>
   <si>
+    <t>Timing</t>
+  </si>
+  <si>
     <t>Tuition</t>
   </si>
   <si>
@@ -385,6 +396,9 @@
     <t>Per Student</t>
   </si>
   <si>
+    <t>Default</t>
+  </si>
+  <si>
     <t>Registration Fee</t>
   </si>
   <si>
@@ -532,6 +546,48 @@
     <t>No</t>
   </si>
   <si>
+    <t>Enrollment Growth Rate</t>
+  </si>
+  <si>
+    <t>Rent Escalation Rate</t>
+  </si>
+  <si>
+    <t>Tuition Escalation Rate</t>
+  </si>
+  <si>
+    <t>Default Benefits Rate</t>
+  </si>
+  <si>
+    <t>Default Payroll Tax Rate</t>
+  </si>
+  <si>
+    <t>Student Retention Rate</t>
+  </si>
+  <si>
+    <t>REVENUE COLLECTION DEFAULTS</t>
+  </si>
+  <si>
+    <t>Default Billing Months</t>
+  </si>
+  <si>
+    <t>10 months (Aug-May)</t>
+  </si>
+  <si>
+    <t>Default Collection Method</t>
+  </si>
+  <si>
+    <t>Autopay</t>
+  </si>
+  <si>
+    <t>Default Collection Rate</t>
+  </si>
+  <si>
+    <t>Default Collection Delay</t>
+  </si>
+  <si>
+    <t>0 days</t>
+  </si>
+  <si>
     <t>School Model</t>
   </si>
   <si>
@@ -586,9 +642,6 @@
     <t>Capacity Utilization</t>
   </si>
   <si>
-    <t>Enrollment Growth Rate</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -628,6 +681,9 @@
     <t>Loaded Cost</t>
   </si>
   <si>
+    <t>Rates</t>
+  </si>
+  <si>
     <t>5-YEAR TOTAL PERSONNEL COST</t>
   </si>
   <si>
@@ -883,12 +939,24 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
+    <t>Cash Trough: July (Month 1)</t>
+  </si>
+  <si>
+    <t>Your lowest cash point is the month lenders focus on to ensure you won't run out of money before collections start. Plan reserves to cover this trough.</t>
+  </si>
+  <si>
     <t>Bright Horizons Microschool - 5-Year Operating Statement</t>
   </si>
   <si>
+    <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
+  </si>
+  <si>
     <t>Capital &amp; Debt Service</t>
   </si>
   <si>
+    <t>Depreciation</t>
+  </si>
+  <si>
     <t>BOTTOM LINE</t>
   </si>
   <si>
@@ -922,7 +990,7 @@
     <t>Accounts Receivable</t>
   </si>
   <si>
-    <t>Fixed Assets</t>
+    <t>Fixed Assets (Net of Depreciation)</t>
   </si>
   <si>
     <t>Other Assets</t>
@@ -961,7 +1029,13 @@
     <t>Revenue</t>
   </si>
   <si>
-    <t>CFADS (Rev - Pers - OpEx)</t>
+    <t>Depreciation Add-Back</t>
+  </si>
+  <si>
+    <t>Debt Service (Loan)</t>
+  </si>
+  <si>
+    <t>CFADS (NI + Depr + DS)</t>
   </si>
   <si>
     <t>DSCR</t>
@@ -1006,6 +1080,9 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>Current Ratio ≥ 1.1x</t>
+  </si>
+  <si>
     <t>Capacity ≥ 70%</t>
   </si>
   <si>
@@ -1090,7 +1167,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1210,7 +1287,7 @@
     <t>Staffing Burden</t>
   </si>
   <si>
-    <t>Staffing at 31% of revenue leaves room for facilities, programs, and reserves.</t>
+    <t>Staffing at 32% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
     <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
@@ -1237,7 +1314,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>51.8 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>51.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1250,6 +1327,45 @@
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
+  </si>
+  <si>
+    <t>Enrollment Strategy</t>
+  </si>
+  <si>
+    <t>(Not provided)</t>
+  </si>
+  <si>
+    <t>Retention Plan</t>
+  </si>
+  <si>
+    <t>Risk Mitigation</t>
+  </si>
+  <si>
+    <t>Mission &amp; Vision</t>
+  </si>
+  <si>
+    <t>Revenue Assumptions</t>
+  </si>
+  <si>
+    <t>Staffing Philosophy</t>
+  </si>
+  <si>
+    <t>Expense Assumptions</t>
+  </si>
+  <si>
+    <t>Growth Strategy</t>
+  </si>
+  <si>
+    <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1379,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1357,6 +1473,23 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF16A34A"/>
       <sz val="11"/>
@@ -1405,7 +1538,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1435,6 +1568,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1499,7 +1637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1546,8 +1684,11 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1557,17 +1698,17 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1575,10 +1716,10 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1597,17 +1738,17 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1619,20 +1760,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2330,7 +2480,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2343,24 +2493,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B4" s="35">
         <v>12</v>
@@ -2380,7 +2530,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2390,7 +2540,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B7" s="30">
         <v>144000</v>
@@ -2410,7 +2560,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B8" s="30">
         <v>3000</v>
@@ -2430,7 +2580,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B9" s="30">
         <v>84000</v>
@@ -2450,7 +2600,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B10" s="30">
         <v>5000</v>
@@ -2470,7 +2620,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B11" s="30">
         <v>-10</v>
@@ -2490,7 +2640,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="B12" s="32">
         <f>SUM(B7:B11)</f>
@@ -2498,39 +2648,39 @@
       </c>
       <c r="C12" s="32">
         <f>SUM(C7:C11)</f>
-        <v>339797</v>
+        <v>339130</v>
       </c>
       <c r="D12" s="32">
         <f>SUM(D7:D11)</f>
-        <v>426588</v>
+        <v>424882</v>
       </c>
       <c r="E12" s="32">
         <f>SUM(E7:E11)</f>
-        <v>498557</v>
+        <v>495517</v>
       </c>
       <c r="F12" s="32">
         <f>SUM(F7:F11)</f>
-        <v>513513</v>
+        <v>509276</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B14" s="30">
         <v>18467</v>
       </c>
       <c r="C14" s="30">
-        <v>18878</v>
+        <v>18841</v>
       </c>
       <c r="D14" s="30">
-        <v>19390</v>
+        <v>19313</v>
       </c>
       <c r="E14" s="30">
-        <v>19942</v>
+        <v>19821</v>
       </c>
       <c r="F14" s="30">
-        <v>20541</v>
+        <v>20371</v>
       </c>
     </row>
   </sheetData>
@@ -2559,7 +2709,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2572,24 +2722,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2599,7 +2749,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B5" s="30">
         <v>47869</v>
@@ -2619,7 +2769,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B6" s="30">
         <v>12559</v>
@@ -2639,7 +2789,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B7" s="31">
         <f>SUM(B5:B6)</f>
@@ -2664,7 +2814,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -2674,7 +2824,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B9" s="30">
         <v>58506</v>
@@ -2694,7 +2844,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B10" s="31">
         <f>SUM(B9:B9)</f>
@@ -2719,7 +2869,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B12" s="32">
         <f>B7+B10</f>
@@ -2768,7 +2918,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2781,24 +2931,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2808,7 +2958,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="B5" s="30">
         <v>120000</v>
@@ -2828,7 +2978,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B6" s="30">
         <v>2500</v>
@@ -2848,7 +2998,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B7" s="30">
         <v>70000</v>
@@ -2868,7 +3018,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B8" s="30">
         <v>4167</v>
@@ -2888,7 +3038,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="B9" s="30">
         <v>-8</v>
@@ -2908,7 +3058,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B10" s="31">
         <f>SUM(B5:B9)</f>
@@ -2916,24 +3066,24 @@
       </c>
       <c r="C10" s="31">
         <f>SUM(C5:C9)</f>
-        <v>339797</v>
+        <v>339130</v>
       </c>
       <c r="D10" s="31">
         <f>SUM(D5:D9)</f>
-        <v>426588</v>
+        <v>424882</v>
       </c>
       <c r="E10" s="31">
         <f>SUM(E5:E9)</f>
-        <v>498557</v>
+        <v>495517</v>
       </c>
       <c r="F10" s="31">
         <f>SUM(F5:F9)</f>
-        <v>513513</v>
+        <v>509276</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -2943,7 +3093,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B13" s="30">
         <v>58506</v>
@@ -2963,7 +3113,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B14" s="30">
         <v>47869</v>
@@ -2983,7 +3133,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B15" s="30">
         <v>12559</v>
@@ -3003,7 +3153,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B16" s="31">
         <f>SUM(B13:B15)</f>
@@ -3028,7 +3178,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -3038,12 +3188,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="36" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B20" s="30">
         <v>5000</v>
@@ -3063,12 +3213,12 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B22" s="30">
         <v>3000</v>
@@ -3088,12 +3238,12 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="B24" s="30">
         <v>25000</v>
@@ -3113,7 +3263,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B25" s="30">
         <v>3000</v>
@@ -3133,7 +3283,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="B26" s="30">
         <v>2000</v>
@@ -3153,7 +3303,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B27" s="31">
         <f>SUM(B24:B26)</f>
@@ -3178,12 +3328,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B29" s="30">
         <v>2500</v>
@@ -3203,7 +3353,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B30" s="31">
         <f>B20+B22+B27+B29</f>
@@ -3228,7 +3378,7 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
@@ -3238,7 +3388,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B33" s="31" t="str">
         <f>SUM(B33:B32)</f>
@@ -3287,7 +3437,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3300,24 +3450,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B4" s="33">
         <f>'Budget Detail'!B10</f>
@@ -3325,24 +3475,24 @@
       </c>
       <c r="C4" s="33">
         <f>'Budget Detail'!C10</f>
-        <v>339797</v>
+        <v>339130</v>
       </c>
       <c r="D4" s="33">
         <f>'Budget Detail'!D10</f>
-        <v>426588</v>
+        <v>424882</v>
       </c>
       <c r="E4" s="33">
         <f>'Budget Detail'!E10</f>
-        <v>498557</v>
+        <v>495517</v>
       </c>
       <c r="F4" s="33">
         <f>'Budget Detail'!F10</f>
-        <v>513513</v>
+        <v>509276</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B5" s="33">
         <f>'Budget Detail'!B16</f>
@@ -3367,7 +3517,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B6" s="33">
         <f>'Budget Detail'!B30</f>
@@ -3392,7 +3542,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B7" s="33" t="str">
         <f>'Budget Detail'!B33</f>
@@ -3417,7 +3567,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -3442,7 +3592,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3452,7 +3602,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B11" s="32">
         <f>B4-B8</f>
@@ -3460,24 +3610,24 @@
       </c>
       <c r="C11" s="32">
         <f>C4-C8</f>
-        <v>137792</v>
+        <v>137125</v>
       </c>
       <c r="D11" s="32">
         <f>D4-D8</f>
-        <v>215128</v>
+        <v>213423</v>
       </c>
       <c r="E11" s="32">
         <f>E4-E8</f>
-        <v>278131</v>
+        <v>275091</v>
       </c>
       <c r="F11" s="32">
         <f>F4-F8</f>
-        <v>286475</v>
+        <v>282237</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3485,64 +3635,64 @@
       </c>
       <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.40551379</v>
+        <v>0.40434379</v>
       </c>
       <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.50429993</v>
+        <v>0.50230996</v>
       </c>
       <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.55787178</v>
+        <v>0.55515954</v>
       </c>
       <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.55787178</v>
+        <v>0.5541927</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B13" s="30">
         <v>25233</v>
       </c>
       <c r="C13" s="30">
-        <v>163025</v>
+        <v>162357</v>
       </c>
       <c r="D13" s="30">
-        <v>378153</v>
+        <v>375780</v>
       </c>
       <c r="E13" s="30">
-        <v>656284</v>
+        <v>650871</v>
       </c>
       <c r="F13" s="30">
-        <v>942758</v>
+        <v>933108</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B14" s="30">
         <v>15389</v>
       </c>
       <c r="C14" s="30">
-        <v>18878</v>
+        <v>18841</v>
       </c>
       <c r="D14" s="30">
-        <v>19390</v>
+        <v>19313</v>
       </c>
       <c r="E14" s="30">
-        <v>19942</v>
+        <v>19821</v>
       </c>
       <c r="F14" s="30">
-        <v>20541</v>
+        <v>20371</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="B15" s="30">
         <v>13286</v>
@@ -3577,7 +3727,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3587,7 +3737,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3608,48 +3758,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -3667,7 +3817,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B4" s="31">
         <v>9150</v>
@@ -3712,7 +3862,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -3730,7 +3880,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B7" s="30">
         <v>11893</v>
@@ -3775,7 +3925,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B8" s="30">
         <v>4050</v>
@@ -3820,7 +3970,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B9" s="30">
         <v>0</v>
@@ -3865,7 +4015,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -3883,7 +4033,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B12" s="33">
         <f>B7+B8+B9</f>
@@ -3940,7 +4090,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B13" s="33">
         <f>B4-B12</f>
@@ -3997,7 +4147,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="B14" s="37">
         <f>B17+B13</f>
@@ -4054,14 +4204,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B17" s="23">
         <v>0</v>
@@ -4069,7 +4219,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="B18" s="37">
         <f>M14</f>
@@ -4078,16 +4228,40 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B19" s="30">
+        <v>300</v>
+      </c>
+      <c r="B19" s="38">
         <f>MIN(B14:M14)</f>
         <v>-6793</v>
       </c>
     </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:H21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4102,7 +4276,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4111,7 +4285,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4119,29 +4293,39 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+    </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4150,28 +4334,28 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
-        <v>236</v>
+      <c r="A5" s="41" t="s">
+        <v>254</v>
       </c>
       <c r="B5" s="31">
         <v>184667</v>
       </c>
       <c r="C5" s="31">
-        <v>339797</v>
+        <v>339130</v>
       </c>
       <c r="D5" s="31">
-        <v>426588</v>
+        <v>424882</v>
       </c>
       <c r="E5" s="31">
-        <v>498557</v>
+        <v>495517</v>
       </c>
       <c r="F5" s="31">
-        <v>513513</v>
+        <v>509276</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4181,7 +4365,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B8" s="33">
         <v>118934</v>
@@ -4201,7 +4385,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B9" s="33">
         <v>40500</v>
@@ -4221,7 +4405,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="B10" s="33">
         <v>0</v>
@@ -4240,138 +4424,159 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="B11" s="31">
-        <f>SUM(B8:B10)</f>
-        <v>159434</v>
-      </c>
-      <c r="C11" s="31">
-        <f>SUM(C8:C10)</f>
-        <v>202005</v>
-      </c>
-      <c r="D11" s="31">
-        <f>SUM(D8:D10)</f>
-        <v>211460</v>
-      </c>
-      <c r="E11" s="31">
-        <f>SUM(E8:E10)</f>
-        <v>220426</v>
-      </c>
-      <c r="F11" s="31">
-        <f>SUM(F8:F10)</f>
-        <v>227039</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="B14" s="32">
-        <f>B5-B11</f>
-        <v>25233</v>
-      </c>
-      <c r="C14" s="32">
-        <f>C5-C11</f>
-        <v>137792</v>
-      </c>
-      <c r="D14" s="32">
-        <f>D5-D11</f>
-        <v>215128</v>
-      </c>
-      <c r="E14" s="32">
-        <f>E5-E11</f>
-        <v>278131</v>
-      </c>
-      <c r="F14" s="32">
-        <f>F5-F11</f>
-        <v>286475</v>
-      </c>
+      <c r="A11" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="B11" s="33">
+        <v>714</v>
+      </c>
+      <c r="C11" s="33">
+        <v>714</v>
+      </c>
+      <c r="D11" s="33">
+        <v>714</v>
+      </c>
+      <c r="E11" s="33">
+        <v>714</v>
+      </c>
+      <c r="F11" s="33">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="B12" s="31">
+        <f>SUM(B8:B11)</f>
+        <v>160148</v>
+      </c>
+      <c r="C12" s="31">
+        <f>SUM(C8:C11)</f>
+        <v>202719</v>
+      </c>
+      <c r="D12" s="31">
+        <f>SUM(D8:D11)</f>
+        <v>212174</v>
+      </c>
+      <c r="E12" s="31">
+        <f>SUM(E8:E11)</f>
+        <v>221140</v>
+      </c>
+      <c r="F12" s="31">
+        <f>SUM(F8:F11)</f>
+        <v>227753</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B15" s="29">
-        <f>IF(B5=0,0,B14/B5)</f>
-        <v>0.13663809</v>
-      </c>
-      <c r="C15" s="29">
-        <f>IF(C5=0,0,C14/C5)</f>
-        <v>0.40551379</v>
-      </c>
-      <c r="D15" s="29">
-        <f>IF(D5=0,0,D14/D5)</f>
-        <v>0.50429993</v>
-      </c>
-      <c r="E15" s="29">
-        <f>IF(E5=0,0,E14/E5)</f>
-        <v>0.55787178</v>
-      </c>
-      <c r="F15" s="29">
-        <f>IF(F5=0,0,F14/F5)</f>
-        <v>0.55787178</v>
+      <c r="A15" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="B15" s="32">
+        <f>B5-B12</f>
+        <v>24518</v>
+      </c>
+      <c r="C15" s="32">
+        <f>C5-C12</f>
+        <v>136411</v>
+      </c>
+      <c r="D15" s="32">
+        <f>D5-D12</f>
+        <v>212708</v>
+      </c>
+      <c r="E15" s="32">
+        <f>E5-E12</f>
+        <v>274377</v>
+      </c>
+      <c r="F15" s="32">
+        <f>F5-F12</f>
+        <v>281523</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="B16" s="33">
-        <f>B14</f>
-        <v>25233</v>
-      </c>
-      <c r="C16" s="33">
-        <f>B16+C14</f>
-        <v>163025</v>
-      </c>
-      <c r="D16" s="33">
-        <f>C16+D14</f>
-        <v>378153</v>
-      </c>
-      <c r="E16" s="33">
-        <f>D16+E14</f>
-        <v>656284</v>
-      </c>
-      <c r="F16" s="33">
-        <f>E16+F14</f>
-        <v>942758</v>
+      <c r="A16" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="29">
+        <f>IF(B5=0,0,B15/B5)</f>
+        <v>0.13277011</v>
+      </c>
+      <c r="C16" s="29">
+        <f>IF(C5=0,0,C15/C5)</f>
+        <v>0.40223755</v>
+      </c>
+      <c r="D16" s="29">
+        <f>IF(D5=0,0,D15/D5)</f>
+        <v>0.50062882</v>
+      </c>
+      <c r="E16" s="29">
+        <f>IF(E5=0,0,E15/E5)</f>
+        <v>0.55371804</v>
+      </c>
+      <c r="F16" s="29">
+        <f>IF(F5=0,0,F15/F5)</f>
+        <v>0.55279014</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="C17" s="40" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" s="33">
+        <f>B15</f>
+        <v>24518</v>
+      </c>
+      <c r="C17" s="33">
+        <f>B17+C15</f>
+        <v>160929</v>
+      </c>
+      <c r="D17" s="33">
+        <f>C17+D15</f>
+        <v>373637</v>
+      </c>
+      <c r="E17" s="33">
+        <f>D17+E15</f>
+        <v>648014</v>
+      </c>
+      <c r="F17" s="33">
+        <f>E17+F15</f>
+        <v>929536</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="C18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F18" s="43" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4408,24 +4613,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4434,20 +4639,20 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>290</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>215</v>
+      <c r="A5" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -4476,7 +4681,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4489,24 +4694,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4516,72 +4721,72 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B5" s="44">
+        <v>316</v>
+      </c>
+      <c r="B5" s="47">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>62170</v>
       </c>
-      <c r="C5" s="44">
-        <f>B5+'5-Year Operating Stmt'!C14</f>
-        <v>199962</v>
-      </c>
-      <c r="D5" s="44">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
-        <v>415091</v>
-      </c>
-      <c r="E5" s="44">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
-        <v>693221</v>
-      </c>
-      <c r="F5" s="44">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
-        <v>979696</v>
+      <c r="C5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15</f>
+        <v>199295</v>
+      </c>
+      <c r="D5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
+        <v>412717</v>
+      </c>
+      <c r="E5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
+        <v>687808</v>
+      </c>
+      <c r="F5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
+        <v>970045</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="B6" s="30">
-        <v>0</v>
+        <v>1007</v>
       </c>
       <c r="C6" s="30">
-        <v>0</v>
+        <v>1036</v>
       </c>
       <c r="D6" s="30">
-        <v>0</v>
+        <v>1067</v>
       </c>
       <c r="E6" s="30">
-        <v>0</v>
+        <v>1098</v>
       </c>
       <c r="F6" s="30">
-        <v>0</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="B7" s="30">
-        <v>5000</v>
+        <v>4286</v>
       </c>
       <c r="C7" s="30">
-        <v>5000</v>
+        <v>3571</v>
       </c>
       <c r="D7" s="30">
-        <v>5000</v>
+        <v>2857</v>
       </c>
       <c r="E7" s="30">
-        <v>5000</v>
+        <v>2143</v>
       </c>
       <c r="F7" s="30">
-        <v>5000</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="B8" s="30">
         <v>0</v>
@@ -4601,32 +4806,32 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
-        <v>67170</v>
+        <v>67463</v>
       </c>
       <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
-        <v>204962</v>
+        <v>203903</v>
       </c>
       <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
-        <v>420091</v>
+        <v>416642</v>
       </c>
       <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
-        <v>698221</v>
+        <v>691050</v>
       </c>
       <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
-        <v>984696</v>
+        <v>972604</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4636,7 +4841,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="B12" s="30">
         <v>0</v>
@@ -4656,7 +4861,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="B13" s="30">
         <v>0</v>
@@ -4676,7 +4881,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="B14" s="31" t="str">
         <f>SUM(B12:B13)</f>
@@ -4701,7 +4906,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4711,50 +4916,50 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="B17" s="32">
         <f>B9-B14</f>
-        <v>67170</v>
+        <v>67463</v>
       </c>
       <c r="C17" s="32">
         <f>C9-C14</f>
-        <v>204962</v>
+        <v>203903</v>
       </c>
       <c r="D17" s="32">
         <f>D9-D14</f>
-        <v>420091</v>
+        <v>416642</v>
       </c>
       <c r="E17" s="32">
         <f>E9-E14</f>
-        <v>698221</v>
+        <v>691050</v>
       </c>
       <c r="F17" s="32">
         <f>F9-F14</f>
-        <v>984696</v>
+        <v>972604</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="B19" s="45" t="str">
+        <v>327</v>
+      </c>
+      <c r="B19" s="48" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="45" t="str">
+      <c r="C19" s="48" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="45" t="str">
+      <c r="D19" s="48" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="45" t="str">
+      <c r="E19" s="48" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="45" t="str">
+      <c r="F19" s="48" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -4776,7 +4981,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4785,7 +4990,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4798,24 +5003,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4825,27 +5030,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="B5" s="30">
         <v>184667</v>
       </c>
       <c r="C5" s="30">
-        <v>339797</v>
+        <v>339130</v>
       </c>
       <c r="D5" s="30">
-        <v>426588</v>
+        <v>424882</v>
       </c>
       <c r="E5" s="30">
-        <v>498557</v>
+        <v>495517</v>
       </c>
       <c r="F5" s="30">
-        <v>513513</v>
+        <v>509276</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B6" s="30">
         <v>118934</v>
@@ -4865,7 +5070,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B7" s="30">
         <v>40500</v>
@@ -4885,367 +5090,427 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="B8" s="33">
-        <f>B5-B6-B7</f>
         <v>25233</v>
       </c>
       <c r="C8" s="33">
-        <f>C5-C6-C7</f>
-        <v>137792</v>
+        <v>137125</v>
       </c>
       <c r="D8" s="33">
-        <f>D5-D6-D7</f>
-        <v>215128</v>
+        <v>213423</v>
       </c>
       <c r="E8" s="33">
-        <f>E5-E6-E7</f>
-        <v>278131</v>
+        <v>275091</v>
       </c>
       <c r="F8" s="33">
-        <f>F5-F6-F7</f>
-        <v>286475</v>
+        <v>282237</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="B9" s="30">
+        <v>714</v>
+      </c>
+      <c r="C9" s="30">
+        <v>714</v>
+      </c>
+      <c r="D9" s="30">
+        <v>714</v>
+      </c>
+      <c r="E9" s="30">
+        <v>714</v>
+      </c>
+      <c r="F9" s="30">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="B10" s="30">
         <v>0</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C10" s="30">
         <v>0</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D10" s="30">
         <v>0</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E10" s="30">
         <v>0</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F10" s="30">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>311</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>311</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>311</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>311</v>
-      </c>
-      <c r="F10" s="46" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B13" s="30">
-        <v>62170</v>
-      </c>
-      <c r="C13" s="30">
-        <v>199962</v>
-      </c>
-      <c r="D13" s="30">
-        <v>415091</v>
-      </c>
-      <c r="E13" s="30">
-        <v>693221</v>
-      </c>
-      <c r="F13" s="30">
-        <v>979696</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B14" s="47">
-        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
-        <v>142</v>
-      </c>
-      <c r="C14" s="47">
-        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
-        <v>361</v>
-      </c>
-      <c r="D14" s="47">
-        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
-        <v>716</v>
-      </c>
-      <c r="E14" s="47">
-        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
-        <v>1148</v>
-      </c>
-      <c r="F14" s="47">
-        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
-        <v>1575</v>
-      </c>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="B11" s="33">
+        <f>B8+B9+B10</f>
+        <v>25947</v>
+      </c>
+      <c r="C11" s="33">
+        <f>C8+C9+C10</f>
+        <v>137839</v>
+      </c>
+      <c r="D11" s="33">
+        <f>D8+D9+D10</f>
+        <v>214137</v>
+      </c>
+      <c r="E11" s="33">
+        <f>E8+E9+E10</f>
+        <v>275805</v>
+      </c>
+      <c r="F11" s="33">
+        <f>F8+F9+F10</f>
+        <v>282951</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>335</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>335</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>335</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>335</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="B15" s="34">
-        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
-        <v>4.7</v>
-      </c>
-      <c r="C15" s="34">
-        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
-        <v>11.9</v>
-      </c>
-      <c r="D15" s="34">
-        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
-        <v>23.6</v>
-      </c>
-      <c r="E15" s="34">
-        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
-        <v>37.7</v>
-      </c>
-      <c r="F15" s="34">
-        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
-        <v>51.8</v>
+        <v>337</v>
+      </c>
+      <c r="B15" s="30">
+        <v>62170</v>
+      </c>
+      <c r="C15" s="30">
+        <v>199295</v>
+      </c>
+      <c r="D15" s="30">
+        <v>412717</v>
+      </c>
+      <c r="E15" s="30">
+        <v>687808</v>
+      </c>
+      <c r="F15" s="30">
+        <v>970045</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="29">
+        <v>338</v>
+      </c>
+      <c r="B16" s="50">
+        <f>IF((B5-B8)=0,0,(B15/(B5-B8))*365)</f>
+        <v>142</v>
+      </c>
+      <c r="C16" s="50">
+        <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
+        <v>360</v>
+      </c>
+      <c r="D16" s="50">
+        <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
+        <v>712</v>
+      </c>
+      <c r="E16" s="50">
+        <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
+        <v>1139</v>
+      </c>
+      <c r="F16" s="50">
+        <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B17" s="34">
+        <f>IF((B5-B8)=0,0,B15/((B5-B8)/12))</f>
+        <v>4.7</v>
+      </c>
+      <c r="C17" s="34">
+        <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
+        <v>11.8</v>
+      </c>
+      <c r="D17" s="34">
+        <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
+        <v>23.4</v>
+      </c>
+      <c r="E17" s="34">
+        <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
+        <v>37.4</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" s="29">
         <v>0.48</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C18" s="29">
         <v>0.72</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D18" s="29">
         <v>0.88</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E18" s="29">
         <v>1</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F18" s="29">
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="B19" s="30">
-        <v>15389</v>
-      </c>
-      <c r="C19" s="30">
-        <v>18878</v>
-      </c>
-      <c r="D19" s="30">
-        <v>19390</v>
-      </c>
-      <c r="E19" s="30">
-        <v>19942</v>
-      </c>
-      <c r="F19" s="30">
-        <v>20541</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B20" s="30">
-        <v>118934</v>
-      </c>
-      <c r="C20" s="30">
-        <v>147003</v>
-      </c>
-      <c r="D20" s="30">
-        <v>151413</v>
-      </c>
-      <c r="E20" s="30">
-        <v>155955</v>
-      </c>
-      <c r="F20" s="30">
-        <v>160634</v>
-      </c>
+    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>318</v>
+        <v>239</v>
       </c>
       <c r="B21" s="30">
+        <v>15389</v>
+      </c>
+      <c r="C21" s="30">
+        <v>18841</v>
+      </c>
+      <c r="D21" s="30">
+        <v>19313</v>
+      </c>
+      <c r="E21" s="30">
+        <v>19821</v>
+      </c>
+      <c r="F21" s="30">
+        <v>20371</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="B22" s="30">
+        <v>118934</v>
+      </c>
+      <c r="C22" s="30">
+        <v>147003</v>
+      </c>
+      <c r="D22" s="30">
+        <v>151413</v>
+      </c>
+      <c r="E22" s="30">
+        <v>155955</v>
+      </c>
+      <c r="F22" s="30">
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B23" s="30">
         <v>3375</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C23" s="30">
         <v>3056</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D23" s="30">
         <v>2729</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E23" s="30">
         <v>2579</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F23" s="30">
         <v>2656</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="B22" s="48">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="B24" s="51">
         <v>10</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C24" s="51">
         <v>10</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D24" s="51">
         <v>10</v>
       </c>
-      <c r="E22" s="48">
-        <v>9</v>
-      </c>
-      <c r="F22" s="48">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>311</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>311</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>311</v>
-      </c>
-      <c r="E25" s="49" t="s">
-        <v>311</v>
-      </c>
-      <c r="F25" s="49" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="D26" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="F26" s="50" t="s">
-        <v>323</v>
-      </c>
+      <c r="E24" s="51">
+        <v>10</v>
+      </c>
+      <c r="F24" s="51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="B27" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="C27" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="D27" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="E27" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="F27" s="50" t="s">
-        <v>323</v>
+        <v>345</v>
+      </c>
+      <c r="B27" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="F27" s="52" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B28" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="C28" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="D28" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="E28" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="F28" s="50" t="s">
-        <v>323</v>
+        <v>346</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="B29" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="D29" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="E29" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="F29" s="50" t="s">
-        <v>323</v>
+        <v>348</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>350</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -5285,28 +5550,28 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
-        <v>328</v>
-      </c>
-      <c r="B3" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>329</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>112</v>
+      <c r="A3" s="55" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>354</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="B4" s="30">
         <v>20000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="E4" s="30">
         <v>15000</v>
@@ -5314,7 +5579,7 @@
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="11" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="E5" s="30">
         <v>5000</v>
@@ -5322,13 +5587,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="B7" s="32">
         <v>20000</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="E7" s="32">
         <v>20000</v>
@@ -5336,9 +5601,9 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="B8" s="45">
+        <v>360</v>
+      </c>
+      <c r="B8" s="48">
         <v>0</v>
       </c>
     </row>
@@ -5359,7 +5624,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C43"/>
+  <dimension ref="B3:C44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5625,18 +5890,26 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="14" t="s">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="14"/>
+      <c r="C41" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Instructions'!A1"/>
@@ -5661,6 +5934,7 @@
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
     <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
     <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
+    <hyperlink ref="C41" r:id="rId23" location="#'Budget Narrative'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5684,7 +5958,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5694,7 +5968,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -5704,7 +5978,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5712,44 +5986,44 @@
         <v>7</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="B6" s="30">
         <v>184667</v>
       </c>
       <c r="C6" s="30">
-        <v>339797</v>
+        <v>339130</v>
       </c>
       <c r="D6" s="30">
-        <v>426588</v>
+        <v>424882</v>
       </c>
       <c r="E6" s="30">
-        <v>498557</v>
+        <v>495517</v>
       </c>
       <c r="F6" s="30">
-        <v>513513</v>
+        <v>509276</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B7" s="30">
         <v>159434</v>
@@ -5769,87 +6043,87 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B8" s="32">
         <v>25233</v>
       </c>
       <c r="C8" s="32">
-        <v>137792</v>
+        <v>137125</v>
       </c>
       <c r="D8" s="32">
-        <v>215128</v>
+        <v>213423</v>
       </c>
       <c r="E8" s="32">
-        <v>278131</v>
+        <v>275091</v>
       </c>
       <c r="F8" s="32">
-        <v>286475</v>
+        <v>282237</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B9" s="29">
         <v>0.13663808664259927</v>
       </c>
       <c r="C9" s="29">
-        <v>0.40551379205819943</v>
+        <v>0.4043437853073026</v>
       </c>
       <c r="D9" s="29">
-        <v>0.5042999253916937</v>
+        <v>0.5023099573664649</v>
       </c>
       <c r="E9" s="29">
-        <v>0.5578717808219178</v>
+        <v>0.5551595361077036</v>
       </c>
       <c r="F9" s="29">
-        <v>0.5578717808219178</v>
+        <v>0.5541926962730911</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B10" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="C10" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="E10" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="F10" s="53" t="s">
-        <v>311</v>
+        <v>334</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="F10" s="56" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B11" s="47">
+        <v>343</v>
+      </c>
+      <c r="B11" s="50">
         <v>10</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="50">
         <v>10</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="50">
         <v>10</v>
       </c>
-      <c r="E11" s="47">
-        <v>9</v>
-      </c>
-      <c r="F11" s="47">
-        <v>9</v>
+      <c r="E11" s="50">
+        <v>10</v>
+      </c>
+      <c r="F11" s="50">
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -5859,7 +6133,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5867,44 +6141,44 @@
         <v>7</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="B16" s="30">
         <v>147733</v>
       </c>
       <c r="C16" s="30">
-        <v>271838</v>
+        <v>271304</v>
       </c>
       <c r="D16" s="30">
-        <v>341270</v>
+        <v>339906</v>
       </c>
       <c r="E16" s="30">
-        <v>398845</v>
+        <v>396414</v>
       </c>
       <c r="F16" s="30">
-        <v>410811</v>
+        <v>407420</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B17" s="30">
         <v>159434</v>
@@ -5924,81 +6198,81 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B18" s="32">
         <v>-11701</v>
       </c>
       <c r="C18" s="32">
-        <v>69833</v>
+        <v>69299</v>
       </c>
       <c r="D18" s="32">
-        <v>129811</v>
+        <v>128446</v>
       </c>
       <c r="E18" s="32">
-        <v>178419</v>
+        <v>175988</v>
       </c>
       <c r="F18" s="32">
-        <v>183772</v>
+        <v>180382</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B19" s="29">
         <v>-0.07920239169675096</v>
       </c>
       <c r="C19" s="29">
-        <v>0.2568922400727494</v>
+        <v>0.2554297316341282</v>
       </c>
       <c r="D19" s="29">
-        <v>0.38037490673961705</v>
+        <v>0.3778874467080811</v>
       </c>
       <c r="E19" s="29">
-        <v>0.4473397260273973</v>
+        <v>0.4439494201346296</v>
       </c>
       <c r="F19" s="29">
-        <v>0.44733972602739736</v>
+        <v>0.44274087034136395</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B20" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="D20" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="F20" s="53" t="s">
-        <v>311</v>
+        <v>334</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="D20" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="E20" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="F20" s="56" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B21" s="47">
+        <v>343</v>
+      </c>
+      <c r="B21" s="50">
         <v>12</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="50">
         <v>10</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="50">
         <v>10</v>
       </c>
-      <c r="E21" s="47">
+      <c r="E21" s="50">
         <v>10</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F21" s="50">
         <v>10</v>
       </c>
     </row>
@@ -6030,7 +6304,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6042,7 +6316,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B3" s="19"/>
     </row>
@@ -6056,7 +6330,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -6064,7 +6338,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6088,7 +6362,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6096,7 +6370,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6116,45 +6390,45 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="54" t="s">
+      <c r="D12" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="54" t="s">
+      <c r="E12" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="54" t="s">
+      <c r="F12" s="57" t="s">
         <v>106</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="D13" s="30">
         <v>184667</v>
       </c>
       <c r="E13" s="30">
-        <v>339797</v>
+        <v>339130</v>
       </c>
       <c r="F13" s="30">
-        <v>426588</v>
+        <v>424882</v>
       </c>
       <c r="G13" s="30">
-        <v>498557</v>
+        <v>495517</v>
       </c>
       <c r="H13" s="30">
-        <v>513513</v>
+        <v>509276</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D14" s="30">
         <v>159434</v>
@@ -6174,47 +6448,47 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="D15" s="30">
         <v>25233</v>
       </c>
       <c r="E15" s="30">
-        <v>137792</v>
+        <v>137125</v>
       </c>
       <c r="F15" s="30">
-        <v>215128</v>
+        <v>213423</v>
       </c>
       <c r="G15" s="30">
-        <v>278131</v>
+        <v>275091</v>
       </c>
       <c r="H15" s="30">
-        <v>286475</v>
+        <v>282237</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="D16" s="30">
         <v>62170</v>
       </c>
       <c r="E16" s="30">
-        <v>199962</v>
+        <v>199295</v>
       </c>
       <c r="F16" s="30">
-        <v>415091</v>
+        <v>412717</v>
       </c>
       <c r="G16" s="30">
-        <v>693221</v>
+        <v>687808</v>
       </c>
       <c r="H16" s="30">
-        <v>979696</v>
+        <v>970045</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="D17" s="30">
         <v>0</v>
@@ -6234,7 +6508,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -6254,65 +6528,65 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="54" t="s">
+      <c r="D20" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="54" t="s">
+      <c r="E20" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="54" t="s">
+      <c r="F20" s="57" t="s">
         <v>106</v>
+      </c>
+      <c r="G20" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="D21" s="29">
         <v>0.13663808664259927</v>
       </c>
       <c r="E21" s="29">
-        <v>0.40551379205819943</v>
+        <v>0.4043437853073026</v>
       </c>
       <c r="F21" s="29">
-        <v>0.5042999253916937</v>
+        <v>0.5023099573664649</v>
       </c>
       <c r="G21" s="29">
-        <v>0.5578717808219178</v>
+        <v>0.5551595361077036</v>
       </c>
       <c r="H21" s="29">
-        <v>0.5578717808219178</v>
+        <v>0.5541926962730911</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="F22" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="G22" s="53" t="s">
-        <v>311</v>
-      </c>
-      <c r="H22" s="53" t="s">
-        <v>311</v>
+        <v>334</v>
+      </c>
+      <c r="D22" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="E22" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="F22" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="G22" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="H22" s="56" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D23" s="29">
         <v>0.48</v>
@@ -6332,27 +6606,27 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="D24" s="47">
+        <v>374</v>
+      </c>
+      <c r="D24" s="50">
         <v>12</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E24" s="50">
         <v>18</v>
       </c>
-      <c r="F24" s="47">
+      <c r="F24" s="50">
         <v>22</v>
       </c>
-      <c r="G24" s="47">
+      <c r="G24" s="50">
         <v>25</v>
       </c>
-      <c r="H24" s="47">
+      <c r="H24" s="50">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -6393,7 +6667,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6403,645 +6677,645 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="55" t="s">
-        <v>352</v>
-      </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
+      <c r="B3" s="58" t="s">
+        <v>377</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="56" t="s">
-        <v>353</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>354</v>
-      </c>
-      <c r="F4" s="58" t="s">
-        <v>355</v>
+      <c r="B4" s="59" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>379</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>357</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>358</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>359</v>
-      </c>
-      <c r="F6" s="59" t="s">
-        <v>360</v>
-      </c>
-      <c r="G6" s="59" t="s">
-        <v>361</v>
-      </c>
-      <c r="H6" s="59" t="s">
-        <v>362</v>
+        <v>381</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>382</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>383</v>
+      </c>
+      <c r="E6" s="62" t="s">
+        <v>384</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>385</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>386</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="C7" s="60">
+        <v>374</v>
+      </c>
+      <c r="C7" s="63">
         <v>12</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="63">
         <v>18</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="63">
         <v>22</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="63">
         <v>25</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="63">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="C8" s="61">
+        <v>330</v>
+      </c>
+      <c r="C8" s="64">
         <v>184666.6666666667</v>
       </c>
-      <c r="D8" s="61">
-        <v>339797</v>
-      </c>
-      <c r="E8" s="61">
-        <v>426587.88999999996</v>
-      </c>
-      <c r="F8" s="61">
-        <v>498556.69375000003</v>
-      </c>
-      <c r="G8" s="61">
-        <v>513513.3945625001</v>
+      <c r="D8" s="64">
+        <v>339129.56</v>
+      </c>
+      <c r="E8" s="64">
+        <v>424882.21741599997</v>
+      </c>
+      <c r="F8" s="64">
+        <v>495516.93485413</v>
+      </c>
+      <c r="G8" s="64">
+        <v>509275.55642087164</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="C9" s="61">
+        <v>292</v>
+      </c>
+      <c r="C9" s="64">
         <v>118934.16666666667</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="64">
         <v>147002.63</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="64">
         <v>151412.7089</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="64">
         <v>155955.090167</v>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="64">
         <v>160633.74287201</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" s="61">
+        <v>293</v>
+      </c>
+      <c r="C10" s="64">
         <v>40500</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="64">
         <v>55002</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="64">
         <v>60046.93999999999</v>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="64">
         <v>64470.893</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="64">
         <v>66405.01979</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="61">
+        <v>294</v>
+      </c>
+      <c r="C11" s="64">
         <v>0</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="64">
         <v>0</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="64">
         <v>0</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="64">
         <v>0</v>
       </c>
-      <c r="G11" s="61">
+      <c r="G11" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="62">
+        <v>273</v>
+      </c>
+      <c r="C12" s="65">
         <v>25232.5</v>
       </c>
-      <c r="D12" s="62">
-        <v>137792.37</v>
-      </c>
-      <c r="E12" s="62">
-        <v>215128.24109999998</v>
-      </c>
-      <c r="F12" s="62">
-        <v>278130.71058300004</v>
-      </c>
-      <c r="G12" s="62">
-        <v>286474.6319004901</v>
+      <c r="D12" s="65">
+        <v>137124.93</v>
+      </c>
+      <c r="E12" s="65">
+        <v>213422.568516</v>
+      </c>
+      <c r="F12" s="65">
+        <v>275090.95168713003</v>
+      </c>
+      <c r="G12" s="65">
+        <v>282236.7937588616</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="C13" s="62">
+        <v>337</v>
+      </c>
+      <c r="C13" s="65">
         <v>62170</v>
       </c>
-      <c r="D13" s="62">
-        <v>199962.37</v>
-      </c>
-      <c r="E13" s="62">
-        <v>415090.6111</v>
-      </c>
-      <c r="F13" s="62">
-        <v>693221.3216830001</v>
-      </c>
-      <c r="G13" s="62">
-        <v>979695.9535834901</v>
+      <c r="D13" s="65">
+        <v>199294.93</v>
+      </c>
+      <c r="E13" s="65">
+        <v>412717.498516</v>
+      </c>
+      <c r="F13" s="65">
+        <v>687808.45020313</v>
+      </c>
+      <c r="G13" s="65">
+        <v>970045.2439619916</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="C14" s="63">
+        <v>373</v>
+      </c>
+      <c r="C14" s="66">
         <v>0.13663808664259927</v>
       </c>
-      <c r="D14" s="63">
-        <v>0.40551379205819943</v>
-      </c>
-      <c r="E14" s="63">
-        <v>0.5042999253916937</v>
-      </c>
-      <c r="F14" s="63">
-        <v>0.5578717808219178</v>
-      </c>
-      <c r="G14" s="63">
-        <v>0.5578717808219178</v>
+      <c r="D14" s="66">
+        <v>0.4043437853073026</v>
+      </c>
+      <c r="E14" s="66">
+        <v>0.5023099573664649</v>
+      </c>
+      <c r="F14" s="66">
+        <v>0.5551595361077036</v>
+      </c>
+      <c r="G14" s="66">
+        <v>0.5541926962730911</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C15" s="64">
+        <v>239</v>
+      </c>
+      <c r="C15" s="67">
         <v>15388.88888888889</v>
       </c>
-      <c r="D15" s="64">
-        <v>18877.61111111111</v>
-      </c>
-      <c r="E15" s="64">
-        <v>19390.358636363635</v>
-      </c>
-      <c r="F15" s="64">
-        <v>19942.267750000003</v>
-      </c>
-      <c r="G15" s="64">
-        <v>20540.535782500006</v>
-      </c>
-      <c r="H15" s="65" t="s">
-        <v>363</v>
+      <c r="D15" s="67">
+        <v>18840.53111111111</v>
+      </c>
+      <c r="E15" s="67">
+        <v>19312.828064363635</v>
+      </c>
+      <c r="F15" s="67">
+        <v>19820.677394165203</v>
+      </c>
+      <c r="G15" s="67">
+        <v>20371.022256834865</v>
+      </c>
+      <c r="H15" s="68" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="C16" s="66">
+        <v>276</v>
+      </c>
+      <c r="C16" s="69">
         <v>13286.180555555557</v>
       </c>
-      <c r="D16" s="66">
+      <c r="D16" s="69">
         <v>11222.479444444445</v>
       </c>
-      <c r="E16" s="66">
+      <c r="E16" s="69">
         <v>9611.802222727272</v>
       </c>
-      <c r="F16" s="66">
+      <c r="F16" s="69">
         <v>8817.03932668</v>
       </c>
-      <c r="G16" s="66">
+      <c r="G16" s="69">
         <v>9081.550506480402</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="C17" s="61">
+        <v>389</v>
+      </c>
+      <c r="C17" s="64">
         <v>500</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="64">
         <v>515</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="64">
         <v>530.4499999999999</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="64">
         <v>546.3635</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="64">
         <v>562.754405</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="C18" s="67">
+        <v>390</v>
+      </c>
+      <c r="C18" s="70">
         <v>3000</v>
       </c>
-      <c r="D18" s="67">
+      <c r="D18" s="70">
         <v>2060</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="67">
         <v>1736.0181818181816</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="67">
         <v>1573.52688</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="67">
         <v>1620.7326864000001</v>
       </c>
-      <c r="H18" s="65" t="s">
-        <v>366</v>
+      <c r="H18" s="68" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="C19" s="68">
+        <v>392</v>
+      </c>
+      <c r="C19" s="71">
         <v>2102.7083333333335</v>
       </c>
-      <c r="D19" s="68">
-        <v>7655.131666666666</v>
-      </c>
-      <c r="E19" s="68">
-        <v>9778.556413636363</v>
-      </c>
-      <c r="F19" s="68">
-        <v>11125.22842332</v>
-      </c>
-      <c r="G19" s="68">
-        <v>11458.985276019603</v>
+      <c r="D19" s="71">
+        <v>7618.051666666666</v>
+      </c>
+      <c r="E19" s="71">
+        <v>9701.025841636363</v>
+      </c>
+      <c r="F19" s="71">
+        <v>11003.6380674852</v>
+      </c>
+      <c r="G19" s="71">
+        <v>11289.471750354463</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="C20" s="69">
+        <v>393</v>
+      </c>
+      <c r="C20" s="72">
         <v>0.644047833935018</v>
       </c>
-      <c r="D20" s="63">
-        <v>0.4326189754471052</v>
-      </c>
-      <c r="E20" s="63">
-        <v>0.3549390698831137</v>
-      </c>
-      <c r="F20" s="63">
-        <v>0.3128131506849315</v>
-      </c>
-      <c r="G20" s="63">
-        <v>0.3128131506849315</v>
-      </c>
-      <c r="H20" s="65" t="s">
-        <v>369</v>
+      <c r="D20" s="66">
+        <v>0.43347041172111334</v>
+      </c>
+      <c r="E20" s="66">
+        <v>0.35636395851265434</v>
+      </c>
+      <c r="F20" s="66">
+        <v>0.314732109434181</v>
+      </c>
+      <c r="G20" s="66">
+        <v>0.31541616487727187</v>
+      </c>
+      <c r="H20" s="68" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="C21" s="69">
+        <v>395</v>
+      </c>
+      <c r="C21" s="72">
         <v>0.19494584837545123</v>
       </c>
-      <c r="D21" s="63">
-        <v>0.10912397696271597</v>
-      </c>
-      <c r="E21" s="63">
-        <v>0.0895299676697339</v>
-      </c>
-      <c r="F21" s="63">
-        <v>0.0789041095890411</v>
-      </c>
-      <c r="G21" s="63">
-        <v>0.0789041095890411</v>
-      </c>
-      <c r="H21" s="65" t="s">
-        <v>371</v>
+      <c r="D21" s="66">
+        <v>0.10933874357634882</v>
+      </c>
+      <c r="E21" s="66">
+        <v>0.0898893821263553</v>
+      </c>
+      <c r="F21" s="66">
+        <v>0.07938814848291784</v>
+      </c>
+      <c r="G21" s="66">
+        <v>0.07956069489130392</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="C22" s="63">
+        <v>397</v>
+      </c>
+      <c r="C22" s="66">
         <v>0.13663808664259935</v>
       </c>
-      <c r="D22" s="63">
-        <v>0.40551379205819943</v>
-      </c>
-      <c r="E22" s="63">
-        <v>0.5042999253916934</v>
-      </c>
-      <c r="F22" s="63">
-        <v>0.5578717808219178</v>
-      </c>
-      <c r="G22" s="63">
-        <v>0.5578717808219178</v>
-      </c>
-      <c r="H22" s="65" t="s">
-        <v>373</v>
+      <c r="D22" s="66">
+        <v>0.4043437853073026</v>
+      </c>
+      <c r="E22" s="66">
+        <v>0.5023099573664649</v>
+      </c>
+      <c r="F22" s="66">
+        <v>0.5551595361077037</v>
+      </c>
+      <c r="G22" s="66">
+        <v>0.5541926962730912</v>
+      </c>
+      <c r="H22" s="68" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="C23" s="70">
+        <v>399</v>
+      </c>
+      <c r="C23" s="73">
         <v>3</v>
       </c>
-      <c r="D23" s="70">
+      <c r="D23" s="73">
         <v>3</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E23" s="73">
         <v>3</v>
       </c>
-      <c r="F23" s="70">
+      <c r="F23" s="73">
         <v>3</v>
       </c>
-      <c r="G23" s="70">
+      <c r="G23" s="73">
         <v>3</v>
       </c>
-      <c r="H23" s="65" t="s">
-        <v>375</v>
+      <c r="H23" s="68" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="C24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="D24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="E24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="F24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="G24" s="71" t="s">
-        <v>311</v>
-      </c>
-      <c r="H24" s="65" t="s">
-        <v>311</v>
+        <v>334</v>
+      </c>
+      <c r="C24" s="74" t="s">
+        <v>335</v>
+      </c>
+      <c r="D24" s="74" t="s">
+        <v>335</v>
+      </c>
+      <c r="E24" s="74" t="s">
+        <v>335</v>
+      </c>
+      <c r="F24" s="74" t="s">
+        <v>335</v>
+      </c>
+      <c r="G24" s="74" t="s">
+        <v>335</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="39" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>401</v>
+      </c>
+      <c r="C25" s="42" t="str">
+        <f>IF('5-Year Operating Stmt'!B17&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+      <c r="D25" s="75" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C17&gt;=0,'5-Year Operating Stmt'!B17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+      <c r="E25" s="75" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D17&gt;=0,'5-Year Operating Stmt'!C17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+      <c r="F25" s="75" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E17&gt;=0,'5-Year Operating Stmt'!D17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+      <c r="G25" s="75" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="65" t="s">
-        <v>357</v>
+      <c r="H25" s="68" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="C26" s="73">
+        <v>402</v>
+      </c>
+      <c r="C26" s="76">
         <v>5</v>
       </c>
-      <c r="D26" s="74">
+      <c r="D26" s="77">
         <v>12</v>
       </c>
-      <c r="E26" s="70">
-        <v>24</v>
-      </c>
-      <c r="F26" s="70">
-        <v>38</v>
-      </c>
-      <c r="G26" s="70">
-        <v>52</v>
-      </c>
-      <c r="H26" s="65" t="s">
-        <v>378</v>
+      <c r="E26" s="77">
+        <v>23</v>
+      </c>
+      <c r="F26" s="73">
+        <v>37</v>
+      </c>
+      <c r="G26" s="73">
+        <v>51</v>
+      </c>
+      <c r="H26" s="68" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="C27" s="70">
+        <v>338</v>
+      </c>
+      <c r="C27" s="73">
         <v>142</v>
       </c>
-      <c r="D27" s="70">
-        <v>361</v>
-      </c>
-      <c r="E27" s="70">
-        <v>716</v>
-      </c>
-      <c r="F27" s="70">
-        <v>1148</v>
-      </c>
-      <c r="G27" s="70">
-        <v>1575</v>
-      </c>
-      <c r="H27" s="65" t="s">
-        <v>379</v>
+      <c r="D27" s="73">
+        <v>360</v>
+      </c>
+      <c r="E27" s="73">
+        <v>712</v>
+      </c>
+      <c r="F27" s="73">
+        <v>1139</v>
+      </c>
+      <c r="G27" s="73">
+        <v>1559</v>
+      </c>
+      <c r="H27" s="68" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="41" t="s">
-        <v>384</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>386</v>
-      </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
-        <v>387</v>
-      </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
+      <c r="B30" s="44" t="s">
+        <v>409</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="D30" s="78" t="s">
+        <v>411</v>
+      </c>
+      <c r="E30" s="78"/>
+      <c r="F30" s="79" t="s">
+        <v>412</v>
+      </c>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="41" t="s">
-        <v>388</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D31" s="75" t="s">
-        <v>389</v>
-      </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
-        <v>390</v>
-      </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
+      <c r="B31" s="44" t="s">
+        <v>413</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="D31" s="78" t="s">
+        <v>414</v>
+      </c>
+      <c r="E31" s="78"/>
+      <c r="F31" s="79" t="s">
+        <v>415</v>
+      </c>
+      <c r="G31" s="79"/>
+      <c r="H31" s="79"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="41" t="s">
-        <v>391</v>
-      </c>
-      <c r="C32" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D32" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
+      <c r="B32" s="44" t="s">
+        <v>416</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="D32" s="78" t="s">
+        <v>417</v>
+      </c>
+      <c r="E32" s="78"/>
+      <c r="F32" s="79" t="s">
+        <v>418</v>
+      </c>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="41" t="s">
-        <v>394</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D33" s="75" t="s">
-        <v>395</v>
-      </c>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76" t="s">
-        <v>396</v>
-      </c>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
+      <c r="B33" s="44" t="s">
+        <v>419</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="D33" s="78" t="s">
+        <v>420</v>
+      </c>
+      <c r="E33" s="78"/>
+      <c r="F33" s="79" t="s">
+        <v>421</v>
+      </c>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="41" t="s">
-        <v>397</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D34" s="75" t="s">
-        <v>398</v>
-      </c>
-      <c r="E34" s="75"/>
-      <c r="F34" s="76" t="s">
-        <v>399</v>
-      </c>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
+      <c r="B34" s="44" t="s">
+        <v>422</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="D34" s="78" t="s">
+        <v>423</v>
+      </c>
+      <c r="E34" s="78"/>
+      <c r="F34" s="79" t="s">
+        <v>424</v>
+      </c>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="41" t="s">
-        <v>400</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="D35" s="75" t="s">
-        <v>401</v>
-      </c>
-      <c r="E35" s="75"/>
-      <c r="F35" s="76" t="s">
-        <v>402</v>
-      </c>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
+      <c r="B35" s="44" t="s">
+        <v>425</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="D35" s="78" t="s">
+        <v>426</v>
+      </c>
+      <c r="E35" s="78"/>
+      <c r="F35" s="79" t="s">
+        <v>427</v>
+      </c>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="41" t="s">
-        <v>403</v>
+      <c r="B37" s="44" t="s">
+        <v>428</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="77" t="s">
-        <v>405</v>
-      </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="B39" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7149,12 +7423,225 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="21"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="B3" s="19"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="B4" s="81"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="B7" s="81"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="B9" s="19"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="B10" s="81"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="B12" s="19"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="B13" s="81"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="B15" s="19"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="B16" s="81"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="B18" s="19"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="B19" s="81"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="B21" s="19"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="B22" s="81"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="B24" s="19"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="B25" s="81"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="B27" s="19"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="B28" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A28:B28"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="82" t="s">
+        <v>442</v>
+      </c>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="83" t="s">
+        <v>443</v>
+      </c>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -7164,7 +7651,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7178,18 +7665,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -7232,10 +7719,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7256,7 +7743,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="20">
         <v>7</v>
@@ -7264,7 +7751,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="20">
         <v>25</v>
@@ -7272,7 +7759,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -7286,24 +7773,24 @@
         <v>7</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B17" s="22">
         <v>12</v>
@@ -7323,7 +7810,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7332,32 +7819,35 @@
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D21" s="23">
         <v>12000</v>
@@ -7365,16 +7855,19 @@
       <c r="E21" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D22" s="23">
         <v>250</v>
@@ -7382,16 +7875,19 @@
       <c r="E22" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>116</v>
       </c>
       <c r="D23" s="23">
         <v>7000</v>
@@ -7399,16 +7895,19 @@
       <c r="E23" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D24" s="23">
         <v>5000</v>
@@ -7416,16 +7915,19 @@
       <c r="E24" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D25" s="23">
         <v>10</v>
@@ -7433,10 +7935,13 @@
       <c r="E25" s="24">
         <v>0</v>
       </c>
+      <c r="F25" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
@@ -7447,36 +7952,36 @@
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D29" s="25">
         <v>1</v>
@@ -7493,13 +7998,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D30" s="25">
         <v>1</v>
@@ -7516,13 +8021,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D31" s="25">
         <v>0.5</v>
@@ -7539,7 +8044,7 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -7550,30 +8055,30 @@
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D35" s="23">
         <v>2500</v>
@@ -7584,13 +8089,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D36" s="23">
         <v>300</v>
@@ -7601,13 +8106,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D37" s="23">
         <v>2400</v>
@@ -7618,13 +8123,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D38" s="23">
         <v>500</v>
@@ -7635,13 +8140,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D39" s="23">
         <v>300</v>
@@ -7652,13 +8157,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D40" s="23">
         <v>3000</v>
@@ -7669,7 +8174,7 @@
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
@@ -7680,27 +8185,27 @@
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C44" s="23">
         <v>30000</v>
@@ -7714,7 +8219,7 @@
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -7725,29 +8230,29 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B47" s="24">
         <v>0.03</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B48" s="24">
         <v>0.03</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B49" s="25">
         <v>0.8333333333333334</v>
@@ -7755,7 +8260,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B50" s="23">
         <v>0</v>
@@ -7763,10 +8268,101 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>165</v>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B55" s="24">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B56" s="24">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B57" s="24">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B62" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -7801,10 +8397,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7825,10 +8421,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7841,7 +8437,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -7849,66 +8445,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -7951,24 +8547,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -7978,7 +8574,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B6" s="27">
         <v>12</v>
@@ -7998,7 +8594,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="22">
         <v>25</v>
@@ -8006,7 +8602,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B8" s="28">
         <f>B6/$B$7</f>
@@ -8031,10 +8627,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="C10" s="29">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
@@ -8079,7 +8675,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8092,24 +8688,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8119,7 +8715,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B5" s="30">
         <v>144000</v>
@@ -8139,7 +8735,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B6" s="30">
         <v>3000</v>
@@ -8159,7 +8755,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B7" s="31">
         <f>SUM(B5,B6)</f>
@@ -8184,7 +8780,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -8194,7 +8790,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B9" s="30">
         <v>-10</v>
@@ -8214,7 +8810,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B10" s="31">
         <f>SUM(B9)</f>
@@ -8239,7 +8835,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -8249,7 +8845,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B12" s="30">
         <v>84000</v>
@@ -8269,7 +8865,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B13" s="31">
         <f>SUM(B12)</f>
@@ -8294,7 +8890,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -8304,7 +8900,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B15" s="23">
         <v>5000</v>
@@ -8324,7 +8920,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B16" s="31">
         <f>SUM(B15)</f>
@@ -8349,7 +8945,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B18" s="32">
         <f>SUM(B7,B10,B13,B16)</f>
@@ -8357,19 +8953,19 @@
       </c>
       <c r="C18" s="32">
         <f>SUM(C7,C10,C13,C16)</f>
-        <v>339797</v>
+        <v>339130</v>
       </c>
       <c r="D18" s="32">
         <f>SUM(D7,D10,D13,D16)</f>
-        <v>426588</v>
+        <v>424882</v>
       </c>
       <c r="E18" s="32">
         <f>SUM(E7,E10,E13,E16)</f>
-        <v>498557</v>
+        <v>495517</v>
       </c>
       <c r="F18" s="32">
         <f>SUM(F7,F10,F13,F16)</f>
-        <v>513513</v>
+        <v>509276</v>
       </c>
     </row>
   </sheetData>
@@ -8389,7 +8985,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -8398,9 +8994,10 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>61</v>
       </c>
@@ -8410,36 +9007,40 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C4" s="25">
         <v>1</v>
@@ -8456,13 +9057,16 @@
       <c r="G4" s="33">
         <v>70208</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C5" s="25">
         <v>1</v>
@@ -8479,13 +9083,16 @@
       <c r="G5" s="33">
         <v>57443</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C6" s="25">
         <v>0.5</v>
@@ -8502,10 +9109,13 @@
       <c r="G6" s="33">
         <v>15071</v>
       </c>
+      <c r="H6" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -8519,24 +9129,24 @@
         <v>7</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B10" s="32">
         <v>118934</v>
@@ -8556,27 +9166,27 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B11" s="29">
         <v>0.5367065282791817</v>
       </c>
       <c r="C11" s="29">
-        <v>0.4326189754471052</v>
+        <v>0.43347041172111334</v>
       </c>
       <c r="D11" s="29">
-        <v>0.3549390698831137</v>
+        <v>0.35636395851265434</v>
       </c>
       <c r="E11" s="29">
-        <v>0.3128131506849315</v>
+        <v>0.314732109434181</v>
       </c>
       <c r="F11" s="29">
-        <v>0.3128131506849315</v>
+        <v>0.31541616487727187</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B12" s="34">
         <v>4.8</v>
@@ -8596,7 +9206,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -8620,7 +9230,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8633,24 +9243,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8660,7 +9270,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B5" s="30">
         <v>6000</v>
@@ -8680,7 +9290,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
@@ -8705,7 +9315,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -8715,7 +9325,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B8" s="30">
         <v>3600</v>
@@ -8735,7 +9345,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -8760,7 +9370,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -8770,7 +9380,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B11" s="30">
         <v>30000</v>
@@ -8790,7 +9400,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B12" s="30">
         <v>3600</v>
@@ -8810,7 +9420,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B13" s="30">
         <v>2400</v>
@@ -8830,7 +9440,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B11:B13)</f>
@@ -8855,7 +9465,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -8865,7 +9475,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="B16" s="30">
         <v>3000</v>
@@ -8885,7 +9495,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B17" s="31">
         <f>SUM(B16:B16)</f>
@@ -8910,7 +9520,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B19" s="32">
         <f>B6+B9+B14+B17</f>
@@ -8960,7 +9570,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8970,30 +9580,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C4" s="23">
         <v>30000</v>
@@ -9010,7 +9620,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="F6" s="32">
         <v>6960</v>
@@ -9018,7 +9628,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="F7" s="31">
         <v>30000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -27,14 +27,15 @@
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
+    <sheet sheetId="24" name="Assumptions Memo" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Decision History" state="visible" r:id="rId28"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="447">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -42,7 +43,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · llc_single</t>
+    <t>Generated May 1, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -162,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1167,7 +1168,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1357,6 +1358,15 @@
   </si>
   <si>
     <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Assumptions Memo</t>
+  </si>
+  <si>
+    <t>Founder-supplied reasoning for each assumption captured during the wizard. Empty when no rationale was entered for that area.</t>
+  </si>
+  <si>
+    <t>No founder rationale captured.</t>
   </si>
   <si>
     <t>Decision History</t>
@@ -1379,7 +1389,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1537,6 +1547,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1637,7 +1652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1778,6 +1793,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -7573,6 +7592,54 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="82" t="s">
+        <v>442</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="83" t="s">
+        <v>443</v>
+      </c>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7591,7 +7658,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="15" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -7601,26 +7668,26 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
-        <v>442</v>
-      </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
+      <c r="B2" s="84" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="83" t="s">
-        <v>443</v>
-      </c>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
+      <c r="B4" s="85" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -43,7 +43,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · llc_single</t>
+    <t>Generated May 7, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -163,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1168,7 +1168,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1273,7 +1273,7 @@
     <t>The model reaches profit early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1288,7 +1288,7 @@
     <t>Staffing Burden</t>
   </si>
   <si>
-    <t>Staffing at 32% of revenue leaves room for facilities, programs, and reserves.</t>
+    <t>Staffing at 31% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
     <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
@@ -1315,7 +1315,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>51.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>52.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -3085,19 +3085,19 @@
       </c>
       <c r="C10" s="31">
         <f>SUM(C5:C9)</f>
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D10" s="31">
         <f>SUM(D5:D9)</f>
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E10" s="31">
         <f>SUM(E5:E9)</f>
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F10" s="31">
         <f>SUM(F5:F9)</f>
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3494,19 +3494,19 @@
       </c>
       <c r="C4" s="33">
         <f>'Budget Detail'!C10</f>
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D4" s="33">
         <f>'Budget Detail'!D10</f>
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E4" s="33">
         <f>'Budget Detail'!E10</f>
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F4" s="33">
         <f>'Budget Detail'!F10</f>
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3625,23 +3625,23 @@
       </c>
       <c r="B11" s="32">
         <f>B4-B8</f>
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="C11" s="32">
         <f>C4-C8</f>
-        <v>137125</v>
+        <v>138507</v>
       </c>
       <c r="D11" s="32">
         <f>D4-D8</f>
-        <v>213423</v>
+        <v>216486</v>
       </c>
       <c r="E11" s="32">
         <f>E4-E8</f>
-        <v>275091</v>
+        <v>280092</v>
       </c>
       <c r="F11" s="32">
         <f>F4-F8</f>
-        <v>282237</v>
+        <v>289046</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3654,19 +3654,19 @@
       </c>
       <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.40434379</v>
+        <v>0.40676208</v>
       </c>
       <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.50230996</v>
+        <v>0.50587283</v>
       </c>
       <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.55515954</v>
+        <v>0.55960384</v>
       </c>
       <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.5541927</v>
+        <v>0.56007487</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3674,19 +3674,19 @@
         <v>275</v>
       </c>
       <c r="B13" s="30">
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="C13" s="30">
-        <v>162357</v>
+        <v>163740</v>
       </c>
       <c r="D13" s="30">
-        <v>375780</v>
+        <v>380226</v>
       </c>
       <c r="E13" s="30">
-        <v>650871</v>
+        <v>660318</v>
       </c>
       <c r="F13" s="30">
-        <v>933108</v>
+        <v>949364</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3697,16 +3697,16 @@
         <v>15389</v>
       </c>
       <c r="C14" s="30">
-        <v>18841</v>
+        <v>18917</v>
       </c>
       <c r="D14" s="30">
-        <v>19313</v>
+        <v>19452</v>
       </c>
       <c r="E14" s="30">
-        <v>19821</v>
+        <v>20021</v>
       </c>
       <c r="F14" s="30">
-        <v>20371</v>
+        <v>20643</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4360,16 +4360,16 @@
         <v>184667</v>
       </c>
       <c r="C5" s="31">
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D5" s="31">
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E5" s="31">
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F5" s="31">
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4507,19 +4507,19 @@
       </c>
       <c r="C15" s="32">
         <f>C5-C12</f>
-        <v>136411</v>
+        <v>137793</v>
       </c>
       <c r="D15" s="32">
         <f>D5-D12</f>
-        <v>212708</v>
+        <v>215772</v>
       </c>
       <c r="E15" s="32">
         <f>E5-E12</f>
-        <v>274377</v>
+        <v>279377</v>
       </c>
       <c r="F15" s="32">
         <f>F5-F12</f>
-        <v>281523</v>
+        <v>288332</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4532,19 +4532,19 @@
       </c>
       <c r="C16" s="29">
         <f>IF(C5=0,0,C15/C5)</f>
-        <v>0.40223755</v>
+        <v>0.4046644</v>
       </c>
       <c r="D16" s="29">
         <f>IF(D5=0,0,D15/D5)</f>
-        <v>0.50062882</v>
+        <v>0.50420372</v>
       </c>
       <c r="E16" s="29">
         <f>IF(E5=0,0,E15/E5)</f>
-        <v>0.55371804</v>
+        <v>0.55817675</v>
       </c>
       <c r="F16" s="29">
         <f>IF(F5=0,0,F15/F5)</f>
-        <v>0.55279014</v>
+        <v>0.55869082</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4557,19 +4557,19 @@
       </c>
       <c r="C17" s="33">
         <f>B17+C15</f>
-        <v>160929</v>
+        <v>162311</v>
       </c>
       <c r="D17" s="33">
         <f>C17+D15</f>
-        <v>373637</v>
+        <v>378083</v>
       </c>
       <c r="E17" s="33">
         <f>D17+E15</f>
-        <v>648014</v>
+        <v>657460</v>
       </c>
       <c r="F17" s="33">
         <f>E17+F15</f>
-        <v>929536</v>
+        <v>945792</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4748,19 +4748,19 @@
       </c>
       <c r="C5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15</f>
-        <v>199295</v>
+        <v>200677</v>
       </c>
       <c r="D5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
-        <v>412717</v>
+        <v>417164</v>
       </c>
       <c r="E5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
-        <v>687808</v>
+        <v>697255</v>
       </c>
       <c r="F5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
-        <v>970045</v>
+        <v>986301</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4833,19 +4833,19 @@
       </c>
       <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
-        <v>203903</v>
+        <v>205285</v>
       </c>
       <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
-        <v>416642</v>
+        <v>421088</v>
       </c>
       <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
-        <v>691050</v>
+        <v>700496</v>
       </c>
       <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
-        <v>972604</v>
+        <v>988860</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4943,19 +4943,19 @@
       </c>
       <c r="C17" s="32">
         <f>C9-C14</f>
-        <v>203903</v>
+        <v>205285</v>
       </c>
       <c r="D17" s="32">
         <f>D9-D14</f>
-        <v>416642</v>
+        <v>421088</v>
       </c>
       <c r="E17" s="32">
         <f>E9-E14</f>
-        <v>691050</v>
+        <v>700496</v>
       </c>
       <c r="F17" s="32">
         <f>F9-F14</f>
-        <v>972604</v>
+        <v>988860</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5055,16 +5055,16 @@
         <v>184667</v>
       </c>
       <c r="C5" s="30">
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D5" s="30">
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E5" s="30">
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F5" s="30">
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5112,19 +5112,19 @@
         <v>273</v>
       </c>
       <c r="B8" s="33">
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="C8" s="33">
-        <v>137125</v>
+        <v>138507</v>
       </c>
       <c r="D8" s="33">
-        <v>213423</v>
+        <v>216486</v>
       </c>
       <c r="E8" s="33">
-        <v>275091</v>
+        <v>280092</v>
       </c>
       <c r="F8" s="33">
-        <v>282237</v>
+        <v>289046</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5177,19 +5177,19 @@
       </c>
       <c r="C11" s="33">
         <f>C8+C9+C10</f>
-        <v>137839</v>
+        <v>139222</v>
       </c>
       <c r="D11" s="33">
         <f>D8+D9+D10</f>
-        <v>214137</v>
+        <v>217200</v>
       </c>
       <c r="E11" s="33">
         <f>E8+E9+E10</f>
-        <v>275805</v>
+        <v>280806</v>
       </c>
       <c r="F11" s="33">
         <f>F8+F9+F10</f>
-        <v>282951</v>
+        <v>289761</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5230,16 +5230,16 @@
         <v>62170</v>
       </c>
       <c r="C15" s="30">
-        <v>199295</v>
+        <v>200677</v>
       </c>
       <c r="D15" s="30">
-        <v>412717</v>
+        <v>417164</v>
       </c>
       <c r="E15" s="30">
-        <v>687808</v>
+        <v>697255</v>
       </c>
       <c r="F15" s="30">
-        <v>970045</v>
+        <v>986301</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5252,19 +5252,19 @@
       </c>
       <c r="C16" s="50">
         <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D16" s="50">
         <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="E16" s="50">
         <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
-        <v>1139</v>
+        <v>1155</v>
       </c>
       <c r="F16" s="50">
         <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
-        <v>1559</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5277,19 +5277,19 @@
       </c>
       <c r="C17" s="34">
         <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="D17" s="34">
         <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="E17" s="34">
         <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
-        <v>37.4</v>
+        <v>38</v>
       </c>
       <c r="F17" s="34">
         <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
-        <v>51.3</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5330,16 +5330,16 @@
         <v>15389</v>
       </c>
       <c r="C21" s="30">
-        <v>18841</v>
+        <v>18917</v>
       </c>
       <c r="D21" s="30">
-        <v>19313</v>
+        <v>19452</v>
       </c>
       <c r="E21" s="30">
-        <v>19821</v>
+        <v>20021</v>
       </c>
       <c r="F21" s="30">
-        <v>20371</v>
+        <v>20643</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -5396,10 +5396,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24" s="51">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6028,16 +6028,16 @@
         <v>184667</v>
       </c>
       <c r="C6" s="30">
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="D6" s="30">
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="E6" s="30">
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="F6" s="30">
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6065,19 +6065,19 @@
         <v>273</v>
       </c>
       <c r="B8" s="32">
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="C8" s="32">
-        <v>137125</v>
+        <v>138507</v>
       </c>
       <c r="D8" s="32">
-        <v>213423</v>
+        <v>216486</v>
       </c>
       <c r="E8" s="32">
-        <v>275091</v>
+        <v>280092</v>
       </c>
       <c r="F8" s="32">
-        <v>282237</v>
+        <v>289046</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6085,19 +6085,19 @@
         <v>274</v>
       </c>
       <c r="B9" s="29">
-        <v>0.13663808664259927</v>
+        <v>0.13663808664259913</v>
       </c>
       <c r="C9" s="29">
-        <v>0.4043437853073026</v>
+        <v>0.4067620818062212</v>
       </c>
       <c r="D9" s="29">
-        <v>0.5023099573664649</v>
+        <v>0.5058728257176494</v>
       </c>
       <c r="E9" s="29">
-        <v>0.5551595361077036</v>
+        <v>0.5596038436877832</v>
       </c>
       <c r="F9" s="29">
-        <v>0.5541926962730911</v>
+        <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6134,10 +6134,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="50">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="50">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6183,16 +6183,16 @@
         <v>147733</v>
       </c>
       <c r="C16" s="30">
-        <v>271304</v>
+        <v>272410</v>
       </c>
       <c r="D16" s="30">
-        <v>339906</v>
+        <v>342357</v>
       </c>
       <c r="E16" s="30">
-        <v>396414</v>
+        <v>400414</v>
       </c>
       <c r="F16" s="30">
-        <v>407420</v>
+        <v>412868</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6223,16 +6223,16 @@
         <v>-11701</v>
       </c>
       <c r="C18" s="32">
-        <v>69299</v>
+        <v>70405</v>
       </c>
       <c r="D18" s="32">
-        <v>128446</v>
+        <v>130897</v>
       </c>
       <c r="E18" s="32">
-        <v>175988</v>
+        <v>179988</v>
       </c>
       <c r="F18" s="32">
-        <v>180382</v>
+        <v>185829</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6243,16 +6243,16 @@
         <v>-0.07920239169675096</v>
       </c>
       <c r="C19" s="29">
-        <v>0.2554297316341282</v>
+        <v>0.2584526022577766</v>
       </c>
       <c r="D19" s="29">
-        <v>0.3778874467080811</v>
+        <v>0.3823410321470617</v>
       </c>
       <c r="E19" s="29">
-        <v>0.4439494201346296</v>
+        <v>0.4495048046097289</v>
       </c>
       <c r="F19" s="29">
-        <v>0.44274087034136395</v>
+        <v>0.45009358278672595</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6433,16 +6433,16 @@
         <v>184667</v>
       </c>
       <c r="E13" s="30">
-        <v>339130</v>
+        <v>340512</v>
       </c>
       <c r="F13" s="30">
-        <v>424882</v>
+        <v>427946</v>
       </c>
       <c r="G13" s="30">
-        <v>495517</v>
+        <v>500518</v>
       </c>
       <c r="H13" s="30">
-        <v>509276</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -6470,19 +6470,19 @@
         <v>273</v>
       </c>
       <c r="D15" s="30">
-        <v>25233</v>
+        <v>25232</v>
       </c>
       <c r="E15" s="30">
-        <v>137125</v>
+        <v>138507</v>
       </c>
       <c r="F15" s="30">
-        <v>213423</v>
+        <v>216486</v>
       </c>
       <c r="G15" s="30">
-        <v>275091</v>
+        <v>280092</v>
       </c>
       <c r="H15" s="30">
-        <v>282237</v>
+        <v>289046</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -6493,16 +6493,16 @@
         <v>62170</v>
       </c>
       <c r="E16" s="30">
-        <v>199295</v>
+        <v>200677</v>
       </c>
       <c r="F16" s="30">
-        <v>412717</v>
+        <v>417164</v>
       </c>
       <c r="G16" s="30">
-        <v>687808</v>
+        <v>697255</v>
       </c>
       <c r="H16" s="30">
-        <v>970045</v>
+        <v>986301</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6568,19 +6568,19 @@
         <v>373</v>
       </c>
       <c r="D21" s="29">
-        <v>0.13663808664259927</v>
+        <v>0.13663808664259913</v>
       </c>
       <c r="E21" s="29">
-        <v>0.4043437853073026</v>
+        <v>0.4067620818062212</v>
       </c>
       <c r="F21" s="29">
-        <v>0.5023099573664649</v>
+        <v>0.5058728257176494</v>
       </c>
       <c r="G21" s="29">
-        <v>0.5551595361077036</v>
+        <v>0.5596038436877832</v>
       </c>
       <c r="H21" s="29">
-        <v>0.5541926962730911</v>
+        <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6674,7 +6674,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:I39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6684,7 +6684,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>376</v>
       </c>
@@ -6694,8 +6694,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
         <v>377</v>
       </c>
@@ -6705,6 +6706,7 @@
       <c r="F3" s="58"/>
       <c r="G3" s="58"/>
       <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="59" t="s">
@@ -6765,19 +6767,19 @@
         <v>330</v>
       </c>
       <c r="C8" s="64">
-        <v>184666.6666666667</v>
+        <v>184666.66666666666</v>
       </c>
       <c r="D8" s="64">
-        <v>339129.56</v>
+        <v>340512</v>
       </c>
       <c r="E8" s="64">
-        <v>424882.21741599997</v>
+        <v>427945.8</v>
       </c>
       <c r="F8" s="64">
-        <v>495516.93485413</v>
+        <v>500517.5</v>
       </c>
       <c r="G8" s="64">
-        <v>509275.55642087164</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -6791,10 +6793,10 @@
         <v>147002.63</v>
       </c>
       <c r="E9" s="64">
-        <v>151412.7089</v>
+        <v>151412.70889999997</v>
       </c>
       <c r="F9" s="64">
-        <v>155955.090167</v>
+        <v>155955.09016700002</v>
       </c>
       <c r="G9" s="64">
         <v>160633.74287201</v>
@@ -6845,19 +6847,19 @@
         <v>273</v>
       </c>
       <c r="C12" s="65">
-        <v>25232.5</v>
+        <v>25232.49999999997</v>
       </c>
       <c r="D12" s="65">
-        <v>137124.93</v>
+        <v>138507.37</v>
       </c>
       <c r="E12" s="65">
-        <v>213422.568516</v>
+        <v>216486.15110000002</v>
       </c>
       <c r="F12" s="65">
-        <v>275090.95168713003</v>
+        <v>280091.516833</v>
       </c>
       <c r="G12" s="65">
-        <v>282236.7937588616</v>
+        <v>289046.23733798997</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -6868,16 +6870,16 @@
         <v>62170</v>
       </c>
       <c r="D13" s="65">
-        <v>199294.93</v>
+        <v>200677.37</v>
       </c>
       <c r="E13" s="65">
-        <v>412717.498516</v>
+        <v>417163.5211</v>
       </c>
       <c r="F13" s="65">
-        <v>687808.45020313</v>
+        <v>697255.037933</v>
       </c>
       <c r="G13" s="65">
-        <v>970045.2439619916</v>
+        <v>986301.27527099</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -6885,19 +6887,19 @@
         <v>373</v>
       </c>
       <c r="C14" s="66">
-        <v>0.13663808664259927</v>
+        <v>0.13663808664259913</v>
       </c>
       <c r="D14" s="66">
-        <v>0.4043437853073026</v>
+        <v>0.4067620818062212</v>
       </c>
       <c r="E14" s="66">
-        <v>0.5023099573664649</v>
+        <v>0.5058728257176494</v>
       </c>
       <c r="F14" s="66">
-        <v>0.5551595361077036</v>
+        <v>0.5596038436877832</v>
       </c>
       <c r="G14" s="66">
-        <v>0.5541926962730911</v>
+        <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
@@ -6905,19 +6907,19 @@
         <v>239</v>
       </c>
       <c r="C15" s="67">
-        <v>15388.88888888889</v>
+        <v>15388.888888888889</v>
       </c>
       <c r="D15" s="67">
-        <v>18840.53111111111</v>
+        <v>18917.333333333332</v>
       </c>
       <c r="E15" s="67">
-        <v>19312.828064363635</v>
+        <v>19452.081818181818</v>
       </c>
       <c r="F15" s="67">
-        <v>19820.677394165203</v>
+        <v>20020.7</v>
       </c>
       <c r="G15" s="67">
-        <v>20371.022256834865</v>
+        <v>20643.4</v>
       </c>
       <c r="H15" s="68" t="s">
         <v>388</v>
@@ -6991,19 +6993,19 @@
         <v>392</v>
       </c>
       <c r="C19" s="71">
-        <v>2102.7083333333335</v>
+        <v>2102.7083333333308</v>
       </c>
       <c r="D19" s="71">
-        <v>7618.051666666666</v>
+        <v>7694.853888888889</v>
       </c>
       <c r="E19" s="71">
-        <v>9701.025841636363</v>
+        <v>9840.279595454545</v>
       </c>
       <c r="F19" s="71">
-        <v>11003.6380674852</v>
+        <v>11203.66067332</v>
       </c>
       <c r="G19" s="71">
-        <v>11289.471750354463</v>
+        <v>11561.8494935196</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
@@ -7011,19 +7013,19 @@
         <v>393</v>
       </c>
       <c r="C20" s="72">
-        <v>0.644047833935018</v>
+        <v>0.6440478339350181</v>
       </c>
       <c r="D20" s="66">
-        <v>0.43347041172111334</v>
+        <v>0.4317105711399305</v>
       </c>
       <c r="E20" s="66">
-        <v>0.35636395851265434</v>
+        <v>0.3538128167165094</v>
       </c>
       <c r="F20" s="66">
-        <v>0.314732109434181</v>
+        <v>0.31158768707787443</v>
       </c>
       <c r="G20" s="66">
-        <v>0.31541616487727187</v>
+        <v>0.3112544307081392</v>
       </c>
       <c r="H20" s="68" t="s">
         <v>394</v>
@@ -7034,19 +7036,19 @@
         <v>395</v>
       </c>
       <c r="C21" s="72">
-        <v>0.19494584837545123</v>
+        <v>0.19494584837545129</v>
       </c>
       <c r="D21" s="66">
-        <v>0.10933874357634882</v>
+        <v>0.10889484071045955</v>
       </c>
       <c r="E21" s="66">
-        <v>0.0898893821263553</v>
+        <v>0.0892458811372842</v>
       </c>
       <c r="F21" s="66">
-        <v>0.07938814848291784</v>
+        <v>0.07859499817688692</v>
       </c>
       <c r="G21" s="66">
-        <v>0.07956069489130392</v>
+        <v>0.07851093746185223</v>
       </c>
       <c r="H21" s="68" t="s">
         <v>396</v>
@@ -7057,19 +7059,19 @@
         <v>397</v>
       </c>
       <c r="C22" s="66">
-        <v>0.13663808664259935</v>
+        <v>0.13663808664259922</v>
       </c>
       <c r="D22" s="66">
-        <v>0.4043437853073026</v>
+        <v>0.4067620818062212</v>
       </c>
       <c r="E22" s="66">
-        <v>0.5023099573664649</v>
+        <v>0.5058728257176494</v>
       </c>
       <c r="F22" s="66">
-        <v>0.5551595361077037</v>
+        <v>0.5596038436877832</v>
       </c>
       <c r="G22" s="66">
-        <v>0.5541926962730912</v>
+        <v>0.5600748662293809</v>
       </c>
       <c r="H22" s="68" t="s">
         <v>398</v>
@@ -7159,14 +7161,14 @@
       <c r="D26" s="77">
         <v>12</v>
       </c>
-      <c r="E26" s="77">
-        <v>23</v>
+      <c r="E26" s="73">
+        <v>24</v>
       </c>
       <c r="F26" s="73">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G26" s="73">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H26" s="68" t="s">
         <v>403</v>
@@ -7180,22 +7182,22 @@
         <v>142</v>
       </c>
       <c r="D27" s="73">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E27" s="73">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="F27" s="73">
-        <v>1139</v>
+        <v>1155</v>
       </c>
       <c r="G27" s="73">
-        <v>1559</v>
+        <v>1586</v>
       </c>
       <c r="H27" s="68" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>405</v>
       </c>
@@ -7211,8 +7213,9 @@
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="44" t="s">
         <v>409</v>
       </c>
@@ -7228,8 +7231,9 @@
       </c>
       <c r="G30" s="79"/>
       <c r="H30" s="79"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="79"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="44" t="s">
         <v>413</v>
       </c>
@@ -7245,8 +7249,9 @@
       </c>
       <c r="G31" s="79"/>
       <c r="H31" s="79"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="79"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="44" t="s">
         <v>416</v>
       </c>
@@ -7262,8 +7267,9 @@
       </c>
       <c r="G32" s="79"/>
       <c r="H32" s="79"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="79"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="44" t="s">
         <v>419</v>
       </c>
@@ -7279,8 +7285,9 @@
       </c>
       <c r="G33" s="79"/>
       <c r="H33" s="79"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="79"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="44" t="s">
         <v>422</v>
       </c>
@@ -7296,8 +7303,9 @@
       </c>
       <c r="G34" s="79"/>
       <c r="H34" s="79"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="79"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="44" t="s">
         <v>425</v>
       </c>
@@ -7313,6 +7321,7 @@
       </c>
       <c r="G35" s="79"/>
       <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="44" t="s">
@@ -7325,7 +7334,7 @@
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="80" t="s">
         <v>430</v>
       </c>
@@ -7335,27 +7344,28 @@
       <c r="F39" s="80"/>
       <c r="G39" s="80"/>
       <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B39:I39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7824,7 +7834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>103</v>
       </c>
@@ -7833,7 +7843,6 @@
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -8737,7 +8746,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9180,7 +9189,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>216</v>
       </c>
@@ -9189,7 +9198,6 @@
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
@@ -9292,7 +9300,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Microschool_Startup.xlsx
@@ -24,18 +24,19 @@
     <sheet sheetId="18" name="DSCR &amp; Covenants" state="visible" r:id="rId21"/>
     <sheet sheetId="19" name="Sources &amp; Uses" state="visible" r:id="rId22"/>
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
-    <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
+    <sheet sheetId="21" name="Lender Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Assumptions Memo" state="visible" r:id="rId27"/>
-    <sheet sheetId="25" name="Decision History" state="visible" r:id="rId28"/>
+    <sheet sheetId="24" name="Assumptions Confidence" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Assumptions Memo" state="visible" r:id="rId28"/>
+    <sheet sheetId="26" name="Decision History" state="visible" r:id="rId29"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="470">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -43,7 +44,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · llc_single</t>
+    <t>Generated May 9, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -130,7 +131,7 @@
     <t>SchoolStack Budget</t>
   </si>
   <si>
-    <t>5-Year Financial Model &amp; Underwriting Workbook</t>
+    <t>5-Year Financial Model — Founder Planning Workbook</t>
   </si>
   <si>
     <t>School Name</t>
@@ -163,7 +164,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>May 7, 2026</t>
+    <t>May 9, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -304,7 +305,7 @@
     <t>21.</t>
   </si>
   <si>
-    <t>Underwriting Snapshot</t>
+    <t>Lender Snapshot</t>
   </si>
   <si>
     <t>22.</t>
@@ -319,6 +320,12 @@
     <t>Budget Narrative</t>
   </si>
   <si>
+    <t>24.</t>
+  </si>
+  <si>
+    <t>Assumptions Confidence</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -427,6 +434,39 @@
     <t>% of Base</t>
   </si>
   <si>
+    <t>REVENUE QUALITY</t>
+  </si>
+  <si>
+    <t>Bucket</t>
+  </si>
+  <si>
+    <t>Contracted</t>
+  </si>
+  <si>
+    <t>Projected</t>
+  </si>
+  <si>
+    <t>Donor-dependent</t>
+  </si>
+  <si>
+    <t>Policy-dependent</t>
+  </si>
+  <si>
+    <t>Contracted %</t>
+  </si>
+  <si>
+    <t>Projected %</t>
+  </si>
+  <si>
+    <t>Donor-dependent %</t>
+  </si>
+  <si>
+    <t>Policy-dependent %</t>
+  </si>
+  <si>
+    <t>Hard Rev Coverage (Contracted ÷ Fixed + Debt)</t>
+  </si>
+  <si>
     <t>STAFFING</t>
   </si>
   <si>
@@ -940,7 +980,7 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
-    <t>Cash Trough: July (Month 1)</t>
+    <t>Cash Trough: September (Month 3)</t>
   </si>
   <si>
     <t>Your lowest cash point is the month lenders focus on to ensure you won't run out of money before collections start. Plan reserves to cover this trough.</t>
@@ -952,7 +992,10 @@
     <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
   </si>
   <si>
-    <t>Capital &amp; Debt Service</t>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Principal &amp; Capital Outlays</t>
   </si>
   <si>
     <t>Depreciation</t>
@@ -1051,6 +1094,9 @@
     <t>Ending Cash</t>
   </si>
   <si>
+    <t>Working-Capital Cash (basis for runway/days)</t>
+  </si>
+  <si>
     <t>Days Cash on Hand</t>
   </si>
   <si>
@@ -1135,7 +1181,7 @@
     <t>Enrollment: -20%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
-    <t>Underwriting Snapshot - Loan Committee Summary</t>
+    <t>Lender Conversation Snapshot - Summary</t>
   </si>
   <si>
     <t>Entity</t>
@@ -1162,13 +1208,34 @@
     <t>Enrollment</t>
   </si>
   <si>
+    <t>BREAK-EVEN &amp; DOWNSIDE</t>
+  </si>
+  <si>
+    <t>Break-Even Students</t>
+  </si>
+  <si>
+    <t>Break-Even Utilization %</t>
+  </si>
+  <si>
+    <t>-10% Enrollment: DSCR</t>
+  </si>
+  <si>
+    <t>-10% Enrollment: Ending Cash</t>
+  </si>
+  <si>
+    <t>-20% Enrollment: DSCR</t>
+  </si>
+  <si>
+    <t>-20% Enrollment: Ending Cash</t>
+  </si>
+  <si>
     <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
   </si>
   <si>
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1358,6 +1425,9 @@
   </si>
   <si>
     <t>Additional Context</t>
+  </si>
+  <si>
+    <t>No assumptions tagged yet — open the wizard and tag each major assumption (Actuals, Signed agreement, Written quote, Research, Estimate) with a one-line evidence note. The tags surface here, in the lender PDF, and on share links.</t>
   </si>
   <si>
     <t>Assumptions Memo</t>
@@ -1382,14 +1452,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0;#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.00x"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;×&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1483,11 +1554,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FFDC2626"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <i/>
       <color rgb="FF9CA3AF"/>
       <sz val="9"/>
@@ -1553,7 +1619,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1583,11 +1649,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1686,24 +1747,24 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1713,28 +1774,28 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1753,17 +1814,17 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1775,29 +1836,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2499,7 +2560,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2512,44 +2573,44 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="35">
+        <v>111</v>
+      </c>
+      <c r="B4" s="36">
         <v>12</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="36">
         <v>18</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="36">
         <v>22</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="36">
         <v>25</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="36">
         <v>25</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2559,146 +2620,146 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="30">
+        <v>119</v>
+      </c>
+      <c r="B7" s="25">
         <v>144000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>222480</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>280078</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>327818</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>337653</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="30">
+        <v>123</v>
+      </c>
+      <c r="B8" s="25">
         <v>3000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>4635</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>5835</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>6830</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>7034</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="30">
+        <v>124</v>
+      </c>
+      <c r="B9" s="25">
         <v>84000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>129780</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>163379</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>191227</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>196964</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="30">
+        <v>126</v>
+      </c>
+      <c r="B10" s="25">
         <v>5000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="25">
         <v>5150</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="25">
         <v>5305</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="25">
         <v>5464</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="25">
         <v>5628</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="30">
+        <v>129</v>
+      </c>
+      <c r="B11" s="25">
         <v>-10</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="25">
         <v>-10</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="25">
         <v>-11</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="25">
         <v>-11</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="25">
         <v>-11</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B12" s="32">
+        <v>251</v>
+      </c>
+      <c r="B12" s="33">
         <f>SUM(B7:B11)</f>
         <v>221600</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>SUM(C7:C11)</f>
         <v>339130</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <f>SUM(D7:D11)</f>
         <v>424882</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>SUM(E7:E11)</f>
         <v>495517</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <f>SUM(F7:F11)</f>
         <v>509276</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B14" s="30">
+        <v>252</v>
+      </c>
+      <c r="B14" s="25">
         <v>18467</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="25">
         <v>18841</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="25">
         <v>19313</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="25">
         <v>19821</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="25">
         <v>20371</v>
       </c>
     </row>
@@ -2728,7 +2789,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2741,24 +2802,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2768,72 +2829,72 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="30">
+        <v>254</v>
+      </c>
+      <c r="B5" s="25">
         <v>47869</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>59166</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>60941</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>62769</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>64652</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B6" s="30">
+        <v>255</v>
+      </c>
+      <c r="B6" s="25">
         <v>12559</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>15523</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>15989</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>16468</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>16963</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="31">
+        <v>256</v>
+      </c>
+      <c r="B7" s="32">
         <f>SUM(B5:B6)</f>
         <v>60428</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>SUM(C5:C6)</f>
         <v>74689</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>SUM(D5:D6)</f>
         <v>76930</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>SUM(E5:E6)</f>
         <v>79237</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>SUM(F5:F6)</f>
         <v>81615</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -2843,70 +2904,70 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="B9" s="30">
+        <v>257</v>
+      </c>
+      <c r="B9" s="25">
         <v>58506</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>72314</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>74483</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>76718</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>79019</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10" s="31">
+        <v>258</v>
+      </c>
+      <c r="B10" s="32">
         <f>SUM(B9:B9)</f>
         <v>58506</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>SUM(C9:C9)</f>
         <v>72314</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>SUM(D9:D9)</f>
         <v>74483</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>SUM(E9:E9)</f>
         <v>76718</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>SUM(F9:F9)</f>
         <v>79019</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="B12" s="32">
+        <v>259</v>
+      </c>
+      <c r="B12" s="33">
         <f>B7+B10</f>
         <v>118934</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>C7+C10</f>
         <v>147003</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <f>D7+D10</f>
         <v>151413</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>E7+E10</f>
         <v>155955</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <f>F7+F10</f>
         <v>160634</v>
       </c>
@@ -2937,7 +2998,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2950,24 +3011,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2977,132 +3038,132 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B5" s="30">
+        <v>262</v>
+      </c>
+      <c r="B5" s="25">
         <v>120000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>222480</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>280078</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>327818</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B6" s="30">
+        <v>263</v>
+      </c>
+      <c r="B6" s="25">
         <v>2500</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>4635</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>5835</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>6830</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="B7" s="30">
+        <v>264</v>
+      </c>
+      <c r="B7" s="25">
         <v>70000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>129780</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>163379</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>191227</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>196964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B8" s="30">
+        <v>265</v>
+      </c>
+      <c r="B8" s="25">
         <v>4167</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>5150</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>5305</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>5464</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>5628</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="30">
+        <v>266</v>
+      </c>
+      <c r="B9" s="25">
         <v>-8</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>-10</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>-11</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>-11</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>-11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B10" s="31">
+        <v>267</v>
+      </c>
+      <c r="B10" s="32">
         <f>SUM(B5:B9)</f>
         <v>184667</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>SUM(C5:C9)</f>
         <v>340512</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>SUM(D5:D9)</f>
         <v>427946</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>SUM(E5:E9)</f>
         <v>500518</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>SUM(F5:F9)</f>
         <v>516085</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -3112,92 +3173,92 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B13" s="30">
+        <v>269</v>
+      </c>
+      <c r="B13" s="25">
         <v>58506</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <v>72314</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="25">
         <v>74483</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>76718</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>79019</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" s="30">
+        <v>270</v>
+      </c>
+      <c r="B14" s="25">
         <v>47869</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="25">
         <v>59166</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="25">
         <v>60941</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="25">
         <v>62769</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="25">
         <v>64652</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B15" s="30">
+        <v>271</v>
+      </c>
+      <c r="B15" s="25">
         <v>12559</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="25">
         <v>15523</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="25">
         <v>15989</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="25">
         <v>16468</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="25">
         <v>16963</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B16" s="31">
+        <v>230</v>
+      </c>
+      <c r="B16" s="32">
         <f>SUM(B13:B15)</f>
         <v>118934</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>SUM(C13:C15)</f>
         <v>147003</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>SUM(D13:D15)</f>
         <v>151413</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>SUM(E13:E15)</f>
         <v>155955</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>SUM(F13:F15)</f>
         <v>160634</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -3206,198 +3267,198 @@
       <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
-        <v>151</v>
+      <c r="A19" s="37" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B20" s="30">
+        <v>272</v>
+      </c>
+      <c r="B20" s="25">
         <v>5000</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="25">
         <v>9270</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="25">
         <v>11670</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="25">
         <v>13659</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="25">
         <v>14069</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
-        <v>152</v>
+      <c r="A21" s="37" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="B22" s="30">
+        <v>273</v>
+      </c>
+      <c r="B22" s="25">
         <v>3000</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="25">
         <v>5562</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="25">
         <v>7002</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="25">
         <v>8195</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="25">
         <v>8441</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
-        <v>146</v>
+      <c r="A23" s="37" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B24" s="30">
+        <v>274</v>
+      </c>
+      <c r="B24" s="25">
         <v>25000</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="25">
         <v>30900</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="25">
         <v>31827</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="25">
         <v>32782</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="B25" s="30">
+        <v>275</v>
+      </c>
+      <c r="B25" s="25">
         <v>3000</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="25">
         <v>3708</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="25">
         <v>3819</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="25">
         <v>3934</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="25">
         <v>4052</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="B26" s="30">
+        <v>276</v>
+      </c>
+      <c r="B26" s="25">
         <v>2000</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="25">
         <v>2472</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="25">
         <v>2546</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="25">
         <v>2623</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="25">
         <v>2701</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="B27" s="31">
+        <v>277</v>
+      </c>
+      <c r="B27" s="32">
         <f>SUM(B24:B26)</f>
         <v>30000</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <f>SUM(C24:C26)</f>
         <v>37080</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <f>SUM(D24:D26)</f>
         <v>38192</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <f>SUM(E24:E26)</f>
         <v>39338</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <f>SUM(F24:F26)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
-        <v>154</v>
+      <c r="A28" s="37" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B29" s="30">
+        <v>278</v>
+      </c>
+      <c r="B29" s="25">
         <v>2500</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="25">
         <v>3090</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="25">
         <v>3183</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="25">
         <v>3278</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="25">
         <v>3377</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B30" s="31">
+        <v>279</v>
+      </c>
+      <c r="B30" s="32">
         <f>B20+B22+B27+B29</f>
         <v>40500</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="32">
         <f>C20+C22+C27+C29</f>
         <v>55002</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="32">
         <f>D20+D22+D27+D29</f>
         <v>60047</v>
       </c>
-      <c r="E30" s="31">
+      <c r="E30" s="32">
         <f>E20+E22+E27+E29</f>
         <v>64471</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="32">
         <f>F20+F22+F27+F29</f>
         <v>66405</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
@@ -3407,25 +3468,25 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="B33" s="31" t="str">
+        <v>281</v>
+      </c>
+      <c r="B33" s="32" t="str">
         <f>SUM(B33:B32)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="31" t="str">
+      <c r="C33" s="32" t="str">
         <f>SUM(C33:C32)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="31" t="str">
+      <c r="D33" s="32" t="str">
         <f>SUM(D33:D32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="31" t="str">
+      <c r="E33" s="32" t="str">
         <f>SUM(E33:E32)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="31" t="str">
+      <c r="F33" s="32" t="str">
         <f>SUM(F33:F32)</f>
         <v>0</v>
       </c>
@@ -3456,7 +3517,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3469,149 +3530,149 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="33">
+        <v>267</v>
+      </c>
+      <c r="B4" s="34">
         <f>'Budget Detail'!B10</f>
         <v>184667</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="34">
         <f>'Budget Detail'!C10</f>
         <v>340512</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="34">
         <f>'Budget Detail'!D10</f>
         <v>427946</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="34">
         <f>'Budget Detail'!E10</f>
         <v>500518</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="34">
         <f>'Budget Detail'!F10</f>
         <v>516085</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="33">
+        <v>230</v>
+      </c>
+      <c r="B5" s="34">
         <f>'Budget Detail'!B16</f>
         <v>118934</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="34">
         <f>'Budget Detail'!C16</f>
         <v>147003</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="34">
         <f>'Budget Detail'!D16</f>
         <v>151413</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="34">
         <f>'Budget Detail'!E16</f>
         <v>155955</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="34">
         <f>'Budget Detail'!F16</f>
         <v>160634</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B6" s="33">
+        <v>279</v>
+      </c>
+      <c r="B6" s="34">
         <f>'Budget Detail'!B30</f>
         <v>40500</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>'Budget Detail'!C30</f>
         <v>55002</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="34">
         <f>'Budget Detail'!D30</f>
         <v>60047</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="34">
         <f>'Budget Detail'!E30</f>
         <v>64471</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="34">
         <f>'Budget Detail'!F30</f>
         <v>66405</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="B7" s="33" t="str">
+        <v>283</v>
+      </c>
+      <c r="B7" s="34" t="str">
         <f>'Budget Detail'!B33</f>
         <v>0</v>
       </c>
-      <c r="C7" s="33" t="str">
+      <c r="C7" s="34" t="str">
         <f>'Budget Detail'!C33</f>
         <v>0</v>
       </c>
-      <c r="D7" s="33" t="str">
+      <c r="D7" s="34" t="str">
         <f>'Budget Detail'!D33</f>
         <v>0</v>
       </c>
-      <c r="E7" s="33" t="str">
+      <c r="E7" s="34" t="str">
         <f>'Budget Detail'!E33</f>
         <v>0</v>
       </c>
-      <c r="F7" s="33" t="str">
+      <c r="F7" s="34" t="str">
         <f>'Budget Detail'!F33</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="31">
+        <v>284</v>
+      </c>
+      <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
         <v>159434</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>SUM(C5:C7)</f>
         <v>202005</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>SUM(D5:D7)</f>
         <v>211460</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
         <v>220426</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
         <v>227039</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3621,111 +3682,111 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B11" s="32">
+        <v>286</v>
+      </c>
+      <c r="B11" s="33">
         <f>B4-B8</f>
         <v>25232</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>C4-C8</f>
         <v>138507</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>D4-D8</f>
         <v>216486</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="33">
         <f>E4-E8</f>
         <v>280092</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <f>F4-F8</f>
         <v>289046</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B12" s="29">
+        <v>287</v>
+      </c>
+      <c r="B12" s="26">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.13663809</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="26">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.40676208</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="26">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.50587283</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="26">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.55960384</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="26">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.56007487</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="B13" s="30">
+        <v>288</v>
+      </c>
+      <c r="B13" s="25">
         <v>25232</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <v>163740</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="25">
         <v>380226</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>660318</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>949364</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B14" s="30">
+        <v>252</v>
+      </c>
+      <c r="B14" s="25">
         <v>15389</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="25">
         <v>18917</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="25">
         <v>19452</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="25">
         <v>20021</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="25">
         <v>20643</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="B15" s="30">
+        <v>289</v>
+      </c>
+      <c r="B15" s="25">
         <v>13286</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="25">
         <v>11222</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="25">
         <v>9612</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="25">
         <v>8817</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="25">
         <v>9082</v>
       </c>
     </row>
@@ -3756,7 +3817,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3777,48 +3838,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -3836,52 +3897,52 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="31">
-        <v>9150</v>
-      </c>
-      <c r="C4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="D4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="E4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="F4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="G4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="H4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="I4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="J4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="K4" s="31">
-        <v>22110</v>
-      </c>
-      <c r="L4" s="31">
+        <v>267</v>
+      </c>
+      <c r="B4" s="32">
+        <v>26250</v>
+      </c>
+      <c r="C4" s="32">
         <v>13210</v>
       </c>
-      <c r="M4" s="31">
+      <c r="D4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="E4" s="32">
+        <v>34210</v>
+      </c>
+      <c r="F4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="G4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="H4" s="32">
+        <v>34210</v>
+      </c>
+      <c r="I4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="J4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="K4" s="32">
+        <v>34210</v>
+      </c>
+      <c r="L4" s="32">
+        <v>13210</v>
+      </c>
+      <c r="M4" s="32">
         <v>250</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="32">
         <f>SUM(B4:M4)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -3899,142 +3960,142 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B7" s="30">
+        <v>305</v>
+      </c>
+      <c r="B7" s="25">
         <v>11893</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>11893</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>11893</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>11893</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>11893</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="25">
         <v>11893</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="25">
         <v>11893</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="25">
         <v>11893</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="25">
         <v>11893</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="25">
         <v>11893</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="25">
         <v>0</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="25">
         <v>0</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="25">
         <f>SUM(B7:M7)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="B8" s="30">
+        <v>306</v>
+      </c>
+      <c r="B8" s="25">
         <v>4050</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>4050</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>4050</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>4050</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>4050</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="25">
         <v>4050</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="25">
         <v>4050</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="25">
         <v>4050</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="25">
         <v>4050</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="25">
         <v>4050</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="25">
         <v>0</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="25">
         <v>0</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="25">
         <f>SUM(B8:M8)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B9" s="30">
+        <v>307</v>
+      </c>
+      <c r="B9" s="25">
         <v>0</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>0</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>0</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>0</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>0</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="25">
         <v>0</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="25">
         <v>0</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="25">
         <v>0</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="25">
         <v>0</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="25">
         <v>0</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="25">
         <v>0</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="25">
         <v>0</v>
       </c>
-      <c r="N9" s="30" t="str">
+      <c r="N9" s="25" t="str">
         <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4052,185 +4113,185 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B12" s="33">
+        <v>284</v>
+      </c>
+      <c r="B12" s="34">
         <f>B7+B8+B9</f>
         <v>15943</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>C7+C8+C9</f>
         <v>15943</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>D7+D8+D9</f>
         <v>15943</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>E7+E8+E9</f>
         <v>15943</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>F7+F8+F9</f>
         <v>15943</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="34">
         <f>G7+G8+G9</f>
         <v>15943</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="34">
         <f>H7+H8+H9</f>
         <v>15943</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="34">
         <f>I7+I8+I9</f>
         <v>15943</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="34">
         <f>J7+J8+J9</f>
         <v>15943</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="34">
         <f>K7+K8+K9</f>
         <v>15943</v>
       </c>
-      <c r="L12" s="33" t="str">
+      <c r="L12" s="34" t="str">
         <f>L7+L8+L9</f>
         <v>0</v>
       </c>
-      <c r="M12" s="33" t="str">
+      <c r="M12" s="34" t="str">
         <f>M7+M8+M9</f>
         <v>0</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="34">
         <f>SUM(B12:M12)</f>
         <v>159430</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="B13" s="33">
+        <v>309</v>
+      </c>
+      <c r="B13" s="34">
         <f>B4-B12</f>
-        <v>-6793</v>
-      </c>
-      <c r="C13" s="33">
+        <v>10307</v>
+      </c>
+      <c r="C13" s="34">
         <f>C4-C12</f>
-        <v>6167</v>
-      </c>
-      <c r="D13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="D13" s="34">
         <f>D4-D12</f>
-        <v>6167</v>
-      </c>
-      <c r="E13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="E13" s="34">
         <f>E4-E12</f>
-        <v>6167</v>
-      </c>
-      <c r="F13" s="33">
+        <v>18267</v>
+      </c>
+      <c r="F13" s="34">
         <f>F4-F12</f>
-        <v>6167</v>
-      </c>
-      <c r="G13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="G13" s="34">
         <f>G4-G12</f>
-        <v>6167</v>
-      </c>
-      <c r="H13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="H13" s="34">
         <f>H4-H12</f>
-        <v>6167</v>
-      </c>
-      <c r="I13" s="33">
+        <v>18267</v>
+      </c>
+      <c r="I13" s="34">
         <f>I4-I12</f>
-        <v>6167</v>
-      </c>
-      <c r="J13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="J13" s="34">
         <f>J4-J12</f>
-        <v>6167</v>
-      </c>
-      <c r="K13" s="33">
+        <v>-2733</v>
+      </c>
+      <c r="K13" s="34">
         <f>K4-K12</f>
-        <v>6167</v>
-      </c>
-      <c r="L13" s="33">
+        <v>18267</v>
+      </c>
+      <c r="L13" s="34">
         <f>L4-L12</f>
         <v>13210</v>
       </c>
-      <c r="M13" s="33">
+      <c r="M13" s="34">
         <f>M4-M12</f>
         <v>250</v>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="34">
         <f>SUM(B13:M13)</f>
         <v>62170</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="B14" s="37">
+        <v>310</v>
+      </c>
+      <c r="B14" s="38">
         <f>B17+B13</f>
-        <v>-6793</v>
-      </c>
-      <c r="C14" s="37">
+        <v>10307</v>
+      </c>
+      <c r="C14" s="38">
         <f>B14+C13</f>
-        <v>-626</v>
-      </c>
-      <c r="D14" s="37">
+        <v>7574</v>
+      </c>
+      <c r="D14" s="38">
         <f>C14+D13</f>
-        <v>5541</v>
-      </c>
-      <c r="E14" s="37">
+        <v>4841</v>
+      </c>
+      <c r="E14" s="38">
         <f>D14+E13</f>
-        <v>11708</v>
-      </c>
-      <c r="F14" s="37">
+        <v>23108</v>
+      </c>
+      <c r="F14" s="38">
         <f>E14+F13</f>
-        <v>17875</v>
-      </c>
-      <c r="G14" s="37">
+        <v>20375</v>
+      </c>
+      <c r="G14" s="38">
         <f>F14+G13</f>
-        <v>24042</v>
-      </c>
-      <c r="H14" s="37">
+        <v>17642</v>
+      </c>
+      <c r="H14" s="38">
         <f>G14+H13</f>
-        <v>30209</v>
-      </c>
-      <c r="I14" s="37">
+        <v>35909</v>
+      </c>
+      <c r="I14" s="38">
         <f>H14+I13</f>
-        <v>36376</v>
-      </c>
-      <c r="J14" s="37">
+        <v>33176</v>
+      </c>
+      <c r="J14" s="38">
         <f>I14+J13</f>
-        <v>42543</v>
-      </c>
-      <c r="K14" s="37">
+        <v>30443</v>
+      </c>
+      <c r="K14" s="38">
         <f>J14+K13</f>
         <v>48710</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="38">
         <f>K14+L13</f>
         <v>61920</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="38">
         <f>L14+M13</f>
         <v>62170</v>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="33">
         <f>M14</f>
         <v>62170</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B17" s="23">
         <v>0</v>
@@ -4238,25 +4299,25 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="B18" s="37">
+        <v>312</v>
+      </c>
+      <c r="B18" s="38">
         <f>M14</f>
         <v>62170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="B19" s="38">
+        <v>313</v>
+      </c>
+      <c r="B19" s="25">
         <f>MIN(B14:M14)</f>
-        <v>-6793</v>
+        <v>4841</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -4266,7 +4327,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="39" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="39"/>
@@ -4295,7 +4356,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4304,7 +4365,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4314,7 +4375,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -4327,24 +4388,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4354,27 +4415,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="B5" s="31">
+        <v>267</v>
+      </c>
+      <c r="B5" s="32">
         <v>184667</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <v>340512</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="32">
         <v>427946</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <v>500518</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <v>516085</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4384,211 +4445,231 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="B8" s="33">
+        <v>305</v>
+      </c>
+      <c r="B8" s="34">
         <v>118934</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <v>147003</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <v>151413</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <v>155955</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <v>160634</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B9" s="33">
+        <v>306</v>
+      </c>
+      <c r="B9" s="34">
         <v>40500</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <v>55002</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="34">
         <v>60047</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="34">
         <v>64471</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="34">
         <v>66405</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="B10" s="33">
+        <v>318</v>
+      </c>
+      <c r="B10" s="34">
         <v>0</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="34">
         <v>0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <v>0</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <v>0</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="B11" s="33">
+        <v>319</v>
+      </c>
+      <c r="B11" s="34">
+        <v>0</v>
+      </c>
+      <c r="C11" s="34">
+        <v>0</v>
+      </c>
+      <c r="D11" s="34">
+        <v>0</v>
+      </c>
+      <c r="E11" s="34">
+        <v>0</v>
+      </c>
+      <c r="F11" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="34">
         <v>714</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C12" s="34">
         <v>714</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D12" s="34">
         <v>714</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E12" s="34">
         <v>714</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F12" s="34">
         <v>714</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="B12" s="31">
-        <f>SUM(B8:B11)</f>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="B13" s="32">
+        <f>SUM(B8:B12)</f>
         <v>160148</v>
       </c>
-      <c r="C12" s="31">
-        <f>SUM(C8:C11)</f>
+      <c r="C13" s="32">
+        <f>SUM(C8:C12)</f>
         <v>202719</v>
       </c>
-      <c r="D12" s="31">
-        <f>SUM(D8:D11)</f>
+      <c r="D13" s="32">
+        <f>SUM(D8:D12)</f>
         <v>212174</v>
       </c>
-      <c r="E12" s="31">
-        <f>SUM(E8:E11)</f>
+      <c r="E13" s="32">
+        <f>SUM(E8:E12)</f>
         <v>221140</v>
       </c>
-      <c r="F12" s="31">
-        <f>SUM(F8:F11)</f>
+      <c r="F13" s="32">
+        <f>SUM(F8:F12)</f>
         <v>227753</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
-        <v>273</v>
-      </c>
-      <c r="B15" s="32">
-        <f>B5-B12</f>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="B16" s="33">
+        <f>B5-B13</f>
         <v>24518</v>
       </c>
-      <c r="C15" s="32">
-        <f>C5-C12</f>
+      <c r="C16" s="33">
+        <f>C5-C13</f>
         <v>137793</v>
       </c>
-      <c r="D15" s="32">
-        <f>D5-D12</f>
+      <c r="D16" s="33">
+        <f>D5-D13</f>
         <v>215772</v>
       </c>
-      <c r="E15" s="32">
-        <f>E5-E12</f>
+      <c r="E16" s="33">
+        <f>E5-E13</f>
         <v>279377</v>
       </c>
-      <c r="F15" s="32">
-        <f>F5-F12</f>
+      <c r="F16" s="33">
+        <f>F5-F13</f>
         <v>288332</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B16" s="29">
-        <f>IF(B5=0,0,B15/B5)</f>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B17" s="26">
+        <f>IF(B5=0,0,B16/B5)</f>
         <v>0.13277011</v>
       </c>
-      <c r="C16" s="29">
-        <f>IF(C5=0,0,C15/C5)</f>
+      <c r="C17" s="26">
+        <f>IF(C5=0,0,C16/C5)</f>
         <v>0.4046644</v>
       </c>
-      <c r="D16" s="29">
-        <f>IF(D5=0,0,D15/D5)</f>
+      <c r="D17" s="26">
+        <f>IF(D5=0,0,D16/D5)</f>
         <v>0.50420372</v>
       </c>
-      <c r="E16" s="29">
-        <f>IF(E5=0,0,E15/E5)</f>
+      <c r="E17" s="26">
+        <f>IF(E5=0,0,E16/E5)</f>
         <v>0.55817675</v>
       </c>
-      <c r="F16" s="29">
-        <f>IF(F5=0,0,F15/F5)</f>
+      <c r="F17" s="26">
+        <f>IF(F5=0,0,F16/F5)</f>
         <v>0.55869082</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="B17" s="33">
-        <f>B15</f>
-        <v>24518</v>
-      </c>
-      <c r="C17" s="33">
-        <f>B17+C15</f>
-        <v>162311</v>
-      </c>
-      <c r="D17" s="33">
-        <f>C17+D15</f>
-        <v>378083</v>
-      </c>
-      <c r="E17" s="33">
-        <f>D17+E15</f>
-        <v>657460</v>
-      </c>
-      <c r="F17" s="33">
-        <f>E17+F15</f>
-        <v>945792</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>309</v>
-      </c>
-      <c r="C18" s="43" t="s">
+        <v>288</v>
+      </c>
+      <c r="B18" s="34">
+        <f>B16</f>
+        <v>24518</v>
+      </c>
+      <c r="C18" s="34">
+        <f>B18+C16</f>
+        <v>162311</v>
+      </c>
+      <c r="D18" s="34">
+        <f>C18+D16</f>
+        <v>378083</v>
+      </c>
+      <c r="E18" s="34">
+        <f>D18+E16</f>
+        <v>657460</v>
+      </c>
+      <c r="F18" s="34">
+        <f>E18+F16</f>
+        <v>945792</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="43" t="s">
+      <c r="F19" s="43" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4632,24 +4713,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4659,19 +4740,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4700,7 +4781,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4713,24 +4794,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4740,117 +4821,117 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B5" s="47">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>62170</v>
       </c>
       <c r="C5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15</f>
+        <f>B5+'5-Year Operating Stmt'!C16</f>
         <v>200677</v>
       </c>
       <c r="D5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
+        <f>B5+'5-Year Operating Stmt'!C16+'5-Year Operating Stmt'!D16</f>
         <v>417164</v>
       </c>
       <c r="E5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
+        <f>B5+'5-Year Operating Stmt'!C16+'5-Year Operating Stmt'!D16+'5-Year Operating Stmt'!E16</f>
         <v>697255</v>
       </c>
       <c r="F5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
+        <f>B5+'5-Year Operating Stmt'!C16+'5-Year Operating Stmt'!D16+'5-Year Operating Stmt'!E16+'5-Year Operating Stmt'!F16</f>
         <v>986301</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B6" s="30">
+        <v>331</v>
+      </c>
+      <c r="B6" s="25">
         <v>1007</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>1036</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>1067</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>1098</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>1131</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="B7" s="30">
+        <v>332</v>
+      </c>
+      <c r="B7" s="25">
         <v>4286</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>3571</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>2857</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>2143</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>1429</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B8" s="30">
+        <v>333</v>
+      </c>
+      <c r="B8" s="25">
         <v>0</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>0</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>0</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>0</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="B9" s="31">
+        <v>334</v>
+      </c>
+      <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
         <v>67463</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
         <v>205285</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
         <v>421088</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
         <v>700496</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
         <v>988860</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4860,72 +4941,72 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="B12" s="30">
+        <v>336</v>
+      </c>
+      <c r="B12" s="25">
         <v>0</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="25">
         <v>0</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="25">
         <v>0</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="25">
         <v>0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="B13" s="30">
+        <v>337</v>
+      </c>
+      <c r="B13" s="25">
         <v>0</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <v>0</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="25">
         <v>0</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>0</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="B14" s="31" t="str">
+        <v>338</v>
+      </c>
+      <c r="B14" s="32" t="str">
         <f>SUM(B12:B13)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="31" t="str">
+      <c r="C14" s="32" t="str">
         <f>SUM(C12:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="31" t="str">
+      <c r="D14" s="32" t="str">
         <f>SUM(D12:D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="31" t="str">
+      <c r="E14" s="32" t="str">
         <f>SUM(E12:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="31" t="str">
+      <c r="F14" s="32" t="str">
         <f>SUM(F12:F13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4935,32 +5016,32 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="B17" s="32">
+        <v>340</v>
+      </c>
+      <c r="B17" s="33">
         <f>B9-B14</f>
         <v>67463</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>C9-C14</f>
         <v>205285</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <f>D9-D14</f>
         <v>421088</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>E9-E14</f>
         <v>700496</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>F9-F14</f>
         <v>988860</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B19" s="48" t="str">
         <f>B9-B14-B17</f>
@@ -5000,7 +5081,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -5009,7 +5090,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5022,24 +5103,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5049,172 +5130,172 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B5" s="30">
+        <v>344</v>
+      </c>
+      <c r="B5" s="25">
         <v>184667</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>340512</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>427946</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>500518</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>516085</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B6" s="30">
+        <v>305</v>
+      </c>
+      <c r="B6" s="25">
         <v>118934</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>147003</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>151413</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>155955</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>160634</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="B7" s="30">
+        <v>306</v>
+      </c>
+      <c r="B7" s="25">
         <v>40500</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>55002</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>60047</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>64471</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>66405</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B8" s="33">
+        <v>286</v>
+      </c>
+      <c r="B8" s="34">
         <v>25232</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <v>138507</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <v>216486</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <v>280092</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <v>289046</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B9" s="30">
+        <v>345</v>
+      </c>
+      <c r="B9" s="25">
         <v>714</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>714</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>714</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>714</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>714</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="B10" s="30">
+        <v>346</v>
+      </c>
+      <c r="B10" s="25">
         <v>0</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="25">
         <v>0</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="25">
         <v>0</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="25">
         <v>0</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="B11" s="33">
+        <v>347</v>
+      </c>
+      <c r="B11" s="34">
         <f>B8+B9+B10</f>
         <v>25947</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="34">
         <f>C8+C9+C10</f>
         <v>139222</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="34">
         <f>D8+D9+D10</f>
         <v>217200</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="34">
         <f>E8+E9+E10</f>
         <v>280806</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="34">
         <f>F8+F9+F10</f>
         <v>289761</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F12" s="49" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -5224,312 +5305,332 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="B15" s="30">
+        <v>351</v>
+      </c>
+      <c r="B15" s="25">
+        <v>40232</v>
+      </c>
+      <c r="C15" s="25">
+        <v>178740</v>
+      </c>
+      <c r="D15" s="25">
+        <v>395226</v>
+      </c>
+      <c r="E15" s="25">
+        <v>675318</v>
+      </c>
+      <c r="F15" s="25">
+        <v>964364</v>
+      </c>
+    </row>
+    <row r="16" hidden="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="B16" s="25">
         <v>62170</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C16" s="25">
         <v>200677</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D16" s="25">
         <v>417164</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E16" s="25">
         <v>697255</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F16" s="25">
         <v>986301</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="B16" s="50">
-        <f>IF((B5-B8)=0,0,(B15/(B5-B8))*365)</f>
-        <v>142</v>
-      </c>
-      <c r="C16" s="50">
-        <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
-        <v>363</v>
-      </c>
-      <c r="D16" s="50">
-        <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
-        <v>720</v>
-      </c>
-      <c r="E16" s="50">
-        <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
-        <v>1155</v>
-      </c>
-      <c r="F16" s="50">
-        <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
-        <v>1586</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="B17" s="34">
-        <f>IF((B5-B8)=0,0,B15/((B5-B8)/12))</f>
-        <v>4.7</v>
-      </c>
-      <c r="C17" s="34">
-        <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
-        <v>11.9</v>
-      </c>
-      <c r="D17" s="34">
-        <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
-        <v>23.7</v>
-      </c>
-      <c r="E17" s="34">
-        <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
-        <v>38</v>
-      </c>
-      <c r="F17" s="34">
-        <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
-        <v>52.1</v>
+        <v>353</v>
+      </c>
+      <c r="B17" s="50">
+        <f>IF((B5-B8)=0,0,(B16/(B5-B8))*365)</f>
+        <v>142</v>
+      </c>
+      <c r="C17" s="50">
+        <f>IF((C5-C8)=0,0,(C16/(C5-C8))*365)</f>
+        <v>363</v>
+      </c>
+      <c r="D17" s="50">
+        <f>IF((D5-D8)=0,0,(D16/(D5-D8))*365)</f>
+        <v>720</v>
+      </c>
+      <c r="E17" s="50">
+        <f>IF((E5-E8)=0,0,(E16/(E5-E8))*365)</f>
+        <v>1155</v>
+      </c>
+      <c r="F17" s="50">
+        <f>IF((F5-F8)=0,0,(F16/(F5-F8))*365)</f>
+        <v>1586</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B18" s="29">
+        <v>354</v>
+      </c>
+      <c r="B18" s="35">
+        <f>IF((B5-B8)=0,0,B16/((B5-B8)/12))</f>
+        <v>4.7</v>
+      </c>
+      <c r="C18" s="35">
+        <f>IF((C5-C8)=0,0,C16/((C5-C8)/12))</f>
+        <v>11.9</v>
+      </c>
+      <c r="D18" s="35">
+        <f>IF((D5-D8)=0,0,D16/((D5-D8)/12))</f>
+        <v>23.7</v>
+      </c>
+      <c r="E18" s="35">
+        <f>IF((E5-E8)=0,0,E16/((E5-E8)/12))</f>
+        <v>38</v>
+      </c>
+      <c r="F18" s="35">
+        <f>IF((F5-F8)=0,0,F16/((F5-F8)/12))</f>
+        <v>52.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="26">
         <v>0.48</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="26">
         <v>0.72</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D19" s="26">
         <v>0.88</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E19" s="26">
         <v>1</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F19" s="26">
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B21" s="30">
-        <v>15389</v>
-      </c>
-      <c r="C21" s="30">
-        <v>18917</v>
-      </c>
-      <c r="D21" s="30">
-        <v>19452</v>
-      </c>
-      <c r="E21" s="30">
-        <v>20021</v>
-      </c>
-      <c r="F21" s="30">
-        <v>20643</v>
-      </c>
+    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="B22" s="30">
-        <v>118934</v>
-      </c>
-      <c r="C22" s="30">
-        <v>147003</v>
-      </c>
-      <c r="D22" s="30">
-        <v>151413</v>
-      </c>
-      <c r="E22" s="30">
-        <v>155955</v>
-      </c>
-      <c r="F22" s="30">
-        <v>160634</v>
+        <v>252</v>
+      </c>
+      <c r="B22" s="25">
+        <v>15389</v>
+      </c>
+      <c r="C22" s="25">
+        <v>18917</v>
+      </c>
+      <c r="D22" s="25">
+        <v>19452</v>
+      </c>
+      <c r="E22" s="25">
+        <v>20021</v>
+      </c>
+      <c r="F22" s="25">
+        <v>20643</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="B23" s="30">
+        <v>356</v>
+      </c>
+      <c r="B23" s="25">
+        <v>118934</v>
+      </c>
+      <c r="C23" s="25">
+        <v>147003</v>
+      </c>
+      <c r="D23" s="25">
+        <v>151413</v>
+      </c>
+      <c r="E23" s="25">
+        <v>155955</v>
+      </c>
+      <c r="F23" s="25">
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="B24" s="25">
         <v>3375</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C24" s="25">
         <v>3056</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D24" s="25">
         <v>2729</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E24" s="25">
         <v>2579</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F24" s="25">
         <v>2656</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="B24" s="51">
-        <v>10</v>
-      </c>
-      <c r="C24" s="51">
-        <v>10</v>
-      </c>
-      <c r="D24" s="51">
-        <v>10</v>
-      </c>
-      <c r="E24" s="51">
-        <v>9</v>
-      </c>
-      <c r="F24" s="51">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="B27" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="D27" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="E27" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="F27" s="52" t="s">
-        <v>335</v>
-      </c>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="B25" s="51">
+        <v>11</v>
+      </c>
+      <c r="C25" s="51">
+        <v>11</v>
+      </c>
+      <c r="D25" s="51">
+        <v>11</v>
+      </c>
+      <c r="E25" s="51">
+        <v>11</v>
+      </c>
+      <c r="F25" s="51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="B28" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="C28" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="E28" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="F28" s="53" t="s">
-        <v>347</v>
+        <v>360</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B29" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="D29" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="E29" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="F29" s="52" t="s">
-        <v>335</v>
+        <v>361</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B30" s="52" t="s">
         <v>349</v>
       </c>
-      <c r="B30" s="54" t="s">
-        <v>350</v>
-      </c>
-      <c r="C30" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="D30" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="E30" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="F30" s="53" t="s">
-        <v>347</v>
+      <c r="C30" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>349</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>347</v>
+        <v>364</v>
+      </c>
+      <c r="B31" s="54" t="s">
+        <v>365</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="E31" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="F31" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="F32" s="53" t="s">
-        <v>347</v>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="B33" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="F33" s="53" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -5570,57 +5671,57 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D3" s="55" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="B4" s="30">
+        <v>370</v>
+      </c>
+      <c r="B4" s="25">
         <v>20000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="E4" s="30">
+        <v>371</v>
+      </c>
+      <c r="E4" s="25">
         <v>15000</v>
       </c>
     </row>
     <row r="5" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D5" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="E5" s="30">
+        <v>372</v>
+      </c>
+      <c r="E5" s="25">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="B7" s="32">
+        <v>373</v>
+      </c>
+      <c r="B7" s="33">
         <v>20000</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="E7" s="32">
+        <v>374</v>
+      </c>
+      <c r="E7" s="33">
         <v>20000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="B8" s="48">
         <v>0</v>
@@ -5643,7 +5744,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C44"/>
+  <dimension ref="B3:C45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5917,18 +6018,26 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="14" t="s">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="14"/>
+      <c r="C42" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Instructions'!A1"/>
@@ -5951,9 +6060,10 @@
     <hyperlink ref="C36" r:id="rId18" location="#'DSCR &amp; Covenants'!A1"/>
     <hyperlink ref="C37" r:id="rId19" location="#'Sources &amp; Uses'!A1"/>
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
-    <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
+    <hyperlink ref="C39" r:id="rId21" location="#'Lender Snapshot'!A1"/>
     <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
     <hyperlink ref="C41" r:id="rId23" location="#'Budget Narrative'!A1"/>
+    <hyperlink ref="C42" r:id="rId24" location="#'Assumptions Confidence'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5977,7 +6087,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5987,7 +6097,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -5997,7 +6107,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6005,124 +6115,124 @@
         <v>7</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B6" s="30">
+        <v>344</v>
+      </c>
+      <c r="B6" s="25">
         <v>184667</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>340512</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>427946</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>500518</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>516085</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="30">
+        <v>284</v>
+      </c>
+      <c r="B7" s="25">
         <v>159434</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="25">
         <v>202005</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>211460</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="25">
         <v>220426</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="25">
         <v>227039</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B8" s="32">
+        <v>286</v>
+      </c>
+      <c r="B8" s="33">
         <v>25232</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <v>138507</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <v>216486</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <v>280092</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <v>289046</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B9" s="29">
+        <v>287</v>
+      </c>
+      <c r="B9" s="26">
         <v>0.13663808664259913</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="26">
         <v>0.4067620818062212</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="26">
         <v>0.5058728257176494</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="26">
         <v>0.5596038436877832</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="26">
         <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B11" s="50">
         <v>10</v>
@@ -6142,7 +6252,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6152,7 +6262,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6160,124 +6270,124 @@
         <v>7</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" s="30">
+        <v>344</v>
+      </c>
+      <c r="B16" s="25">
         <v>147733</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="25">
         <v>272410</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="25">
         <v>342357</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="25">
         <v>400414</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="25">
         <v>412868</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B17" s="30">
+        <v>284</v>
+      </c>
+      <c r="B17" s="25">
         <v>159434</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="25">
         <v>202005</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="25">
         <v>211460</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="25">
         <v>220426</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="25">
         <v>227039</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B18" s="32">
+        <v>286</v>
+      </c>
+      <c r="B18" s="33">
         <v>-11701</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <v>70405</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <v>130897</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <v>179988</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <v>185829</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B19" s="29">
+        <v>287</v>
+      </c>
+      <c r="B19" s="26">
         <v>-0.07920239169675096</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="26">
         <v>0.2584526022577766</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="26">
         <v>0.3823410321470617</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="26">
         <v>0.4495048046097289</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="26">
         <v>0.45009358278672595</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F20" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B21" s="50">
         <v>12</v>
@@ -6312,7 +6422,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -6323,7 +6433,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6335,7 +6445,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B3" s="19"/>
     </row>
@@ -6349,7 +6459,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -6357,7 +6467,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6381,7 +6491,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6389,7 +6499,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6410,124 +6520,124 @@
         <v>7</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E12" s="57" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H12" s="57" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="D13" s="30">
+        <v>344</v>
+      </c>
+      <c r="D13" s="25">
         <v>184667</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>340512</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>427946</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="25">
         <v>500518</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="25">
         <v>516085</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="D14" s="30">
+        <v>284</v>
+      </c>
+      <c r="D14" s="25">
         <v>159434</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="25">
         <v>202005</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="25">
         <v>211460</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="25">
         <v>220426</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="25">
         <v>227039</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="D15" s="30">
+        <v>286</v>
+      </c>
+      <c r="D15" s="25">
         <v>25232</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="25">
         <v>138507</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="25">
         <v>216486</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="25">
         <v>280092</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="25">
         <v>289046</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="D16" s="30">
+        <v>385</v>
+      </c>
+      <c r="D16" s="25">
         <v>62170</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="25">
         <v>200677</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="25">
         <v>417164</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="25">
         <v>697255</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="25">
         <v>986301</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="D17" s="30">
+        <v>386</v>
+      </c>
+      <c r="D17" s="25">
         <v>0</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="25">
         <v>0</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="25">
         <v>0</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="25">
         <v>0</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -6548,84 +6658,84 @@
         <v>7</v>
       </c>
       <c r="D20" s="57" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E20" s="57" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F20" s="57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G20" s="57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H20" s="57" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="D21" s="29">
+        <v>388</v>
+      </c>
+      <c r="D21" s="26">
         <v>0.13663808664259913</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="26">
         <v>0.4067620818062212</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="26">
         <v>0.5058728257176494</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="26">
         <v>0.5596038436877832</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="26">
         <v>0.5600748662293807</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="G22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="H22" s="56" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="29">
+        <v>214</v>
+      </c>
+      <c r="D23" s="26">
         <v>0.48</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="26">
         <v>0.72</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="26">
         <v>0.88</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="26">
         <v>1</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="26">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="D24" s="50">
         <v>12</v>
@@ -6643,22 +6753,180 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
+    <row r="26" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="G27" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D28" s="50">
+        <v>11</v>
+      </c>
+      <c r="E28" s="50">
+        <v>11</v>
+      </c>
+      <c r="F28" s="50">
+        <v>11</v>
+      </c>
+      <c r="G28" s="50">
+        <v>11</v>
+      </c>
+      <c r="H28" s="50">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="D29" s="26">
+        <v>0.44</v>
+      </c>
+      <c r="E29" s="26">
+        <v>0.44</v>
+      </c>
+      <c r="F29" s="26">
+        <v>0.44</v>
+      </c>
+      <c r="G29" s="26">
+        <v>0.44</v>
+      </c>
+      <c r="H29" s="26">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="D30" s="56">
+        <v>1.56</v>
+      </c>
+      <c r="E30" s="56">
+        <v>14.81</v>
+      </c>
+      <c r="F30" s="56">
+        <v>25.89</v>
+      </c>
+      <c r="G30" s="56">
+        <v>34.9</v>
+      </c>
+      <c r="H30" s="56">
+        <v>36.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D31" s="25">
+        <v>18898</v>
+      </c>
+      <c r="E31" s="25">
+        <v>115034</v>
+      </c>
+      <c r="F31" s="25">
+        <v>288247</v>
+      </c>
+      <c r="G31" s="25">
+        <v>524160</v>
+      </c>
+      <c r="H31" s="25">
+        <v>768075</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="D32" s="56" t="s">
+        <v>349</v>
+      </c>
+      <c r="E32" s="56">
+        <v>9.71</v>
+      </c>
+      <c r="F32" s="56">
+        <v>20.63</v>
+      </c>
+      <c r="G32" s="56">
+        <v>26.78</v>
+      </c>
+      <c r="H32" s="56">
+        <v>27.68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="D33" s="25">
+        <v>4523</v>
+      </c>
+      <c r="E33" s="25">
+        <v>65131</v>
+      </c>
+      <c r="F33" s="25">
+        <v>201757</v>
+      </c>
+      <c r="G33" s="25">
+        <v>381152</v>
+      </c>
+      <c r="H33" s="25">
+        <v>566866</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A35:H35"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6686,7 +6954,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6698,7 +6966,7 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="C3" s="58"/>
       <c r="D3" s="58"/>
@@ -6710,41 +6978,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="59" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="D4" s="60" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="E6" s="62" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="F6" s="62" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="G6" s="62" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="H6" s="62" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="C7" s="63">
         <v>12</v>
@@ -6764,7 +7032,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C8" s="64">
         <v>184666.66666666666</v>
@@ -6784,7 +7052,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C9" s="64">
         <v>118934.16666666667</v>
@@ -6804,7 +7072,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C10" s="64">
         <v>40500</v>
@@ -6824,7 +7092,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C11" s="64">
         <v>0</v>
@@ -6844,7 +7112,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C12" s="65">
         <v>25232.49999999997</v>
@@ -6864,7 +7132,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C13" s="65">
         <v>62170</v>
@@ -6884,7 +7152,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="C14" s="66">
         <v>0.13663808664259913</v>
@@ -6904,7 +7172,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="C15" s="67">
         <v>15388.888888888889</v>
@@ -6922,12 +7190,12 @@
         <v>20643.4</v>
       </c>
       <c r="H15" s="68" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C16" s="69">
         <v>13286.180555555557</v>
@@ -6947,7 +7215,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="C17" s="64">
         <v>500</v>
@@ -6967,7 +7235,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C18" s="70">
         <v>3000</v>
@@ -6985,12 +7253,12 @@
         <v>1620.7326864000001</v>
       </c>
       <c r="H18" s="68" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="C19" s="71">
         <v>2102.7083333333308</v>
@@ -7010,7 +7278,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="C20" s="72">
         <v>0.6440478339350181</v>
@@ -7028,12 +7296,12 @@
         <v>0.3112544307081392</v>
       </c>
       <c r="H20" s="68" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C21" s="72">
         <v>0.19494584837545129</v>
@@ -7051,12 +7319,12 @@
         <v>0.07851093746185223</v>
       </c>
       <c r="H21" s="68" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="C22" s="66">
         <v>0.13663808664259922</v>
@@ -7074,12 +7342,12 @@
         <v>0.5600748662293809</v>
       </c>
       <c r="H22" s="68" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="C23" s="73">
         <v>3</v>
@@ -7097,63 +7365,63 @@
         <v>3</v>
       </c>
       <c r="H23" s="68" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="G24" s="74" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="H24" s="68" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="C25" s="42" t="str">
-        <f>IF('5-Year Operating Stmt'!B17&gt;=0,"✓ Break-even","")</f>
+        <f>IF('5-Year Operating Stmt'!B18&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="D25" s="75" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C17&gt;=0,'5-Year Operating Stmt'!B17&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!C18&gt;=0,'5-Year Operating Stmt'!B18&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E25" s="75" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D17&gt;=0,'5-Year Operating Stmt'!C17&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!D18&gt;=0,'5-Year Operating Stmt'!C18&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F25" s="75" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E17&gt;=0,'5-Year Operating Stmt'!D17&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!E18&gt;=0,'5-Year Operating Stmt'!D18&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G25" s="75" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!F18&gt;=0,'5-Year Operating Stmt'!E18&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H25" s="68" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="C26" s="76">
         <v>5</v>
@@ -7171,12 +7439,12 @@
         <v>52</v>
       </c>
       <c r="H26" s="68" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="C27" s="73">
         <v>142</v>
@@ -7194,22 +7462,22 @@
         <v>1586</v>
       </c>
       <c r="H27" s="68" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
@@ -7217,17 +7485,17 @@
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="44" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D30" s="78" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="E30" s="78"/>
       <c r="F30" s="79" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="G30" s="79"/>
       <c r="H30" s="79"/>
@@ -7235,17 +7503,17 @@
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="44" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D31" s="78" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="E31" s="78"/>
       <c r="F31" s="79" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="G31" s="79"/>
       <c r="H31" s="79"/>
@@ -7253,17 +7521,17 @@
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="44" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D32" s="78" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="E32" s="78"/>
       <c r="F32" s="79" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="G32" s="79"/>
       <c r="H32" s="79"/>
@@ -7271,17 +7539,17 @@
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="44" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D33" s="78" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="E33" s="78"/>
       <c r="F33" s="79" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="G33" s="79"/>
       <c r="H33" s="79"/>
@@ -7289,17 +7557,17 @@
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="44" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D34" s="78" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="E34" s="78"/>
       <c r="F34" s="79" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="G34" s="79"/>
       <c r="H34" s="79"/>
@@ -7307,17 +7575,17 @@
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="44" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D35" s="78" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="E35" s="78"/>
       <c r="F35" s="79" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="G35" s="79"/>
       <c r="H35" s="79"/>
@@ -7325,10 +7593,10 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="44" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -7336,7 +7604,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="80" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="C39" s="80"/>
       <c r="D39" s="80"/>
@@ -7472,109 +7740,109 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="B3" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B4" s="81"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="B6" s="19"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B7" s="81"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="B9" s="19"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B10" s="81"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="B12" s="19"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B13" s="81"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="B15" s="19"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B16" s="81"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="B18" s="19"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B19" s="81"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="B21" s="19"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B22" s="81"/>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="B24" s="19"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B25" s="81"/>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="B27" s="19"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="81" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B28" s="81"/>
     </row>
@@ -7604,6 +7872,52 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="81" t="s">
+        <v>463</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -7614,21 +7928,21 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="82" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="B2" s="82"/>
       <c r="C2" s="82"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="83" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="B4" s="83"/>
       <c r="C4" s="83"/>
@@ -7647,7 +7961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -7668,7 +7982,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="15" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -7679,7 +7993,7 @@
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="84" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="C2" s="84"/>
       <c r="D2" s="84"/>
@@ -7690,7 +8004,7 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="85" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="C4" s="85"/>
       <c r="D4" s="85"/>
@@ -7718,7 +8032,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -7728,7 +8042,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7742,18 +8056,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -7796,10 +8110,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7820,7 +8134,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B12" s="20">
         <v>7</v>
@@ -7828,7 +8142,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="20">
         <v>25</v>
@@ -7836,7 +8150,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -7849,24 +8163,24 @@
         <v>7</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B17" s="22">
         <v>12</v>
@@ -7886,7 +8200,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7897,33 +8211,33 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D21" s="23">
         <v>12000</v>
@@ -7932,18 +8246,18 @@
         <v>0</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="D22" s="23">
         <v>250</v>
@@ -7952,18 +8266,18 @@
         <v>0</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D23" s="23">
         <v>7000</v>
@@ -7972,18 +8286,18 @@
         <v>0</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D24" s="23">
         <v>5000</v>
@@ -7992,18 +8306,18 @@
         <v>0</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D25" s="23">
         <v>10</v>
@@ -8012,408 +8326,527 @@
         <v>0</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="E28" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="B29" s="25">
+        <v>-12000</v>
+      </c>
+      <c r="C29" s="25">
+        <v>-22248</v>
+      </c>
+      <c r="D29" s="25">
+        <v>-28007.76</v>
+      </c>
+      <c r="E29" s="25">
+        <v>-32781.81</v>
+      </c>
+      <c r="F29" s="25">
+        <v>-33765.2643</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="B30" s="25">
+        <v>122500</v>
+      </c>
+      <c r="C30" s="25">
+        <v>227115</v>
+      </c>
+      <c r="D30" s="25">
+        <v>285912.55</v>
+      </c>
+      <c r="E30" s="25">
+        <v>334647.64375</v>
+      </c>
+      <c r="F30" s="25">
+        <v>344687.07306250004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="B31" s="25">
+        <v>4166.666666666667</v>
+      </c>
+      <c r="C31" s="25">
+        <v>5150</v>
+      </c>
+      <c r="D31" s="25">
+        <v>5304.5</v>
+      </c>
+      <c r="E31" s="25">
+        <v>5463.635</v>
+      </c>
+      <c r="F31" s="25">
+        <v>5627.54405</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B32" s="25">
+        <v>70000</v>
+      </c>
+      <c r="C32" s="25">
+        <v>129780</v>
+      </c>
+      <c r="D32" s="25">
+        <v>163378.59999999998</v>
+      </c>
+      <c r="E32" s="25">
+        <v>191227.225</v>
+      </c>
+      <c r="F32" s="25">
+        <v>196964.04175000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="B33" s="26">
+        <v>-0.06498194945848376</v>
+      </c>
+      <c r="C33" s="26">
+        <v>-0.06547438617762959</v>
+      </c>
+      <c r="D33" s="26">
+        <v>-0.06565530962447153</v>
+      </c>
+      <c r="E33" s="26">
+        <v>-0.06575342465753424</v>
+      </c>
+      <c r="F33" s="26">
+        <v>-0.06575342465753424</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="25">
+      <c r="B34" s="26">
+        <v>0.6633574007220217</v>
+      </c>
+      <c r="C34" s="26">
+        <v>0.6683843588966354</v>
+      </c>
+      <c r="D34" s="26">
+        <v>0.6702312857498135</v>
+      </c>
+      <c r="E34" s="26">
+        <v>0.6712328767123287</v>
+      </c>
+      <c r="F34" s="26">
+        <v>0.6712328767123287</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" s="26">
+        <v>0.02256317689530686</v>
+      </c>
+      <c r="C35" s="26">
+        <v>0.01515610791148833</v>
+      </c>
+      <c r="D35" s="26">
+        <v>0.012434717731907487</v>
+      </c>
+      <c r="E35" s="26">
+        <v>0.010958904109589041</v>
+      </c>
+      <c r="F35" s="26">
+        <v>0.01095890410958904</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" s="26">
+        <v>0.37906137184115524</v>
+      </c>
+      <c r="C36" s="26">
+        <v>0.38193391936950594</v>
+      </c>
+      <c r="D36" s="26">
+        <v>0.38298930614275056</v>
+      </c>
+      <c r="E36" s="26">
+        <v>0.3835616438356164</v>
+      </c>
+      <c r="F36" s="26">
+        <v>0.3835616438356164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" s="27">
+        <v>-0.07745225122498264</v>
+      </c>
+      <c r="C37" s="27">
+        <v>-0.1215720233091732</v>
+      </c>
+      <c r="D37" s="27">
+        <v>-0.14944429416974292</v>
+      </c>
+      <c r="E37" s="27">
+        <v>-0.17077853976927615</v>
+      </c>
+      <c r="F37" s="27">
+        <v>-0.1717165314906201</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+    </row>
+    <row r="40" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="28">
         <v>1</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E41" s="23">
         <v>55000</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F41" s="24">
         <v>0.2</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G41" s="24">
         <v>0.0765</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D30" s="25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" s="28">
         <v>1</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E42" s="23">
         <v>45000</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F42" s="24">
         <v>0.2</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G42" s="24">
         <v>0.0765</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D31" s="25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="28">
         <v>0.5</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E43" s="23">
         <v>28000</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F43" s="24">
         <v>0</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G43" s="24">
         <v>0.0765</v>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C34" s="21" t="s">
+    <row r="45" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+    </row>
+    <row r="46" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="B46" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="C46" s="21" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="D46" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" s="23">
+        <v>2500</v>
+      </c>
+      <c r="E47" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D48" s="23">
+        <v>300</v>
+      </c>
+      <c r="E48" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="23">
+        <v>2400</v>
+      </c>
+      <c r="E49" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="23">
+        <v>500</v>
+      </c>
+      <c r="E50" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51" s="23">
+        <v>300</v>
+      </c>
+      <c r="E51" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D52" s="23">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+    </row>
+    <row r="55" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C35" s="11" t="s">
+      <c r="C55" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="23">
-        <v>2500</v>
-      </c>
-      <c r="E35" s="24">
+      <c r="E55" s="21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" s="23">
+        <v>30000</v>
+      </c>
+      <c r="D56" s="24">
+        <v>0.06</v>
+      </c>
+      <c r="E56" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="24">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" s="23">
-        <v>300</v>
-      </c>
-      <c r="E36" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" s="23">
-        <v>2400</v>
-      </c>
-      <c r="E37" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="23">
-        <v>500</v>
-      </c>
-      <c r="E38" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="23">
-        <v>300</v>
-      </c>
-      <c r="E39" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D40" s="23">
-        <v>3000</v>
-      </c>
-      <c r="E40" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-    </row>
-    <row r="43" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C44" s="23">
-        <v>30000</v>
-      </c>
-      <c r="D44" s="24">
-        <v>0.06</v>
-      </c>
-      <c r="E44" s="22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B47" s="24">
-        <v>0.03</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B48" s="24">
-        <v>0.03</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B49" s="25">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B50" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B52" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="B53" s="24">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B54" s="24">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B55" s="24">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B56" s="24">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="B57" s="24">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="59" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="19" t="s">
+      <c r="C59" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="B60" s="24">
+        <v>0.03</v>
+      </c>
+      <c r="C60" s="29" t="s">
         <v>178</v>
       </c>
     </row>
@@ -8421,24 +8854,115 @@
       <c r="A61" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B61" s="20" t="s">
-        <v>180</v>
+      <c r="B61" s="28">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B62" s="24">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="B62" s="23">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B63" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B63" s="20" t="s">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
         <v>183</v>
+      </c>
+      <c r="B64" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B66" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B67" s="24">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B68" s="24">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B69" s="24">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B74" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -8473,10 +8997,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8497,10 +9021,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -8513,7 +9037,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -8521,66 +9045,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -8623,24 +9147,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -8650,27 +9174,27 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="27">
+        <v>111</v>
+      </c>
+      <c r="B6" s="30">
         <v>12</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="30">
         <v>18</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="30">
         <v>22</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="30">
         <v>25</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="30">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B7" s="22">
         <v>25</v>
@@ -8678,49 +9202,49 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B8" s="28">
+        <v>214</v>
+      </c>
+      <c r="B8" s="31">
         <f>B6/$B$7</f>
         <v>0.48</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="31">
         <f>C6/$B$7</f>
         <v>0.72</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="31">
         <f>D6/$B$7</f>
         <v>0.88</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f>E6/$B$7</f>
         <v>1</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="31">
         <f>F6/$B$7</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="29">
+        <v>215</v>
+      </c>
+      <c r="C10" s="26">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
         <v>0.5</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="26">
         <f>IF(C6=0,0,(D6-C6)/C6)</f>
         <v>0.22222222</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="26">
         <f>IF(D6=0,0,(E6-D6)/D6)</f>
         <v>0.13636364</v>
       </c>
-      <c r="F10" s="29" t="str">
+      <c r="F10" s="26" t="str">
         <f>IF(E6=0,0,(F6-E6)/E6)</f>
         <v>0</v>
       </c>
@@ -8751,7 +9275,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8764,24 +9288,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8791,72 +9315,72 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="30">
+        <v>119</v>
+      </c>
+      <c r="B5" s="25">
         <v>144000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>222480</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>280078</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>327818</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>337653</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="30">
+        <v>123</v>
+      </c>
+      <c r="B6" s="25">
         <v>3000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>4635</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>5835</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="25">
         <v>6830</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="25">
         <v>7034</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="31">
+        <v>218</v>
+      </c>
+      <c r="B7" s="32">
         <f>SUM(B5,B6)</f>
         <v>147000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>SUM(C5,C6)</f>
         <v>227115</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>SUM(D5,D6)</f>
         <v>285913</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>SUM(E5,E6)</f>
         <v>334648</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>SUM(F5,F6)</f>
         <v>344687</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -8866,52 +9390,52 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="30">
+        <v>129</v>
+      </c>
+      <c r="B9" s="25">
         <v>-10</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="25">
         <v>-10</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>-11</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="25">
         <v>-11</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="25">
         <v>-11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="B10" s="31">
+        <v>220</v>
+      </c>
+      <c r="B10" s="32">
         <f>SUM(B9)</f>
         <v>-10</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>SUM(C9)</f>
         <v>-10</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>SUM(D9)</f>
         <v>-11</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>SUM(E9)</f>
         <v>-11</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>SUM(F9)</f>
         <v>-11</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -8921,52 +9445,52 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="30">
+        <v>124</v>
+      </c>
+      <c r="B12" s="25">
         <v>84000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="25">
         <v>129780</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="25">
         <v>163379</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="25">
         <v>191227</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="25">
         <v>196964</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="B13" s="31">
+        <v>222</v>
+      </c>
+      <c r="B13" s="32">
         <f>SUM(B12)</f>
         <v>84000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>SUM(C12)</f>
         <v>129780</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>SUM(D12)</f>
         <v>163379</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>SUM(E12)</f>
         <v>191227</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>SUM(F12)</f>
         <v>196964</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -8976,70 +9500,70 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B15" s="23">
         <v>5000</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="25">
         <v>5150</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="25">
         <v>5305</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="25">
         <v>5464</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="25">
         <v>5628</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="B16" s="31">
+        <v>224</v>
+      </c>
+      <c r="B16" s="32">
         <f>SUM(B15)</f>
         <v>5000</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>SUM(C15)</f>
         <v>5150</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>SUM(D15)</f>
         <v>5305</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>SUM(E15)</f>
         <v>5464</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>SUM(F15)</f>
         <v>5628</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="32">
+        <v>225</v>
+      </c>
+      <c r="B18" s="33">
         <f>SUM(B7,B10,B13,B16)</f>
         <v>221600</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <f>SUM(C7,C10,C13,C16)</f>
         <v>339130</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <f>SUM(D7,D10,D13,D16)</f>
         <v>424882</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <f>SUM(E7,E10,E13,E16)</f>
         <v>495517</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <f>SUM(F7,F10,F13,F16)</f>
         <v>509276</v>
       </c>
@@ -9087,38 +9611,38 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="25">
+        <v>151</v>
+      </c>
+      <c r="C4" s="28">
         <v>1</v>
       </c>
       <c r="D4" s="23">
@@ -9130,21 +9654,21 @@
       <c r="F4" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="34">
         <v>70208</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="25">
+        <v>154</v>
+      </c>
+      <c r="C5" s="28">
         <v>1</v>
       </c>
       <c r="D5" s="23">
@@ -9156,21 +9680,21 @@
       <c r="F5" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="34">
         <v>57443</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="25">
+        <v>154</v>
+      </c>
+      <c r="C6" s="28">
         <v>0.5</v>
       </c>
       <c r="D6" s="23">
@@ -9182,16 +9706,16 @@
       <c r="F6" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="34">
         <v>15071</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -9204,78 +9728,78 @@
         <v>7</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="32">
+        <v>230</v>
+      </c>
+      <c r="B10" s="33">
         <v>118934</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <v>147003</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="33">
         <v>151413</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="33">
         <v>155955</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="33">
         <v>160634</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="29">
+        <v>231</v>
+      </c>
+      <c r="B11" s="26">
         <v>0.5367065282791817</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="26">
         <v>0.43347041172111334</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="26">
         <v>0.35636395851265434</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="26">
         <v>0.314732109434181</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="26">
         <v>0.31541616487727187</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="34">
+        <v>232</v>
+      </c>
+      <c r="B12" s="35">
         <v>4.8</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="35">
         <v>7.2</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="35">
         <v>8.8</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="35">
         <v>10</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="35">
         <v>10</v>
       </c>
     </row>
@@ -9305,7 +9829,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9318,24 +9842,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -9345,52 +9869,52 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="30">
+        <v>234</v>
+      </c>
+      <c r="B5" s="25">
         <v>6000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="25">
         <v>9270</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="25">
         <v>11670</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="25">
         <v>13659</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="25">
         <v>14069</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="31">
+        <v>235</v>
+      </c>
+      <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>SUM(C5:C5)</f>
         <v>9270</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="32">
         <f>SUM(D5:D5)</f>
         <v>11670</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>SUM(E5:E5)</f>
         <v>13659</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>SUM(F5:F5)</f>
         <v>14069</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -9400,52 +9924,52 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="30">
+        <v>236</v>
+      </c>
+      <c r="B8" s="25">
         <v>3600</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="25">
         <v>5562</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>7002</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="25">
         <v>8195</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="25">
         <v>8441</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="31">
+        <v>237</v>
+      </c>
+      <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
         <v>3600</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C8:C8)</f>
         <v>5562</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D8:D8)</f>
         <v>7002</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E8:E8)</f>
         <v>8195</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F8:F8)</f>
         <v>8441</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -9455,92 +9979,92 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B11" s="30">
+        <v>238</v>
+      </c>
+      <c r="B11" s="25">
         <v>30000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="25">
         <v>30900</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="25">
         <v>31827</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="25">
         <v>32782</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B12" s="30">
+        <v>239</v>
+      </c>
+      <c r="B12" s="25">
         <v>3600</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="25">
         <v>3708</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="25">
         <v>3819</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="25">
         <v>3934</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="25">
         <v>4052</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B13" s="30">
+        <v>240</v>
+      </c>
+      <c r="B13" s="25">
         <v>2400</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <v>2472</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="25">
         <v>2546</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="25">
         <v>2623</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="25">
         <v>2701</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="B14" s="31">
+        <v>241</v>
+      </c>
+      <c r="B14" s="32">
         <f>SUM(B11:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C11:C13)</f>
         <v>37080</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D11:D13)</f>
         <v>38192</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E11:E13)</f>
         <v>39338</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F11:F13)</f>
         <v>40518</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -9550,70 +10074,70 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B16" s="30">
+        <v>242</v>
+      </c>
+      <c r="B16" s="25">
         <v>3000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="25">
         <v>3090</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="25">
         <v>3183</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="25">
         <v>3278</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="25">
         <v>3377</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B17" s="31">
+        <v>243</v>
+      </c>
+      <c r="B17" s="32">
         <f>SUM(B16:B16)</f>
         <v>3000</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>SUM(C16:C16)</f>
         <v>3090</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>SUM(D16:D16)</f>
         <v>3183</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>SUM(E16:E16)</f>
         <v>3278</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>SUM(F16:F16)</f>
         <v>3377</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="B19" s="32">
+        <v>244</v>
+      </c>
+      <c r="B19" s="33">
         <f>B6+B9+B14+B17</f>
         <v>48600</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="33">
         <f>C6+C9+C14+C17</f>
         <v>55002</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="33">
         <f>D6+D9+D14+D17</f>
         <v>60047</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="33">
         <f>E6+E9+E14+E17</f>
         <v>64471</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="33">
         <f>F6+F9+F14+F17</f>
         <v>66405</v>
       </c>
@@ -9645,7 +10169,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9655,30 +10179,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>132</v>
+        <v>145<